--- a/data/freight/Baltic air freight index.xlsx
+++ b/data/freight/Baltic air freight index.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\USER\PycharmProjects\AlternativeData\data\freight\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2E69E343-C0E0-433F-BB3B-F825C05B2A4A}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6E87EE47-A0AE-4972-B80F-5A72E447571B}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="0" windowWidth="22260" windowHeight="12645" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -101,7 +101,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <numFmts count="3">
-    <numFmt numFmtId="43" formatCode="_-* #,##0.00_-;\-* #,##0.00_-;_-* &quot;-&quot;??_-;_-@_-"/>
+    <numFmt numFmtId="176" formatCode="_-* #,##0.00_-;\-* #,##0.00_-;_-* &quot;-&quot;??_-;_-@_-"/>
     <numFmt numFmtId="177" formatCode="_(* #,##0_);_(* \(#,##0\);_(* &quot;-&quot;??_);_(@_)"/>
     <numFmt numFmtId="178" formatCode="yyyy\-mm\-dd;@"/>
   </numFmts>
@@ -194,7 +194,7 @@
   </borders>
   <cellStyleXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
-    <xf numFmtId="43" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="176" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
@@ -505,7 +505,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:H419"/>
+  <dimension ref="A1:H420"/>
   <sheetFormatPr defaultRowHeight="13.5" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="10.875" style="1" bestFit="1" customWidth="1"/>
@@ -11405,6 +11405,11 @@
       </c>
       <c r="H419" s="4">
         <v>5821</v>
+      </c>
+    </row>
+    <row r="420" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A420" s="1">
+        <v>46020</v>
       </c>
     </row>
   </sheetData>

--- a/data/freight/Baltic air freight index.xlsx
+++ b/data/freight/Baltic air freight index.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\USER\PycharmProjects\AlternativeData\data\freight\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DD9E198C-3D35-4201-896C-BD36AA61EA2A}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{61650C34-A245-4A0D-9F96-E63C5C2B6190}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="780" windowWidth="36000" windowHeight="22605" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -26,7 +26,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="440" uniqueCount="24">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="441" uniqueCount="24">
   <si>
     <t>Shanghai Pudong Outbound</t>
   </si>
@@ -542,7 +542,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:K420"/>
+  <dimension ref="A1:K421"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="9.875" style="5" bestFit="1" customWidth="1"/>
@@ -15664,6 +15664,21 @@
       </c>
       <c r="K420" s="9">
         <v>5821</v>
+      </c>
+    </row>
+    <row r="421" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A421" s="8">
+        <f t="shared" ref="A421" si="7">B421-1</f>
+        <v>46026</v>
+      </c>
+      <c r="B421" s="6">
+        <v>46027</v>
+      </c>
+      <c r="C421" s="10">
+        <v>0.70833333333333337</v>
+      </c>
+      <c r="D421" s="6" t="s">
+        <v>21</v>
       </c>
     </row>
   </sheetData>

--- a/data/freight/Baltic air freight index.xlsx
+++ b/data/freight/Baltic air freight index.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="20417"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="11214"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\USER\PycharmProjects\AlternativeData\data\freight\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/junghunlee/Desktop/Pycharm/AlternativeData/data/freight/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{61650C34-A245-4A0D-9F96-E63C5C2B6190}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A9B1DA0D-A4BA-7845-93BC-E63D6A92CA76}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="780" windowWidth="36000" windowHeight="22605" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="16320" yWindow="780" windowWidth="19680" windowHeight="20760" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="BAI" sheetId="1" r:id="rId1"/>
@@ -20,6 +20,17 @@
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
+    </ext>
+    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
+      <xcalcf:calcFeatures>
+        <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:Single"/>
+        <xcalcf:feature name="microsoft.com:FV"/>
+        <xcalcf:feature name="microsoft.com:CNMTM"/>
+        <xcalcf:feature name="microsoft.com:LET_WF"/>
+        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
+        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
+      </xcalcf:calcFeatures>
     </ext>
   </extLst>
 </workbook>
@@ -116,29 +127,29 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <numFmts count="4">
-    <numFmt numFmtId="176" formatCode="_-* #,##0.00_-;\-* #,##0.00_-;_-* &quot;-&quot;??_-;_-@_-"/>
-    <numFmt numFmtId="177" formatCode="_(* #,##0_);_(* \(#,##0\);_(* &quot;-&quot;??_);_(@_)"/>
-    <numFmt numFmtId="178" formatCode="yyyy\-mm\-dd;@"/>
-    <numFmt numFmtId="179" formatCode="[$-F400]h:mm:ss\ AM/PM"/>
+    <numFmt numFmtId="164" formatCode="_-* #,##0.00_-;\-* #,##0.00_-;_-* &quot;-&quot;??_-;_-@_-"/>
+    <numFmt numFmtId="165" formatCode="_(* #,##0_);_(* \(#,##0\);_(* &quot;-&quot;??_);_(@_)"/>
+    <numFmt numFmtId="166" formatCode="yyyy\-mm\-dd;@"/>
+    <numFmt numFmtId="167" formatCode="[$-F400]h:mm:ss\ AM/PM"/>
   </numFmts>
-  <fonts count="10" x14ac:knownFonts="1">
+  <fonts count="10">
     <font>
       <sz val="11"/>
       <color theme="1"/>
-      <name val="맑은 고딕"/>
+      <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
     </font>
     <font>
       <sz val="11"/>
       <color theme="1"/>
-      <name val="맑은 고딕"/>
+      <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
     </font>
     <font>
       <sz val="8"/>
-      <name val="맑은 고딕"/>
+      <name val="Calibri"/>
       <family val="3"/>
       <charset val="129"/>
       <scheme val="minor"/>
@@ -160,7 +171,7 @@
     <font>
       <sz val="10"/>
       <color theme="1"/>
-      <name val="맑은 고딕"/>
+      <name val="Calibri"/>
       <family val="3"/>
       <charset val="129"/>
       <scheme val="minor"/>
@@ -177,7 +188,7 @@
       <b/>
       <sz val="10"/>
       <color theme="1"/>
-      <name val="맑은 고딕"/>
+      <name val="Calibri"/>
       <family val="3"/>
       <charset val="129"/>
       <scheme val="minor"/>
@@ -186,14 +197,14 @@
       <b/>
       <sz val="10"/>
       <color theme="1"/>
-      <name val="맑은 고딕"/>
+      <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
     </font>
     <font>
       <sz val="10"/>
       <color theme="1"/>
-      <name val="맑은 고딕"/>
+      <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
     </font>
@@ -217,7 +228,7 @@
   </borders>
   <cellStyleXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
-    <xf numFmtId="176" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="164" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
@@ -235,17 +246,17 @@
     </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="178" fontId="9" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="166" fontId="9" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="177" fontId="8" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1">
+    <xf numFmtId="165" fontId="8" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="178" fontId="9" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="177" fontId="9" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1">
+    <xf numFmtId="166" fontId="9" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="165" fontId="9" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="179" fontId="9" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="167" fontId="9" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="2">
@@ -254,17 +265,17 @@
     <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="178" fontId="8" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="166" fontId="8" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="179" fontId="8" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="167" fontId="8" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="3">
-    <cellStyle name="쉼표" xfId="1" builtinId="3"/>
-    <cellStyle name="표준" xfId="0" builtinId="0"/>
-    <cellStyle name="하이퍼링크" xfId="2" builtinId="8"/>
+    <cellStyle name="Comma" xfId="1" builtinId="3"/>
+    <cellStyle name="Hyperlink" xfId="2" builtinId="8"/>
+    <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
@@ -543,20 +554,20 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:K421"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="9" defaultRowHeight="14"/>
   <cols>
-    <col min="1" max="1" width="9.875" style="5" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="11.125" style="6" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="11.125" style="10" customWidth="1"/>
-    <col min="4" max="4" width="11.125" style="6" customWidth="1"/>
+    <col min="1" max="1" width="9.83203125" style="5" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="11.1640625" style="6" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="11.1640625" style="10" customWidth="1"/>
+    <col min="4" max="4" width="11.1640625" style="6" customWidth="1"/>
     <col min="5" max="8" width="8.5" style="9" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="9.375" style="9" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="9.33203125" style="9" bestFit="1" customWidth="1"/>
     <col min="10" max="10" width="8.5" style="9" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="9.375" style="9" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="9.33203125" style="9" bestFit="1" customWidth="1"/>
     <col min="12" max="16384" width="9" style="5"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:11" ht="15" customHeight="1">
       <c r="A1" s="12" t="s">
         <v>18</v>
       </c>
@@ -591,7 +602,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="2" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:11">
       <c r="A2" s="12"/>
       <c r="B2" s="13"/>
       <c r="C2" s="14"/>
@@ -618,7 +629,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="3" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:11">
       <c r="A3" s="8">
         <f>B3-1</f>
         <v>43100</v>
@@ -654,7 +665,7 @@
         <v>3169</v>
       </c>
     </row>
-    <row r="4" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:11">
       <c r="A4" s="8">
         <f t="shared" ref="A4:A67" si="0">B4-1</f>
         <v>43107</v>
@@ -690,7 +701,7 @@
         <v>2961</v>
       </c>
     </row>
-    <row r="5" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:11">
       <c r="A5" s="8">
         <f t="shared" si="0"/>
         <v>43114</v>
@@ -726,7 +737,7 @@
         <v>2650</v>
       </c>
     </row>
-    <row r="6" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:11">
       <c r="A6" s="8">
         <f t="shared" si="0"/>
         <v>43121</v>
@@ -762,7 +773,7 @@
         <v>2807</v>
       </c>
     </row>
-    <row r="7" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:11">
       <c r="A7" s="8">
         <f t="shared" si="0"/>
         <v>43128</v>
@@ -798,7 +809,7 @@
         <v>2904</v>
       </c>
     </row>
-    <row r="8" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:11">
       <c r="A8" s="8">
         <f t="shared" si="0"/>
         <v>43135</v>
@@ -834,7 +845,7 @@
         <v>2899</v>
       </c>
     </row>
-    <row r="9" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:11">
       <c r="A9" s="8">
         <f t="shared" si="0"/>
         <v>43142</v>
@@ -870,7 +881,7 @@
         <v>2901</v>
       </c>
     </row>
-    <row r="10" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:11">
       <c r="A10" s="8">
         <f t="shared" si="0"/>
         <v>43149</v>
@@ -906,7 +917,7 @@
         <v>2727</v>
       </c>
     </row>
-    <row r="11" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:11">
       <c r="A11" s="8">
         <f t="shared" si="0"/>
         <v>43156</v>
@@ -942,7 +953,7 @@
         <v>2761</v>
       </c>
     </row>
-    <row r="12" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:11">
       <c r="A12" s="8">
         <f t="shared" si="0"/>
         <v>43163</v>
@@ -978,7 +989,7 @@
         <v>2517</v>
       </c>
     </row>
-    <row r="13" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:11">
       <c r="A13" s="8">
         <f t="shared" si="0"/>
         <v>43170</v>
@@ -1014,7 +1025,7 @@
         <v>2740</v>
       </c>
     </row>
-    <row r="14" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:11">
       <c r="A14" s="8">
         <f t="shared" si="0"/>
         <v>43177</v>
@@ -1050,7 +1061,7 @@
         <v>2752</v>
       </c>
     </row>
-    <row r="15" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:11">
       <c r="A15" s="8">
         <f t="shared" si="0"/>
         <v>43184</v>
@@ -1086,7 +1097,7 @@
         <v>2814</v>
       </c>
     </row>
-    <row r="16" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:11">
       <c r="A16" s="8">
         <f t="shared" si="0"/>
         <v>43191</v>
@@ -1122,7 +1133,7 @@
         <v>2989</v>
       </c>
     </row>
-    <row r="17" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:11">
       <c r="A17" s="8">
         <f t="shared" si="0"/>
         <v>43198</v>
@@ -1158,7 +1169,7 @@
         <v>3053</v>
       </c>
     </row>
-    <row r="18" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:11">
       <c r="A18" s="8">
         <f t="shared" si="0"/>
         <v>43205</v>
@@ -1194,7 +1205,7 @@
         <v>2992</v>
       </c>
     </row>
-    <row r="19" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:11">
       <c r="A19" s="8">
         <f t="shared" si="0"/>
         <v>43212</v>
@@ -1230,7 +1241,7 @@
         <v>3134</v>
       </c>
     </row>
-    <row r="20" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:11">
       <c r="A20" s="8">
         <f t="shared" si="0"/>
         <v>43219</v>
@@ -1266,7 +1277,7 @@
         <v>3103</v>
       </c>
     </row>
-    <row r="21" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:11">
       <c r="A21" s="8">
         <f t="shared" si="0"/>
         <v>43226</v>
@@ -1302,7 +1313,7 @@
         <v>2954</v>
       </c>
     </row>
-    <row r="22" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:11">
       <c r="A22" s="8">
         <f t="shared" si="0"/>
         <v>43233</v>
@@ -1338,7 +1349,7 @@
         <v>2913</v>
       </c>
     </row>
-    <row r="23" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:11">
       <c r="A23" s="8">
         <f t="shared" si="0"/>
         <v>43240</v>
@@ -1374,7 +1385,7 @@
         <v>2924</v>
       </c>
     </row>
-    <row r="24" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:11">
       <c r="A24" s="8">
         <f t="shared" si="0"/>
         <v>43247</v>
@@ -1410,7 +1421,7 @@
         <v>2888</v>
       </c>
     </row>
-    <row r="25" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:11">
       <c r="A25" s="8">
         <f t="shared" si="0"/>
         <v>43254</v>
@@ -1446,7 +1457,7 @@
         <v>2904</v>
       </c>
     </row>
-    <row r="26" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:11">
       <c r="A26" s="8">
         <f t="shared" si="0"/>
         <v>43261</v>
@@ -1482,7 +1493,7 @@
         <v>2959</v>
       </c>
     </row>
-    <row r="27" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:11">
       <c r="A27" s="8">
         <f t="shared" si="0"/>
         <v>43268</v>
@@ -1518,7 +1529,7 @@
         <v>2873</v>
       </c>
     </row>
-    <row r="28" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:11">
       <c r="A28" s="8">
         <f t="shared" si="0"/>
         <v>43275</v>
@@ -1554,7 +1565,7 @@
         <v>2769</v>
       </c>
     </row>
-    <row r="29" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:11">
       <c r="A29" s="8">
         <f t="shared" si="0"/>
         <v>43282</v>
@@ -1590,7 +1601,7 @@
         <v>3014</v>
       </c>
     </row>
-    <row r="30" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:11">
       <c r="A30" s="8">
         <f t="shared" si="0"/>
         <v>43289</v>
@@ -1626,7 +1637,7 @@
         <v>3033</v>
       </c>
     </row>
-    <row r="31" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:11">
       <c r="A31" s="8">
         <f t="shared" si="0"/>
         <v>43296</v>
@@ -1662,7 +1673,7 @@
         <v>2930</v>
       </c>
     </row>
-    <row r="32" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:11">
       <c r="A32" s="8">
         <f t="shared" si="0"/>
         <v>43303</v>
@@ -1698,7 +1709,7 @@
         <v>3182</v>
       </c>
     </row>
-    <row r="33" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:11">
       <c r="A33" s="8">
         <f t="shared" si="0"/>
         <v>43310</v>
@@ -1734,7 +1745,7 @@
         <v>3174</v>
       </c>
     </row>
-    <row r="34" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:11">
       <c r="A34" s="8">
         <f t="shared" si="0"/>
         <v>43317</v>
@@ -1770,7 +1781,7 @@
         <v>3183</v>
       </c>
     </row>
-    <row r="35" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:11">
       <c r="A35" s="8">
         <f t="shared" si="0"/>
         <v>43324</v>
@@ -1806,7 +1817,7 @@
         <v>3078</v>
       </c>
     </row>
-    <row r="36" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:11">
       <c r="A36" s="8">
         <f t="shared" si="0"/>
         <v>43331</v>
@@ -1842,7 +1853,7 @@
         <v>3135</v>
       </c>
     </row>
-    <row r="37" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="37" spans="1:11">
       <c r="A37" s="8">
         <f t="shared" si="0"/>
         <v>43338</v>
@@ -1878,7 +1889,7 @@
         <v>3138</v>
       </c>
     </row>
-    <row r="38" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="38" spans="1:11">
       <c r="A38" s="8">
         <f t="shared" si="0"/>
         <v>43345</v>
@@ -1914,7 +1925,7 @@
         <v>3417</v>
       </c>
     </row>
-    <row r="39" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="39" spans="1:11">
       <c r="A39" s="8">
         <f t="shared" si="0"/>
         <v>43352</v>
@@ -1950,7 +1961,7 @@
         <v>3427</v>
       </c>
     </row>
-    <row r="40" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="40" spans="1:11">
       <c r="A40" s="8">
         <f t="shared" si="0"/>
         <v>43359</v>
@@ -1986,7 +1997,7 @@
         <v>3254</v>
       </c>
     </row>
-    <row r="41" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="41" spans="1:11">
       <c r="A41" s="8">
         <f t="shared" si="0"/>
         <v>43366</v>
@@ -2022,7 +2033,7 @@
         <v>3334</v>
       </c>
     </row>
-    <row r="42" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="42" spans="1:11">
       <c r="A42" s="8">
         <f t="shared" si="0"/>
         <v>43373</v>
@@ -2058,7 +2069,7 @@
         <v>3450</v>
       </c>
     </row>
-    <row r="43" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="43" spans="1:11">
       <c r="A43" s="8">
         <f t="shared" si="0"/>
         <v>43380</v>
@@ -2094,7 +2105,7 @@
         <v>3267</v>
       </c>
     </row>
-    <row r="44" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="44" spans="1:11">
       <c r="A44" s="8">
         <f t="shared" si="0"/>
         <v>43387</v>
@@ -2130,7 +2141,7 @@
         <v>3296</v>
       </c>
     </row>
-    <row r="45" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="45" spans="1:11">
       <c r="A45" s="8">
         <f t="shared" si="0"/>
         <v>43394</v>
@@ -2166,7 +2177,7 @@
         <v>3511</v>
       </c>
     </row>
-    <row r="46" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="46" spans="1:11">
       <c r="A46" s="8">
         <f t="shared" si="0"/>
         <v>43401</v>
@@ -2202,7 +2213,7 @@
         <v>3658</v>
       </c>
     </row>
-    <row r="47" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="47" spans="1:11">
       <c r="A47" s="8">
         <f t="shared" si="0"/>
         <v>43408</v>
@@ -2238,7 +2249,7 @@
         <v>3881</v>
       </c>
     </row>
-    <row r="48" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="48" spans="1:11">
       <c r="A48" s="8">
         <f t="shared" si="0"/>
         <v>43415</v>
@@ -2274,7 +2285,7 @@
         <v>3696</v>
       </c>
     </row>
-    <row r="49" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="49" spans="1:11">
       <c r="A49" s="8">
         <f t="shared" si="0"/>
         <v>43422</v>
@@ -2310,7 +2321,7 @@
         <v>3795</v>
       </c>
     </row>
-    <row r="50" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="50" spans="1:11">
       <c r="A50" s="8">
         <f t="shared" si="0"/>
         <v>43429</v>
@@ -2346,7 +2357,7 @@
         <v>3690</v>
       </c>
     </row>
-    <row r="51" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="51" spans="1:11">
       <c r="A51" s="8">
         <f t="shared" si="0"/>
         <v>43436</v>
@@ -2382,7 +2393,7 @@
         <v>3542</v>
       </c>
     </row>
-    <row r="52" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="52" spans="1:11">
       <c r="A52" s="8">
         <f t="shared" si="0"/>
         <v>43443</v>
@@ -2418,7 +2429,7 @@
         <v>3372</v>
       </c>
     </row>
-    <row r="53" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="53" spans="1:11">
       <c r="A53" s="8">
         <f t="shared" si="0"/>
         <v>43450</v>
@@ -2454,7 +2465,7 @@
         <v>3495</v>
       </c>
     </row>
-    <row r="54" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="54" spans="1:11">
       <c r="A54" s="8">
         <f t="shared" si="0"/>
         <v>43457</v>
@@ -2490,7 +2501,7 @@
         <v>3197</v>
       </c>
     </row>
-    <row r="55" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="55" spans="1:11">
       <c r="A55" s="8">
         <f t="shared" si="0"/>
         <v>43464</v>
@@ -2526,7 +2537,7 @@
         <v>3164</v>
       </c>
     </row>
-    <row r="56" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="56" spans="1:11">
       <c r="A56" s="8">
         <f t="shared" si="0"/>
         <v>43471</v>
@@ -2562,7 +2573,7 @@
         <v>3171</v>
       </c>
     </row>
-    <row r="57" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="57" spans="1:11">
       <c r="A57" s="8">
         <f t="shared" si="0"/>
         <v>43478</v>
@@ -2598,7 +2609,7 @@
         <v>3147</v>
       </c>
     </row>
-    <row r="58" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="58" spans="1:11">
       <c r="A58" s="8">
         <f t="shared" si="0"/>
         <v>43485</v>
@@ -2634,7 +2645,7 @@
         <v>3195</v>
       </c>
     </row>
-    <row r="59" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="59" spans="1:11">
       <c r="A59" s="8">
         <f t="shared" si="0"/>
         <v>43492</v>
@@ -2670,7 +2681,7 @@
         <v>3054</v>
       </c>
     </row>
-    <row r="60" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="60" spans="1:11">
       <c r="A60" s="8">
         <f t="shared" si="0"/>
         <v>43499</v>
@@ -2706,7 +2717,7 @@
         <v>3148</v>
       </c>
     </row>
-    <row r="61" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="61" spans="1:11">
       <c r="A61" s="8">
         <f t="shared" si="0"/>
         <v>43506</v>
@@ -2742,7 +2753,7 @@
         <v>3187</v>
       </c>
     </row>
-    <row r="62" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="62" spans="1:11">
       <c r="A62" s="8">
         <f t="shared" si="0"/>
         <v>43513</v>
@@ -2778,7 +2789,7 @@
         <v>3215</v>
       </c>
     </row>
-    <row r="63" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="63" spans="1:11">
       <c r="A63" s="8">
         <f t="shared" si="0"/>
         <v>43520</v>
@@ -2814,7 +2825,7 @@
         <v>3068</v>
       </c>
     </row>
-    <row r="64" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="64" spans="1:11">
       <c r="A64" s="8">
         <f t="shared" si="0"/>
         <v>43527</v>
@@ -2850,7 +2861,7 @@
         <v>2976</v>
       </c>
     </row>
-    <row r="65" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="65" spans="1:11">
       <c r="A65" s="8">
         <f t="shared" si="0"/>
         <v>43534</v>
@@ -2886,7 +2897,7 @@
         <v>2897</v>
       </c>
     </row>
-    <row r="66" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="66" spans="1:11">
       <c r="A66" s="8">
         <f t="shared" si="0"/>
         <v>43541</v>
@@ -2922,7 +2933,7 @@
         <v>2954</v>
       </c>
     </row>
-    <row r="67" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="67" spans="1:11">
       <c r="A67" s="8">
         <f t="shared" si="0"/>
         <v>43548</v>
@@ -2958,7 +2969,7 @@
         <v>2955</v>
       </c>
     </row>
-    <row r="68" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="68" spans="1:11">
       <c r="A68" s="8">
         <f t="shared" ref="A68:A131" si="1">B68-1</f>
         <v>43555</v>
@@ -2994,7 +3005,7 @@
         <v>2977</v>
       </c>
     </row>
-    <row r="69" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="69" spans="1:11">
       <c r="A69" s="8">
         <f t="shared" si="1"/>
         <v>43562</v>
@@ -3030,7 +3041,7 @@
         <v>3113</v>
       </c>
     </row>
-    <row r="70" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="70" spans="1:11">
       <c r="A70" s="8">
         <f t="shared" si="1"/>
         <v>43569</v>
@@ -3066,7 +3077,7 @@
         <v>2876</v>
       </c>
     </row>
-    <row r="71" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="71" spans="1:11">
       <c r="A71" s="8">
         <f t="shared" si="1"/>
         <v>43576</v>
@@ -3102,7 +3113,7 @@
         <v>2704</v>
       </c>
     </row>
-    <row r="72" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="72" spans="1:11">
       <c r="A72" s="8">
         <f t="shared" si="1"/>
         <v>43583</v>
@@ -3138,7 +3149,7 @@
         <v>2822</v>
       </c>
     </row>
-    <row r="73" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="73" spans="1:11">
       <c r="A73" s="8">
         <f t="shared" si="1"/>
         <v>43590</v>
@@ -3174,7 +3185,7 @@
         <v>2776</v>
       </c>
     </row>
-    <row r="74" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="74" spans="1:11">
       <c r="A74" s="8">
         <f t="shared" si="1"/>
         <v>43597</v>
@@ -3210,7 +3221,7 @@
         <v>2732</v>
       </c>
     </row>
-    <row r="75" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="75" spans="1:11">
       <c r="A75" s="8">
         <f t="shared" si="1"/>
         <v>43604</v>
@@ -3246,7 +3257,7 @@
         <v>2772</v>
       </c>
     </row>
-    <row r="76" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="76" spans="1:11">
       <c r="A76" s="8">
         <f t="shared" si="1"/>
         <v>43611</v>
@@ -3282,7 +3293,7 @@
         <v>2788</v>
       </c>
     </row>
-    <row r="77" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="77" spans="1:11">
       <c r="A77" s="8">
         <f t="shared" si="1"/>
         <v>43618</v>
@@ -3318,7 +3329,7 @@
         <v>2662</v>
       </c>
     </row>
-    <row r="78" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="78" spans="1:11">
       <c r="A78" s="8">
         <f t="shared" si="1"/>
         <v>43625</v>
@@ -3354,7 +3365,7 @@
         <v>2677</v>
       </c>
     </row>
-    <row r="79" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="79" spans="1:11">
       <c r="A79" s="8">
         <f t="shared" si="1"/>
         <v>43632</v>
@@ -3390,7 +3401,7 @@
         <v>2532</v>
       </c>
     </row>
-    <row r="80" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="80" spans="1:11">
       <c r="A80" s="8">
         <f t="shared" si="1"/>
         <v>43639</v>
@@ -3426,7 +3437,7 @@
         <v>2732</v>
       </c>
     </row>
-    <row r="81" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="81" spans="1:11">
       <c r="A81" s="8">
         <f t="shared" si="1"/>
         <v>43646</v>
@@ -3462,7 +3473,7 @@
         <v>2742</v>
       </c>
     </row>
-    <row r="82" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="82" spans="1:11">
       <c r="A82" s="8">
         <f t="shared" si="1"/>
         <v>43653</v>
@@ -3498,7 +3509,7 @@
         <v>2772</v>
       </c>
     </row>
-    <row r="83" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="83" spans="1:11">
       <c r="A83" s="8">
         <f t="shared" si="1"/>
         <v>43660</v>
@@ -3534,7 +3545,7 @@
         <v>2766</v>
       </c>
     </row>
-    <row r="84" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="84" spans="1:11">
       <c r="A84" s="8">
         <f t="shared" si="1"/>
         <v>43667</v>
@@ -3570,7 +3581,7 @@
         <v>2587</v>
       </c>
     </row>
-    <row r="85" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="85" spans="1:11">
       <c r="A85" s="8">
         <f t="shared" si="1"/>
         <v>43674</v>
@@ -3606,7 +3617,7 @@
         <v>2668</v>
       </c>
     </row>
-    <row r="86" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="86" spans="1:11">
       <c r="A86" s="8">
         <f t="shared" si="1"/>
         <v>43681</v>
@@ -3642,7 +3653,7 @@
         <v>2605</v>
       </c>
     </row>
-    <row r="87" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="87" spans="1:11">
       <c r="A87" s="8">
         <f t="shared" si="1"/>
         <v>43688</v>
@@ -3678,7 +3689,7 @@
         <v>2551</v>
       </c>
     </row>
-    <row r="88" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="88" spans="1:11">
       <c r="A88" s="8">
         <f t="shared" si="1"/>
         <v>43695</v>
@@ -3714,7 +3725,7 @@
         <v>2628</v>
       </c>
     </row>
-    <row r="89" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="89" spans="1:11">
       <c r="A89" s="8">
         <f t="shared" si="1"/>
         <v>43702</v>
@@ -3750,7 +3761,7 @@
         <v>2656</v>
       </c>
     </row>
-    <row r="90" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="90" spans="1:11">
       <c r="A90" s="8">
         <f t="shared" si="1"/>
         <v>43709</v>
@@ -3786,7 +3797,7 @@
         <v>2608</v>
       </c>
     </row>
-    <row r="91" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="91" spans="1:11">
       <c r="A91" s="8">
         <f t="shared" si="1"/>
         <v>43716</v>
@@ -3822,7 +3833,7 @@
         <v>2611</v>
       </c>
     </row>
-    <row r="92" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="92" spans="1:11">
       <c r="A92" s="8">
         <f t="shared" si="1"/>
         <v>43723</v>
@@ -3858,7 +3869,7 @@
         <v>2550</v>
       </c>
     </row>
-    <row r="93" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="93" spans="1:11">
       <c r="A93" s="8">
         <f t="shared" si="1"/>
         <v>43730</v>
@@ -3894,7 +3905,7 @@
         <v>2572</v>
       </c>
     </row>
-    <row r="94" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="94" spans="1:11">
       <c r="A94" s="8">
         <f t="shared" si="1"/>
         <v>43737</v>
@@ -3930,7 +3941,7 @@
         <v>2703</v>
       </c>
     </row>
-    <row r="95" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="95" spans="1:11">
       <c r="A95" s="8">
         <f t="shared" si="1"/>
         <v>43744</v>
@@ -3966,7 +3977,7 @@
         <v>2804</v>
       </c>
     </row>
-    <row r="96" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="96" spans="1:11">
       <c r="A96" s="8">
         <f t="shared" si="1"/>
         <v>43751</v>
@@ -4002,7 +4013,7 @@
         <v>2781</v>
       </c>
     </row>
-    <row r="97" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="97" spans="1:11">
       <c r="A97" s="8">
         <f t="shared" si="1"/>
         <v>43758</v>
@@ -4038,7 +4049,7 @@
         <v>2915</v>
       </c>
     </row>
-    <row r="98" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="98" spans="1:11">
       <c r="A98" s="8">
         <f t="shared" si="1"/>
         <v>43765</v>
@@ -4074,7 +4085,7 @@
         <v>3032</v>
       </c>
     </row>
-    <row r="99" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="99" spans="1:11">
       <c r="A99" s="8">
         <f t="shared" si="1"/>
         <v>43772</v>
@@ -4110,7 +4121,7 @@
         <v>3120</v>
       </c>
     </row>
-    <row r="100" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="100" spans="1:11">
       <c r="A100" s="8">
         <f t="shared" si="1"/>
         <v>43779</v>
@@ -4146,7 +4157,7 @@
         <v>3031</v>
       </c>
     </row>
-    <row r="101" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="101" spans="1:11">
       <c r="A101" s="8">
         <f t="shared" si="1"/>
         <v>43786</v>
@@ -4182,7 +4193,7 @@
         <v>3117</v>
       </c>
     </row>
-    <row r="102" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="102" spans="1:11">
       <c r="A102" s="8">
         <f t="shared" si="1"/>
         <v>43793</v>
@@ -4218,7 +4229,7 @@
         <v>3143</v>
       </c>
     </row>
-    <row r="103" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="103" spans="1:11">
       <c r="A103" s="8">
         <f t="shared" si="1"/>
         <v>43800</v>
@@ -4254,7 +4265,7 @@
         <v>3079</v>
       </c>
     </row>
-    <row r="104" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="104" spans="1:11">
       <c r="A104" s="8">
         <f t="shared" si="1"/>
         <v>43807</v>
@@ -4290,7 +4301,7 @@
         <v>3019</v>
       </c>
     </row>
-    <row r="105" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="105" spans="1:11">
       <c r="A105" s="8">
         <f t="shared" si="1"/>
         <v>43814</v>
@@ -4326,7 +4337,7 @@
         <v>2964</v>
       </c>
     </row>
-    <row r="106" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="106" spans="1:11">
       <c r="A106" s="8">
         <f t="shared" si="1"/>
         <v>43821</v>
@@ -4362,7 +4373,7 @@
         <v>2821</v>
       </c>
     </row>
-    <row r="107" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="107" spans="1:11">
       <c r="A107" s="8">
         <f t="shared" si="1"/>
         <v>43828</v>
@@ -4398,7 +4409,7 @@
         <v>2760</v>
       </c>
     </row>
-    <row r="108" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="108" spans="1:11">
       <c r="A108" s="8">
         <f t="shared" si="1"/>
         <v>43835</v>
@@ -4434,7 +4445,7 @@
         <v>2776</v>
       </c>
     </row>
-    <row r="109" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="109" spans="1:11">
       <c r="A109" s="8">
         <f t="shared" si="1"/>
         <v>43842</v>
@@ -4470,7 +4481,7 @@
         <v>2636</v>
       </c>
     </row>
-    <row r="110" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="110" spans="1:11">
       <c r="A110" s="8">
         <f t="shared" si="1"/>
         <v>43849</v>
@@ -4506,7 +4517,7 @@
         <v>2698</v>
       </c>
     </row>
-    <row r="111" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="111" spans="1:11">
       <c r="A111" s="8">
         <f t="shared" si="1"/>
         <v>43856</v>
@@ -4542,7 +4553,7 @@
         <v>2838</v>
       </c>
     </row>
-    <row r="112" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="112" spans="1:11">
       <c r="A112" s="8">
         <f t="shared" si="1"/>
         <v>43863</v>
@@ -4578,7 +4589,7 @@
         <v>2587</v>
       </c>
     </row>
-    <row r="113" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="113" spans="1:11">
       <c r="A113" s="8">
         <f t="shared" si="1"/>
         <v>43870</v>
@@ -4614,7 +4625,7 @@
         <v>2498</v>
       </c>
     </row>
-    <row r="114" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="114" spans="1:11">
       <c r="A114" s="8">
         <f t="shared" si="1"/>
         <v>43877</v>
@@ -4650,7 +4661,7 @@
         <v>2427</v>
       </c>
     </row>
-    <row r="115" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="115" spans="1:11">
       <c r="A115" s="8">
         <f t="shared" si="1"/>
         <v>43884</v>
@@ -4686,7 +4697,7 @@
         <v>2239</v>
       </c>
     </row>
-    <row r="116" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="116" spans="1:11">
       <c r="A116" s="8">
         <f t="shared" si="1"/>
         <v>43891</v>
@@ -4722,7 +4733,7 @@
         <v>2539</v>
       </c>
     </row>
-    <row r="117" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="117" spans="1:11">
       <c r="A117" s="8">
         <f t="shared" si="1"/>
         <v>43898</v>
@@ -4758,7 +4769,7 @@
         <v>3154</v>
       </c>
     </row>
-    <row r="118" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="118" spans="1:11">
       <c r="A118" s="8">
         <f t="shared" si="1"/>
         <v>43905</v>
@@ -4794,7 +4805,7 @@
         <v>3858</v>
       </c>
     </row>
-    <row r="119" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="119" spans="1:11">
       <c r="A119" s="8">
         <f t="shared" si="1"/>
         <v>43912</v>
@@ -4830,7 +4841,7 @@
         <v>4713</v>
       </c>
     </row>
-    <row r="120" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="120" spans="1:11">
       <c r="A120" s="8">
         <f t="shared" si="1"/>
         <v>43919</v>
@@ -4866,7 +4877,7 @@
         <v>5641</v>
       </c>
     </row>
-    <row r="121" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="121" spans="1:11">
       <c r="A121" s="8">
         <f t="shared" si="1"/>
         <v>43926</v>
@@ -4902,7 +4913,7 @@
         <v>6426</v>
       </c>
     </row>
-    <row r="122" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="122" spans="1:11">
       <c r="A122" s="8">
         <f t="shared" si="1"/>
         <v>43933</v>
@@ -4938,7 +4949,7 @@
         <v>7284</v>
       </c>
     </row>
-    <row r="123" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="123" spans="1:11">
       <c r="A123" s="8">
         <f t="shared" si="1"/>
         <v>43940</v>
@@ -4974,7 +4985,7 @@
         <v>7946</v>
       </c>
     </row>
-    <row r="124" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="124" spans="1:11">
       <c r="A124" s="8">
         <f t="shared" si="1"/>
         <v>43947</v>
@@ -5010,7 +5021,7 @@
         <v>8608</v>
       </c>
     </row>
-    <row r="125" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="125" spans="1:11">
       <c r="A125" s="8">
         <f t="shared" si="1"/>
         <v>43954</v>
@@ -5046,7 +5057,7 @@
         <v>9951</v>
       </c>
     </row>
-    <row r="126" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="126" spans="1:11">
       <c r="A126" s="8">
         <f t="shared" si="1"/>
         <v>43961</v>
@@ -5082,7 +5093,7 @@
         <v>10351</v>
       </c>
     </row>
-    <row r="127" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="127" spans="1:11">
       <c r="A127" s="8">
         <f t="shared" si="1"/>
         <v>43968</v>
@@ -5118,7 +5129,7 @@
         <v>11202</v>
       </c>
     </row>
-    <row r="128" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="128" spans="1:11">
       <c r="A128" s="8">
         <f t="shared" si="1"/>
         <v>43975</v>
@@ -5154,7 +5165,7 @@
         <v>9824</v>
       </c>
     </row>
-    <row r="129" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="129" spans="1:11">
       <c r="A129" s="8">
         <f t="shared" si="1"/>
         <v>43982</v>
@@ -5190,7 +5201,7 @@
         <v>7635</v>
       </c>
     </row>
-    <row r="130" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="130" spans="1:11">
       <c r="A130" s="8">
         <f t="shared" si="1"/>
         <v>43989</v>
@@ -5226,7 +5237,7 @@
         <v>5993</v>
       </c>
     </row>
-    <row r="131" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="131" spans="1:11">
       <c r="A131" s="8">
         <f t="shared" si="1"/>
         <v>43996</v>
@@ -5262,7 +5273,7 @@
         <v>4905</v>
       </c>
     </row>
-    <row r="132" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="132" spans="1:11">
       <c r="A132" s="8">
         <f t="shared" ref="A132:A195" si="2">B132-1</f>
         <v>44003</v>
@@ -5298,7 +5309,7 @@
         <v>4035</v>
       </c>
     </row>
-    <row r="133" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="133" spans="1:11">
       <c r="A133" s="8">
         <f t="shared" si="2"/>
         <v>44010</v>
@@ -5334,7 +5345,7 @@
         <v>3835</v>
       </c>
     </row>
-    <row r="134" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="134" spans="1:11">
       <c r="A134" s="8">
         <f t="shared" si="2"/>
         <v>44017</v>
@@ -5370,7 +5381,7 @@
         <v>3711</v>
       </c>
     </row>
-    <row r="135" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="135" spans="1:11">
       <c r="A135" s="8">
         <f t="shared" si="2"/>
         <v>44024</v>
@@ -5406,7 +5417,7 @@
         <v>3775</v>
       </c>
     </row>
-    <row r="136" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="136" spans="1:11">
       <c r="A136" s="8">
         <f t="shared" si="2"/>
         <v>44031</v>
@@ -5442,7 +5453,7 @@
         <v>3862</v>
       </c>
     </row>
-    <row r="137" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="137" spans="1:11">
       <c r="A137" s="8">
         <f t="shared" si="2"/>
         <v>44038</v>
@@ -5478,7 +5489,7 @@
         <v>4050</v>
       </c>
     </row>
-    <row r="138" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="138" spans="1:11">
       <c r="A138" s="8">
         <f t="shared" si="2"/>
         <v>44045</v>
@@ -5514,7 +5525,7 @@
         <v>4535</v>
       </c>
     </row>
-    <row r="139" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="139" spans="1:11">
       <c r="A139" s="8">
         <f t="shared" si="2"/>
         <v>44052</v>
@@ -5550,7 +5561,7 @@
         <v>4425</v>
       </c>
     </row>
-    <row r="140" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="140" spans="1:11">
       <c r="A140" s="8">
         <f t="shared" si="2"/>
         <v>44059</v>
@@ -5586,7 +5597,7 @@
         <v>4121</v>
       </c>
     </row>
-    <row r="141" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="141" spans="1:11">
       <c r="A141" s="8">
         <f t="shared" si="2"/>
         <v>44066</v>
@@ -5622,7 +5633,7 @@
         <v>3819</v>
       </c>
     </row>
-    <row r="142" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="142" spans="1:11">
       <c r="A142" s="8">
         <f t="shared" si="2"/>
         <v>44073</v>
@@ -5658,7 +5669,7 @@
         <v>4332</v>
       </c>
     </row>
-    <row r="143" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="143" spans="1:11">
       <c r="A143" s="8">
         <f t="shared" si="2"/>
         <v>44080</v>
@@ -5694,7 +5705,7 @@
         <v>4498</v>
       </c>
     </row>
-    <row r="144" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="144" spans="1:11">
       <c r="A144" s="8">
         <f t="shared" si="2"/>
         <v>44087</v>
@@ -5730,7 +5741,7 @@
         <v>4225</v>
       </c>
     </row>
-    <row r="145" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="145" spans="1:11">
       <c r="A145" s="8">
         <f t="shared" si="2"/>
         <v>44094</v>
@@ -5766,7 +5777,7 @@
         <v>4242</v>
       </c>
     </row>
-    <row r="146" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="146" spans="1:11">
       <c r="A146" s="8">
         <f t="shared" si="2"/>
         <v>44101</v>
@@ -5802,7 +5813,7 @@
         <v>4340</v>
       </c>
     </row>
-    <row r="147" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="147" spans="1:11">
       <c r="A147" s="8">
         <f t="shared" si="2"/>
         <v>44108</v>
@@ -5838,7 +5849,7 @@
         <v>4375</v>
       </c>
     </row>
-    <row r="148" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="148" spans="1:11">
       <c r="A148" s="8">
         <f t="shared" si="2"/>
         <v>44115</v>
@@ -5874,7 +5885,7 @@
         <v>4297</v>
       </c>
     </row>
-    <row r="149" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="149" spans="1:11">
       <c r="A149" s="8">
         <f t="shared" si="2"/>
         <v>44122</v>
@@ -5910,7 +5921,7 @@
         <v>4957</v>
       </c>
     </row>
-    <row r="150" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="150" spans="1:11">
       <c r="A150" s="8">
         <f t="shared" si="2"/>
         <v>44129</v>
@@ -5946,7 +5957,7 @@
         <v>5696</v>
       </c>
     </row>
-    <row r="151" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="151" spans="1:11">
       <c r="A151" s="8">
         <f t="shared" si="2"/>
         <v>44136</v>
@@ -5982,7 +5993,7 @@
         <v>6193</v>
       </c>
     </row>
-    <row r="152" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="152" spans="1:11">
       <c r="A152" s="8">
         <f t="shared" si="2"/>
         <v>44143</v>
@@ -6018,7 +6029,7 @@
         <v>6336</v>
       </c>
     </row>
-    <row r="153" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="153" spans="1:11">
       <c r="A153" s="8">
         <f t="shared" si="2"/>
         <v>44150</v>
@@ -6054,7 +6065,7 @@
         <v>6128</v>
       </c>
     </row>
-    <row r="154" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="154" spans="1:11">
       <c r="A154" s="8">
         <f t="shared" si="2"/>
         <v>44157</v>
@@ -6090,7 +6101,7 @@
         <v>5805</v>
       </c>
     </row>
-    <row r="155" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="155" spans="1:11">
       <c r="A155" s="8">
         <f t="shared" si="2"/>
         <v>44164</v>
@@ -6126,7 +6137,7 @@
         <v>6359</v>
       </c>
     </row>
-    <row r="156" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="156" spans="1:11">
       <c r="A156" s="8">
         <f t="shared" si="2"/>
         <v>44171</v>
@@ -6162,7 +6173,7 @@
         <v>6501</v>
       </c>
     </row>
-    <row r="157" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="157" spans="1:11">
       <c r="A157" s="8">
         <f t="shared" si="2"/>
         <v>44178</v>
@@ -6198,7 +6209,7 @@
         <v>6639</v>
       </c>
     </row>
-    <row r="158" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="158" spans="1:11">
       <c r="A158" s="8">
         <f t="shared" si="2"/>
         <v>44185</v>
@@ -6234,7 +6245,7 @@
         <v>6623</v>
       </c>
     </row>
-    <row r="159" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="159" spans="1:11">
       <c r="A159" s="8">
         <f t="shared" si="2"/>
         <v>44192</v>
@@ -6270,7 +6281,7 @@
         <v>6235</v>
       </c>
     </row>
-    <row r="160" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="160" spans="1:11">
       <c r="A160" s="8">
         <f t="shared" si="2"/>
         <v>44199</v>
@@ -6306,7 +6317,7 @@
         <v>6313</v>
       </c>
     </row>
-    <row r="161" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="161" spans="1:11">
       <c r="A161" s="8">
         <f t="shared" si="2"/>
         <v>44206</v>
@@ -6342,7 +6353,7 @@
         <v>5714</v>
       </c>
     </row>
-    <row r="162" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="162" spans="1:11">
       <c r="A162" s="8">
         <f t="shared" si="2"/>
         <v>44213</v>
@@ -6378,7 +6389,7 @@
         <v>4512</v>
       </c>
     </row>
-    <row r="163" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="163" spans="1:11">
       <c r="A163" s="8">
         <f t="shared" si="2"/>
         <v>44220</v>
@@ -6414,7 +6425,7 @@
         <v>4555</v>
       </c>
     </row>
-    <row r="164" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="164" spans="1:11">
       <c r="A164" s="8">
         <f t="shared" si="2"/>
         <v>44227</v>
@@ -6450,7 +6461,7 @@
         <v>5245</v>
       </c>
     </row>
-    <row r="165" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="165" spans="1:11">
       <c r="A165" s="8">
         <f t="shared" si="2"/>
         <v>44234</v>
@@ -6486,7 +6497,7 @@
         <v>5649</v>
       </c>
     </row>
-    <row r="166" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="166" spans="1:11">
       <c r="A166" s="8">
         <f t="shared" si="2"/>
         <v>44241</v>
@@ -6522,7 +6533,7 @@
         <v>6333</v>
       </c>
     </row>
-    <row r="167" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="167" spans="1:11">
       <c r="A167" s="8">
         <f t="shared" si="2"/>
         <v>44248</v>
@@ -6558,7 +6569,7 @@
         <v>4242</v>
       </c>
     </row>
-    <row r="168" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="168" spans="1:11">
       <c r="A168" s="8">
         <f t="shared" si="2"/>
         <v>44255</v>
@@ -6594,7 +6605,7 @@
         <v>4791</v>
       </c>
     </row>
-    <row r="169" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="169" spans="1:11">
       <c r="A169" s="8">
         <f t="shared" si="2"/>
         <v>44262</v>
@@ -6630,7 +6641,7 @@
         <v>4641</v>
       </c>
     </row>
-    <row r="170" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="170" spans="1:11">
       <c r="A170" s="8">
         <f t="shared" si="2"/>
         <v>44269</v>
@@ -6666,7 +6677,7 @@
         <v>4365</v>
       </c>
     </row>
-    <row r="171" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="171" spans="1:11">
       <c r="A171" s="8">
         <f t="shared" si="2"/>
         <v>44276</v>
@@ -6702,7 +6713,7 @@
         <v>4549</v>
       </c>
     </row>
-    <row r="172" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="172" spans="1:11">
       <c r="A172" s="8">
         <f t="shared" si="2"/>
         <v>44283</v>
@@ -6738,7 +6749,7 @@
         <v>4728</v>
       </c>
     </row>
-    <row r="173" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="173" spans="1:11">
       <c r="A173" s="8">
         <f t="shared" si="2"/>
         <v>44290</v>
@@ -6774,7 +6785,7 @@
         <v>5485</v>
       </c>
     </row>
-    <row r="174" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="174" spans="1:11">
       <c r="A174" s="8">
         <f t="shared" si="2"/>
         <v>44297</v>
@@ -6810,7 +6821,7 @@
         <v>6192</v>
       </c>
     </row>
-    <row r="175" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="175" spans="1:11">
       <c r="A175" s="8">
         <f t="shared" si="2"/>
         <v>44304</v>
@@ -6846,7 +6857,7 @@
         <v>5842</v>
       </c>
     </row>
-    <row r="176" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="176" spans="1:11">
       <c r="A176" s="8">
         <f t="shared" si="2"/>
         <v>44311</v>
@@ -6882,7 +6893,7 @@
         <v>6366</v>
       </c>
     </row>
-    <row r="177" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="177" spans="1:11">
       <c r="A177" s="8">
         <f t="shared" si="2"/>
         <v>44318</v>
@@ -6918,7 +6929,7 @@
         <v>6907</v>
       </c>
     </row>
-    <row r="178" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="178" spans="1:11">
       <c r="A178" s="8">
         <f t="shared" si="2"/>
         <v>44325</v>
@@ -6954,7 +6965,7 @@
         <v>6230</v>
       </c>
     </row>
-    <row r="179" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="179" spans="1:11">
       <c r="A179" s="8">
         <f t="shared" si="2"/>
         <v>44332</v>
@@ -6990,7 +7001,7 @@
         <v>6092</v>
       </c>
     </row>
-    <row r="180" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="180" spans="1:11">
       <c r="A180" s="8">
         <f t="shared" si="2"/>
         <v>44339</v>
@@ -7026,7 +7037,7 @@
         <v>6452</v>
       </c>
     </row>
-    <row r="181" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="181" spans="1:11">
       <c r="A181" s="8">
         <f t="shared" si="2"/>
         <v>44346</v>
@@ -7062,7 +7073,7 @@
         <v>5834</v>
       </c>
     </row>
-    <row r="182" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="182" spans="1:11">
       <c r="A182" s="8">
         <f t="shared" si="2"/>
         <v>44353</v>
@@ -7098,7 +7109,7 @@
         <v>5722</v>
       </c>
     </row>
-    <row r="183" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="183" spans="1:11">
       <c r="A183" s="8">
         <f t="shared" si="2"/>
         <v>44360</v>
@@ -7134,7 +7145,7 @@
         <v>5443</v>
       </c>
     </row>
-    <row r="184" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="184" spans="1:11">
       <c r="A184" s="8">
         <f t="shared" si="2"/>
         <v>44367</v>
@@ -7170,7 +7181,7 @@
         <v>4973</v>
       </c>
     </row>
-    <row r="185" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="185" spans="1:11">
       <c r="A185" s="8">
         <f t="shared" si="2"/>
         <v>44374</v>
@@ -7206,7 +7217,7 @@
         <v>5258</v>
       </c>
     </row>
-    <row r="186" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="186" spans="1:11">
       <c r="A186" s="8">
         <f t="shared" si="2"/>
         <v>44381</v>
@@ -7242,7 +7253,7 @@
         <v>5338</v>
       </c>
     </row>
-    <row r="187" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="187" spans="1:11">
       <c r="A187" s="8">
         <f t="shared" si="2"/>
         <v>44388</v>
@@ -7278,7 +7289,7 @@
         <v>5987</v>
       </c>
     </row>
-    <row r="188" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="188" spans="1:11">
       <c r="A188" s="8">
         <f t="shared" si="2"/>
         <v>44395</v>
@@ -7314,7 +7325,7 @@
         <v>5801</v>
       </c>
     </row>
-    <row r="189" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="189" spans="1:11">
       <c r="A189" s="8">
         <f t="shared" si="2"/>
         <v>44402</v>
@@ -7350,7 +7361,7 @@
         <v>5421</v>
       </c>
     </row>
-    <row r="190" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="190" spans="1:11">
       <c r="A190" s="8">
         <f t="shared" si="2"/>
         <v>44409</v>
@@ -7386,7 +7397,7 @@
         <v>5883</v>
       </c>
     </row>
-    <row r="191" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="191" spans="1:11">
       <c r="A191" s="8">
         <f t="shared" si="2"/>
         <v>44416</v>
@@ -7422,7 +7433,7 @@
         <v>5967</v>
       </c>
     </row>
-    <row r="192" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="192" spans="1:11">
       <c r="A192" s="8">
         <f t="shared" si="2"/>
         <v>44423</v>
@@ -7458,7 +7469,7 @@
         <v>6015</v>
       </c>
     </row>
-    <row r="193" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="193" spans="1:11">
       <c r="A193" s="8">
         <f t="shared" si="2"/>
         <v>44430</v>
@@ -7494,7 +7505,7 @@
         <v>6147</v>
       </c>
     </row>
-    <row r="194" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="194" spans="1:11">
       <c r="A194" s="8">
         <f t="shared" si="2"/>
         <v>44437</v>
@@ -7530,7 +7541,7 @@
         <v>7552</v>
       </c>
     </row>
-    <row r="195" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="195" spans="1:11">
       <c r="A195" s="8">
         <f t="shared" si="2"/>
         <v>44444</v>
@@ -7566,7 +7577,7 @@
         <v>8099</v>
       </c>
     </row>
-    <row r="196" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="196" spans="1:11">
       <c r="A196" s="8">
         <f t="shared" ref="A196:A259" si="3">B196-1</f>
         <v>44451</v>
@@ -7602,7 +7613,7 @@
         <v>8281</v>
       </c>
     </row>
-    <row r="197" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="197" spans="1:11">
       <c r="A197" s="8">
         <f t="shared" si="3"/>
         <v>44458</v>
@@ -7638,7 +7649,7 @@
         <v>9021</v>
       </c>
     </row>
-    <row r="198" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="198" spans="1:11">
       <c r="A198" s="8">
         <f t="shared" si="3"/>
         <v>44465</v>
@@ -7674,7 +7685,7 @@
         <v>9364</v>
       </c>
     </row>
-    <row r="199" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="199" spans="1:11">
       <c r="A199" s="8">
         <f t="shared" si="3"/>
         <v>44472</v>
@@ -7710,7 +7721,7 @@
         <v>9090</v>
       </c>
     </row>
-    <row r="200" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="200" spans="1:11">
       <c r="A200" s="8">
         <f t="shared" si="3"/>
         <v>44479</v>
@@ -7746,7 +7757,7 @@
         <v>8936</v>
       </c>
     </row>
-    <row r="201" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="201" spans="1:11">
       <c r="A201" s="8">
         <f t="shared" si="3"/>
         <v>44486</v>
@@ -7782,7 +7793,7 @@
         <v>8252</v>
       </c>
     </row>
-    <row r="202" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="202" spans="1:11">
       <c r="A202" s="8">
         <f t="shared" si="3"/>
         <v>44493</v>
@@ -7818,7 +7829,7 @@
         <v>8513</v>
       </c>
     </row>
-    <row r="203" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="203" spans="1:11">
       <c r="A203" s="8">
         <f t="shared" si="3"/>
         <v>44500</v>
@@ -7854,7 +7865,7 @@
         <v>8569</v>
       </c>
     </row>
-    <row r="204" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="204" spans="1:11">
       <c r="A204" s="8">
         <f t="shared" si="3"/>
         <v>44507</v>
@@ -7890,7 +7901,7 @@
         <v>10146</v>
       </c>
     </row>
-    <row r="205" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="205" spans="1:11">
       <c r="A205" s="8">
         <f t="shared" si="3"/>
         <v>44514</v>
@@ -7926,7 +7937,7 @@
         <v>9833</v>
       </c>
     </row>
-    <row r="206" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="206" spans="1:11">
       <c r="A206" s="8">
         <f t="shared" si="3"/>
         <v>44521</v>
@@ -7962,7 +7973,7 @@
         <v>10713</v>
       </c>
     </row>
-    <row r="207" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="207" spans="1:11">
       <c r="A207" s="8">
         <f t="shared" si="3"/>
         <v>44528</v>
@@ -7998,7 +8009,7 @@
         <v>10672</v>
       </c>
     </row>
-    <row r="208" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="208" spans="1:11">
       <c r="A208" s="8">
         <f t="shared" si="3"/>
         <v>44535</v>
@@ -8034,7 +8045,7 @@
         <v>11408</v>
       </c>
     </row>
-    <row r="209" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="209" spans="1:11">
       <c r="A209" s="8">
         <f t="shared" si="3"/>
         <v>44542</v>
@@ -8070,7 +8081,7 @@
         <v>12068</v>
       </c>
     </row>
-    <row r="210" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="210" spans="1:11">
       <c r="A210" s="8">
         <f t="shared" si="3"/>
         <v>44549</v>
@@ -8106,7 +8117,7 @@
         <v>10758</v>
       </c>
     </row>
-    <row r="211" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="211" spans="1:11">
       <c r="A211" s="8">
         <f t="shared" si="3"/>
         <v>44556</v>
@@ -8142,7 +8153,7 @@
         <v>10247</v>
       </c>
     </row>
-    <row r="212" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="212" spans="1:11">
       <c r="A212" s="8">
         <f t="shared" si="3"/>
         <v>44563</v>
@@ -8178,7 +8189,7 @@
         <v>9786</v>
       </c>
     </row>
-    <row r="213" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="213" spans="1:11">
       <c r="A213" s="8">
         <f t="shared" si="3"/>
         <v>44570</v>
@@ -8214,7 +8225,7 @@
         <v>8461</v>
       </c>
     </row>
-    <row r="214" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="214" spans="1:11">
       <c r="A214" s="8">
         <f t="shared" si="3"/>
         <v>44577</v>
@@ -8250,7 +8261,7 @@
         <v>6933</v>
       </c>
     </row>
-    <row r="215" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="215" spans="1:11">
       <c r="A215" s="8">
         <f t="shared" si="3"/>
         <v>44584</v>
@@ -8286,7 +8297,7 @@
         <v>7524</v>
       </c>
     </row>
-    <row r="216" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="216" spans="1:11">
       <c r="A216" s="8">
         <f t="shared" si="3"/>
         <v>44591</v>
@@ -8322,7 +8333,7 @@
         <v>7909</v>
       </c>
     </row>
-    <row r="217" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="217" spans="1:11">
       <c r="A217" s="8">
         <f t="shared" si="3"/>
         <v>44598</v>
@@ -8358,7 +8369,7 @@
         <v>6947</v>
       </c>
     </row>
-    <row r="218" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="218" spans="1:11">
       <c r="A218" s="8">
         <f t="shared" si="3"/>
         <v>44605</v>
@@ -8394,7 +8405,7 @@
         <v>6615</v>
       </c>
     </row>
-    <row r="219" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="219" spans="1:11">
       <c r="A219" s="8">
         <f t="shared" si="3"/>
         <v>44612</v>
@@ -8430,7 +8441,7 @@
         <v>6659</v>
       </c>
     </row>
-    <row r="220" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="220" spans="1:11">
       <c r="A220" s="8">
         <f t="shared" si="3"/>
         <v>44619</v>
@@ -8466,7 +8477,7 @@
         <v>6470</v>
       </c>
     </row>
-    <row r="221" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="221" spans="1:11">
       <c r="A221" s="8">
         <f t="shared" si="3"/>
         <v>44626</v>
@@ -8502,7 +8513,7 @@
         <v>5896</v>
       </c>
     </row>
-    <row r="222" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="222" spans="1:11">
       <c r="A222" s="8">
         <f t="shared" si="3"/>
         <v>44633</v>
@@ -8538,7 +8549,7 @@
         <v>7688</v>
       </c>
     </row>
-    <row r="223" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="223" spans="1:11">
       <c r="A223" s="8">
         <f t="shared" si="3"/>
         <v>44640</v>
@@ -8574,7 +8585,7 @@
         <v>7591</v>
       </c>
     </row>
-    <row r="224" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="224" spans="1:11">
       <c r="A224" s="8">
         <f t="shared" si="3"/>
         <v>44647</v>
@@ -8610,7 +8621,7 @@
         <v>7550</v>
       </c>
     </row>
-    <row r="225" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="225" spans="1:11">
       <c r="A225" s="8">
         <f t="shared" si="3"/>
         <v>44654</v>
@@ -8646,7 +8657,7 @@
         <v>8345</v>
       </c>
     </row>
-    <row r="226" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="226" spans="1:11">
       <c r="A226" s="8">
         <f t="shared" si="3"/>
         <v>44661</v>
@@ -8682,7 +8693,7 @@
         <v>8476</v>
       </c>
     </row>
-    <row r="227" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="227" spans="1:11">
       <c r="A227" s="8">
         <f t="shared" si="3"/>
         <v>44668</v>
@@ -8718,7 +8729,7 @@
         <v>7813</v>
       </c>
     </row>
-    <row r="228" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="228" spans="1:11">
       <c r="A228" s="8">
         <f t="shared" si="3"/>
         <v>44675</v>
@@ -8754,7 +8765,7 @@
         <v>8281</v>
       </c>
     </row>
-    <row r="229" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="229" spans="1:11">
       <c r="A229" s="8">
         <f t="shared" si="3"/>
         <v>44682</v>
@@ -8790,7 +8801,7 @@
         <v>7753</v>
       </c>
     </row>
-    <row r="230" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="230" spans="1:11">
       <c r="A230" s="8">
         <f t="shared" si="3"/>
         <v>44689</v>
@@ -8826,7 +8837,7 @@
         <v>7190</v>
       </c>
     </row>
-    <row r="231" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="231" spans="1:11">
       <c r="A231" s="8">
         <f t="shared" si="3"/>
         <v>44696</v>
@@ -8862,7 +8873,7 @@
         <v>7186</v>
       </c>
     </row>
-    <row r="232" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="232" spans="1:11">
       <c r="A232" s="8">
         <f t="shared" si="3"/>
         <v>44703</v>
@@ -8898,7 +8909,7 @@
         <v>7538</v>
       </c>
     </row>
-    <row r="233" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="233" spans="1:11">
       <c r="A233" s="8">
         <f t="shared" si="3"/>
         <v>44710</v>
@@ -8934,7 +8945,7 @@
         <v>7571</v>
       </c>
     </row>
-    <row r="234" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="234" spans="1:11">
       <c r="A234" s="8">
         <f t="shared" si="3"/>
         <v>44717</v>
@@ -8970,7 +8981,7 @@
         <v>7788</v>
       </c>
     </row>
-    <row r="235" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="235" spans="1:11">
       <c r="A235" s="8">
         <f t="shared" si="3"/>
         <v>44724</v>
@@ -9006,7 +9017,7 @@
         <v>7523</v>
       </c>
     </row>
-    <row r="236" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="236" spans="1:11">
       <c r="A236" s="8">
         <f t="shared" si="3"/>
         <v>44731</v>
@@ -9042,7 +9053,7 @@
         <v>7309</v>
       </c>
     </row>
-    <row r="237" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="237" spans="1:11">
       <c r="A237" s="8">
         <f t="shared" si="3"/>
         <v>44738</v>
@@ -9078,7 +9089,7 @@
         <v>7312</v>
       </c>
     </row>
-    <row r="238" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="238" spans="1:11">
       <c r="A238" s="8">
         <f t="shared" si="3"/>
         <v>44745</v>
@@ -9114,7 +9125,7 @@
         <v>7701</v>
       </c>
     </row>
-    <row r="239" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="239" spans="1:11">
       <c r="A239" s="8">
         <f t="shared" si="3"/>
         <v>44752</v>
@@ -9150,7 +9161,7 @@
         <v>7311</v>
       </c>
     </row>
-    <row r="240" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="240" spans="1:11">
       <c r="A240" s="8">
         <f t="shared" si="3"/>
         <v>44759</v>
@@ -9186,7 +9197,7 @@
         <v>6911</v>
       </c>
     </row>
-    <row r="241" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="241" spans="1:11">
       <c r="A241" s="8">
         <f t="shared" si="3"/>
         <v>44766</v>
@@ -9222,7 +9233,7 @@
         <v>6829</v>
       </c>
     </row>
-    <row r="242" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="242" spans="1:11">
       <c r="A242" s="8">
         <f t="shared" si="3"/>
         <v>44773</v>
@@ -9258,7 +9269,7 @@
         <v>6597</v>
       </c>
     </row>
-    <row r="243" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="243" spans="1:11">
       <c r="A243" s="8">
         <f t="shared" si="3"/>
         <v>44780</v>
@@ -9294,7 +9305,7 @@
         <v>6823</v>
       </c>
     </row>
-    <row r="244" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="244" spans="1:11">
       <c r="A244" s="8">
         <f t="shared" si="3"/>
         <v>44787</v>
@@ -9330,7 +9341,7 @@
         <v>6785</v>
       </c>
     </row>
-    <row r="245" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="245" spans="1:11">
       <c r="A245" s="8">
         <f t="shared" si="3"/>
         <v>44794</v>
@@ -9366,7 +9377,7 @@
         <v>6948</v>
       </c>
     </row>
-    <row r="246" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="246" spans="1:11">
       <c r="A246" s="8">
         <f t="shared" si="3"/>
         <v>44801</v>
@@ -9402,7 +9413,7 @@
         <v>6759</v>
       </c>
     </row>
-    <row r="247" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="247" spans="1:11">
       <c r="A247" s="8">
         <f t="shared" si="3"/>
         <v>44808</v>
@@ -9438,7 +9449,7 @@
         <v>6421</v>
       </c>
     </row>
-    <row r="248" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="248" spans="1:11">
       <c r="A248" s="8">
         <f t="shared" si="3"/>
         <v>44815</v>
@@ -9474,7 +9485,7 @@
         <v>6562</v>
       </c>
     </row>
-    <row r="249" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="249" spans="1:11">
       <c r="A249" s="8">
         <f t="shared" si="3"/>
         <v>44822</v>
@@ -9510,7 +9521,7 @@
         <v>6719</v>
       </c>
     </row>
-    <row r="250" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="250" spans="1:11">
       <c r="A250" s="8">
         <f t="shared" si="3"/>
         <v>44829</v>
@@ -9546,7 +9557,7 @@
         <v>6157</v>
       </c>
     </row>
-    <row r="251" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="251" spans="1:11">
       <c r="A251" s="8">
         <f t="shared" si="3"/>
         <v>44836</v>
@@ -9582,7 +9593,7 @@
         <v>5844</v>
       </c>
     </row>
-    <row r="252" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="252" spans="1:11">
       <c r="A252" s="8">
         <f t="shared" si="3"/>
         <v>44843</v>
@@ -9618,7 +9629,7 @@
         <v>5551</v>
       </c>
     </row>
-    <row r="253" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="253" spans="1:11">
       <c r="A253" s="8">
         <f t="shared" si="3"/>
         <v>44850</v>
@@ -9654,7 +9665,7 @@
         <v>5560</v>
       </c>
     </row>
-    <row r="254" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="254" spans="1:11">
       <c r="A254" s="8">
         <f t="shared" si="3"/>
         <v>44857</v>
@@ -9690,7 +9701,7 @@
         <v>6090</v>
       </c>
     </row>
-    <row r="255" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="255" spans="1:11">
       <c r="A255" s="8">
         <f t="shared" si="3"/>
         <v>44864</v>
@@ -9726,7 +9737,7 @@
         <v>5724</v>
       </c>
     </row>
-    <row r="256" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="256" spans="1:11">
       <c r="A256" s="8">
         <f t="shared" si="3"/>
         <v>44871</v>
@@ -9762,7 +9773,7 @@
         <v>5488</v>
       </c>
     </row>
-    <row r="257" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="257" spans="1:11">
       <c r="A257" s="8">
         <f t="shared" si="3"/>
         <v>44878</v>
@@ -9798,7 +9809,7 @@
         <v>5118</v>
       </c>
     </row>
-    <row r="258" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="258" spans="1:11">
       <c r="A258" s="8">
         <f t="shared" si="3"/>
         <v>44885</v>
@@ -9834,7 +9845,7 @@
         <v>5205</v>
       </c>
     </row>
-    <row r="259" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="259" spans="1:11">
       <c r="A259" s="8">
         <f t="shared" si="3"/>
         <v>44892</v>
@@ -9870,7 +9881,7 @@
         <v>5070</v>
       </c>
     </row>
-    <row r="260" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="260" spans="1:11">
       <c r="A260" s="8">
         <f t="shared" ref="A260:A323" si="4">B260-1</f>
         <v>44899</v>
@@ -9906,7 +9917,7 @@
         <v>5242</v>
       </c>
     </row>
-    <row r="261" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="261" spans="1:11">
       <c r="A261" s="8">
         <f t="shared" si="4"/>
         <v>44906</v>
@@ -9942,7 +9953,7 @@
         <v>4946</v>
       </c>
     </row>
-    <row r="262" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="262" spans="1:11">
       <c r="A262" s="8">
         <f t="shared" si="4"/>
         <v>44913</v>
@@ -9978,7 +9989,7 @@
         <v>5665</v>
       </c>
     </row>
-    <row r="263" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="263" spans="1:11">
       <c r="A263" s="8">
         <f t="shared" si="4"/>
         <v>44920</v>
@@ -10014,7 +10025,7 @@
         <v>5702</v>
       </c>
     </row>
-    <row r="264" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="264" spans="1:11">
       <c r="A264" s="8">
         <f t="shared" si="4"/>
         <v>44927</v>
@@ -10050,7 +10061,7 @@
         <v>5586</v>
       </c>
     </row>
-    <row r="265" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="265" spans="1:11">
       <c r="A265" s="8">
         <f t="shared" si="4"/>
         <v>44934</v>
@@ -10086,7 +10097,7 @@
         <v>5009</v>
       </c>
     </row>
-    <row r="266" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="266" spans="1:11">
       <c r="A266" s="8">
         <f t="shared" si="4"/>
         <v>44941</v>
@@ -10122,7 +10133,7 @@
         <v>5141</v>
       </c>
     </row>
-    <row r="267" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="267" spans="1:11">
       <c r="A267" s="8">
         <f t="shared" si="4"/>
         <v>44948</v>
@@ -10158,7 +10169,7 @@
         <v>4669</v>
       </c>
     </row>
-    <row r="268" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="268" spans="1:11">
       <c r="A268" s="8">
         <f t="shared" si="4"/>
         <v>44955</v>
@@ -10194,7 +10205,7 @@
         <v>4191</v>
       </c>
     </row>
-    <row r="269" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="269" spans="1:11">
       <c r="A269" s="8">
         <f t="shared" si="4"/>
         <v>44962</v>
@@ -10230,7 +10241,7 @@
         <v>4595</v>
       </c>
     </row>
-    <row r="270" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="270" spans="1:11">
       <c r="A270" s="8">
         <f t="shared" si="4"/>
         <v>44969</v>
@@ -10266,7 +10277,7 @@
         <v>4305</v>
       </c>
     </row>
-    <row r="271" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="271" spans="1:11">
       <c r="A271" s="8">
         <f t="shared" si="4"/>
         <v>44976</v>
@@ -10302,7 +10313,7 @@
         <v>4094</v>
       </c>
     </row>
-    <row r="272" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="272" spans="1:11">
       <c r="A272" s="8">
         <f t="shared" si="4"/>
         <v>44983</v>
@@ -10338,7 +10349,7 @@
         <v>3701</v>
       </c>
     </row>
-    <row r="273" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="273" spans="1:11">
       <c r="A273" s="8">
         <f t="shared" si="4"/>
         <v>44990</v>
@@ -10374,7 +10385,7 @@
         <v>4039</v>
       </c>
     </row>
-    <row r="274" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="274" spans="1:11">
       <c r="A274" s="8">
         <f t="shared" si="4"/>
         <v>44997</v>
@@ -10410,7 +10421,7 @@
         <v>4303</v>
       </c>
     </row>
-    <row r="275" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="275" spans="1:11">
       <c r="A275" s="8">
         <f t="shared" si="4"/>
         <v>45004</v>
@@ -10446,7 +10457,7 @@
         <v>4582</v>
       </c>
     </row>
-    <row r="276" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="276" spans="1:11">
       <c r="A276" s="8">
         <f t="shared" si="4"/>
         <v>45011</v>
@@ -10482,7 +10493,7 @@
         <v>4839</v>
       </c>
     </row>
-    <row r="277" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="277" spans="1:11">
       <c r="A277" s="8">
         <f t="shared" si="4"/>
         <v>45018</v>
@@ -10518,7 +10529,7 @@
         <v>4637</v>
       </c>
     </row>
-    <row r="278" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="278" spans="1:11">
       <c r="A278" s="8">
         <f t="shared" si="4"/>
         <v>45025</v>
@@ -10554,7 +10565,7 @@
         <v>4417</v>
       </c>
     </row>
-    <row r="279" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="279" spans="1:11">
       <c r="A279" s="8">
         <f t="shared" si="4"/>
         <v>45032</v>
@@ -10590,7 +10601,7 @@
         <v>4183</v>
       </c>
     </row>
-    <row r="280" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="280" spans="1:11">
       <c r="A280" s="8">
         <f t="shared" si="4"/>
         <v>45039</v>
@@ -10626,7 +10637,7 @@
         <v>4090</v>
       </c>
     </row>
-    <row r="281" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="281" spans="1:11">
       <c r="A281" s="8">
         <f t="shared" si="4"/>
         <v>45046</v>
@@ -10662,7 +10673,7 @@
         <v>3995</v>
       </c>
     </row>
-    <row r="282" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="282" spans="1:11">
       <c r="A282" s="8">
         <f t="shared" si="4"/>
         <v>45053</v>
@@ -10698,7 +10709,7 @@
         <v>3623</v>
       </c>
     </row>
-    <row r="283" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="283" spans="1:11">
       <c r="A283" s="8">
         <f t="shared" si="4"/>
         <v>45060</v>
@@ -10734,7 +10745,7 @@
         <v>3519</v>
       </c>
     </row>
-    <row r="284" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="284" spans="1:11">
       <c r="A284" s="8">
         <f t="shared" si="4"/>
         <v>45067</v>
@@ -10770,7 +10781,7 @@
         <v>3513</v>
       </c>
     </row>
-    <row r="285" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="285" spans="1:11">
       <c r="A285" s="8">
         <f t="shared" si="4"/>
         <v>45074</v>
@@ -10806,7 +10817,7 @@
         <v>3501</v>
       </c>
     </row>
-    <row r="286" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="286" spans="1:11">
       <c r="A286" s="8">
         <f t="shared" si="4"/>
         <v>45081</v>
@@ -10842,7 +10853,7 @@
         <v>3441</v>
       </c>
     </row>
-    <row r="287" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="287" spans="1:11">
       <c r="A287" s="8">
         <f t="shared" si="4"/>
         <v>45088</v>
@@ -10878,7 +10889,7 @@
         <v>3489</v>
       </c>
     </row>
-    <row r="288" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="288" spans="1:11">
       <c r="A288" s="8">
         <f t="shared" si="4"/>
         <v>45095</v>
@@ -10914,7 +10925,7 @@
         <v>3524</v>
       </c>
     </row>
-    <row r="289" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="289" spans="1:11">
       <c r="A289" s="8">
         <f t="shared" si="4"/>
         <v>45102</v>
@@ -10950,7 +10961,7 @@
         <v>3497</v>
       </c>
     </row>
-    <row r="290" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="290" spans="1:11">
       <c r="A290" s="8">
         <f t="shared" si="4"/>
         <v>45109</v>
@@ -10986,7 +10997,7 @@
         <v>3333</v>
       </c>
     </row>
-    <row r="291" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="291" spans="1:11">
       <c r="A291" s="8">
         <f t="shared" si="4"/>
         <v>45116</v>
@@ -11022,7 +11033,7 @@
         <v>3428</v>
       </c>
     </row>
-    <row r="292" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="292" spans="1:11">
       <c r="A292" s="8">
         <f t="shared" si="4"/>
         <v>45123</v>
@@ -11058,7 +11069,7 @@
         <v>3588</v>
       </c>
     </row>
-    <row r="293" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="293" spans="1:11">
       <c r="A293" s="8">
         <f t="shared" si="4"/>
         <v>45130</v>
@@ -11094,7 +11105,7 @@
         <v>3445</v>
       </c>
     </row>
-    <row r="294" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="294" spans="1:11">
       <c r="A294" s="8">
         <f t="shared" si="4"/>
         <v>45137</v>
@@ -11130,7 +11141,7 @@
         <v>3453</v>
       </c>
     </row>
-    <row r="295" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="295" spans="1:11">
       <c r="A295" s="8">
         <f t="shared" si="4"/>
         <v>45144</v>
@@ -11166,7 +11177,7 @@
         <v>3501</v>
       </c>
     </row>
-    <row r="296" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="296" spans="1:11">
       <c r="A296" s="8">
         <f t="shared" si="4"/>
         <v>45151</v>
@@ -11202,7 +11213,7 @@
         <v>3579</v>
       </c>
     </row>
-    <row r="297" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="297" spans="1:11">
       <c r="A297" s="8">
         <f t="shared" si="4"/>
         <v>45158</v>
@@ -11238,7 +11249,7 @@
         <v>3584</v>
       </c>
     </row>
-    <row r="298" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="298" spans="1:11">
       <c r="A298" s="8">
         <f t="shared" si="4"/>
         <v>45165</v>
@@ -11274,7 +11285,7 @@
         <v>3591</v>
       </c>
     </row>
-    <row r="299" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="299" spans="1:11">
       <c r="A299" s="8">
         <f t="shared" si="4"/>
         <v>45172</v>
@@ -11310,7 +11321,7 @@
         <v>3526</v>
       </c>
     </row>
-    <row r="300" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="300" spans="1:11">
       <c r="A300" s="8">
         <f t="shared" si="4"/>
         <v>45179</v>
@@ -11346,7 +11357,7 @@
         <v>3715</v>
       </c>
     </row>
-    <row r="301" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="301" spans="1:11">
       <c r="A301" s="8">
         <f t="shared" si="4"/>
         <v>45186</v>
@@ -11382,7 +11393,7 @@
         <v>3765</v>
       </c>
     </row>
-    <row r="302" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="302" spans="1:11">
       <c r="A302" s="8">
         <f t="shared" si="4"/>
         <v>45193</v>
@@ -11418,7 +11429,7 @@
         <v>3987</v>
       </c>
     </row>
-    <row r="303" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="303" spans="1:11">
       <c r="A303" s="8">
         <f t="shared" si="4"/>
         <v>45200</v>
@@ -11454,7 +11465,7 @@
         <v>4197</v>
       </c>
     </row>
-    <row r="304" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="304" spans="1:11">
       <c r="A304" s="8">
         <f t="shared" si="4"/>
         <v>45207</v>
@@ -11490,7 +11501,7 @@
         <v>4308</v>
       </c>
     </row>
-    <row r="305" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="305" spans="1:11">
       <c r="A305" s="8">
         <f t="shared" si="4"/>
         <v>45214</v>
@@ -11526,7 +11537,7 @@
         <v>4268</v>
       </c>
     </row>
-    <row r="306" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="306" spans="1:11">
       <c r="A306" s="8">
         <f t="shared" si="4"/>
         <v>45221</v>
@@ -11562,7 +11573,7 @@
         <v>4444</v>
       </c>
     </row>
-    <row r="307" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="307" spans="1:11">
       <c r="A307" s="8">
         <f t="shared" si="4"/>
         <v>45228</v>
@@ -11598,7 +11609,7 @@
         <v>4465</v>
       </c>
     </row>
-    <row r="308" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="308" spans="1:11">
       <c r="A308" s="8">
         <f t="shared" si="4"/>
         <v>45235</v>
@@ -11634,7 +11645,7 @@
         <v>4486</v>
       </c>
     </row>
-    <row r="309" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="309" spans="1:11">
       <c r="A309" s="8">
         <f t="shared" si="4"/>
         <v>45242</v>
@@ -11670,7 +11681,7 @@
         <v>4878</v>
       </c>
     </row>
-    <row r="310" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="310" spans="1:11">
       <c r="A310" s="8">
         <f t="shared" si="4"/>
         <v>45249</v>
@@ -11706,7 +11717,7 @@
         <v>5136</v>
       </c>
     </row>
-    <row r="311" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="311" spans="1:11">
       <c r="A311" s="8">
         <f t="shared" si="4"/>
         <v>45256</v>
@@ -11742,7 +11753,7 @@
         <v>5562</v>
       </c>
     </row>
-    <row r="312" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="312" spans="1:11">
       <c r="A312" s="8">
         <f t="shared" si="4"/>
         <v>45263</v>
@@ -11778,7 +11789,7 @@
         <v>5625</v>
       </c>
     </row>
-    <row r="313" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="313" spans="1:11">
       <c r="A313" s="8">
         <f t="shared" si="4"/>
         <v>45270</v>
@@ -11814,7 +11825,7 @@
         <v>5859</v>
       </c>
     </row>
-    <row r="314" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="314" spans="1:11">
       <c r="A314" s="8">
         <f t="shared" si="4"/>
         <v>45277</v>
@@ -11850,7 +11861,7 @@
         <v>5680</v>
       </c>
     </row>
-    <row r="315" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="315" spans="1:11">
       <c r="A315" s="8">
         <f t="shared" si="4"/>
         <v>45284</v>
@@ -11886,7 +11897,7 @@
         <v>5680</v>
       </c>
     </row>
-    <row r="316" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="316" spans="1:11">
       <c r="A316" s="8">
         <f t="shared" si="4"/>
         <v>45291</v>
@@ -11922,7 +11933,7 @@
         <v>3893</v>
       </c>
     </row>
-    <row r="317" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="317" spans="1:11">
       <c r="A317" s="8">
         <f t="shared" si="4"/>
         <v>45298</v>
@@ -11958,7 +11969,7 @@
         <v>3609</v>
       </c>
     </row>
-    <row r="318" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="318" spans="1:11">
       <c r="A318" s="8">
         <f t="shared" si="4"/>
         <v>45305</v>
@@ -11994,7 +12005,7 @@
         <v>3632</v>
       </c>
     </row>
-    <row r="319" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="319" spans="1:11">
       <c r="A319" s="8">
         <f t="shared" si="4"/>
         <v>45312</v>
@@ -12030,7 +12041,7 @@
         <v>3772</v>
       </c>
     </row>
-    <row r="320" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="320" spans="1:11">
       <c r="A320" s="8">
         <f t="shared" si="4"/>
         <v>45319</v>
@@ -12066,7 +12077,7 @@
         <v>4103</v>
       </c>
     </row>
-    <row r="321" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="321" spans="1:11">
       <c r="A321" s="8">
         <f t="shared" si="4"/>
         <v>45326</v>
@@ -12102,7 +12113,7 @@
         <v>4283</v>
       </c>
     </row>
-    <row r="322" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="322" spans="1:11">
       <c r="A322" s="8">
         <f t="shared" si="4"/>
         <v>45333</v>
@@ -12138,7 +12149,7 @@
         <v>4375</v>
       </c>
     </row>
-    <row r="323" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="323" spans="1:11">
       <c r="A323" s="8">
         <f t="shared" si="4"/>
         <v>45340</v>
@@ -12174,7 +12185,7 @@
         <v>3871</v>
       </c>
     </row>
-    <row r="324" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="324" spans="1:11">
       <c r="A324" s="8">
         <f t="shared" ref="A324:A387" si="5">B324-1</f>
         <v>45347</v>
@@ -12210,7 +12221,7 @@
         <v>3455</v>
       </c>
     </row>
-    <row r="325" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="325" spans="1:11">
       <c r="A325" s="8">
         <f t="shared" si="5"/>
         <v>45354</v>
@@ -12246,7 +12257,7 @@
         <v>3638</v>
       </c>
     </row>
-    <row r="326" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="326" spans="1:11">
       <c r="A326" s="8">
         <f t="shared" si="5"/>
         <v>45361</v>
@@ -12282,7 +12293,7 @@
         <v>3888</v>
       </c>
     </row>
-    <row r="327" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="327" spans="1:11">
       <c r="A327" s="8">
         <f t="shared" si="5"/>
         <v>45368</v>
@@ -12318,7 +12329,7 @@
         <v>4235</v>
       </c>
     </row>
-    <row r="328" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="328" spans="1:11">
       <c r="A328" s="8">
         <f t="shared" si="5"/>
         <v>45375</v>
@@ -12354,7 +12365,7 @@
         <v>4396</v>
       </c>
     </row>
-    <row r="329" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="329" spans="1:11">
       <c r="A329" s="8">
         <f t="shared" si="5"/>
         <v>45382</v>
@@ -12390,7 +12401,7 @@
         <v>4400</v>
       </c>
     </row>
-    <row r="330" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="330" spans="1:11">
       <c r="A330" s="8">
         <f t="shared" si="5"/>
         <v>45389</v>
@@ -12426,7 +12437,7 @@
         <v>4447</v>
       </c>
     </row>
-    <row r="331" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="331" spans="1:11">
       <c r="A331" s="8">
         <f t="shared" si="5"/>
         <v>45396</v>
@@ -12462,7 +12473,7 @@
         <v>4472</v>
       </c>
     </row>
-    <row r="332" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="332" spans="1:11">
       <c r="A332" s="8">
         <f t="shared" si="5"/>
         <v>45403</v>
@@ -12498,7 +12509,7 @@
         <v>4580</v>
       </c>
     </row>
-    <row r="333" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="333" spans="1:11">
       <c r="A333" s="8">
         <f t="shared" si="5"/>
         <v>45410</v>
@@ -12534,7 +12545,7 @@
         <v>4632</v>
       </c>
     </row>
-    <row r="334" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="334" spans="1:11">
       <c r="A334" s="8">
         <f t="shared" si="5"/>
         <v>45417</v>
@@ -12570,7 +12581,7 @@
         <v>4708</v>
       </c>
     </row>
-    <row r="335" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="335" spans="1:11">
       <c r="A335" s="8">
         <f t="shared" si="5"/>
         <v>45424</v>
@@ -12606,7 +12617,7 @@
         <v>4710</v>
       </c>
     </row>
-    <row r="336" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="336" spans="1:11">
       <c r="A336" s="8">
         <f t="shared" si="5"/>
         <v>45431</v>
@@ -12642,7 +12653,7 @@
         <v>4881</v>
       </c>
     </row>
-    <row r="337" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="337" spans="1:11">
       <c r="A337" s="8">
         <f t="shared" si="5"/>
         <v>45438</v>
@@ -12678,7 +12689,7 @@
         <v>4955</v>
       </c>
     </row>
-    <row r="338" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="338" spans="1:11">
       <c r="A338" s="8">
         <f t="shared" si="5"/>
         <v>45445</v>
@@ -12714,7 +12725,7 @@
         <v>4865</v>
       </c>
     </row>
-    <row r="339" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="339" spans="1:11">
       <c r="A339" s="8">
         <f t="shared" si="5"/>
         <v>45452</v>
@@ -12750,7 +12761,7 @@
         <v>4808</v>
       </c>
     </row>
-    <row r="340" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="340" spans="1:11">
       <c r="A340" s="8">
         <f t="shared" si="5"/>
         <v>45459</v>
@@ -12786,7 +12797,7 @@
         <v>4783</v>
       </c>
     </row>
-    <row r="341" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="341" spans="1:11">
       <c r="A341" s="8">
         <f t="shared" si="5"/>
         <v>45466</v>
@@ -12822,7 +12833,7 @@
         <v>4757</v>
       </c>
     </row>
-    <row r="342" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="342" spans="1:11">
       <c r="A342" s="8">
         <f t="shared" si="5"/>
         <v>45473</v>
@@ -12858,7 +12869,7 @@
         <v>4736</v>
       </c>
     </row>
-    <row r="343" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="343" spans="1:11">
       <c r="A343" s="8">
         <f t="shared" si="5"/>
         <v>45480</v>
@@ -12894,7 +12905,7 @@
         <v>4879</v>
       </c>
     </row>
-    <row r="344" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="344" spans="1:11">
       <c r="A344" s="8">
         <f t="shared" si="5"/>
         <v>45487</v>
@@ -12930,7 +12941,7 @@
         <v>4737</v>
       </c>
     </row>
-    <row r="345" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="345" spans="1:11">
       <c r="A345" s="8">
         <f t="shared" si="5"/>
         <v>45494</v>
@@ -12966,7 +12977,7 @@
         <v>4594</v>
       </c>
     </row>
-    <row r="346" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="346" spans="1:11">
       <c r="A346" s="8">
         <f t="shared" si="5"/>
         <v>45501</v>
@@ -13002,7 +13013,7 @@
         <v>4598</v>
       </c>
     </row>
-    <row r="347" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="347" spans="1:11">
       <c r="A347" s="8">
         <f t="shared" si="5"/>
         <v>45508</v>
@@ -13038,7 +13049,7 @@
         <v>4565</v>
       </c>
     </row>
-    <row r="348" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="348" spans="1:11">
       <c r="A348" s="8">
         <f t="shared" si="5"/>
         <v>45515</v>
@@ -13074,7 +13085,7 @@
         <v>4647</v>
       </c>
     </row>
-    <row r="349" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="349" spans="1:11">
       <c r="A349" s="8">
         <f t="shared" si="5"/>
         <v>45522</v>
@@ -13110,7 +13121,7 @@
         <v>4591</v>
       </c>
     </row>
-    <row r="350" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="350" spans="1:11">
       <c r="A350" s="8">
         <f t="shared" si="5"/>
         <v>45529</v>
@@ -13146,7 +13157,7 @@
         <v>4788</v>
       </c>
     </row>
-    <row r="351" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="351" spans="1:11">
       <c r="A351" s="8">
         <f t="shared" si="5"/>
         <v>45536</v>
@@ -13182,7 +13193,7 @@
         <v>4920</v>
       </c>
     </row>
-    <row r="352" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="352" spans="1:11">
       <c r="A352" s="8">
         <f t="shared" si="5"/>
         <v>45543</v>
@@ -13218,7 +13229,7 @@
         <v>4829</v>
       </c>
     </row>
-    <row r="353" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="353" spans="1:11">
       <c r="A353" s="8">
         <f t="shared" si="5"/>
         <v>45550</v>
@@ -13254,7 +13265,7 @@
         <v>4815</v>
       </c>
     </row>
-    <row r="354" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="354" spans="1:11">
       <c r="A354" s="8">
         <f t="shared" si="5"/>
         <v>45557</v>
@@ -13290,7 +13301,7 @@
         <v>4837</v>
       </c>
     </row>
-    <row r="355" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="355" spans="1:11">
       <c r="A355" s="8">
         <f t="shared" si="5"/>
         <v>45564</v>
@@ -13326,7 +13337,7 @@
         <v>5053</v>
       </c>
     </row>
-    <row r="356" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="356" spans="1:11">
       <c r="A356" s="8">
         <f t="shared" si="5"/>
         <v>45571</v>
@@ -13362,7 +13373,7 @@
         <v>4879</v>
       </c>
     </row>
-    <row r="357" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="357" spans="1:11">
       <c r="A357" s="8">
         <f t="shared" si="5"/>
         <v>45578</v>
@@ -13398,7 +13409,7 @@
         <v>4831</v>
       </c>
     </row>
-    <row r="358" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="358" spans="1:11">
       <c r="A358" s="8">
         <f t="shared" si="5"/>
         <v>45585</v>
@@ -13434,7 +13445,7 @@
         <v>5006</v>
       </c>
     </row>
-    <row r="359" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="359" spans="1:11">
       <c r="A359" s="8">
         <f t="shared" si="5"/>
         <v>45592</v>
@@ -13470,7 +13481,7 @@
         <v>5190</v>
       </c>
     </row>
-    <row r="360" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="360" spans="1:11">
       <c r="A360" s="8">
         <f t="shared" si="5"/>
         <v>45599</v>
@@ -13506,7 +13517,7 @@
         <v>5493</v>
       </c>
     </row>
-    <row r="361" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="361" spans="1:11">
       <c r="A361" s="8">
         <f t="shared" si="5"/>
         <v>45606</v>
@@ -13542,7 +13553,7 @@
         <v>5494</v>
       </c>
     </row>
-    <row r="362" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="362" spans="1:11">
       <c r="A362" s="8">
         <f t="shared" si="5"/>
         <v>45613</v>
@@ -13578,7 +13589,7 @@
         <v>5339</v>
       </c>
     </row>
-    <row r="363" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="363" spans="1:11">
       <c r="A363" s="8">
         <f t="shared" si="5"/>
         <v>45620</v>
@@ -13614,7 +13625,7 @@
         <v>5225</v>
       </c>
     </row>
-    <row r="364" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="364" spans="1:11">
       <c r="A364" s="8">
         <f t="shared" si="5"/>
         <v>45627</v>
@@ -13650,7 +13661,7 @@
         <v>5585</v>
       </c>
     </row>
-    <row r="365" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="365" spans="1:11">
       <c r="A365" s="8">
         <f t="shared" si="5"/>
         <v>45634</v>
@@ -13686,7 +13697,7 @@
         <v>5777</v>
       </c>
     </row>
-    <row r="366" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="366" spans="1:11">
       <c r="A366" s="8">
         <f t="shared" si="5"/>
         <v>45641</v>
@@ -13722,7 +13733,7 @@
         <v>5722</v>
       </c>
     </row>
-    <row r="367" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="367" spans="1:11">
       <c r="A367" s="8">
         <f t="shared" si="5"/>
         <v>45648</v>
@@ -13758,7 +13769,7 @@
         <v>5327</v>
       </c>
     </row>
-    <row r="368" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="368" spans="1:11">
       <c r="A368" s="8">
         <f t="shared" si="5"/>
         <v>45655</v>
@@ -13794,7 +13805,7 @@
         <v>5327</v>
       </c>
     </row>
-    <row r="369" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="369" spans="1:11">
       <c r="A369" s="8">
         <f t="shared" si="5"/>
         <v>45662</v>
@@ -13830,7 +13841,7 @@
         <v>4966</v>
       </c>
     </row>
-    <row r="370" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="370" spans="1:11">
       <c r="A370" s="8">
         <f t="shared" si="5"/>
         <v>45669</v>
@@ -13866,7 +13877,7 @@
         <v>4484</v>
       </c>
     </row>
-    <row r="371" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="371" spans="1:11">
       <c r="A371" s="8">
         <f t="shared" si="5"/>
         <v>45676</v>
@@ -13902,7 +13913,7 @@
         <v>4243</v>
       </c>
     </row>
-    <row r="372" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="372" spans="1:11">
       <c r="A372" s="8">
         <f t="shared" si="5"/>
         <v>45683</v>
@@ -13938,7 +13949,7 @@
         <v>4447</v>
       </c>
     </row>
-    <row r="373" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="373" spans="1:11">
       <c r="A373" s="8">
         <f t="shared" si="5"/>
         <v>45690</v>
@@ -13974,7 +13985,7 @@
         <v>4327</v>
       </c>
     </row>
-    <row r="374" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="374" spans="1:11">
       <c r="A374" s="8">
         <f t="shared" si="5"/>
         <v>45697</v>
@@ -14010,7 +14021,7 @@
         <v>3962</v>
       </c>
     </row>
-    <row r="375" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="375" spans="1:11">
       <c r="A375" s="8">
         <f t="shared" si="5"/>
         <v>45704</v>
@@ -14046,7 +14057,7 @@
         <v>4284</v>
       </c>
     </row>
-    <row r="376" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="376" spans="1:11">
       <c r="A376" s="8">
         <f t="shared" si="5"/>
         <v>45711</v>
@@ -14082,7 +14093,7 @@
         <v>4127</v>
       </c>
     </row>
-    <row r="377" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="377" spans="1:11">
       <c r="A377" s="8">
         <f t="shared" si="5"/>
         <v>45718</v>
@@ -14118,7 +14129,7 @@
         <v>4086</v>
       </c>
     </row>
-    <row r="378" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="378" spans="1:11">
       <c r="A378" s="8">
         <f t="shared" si="5"/>
         <v>45725</v>
@@ -14154,7 +14165,7 @@
         <v>4002</v>
       </c>
     </row>
-    <row r="379" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="379" spans="1:11">
       <c r="A379" s="8">
         <f t="shared" si="5"/>
         <v>45732</v>
@@ -14190,7 +14201,7 @@
         <v>4218</v>
       </c>
     </row>
-    <row r="380" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="380" spans="1:11">
       <c r="A380" s="8">
         <f t="shared" si="5"/>
         <v>45739</v>
@@ -14226,7 +14237,7 @@
         <v>4547</v>
       </c>
     </row>
-    <row r="381" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="381" spans="1:11">
       <c r="A381" s="8">
         <f t="shared" si="5"/>
         <v>45746</v>
@@ -14262,7 +14273,7 @@
         <v>4573</v>
       </c>
     </row>
-    <row r="382" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="382" spans="1:11">
       <c r="A382" s="8">
         <f t="shared" si="5"/>
         <v>45753</v>
@@ -14298,7 +14309,7 @@
         <v>4689</v>
       </c>
     </row>
-    <row r="383" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="383" spans="1:11">
       <c r="A383" s="8">
         <f t="shared" si="5"/>
         <v>45760</v>
@@ -14334,7 +14345,7 @@
         <v>4662</v>
       </c>
     </row>
-    <row r="384" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="384" spans="1:11">
       <c r="A384" s="8">
         <f t="shared" si="5"/>
         <v>45767</v>
@@ -14370,7 +14381,7 @@
         <v>4697</v>
       </c>
     </row>
-    <row r="385" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="385" spans="1:11">
       <c r="A385" s="8">
         <f t="shared" si="5"/>
         <v>45774</v>
@@ -14406,7 +14417,7 @@
         <v>4411</v>
       </c>
     </row>
-    <row r="386" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="386" spans="1:11">
       <c r="A386" s="8">
         <f t="shared" si="5"/>
         <v>45781</v>
@@ -14442,7 +14453,7 @@
         <v>4304</v>
       </c>
     </row>
-    <row r="387" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="387" spans="1:11">
       <c r="A387" s="8">
         <f t="shared" si="5"/>
         <v>45788</v>
@@ -14478,7 +14489,7 @@
         <v>4343</v>
       </c>
     </row>
-    <row r="388" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="388" spans="1:11">
       <c r="A388" s="8">
         <f t="shared" ref="A388:A420" si="6">B388-1</f>
         <v>45795</v>
@@ -14514,7 +14525,7 @@
         <v>4190</v>
       </c>
     </row>
-    <row r="389" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="389" spans="1:11">
       <c r="A389" s="8">
         <f t="shared" si="6"/>
         <v>45802</v>
@@ -14550,7 +14561,7 @@
         <v>4444</v>
       </c>
     </row>
-    <row r="390" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="390" spans="1:11">
       <c r="A390" s="8">
         <f t="shared" si="6"/>
         <v>45809</v>
@@ -14586,7 +14597,7 @@
         <v>4607</v>
       </c>
     </row>
-    <row r="391" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="391" spans="1:11">
       <c r="A391" s="8">
         <f t="shared" si="6"/>
         <v>45816</v>
@@ -14622,7 +14633,7 @@
         <v>4567</v>
       </c>
     </row>
-    <row r="392" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="392" spans="1:11">
       <c r="A392" s="8">
         <f t="shared" si="6"/>
         <v>45823</v>
@@ -14658,7 +14669,7 @@
         <v>4475</v>
       </c>
     </row>
-    <row r="393" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="393" spans="1:11">
       <c r="A393" s="8">
         <f t="shared" si="6"/>
         <v>45830</v>
@@ -14694,7 +14705,7 @@
         <v>4354</v>
       </c>
     </row>
-    <row r="394" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="394" spans="1:11">
       <c r="A394" s="8">
         <f t="shared" si="6"/>
         <v>45837</v>
@@ -14730,7 +14741,7 @@
         <v>4375</v>
       </c>
     </row>
-    <row r="395" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="395" spans="1:11">
       <c r="A395" s="8">
         <f t="shared" si="6"/>
         <v>45844</v>
@@ -14766,7 +14777,7 @@
         <v>4413</v>
       </c>
     </row>
-    <row r="396" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="396" spans="1:11">
       <c r="A396" s="8">
         <f t="shared" si="6"/>
         <v>45851</v>
@@ -14802,7 +14813,7 @@
         <v>4593</v>
       </c>
     </row>
-    <row r="397" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="397" spans="1:11">
       <c r="A397" s="8">
         <f t="shared" si="6"/>
         <v>45858</v>
@@ -14838,7 +14849,7 @@
         <v>4418</v>
       </c>
     </row>
-    <row r="398" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="398" spans="1:11">
       <c r="A398" s="8">
         <f t="shared" si="6"/>
         <v>45865</v>
@@ -14874,7 +14885,7 @@
         <v>4429</v>
       </c>
     </row>
-    <row r="399" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="399" spans="1:11">
       <c r="A399" s="8">
         <f t="shared" si="6"/>
         <v>45872</v>
@@ -14910,7 +14921,7 @@
         <v>4418</v>
       </c>
     </row>
-    <row r="400" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="400" spans="1:11">
       <c r="A400" s="8">
         <f t="shared" si="6"/>
         <v>45879</v>
@@ -14946,7 +14957,7 @@
         <v>4455</v>
       </c>
     </row>
-    <row r="401" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="401" spans="1:11">
       <c r="A401" s="8">
         <f t="shared" si="6"/>
         <v>45886</v>
@@ -14982,7 +14993,7 @@
         <v>4411</v>
       </c>
     </row>
-    <row r="402" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="402" spans="1:11">
       <c r="A402" s="8">
         <f t="shared" si="6"/>
         <v>45893</v>
@@ -15018,7 +15029,7 @@
         <v>4392</v>
       </c>
     </row>
-    <row r="403" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="403" spans="1:11">
       <c r="A403" s="8">
         <f t="shared" si="6"/>
         <v>45900</v>
@@ -15054,7 +15065,7 @@
         <v>4549</v>
       </c>
     </row>
-    <row r="404" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="404" spans="1:11">
       <c r="A404" s="8">
         <f t="shared" si="6"/>
         <v>45907</v>
@@ -15090,7 +15101,7 @@
         <v>4489</v>
       </c>
     </row>
-    <row r="405" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="405" spans="1:11">
       <c r="A405" s="8">
         <f t="shared" si="6"/>
         <v>45914</v>
@@ -15126,7 +15137,7 @@
         <v>4536</v>
       </c>
     </row>
-    <row r="406" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="406" spans="1:11">
       <c r="A406" s="8">
         <f t="shared" si="6"/>
         <v>45921</v>
@@ -15162,7 +15173,7 @@
         <v>4516</v>
       </c>
     </row>
-    <row r="407" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="407" spans="1:11">
       <c r="A407" s="8">
         <f t="shared" si="6"/>
         <v>45928</v>
@@ -15198,7 +15209,7 @@
         <v>4562</v>
       </c>
     </row>
-    <row r="408" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="408" spans="1:11">
       <c r="A408" s="8">
         <f t="shared" si="6"/>
         <v>45935</v>
@@ -15234,7 +15245,7 @@
         <v>4621</v>
       </c>
     </row>
-    <row r="409" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="409" spans="1:11">
       <c r="A409" s="8">
         <f t="shared" si="6"/>
         <v>45942</v>
@@ -15270,7 +15281,7 @@
         <v>4441</v>
       </c>
     </row>
-    <row r="410" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="410" spans="1:11">
       <c r="A410" s="8">
         <f t="shared" si="6"/>
         <v>45949</v>
@@ -15306,7 +15317,7 @@
         <v>4746</v>
       </c>
     </row>
-    <row r="411" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="411" spans="1:11">
       <c r="A411" s="8">
         <f t="shared" si="6"/>
         <v>45956</v>
@@ -15342,7 +15353,7 @@
         <v>5010</v>
       </c>
     </row>
-    <row r="412" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="412" spans="1:11">
       <c r="A412" s="8">
         <f t="shared" si="6"/>
         <v>45963</v>
@@ -15378,7 +15389,7 @@
         <v>5366</v>
       </c>
     </row>
-    <row r="413" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="413" spans="1:11">
       <c r="A413" s="8">
         <f t="shared" si="6"/>
         <v>45970</v>
@@ -15414,7 +15425,7 @@
         <v>5356</v>
       </c>
     </row>
-    <row r="414" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="414" spans="1:11">
       <c r="A414" s="8">
         <f t="shared" si="6"/>
         <v>45977</v>
@@ -15450,7 +15461,7 @@
         <v>5581</v>
       </c>
     </row>
-    <row r="415" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="415" spans="1:11">
       <c r="A415" s="8">
         <f t="shared" si="6"/>
         <v>45984</v>
@@ -15486,7 +15497,7 @@
         <v>5571</v>
       </c>
     </row>
-    <row r="416" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="416" spans="1:11">
       <c r="A416" s="8">
         <f t="shared" si="6"/>
         <v>45991</v>
@@ -15522,7 +15533,7 @@
         <v>5721</v>
       </c>
     </row>
-    <row r="417" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="417" spans="1:11">
       <c r="A417" s="8">
         <f t="shared" si="6"/>
         <v>45998</v>
@@ -15558,7 +15569,7 @@
         <v>6161</v>
       </c>
     </row>
-    <row r="418" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="418" spans="1:11">
       <c r="A418" s="8">
         <f t="shared" si="6"/>
         <v>46005</v>
@@ -15594,7 +15605,7 @@
         <v>6369</v>
       </c>
     </row>
-    <row r="419" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="419" spans="1:11">
       <c r="A419" s="8">
         <f t="shared" si="6"/>
         <v>46012</v>
@@ -15630,7 +15641,7 @@
         <v>5821</v>
       </c>
     </row>
-    <row r="420" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="420" spans="1:11">
       <c r="A420" s="8">
         <f t="shared" si="6"/>
         <v>46019</v>
@@ -15666,7 +15677,7 @@
         <v>5821</v>
       </c>
     </row>
-    <row r="421" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="421" spans="1:11">
       <c r="A421" s="8">
         <f t="shared" ref="A421" si="7">B421-1</f>
         <v>46026</v>
@@ -15679,6 +15690,27 @@
       </c>
       <c r="D421" s="6" t="s">
         <v>21</v>
+      </c>
+      <c r="E421" s="9">
+        <v>2143</v>
+      </c>
+      <c r="F421" s="9">
+        <v>1984</v>
+      </c>
+      <c r="G421" s="9">
+        <v>3770</v>
+      </c>
+      <c r="H421" s="9">
+        <v>983</v>
+      </c>
+      <c r="I421" s="9">
+        <v>876</v>
+      </c>
+      <c r="J421" s="9">
+        <v>273</v>
+      </c>
+      <c r="K421" s="9">
+        <v>4662</v>
       </c>
     </row>
   </sheetData>
@@ -15697,12 +15729,12 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{362BE34E-9F1D-4DC0-8A14-D289984A66A9}">
   <dimension ref="B2:G3"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="9" defaultRowHeight="14"/>
   <cols>
     <col min="1" max="16384" width="9" style="1"/>
   </cols>
   <sheetData>
-    <row r="2" spans="2:7" x14ac:dyDescent="0.25">
+    <row r="2" spans="2:7" ht="15">
       <c r="B2" s="2" t="s">
         <v>16</v>
       </c>
@@ -15714,7 +15746,7 @@
       <c r="F2" s="3"/>
       <c r="G2" s="3"/>
     </row>
-    <row r="3" spans="2:7" x14ac:dyDescent="0.25">
+    <row r="3" spans="2:7">
       <c r="B3" s="4" t="s">
         <v>15</v>
       </c>

--- a/data/freight/Baltic air freight index.xlsx
+++ b/data/freight/Baltic air freight index.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\USER\PycharmProjects\AlternativeData\data\freight\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{34423D44-9AF5-4DB5-99EC-0EE8E535FC72}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8FA9BE3A-0CE3-48A2-ADA5-066702A732C3}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="16995" yWindow="780" windowWidth="19005" windowHeight="20760" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -26,7 +26,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="447" uniqueCount="24">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="448" uniqueCount="24">
   <si>
     <t>Shanghai Pudong Outbound</t>
   </si>
@@ -119,7 +119,7 @@
     <numFmt numFmtId="43" formatCode="_-* #,##0.00_-;\-* #,##0.00_-;_-* &quot;-&quot;??_-;_-@_-"/>
     <numFmt numFmtId="176" formatCode="_(* #,##0_);_(* \(#,##0\);_(* &quot;-&quot;??_);_(@_)"/>
     <numFmt numFmtId="177" formatCode="yyyy\-mm\-dd;@"/>
-    <numFmt numFmtId="180" formatCode="[$-409]h:mm:ss\ AM/PM;@"/>
+    <numFmt numFmtId="178" formatCode="[$-409]h:mm:ss\ AM/PM;@"/>
   </numFmts>
   <fonts count="10" x14ac:knownFonts="1">
     <font>
@@ -222,7 +222,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="16">
+  <cellXfs count="17">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
@@ -251,17 +251,20 @@
     <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="178" fontId="9" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="177" fontId="8" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="180" fontId="8" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="178" fontId="8" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="180" fontId="9" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
+    <xf numFmtId="14" fontId="9" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="3">
@@ -545,12 +548,12 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:K427"/>
+  <dimension ref="A1:K428"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="12.75" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="11.375" style="11" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="14" style="8" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="11.125" style="15" customWidth="1"/>
+    <col min="3" max="3" width="11.125" style="12" customWidth="1"/>
     <col min="4" max="4" width="11.125" style="8" customWidth="1"/>
     <col min="5" max="8" width="8.625" style="9" bestFit="1" customWidth="1"/>
     <col min="9" max="9" width="9.5" style="9" bestFit="1" customWidth="1"/>
@@ -560,16 +563,16 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A1" s="12" t="s">
+      <c r="A1" s="13" t="s">
         <v>18</v>
       </c>
-      <c r="B1" s="13" t="s">
+      <c r="B1" s="14" t="s">
         <v>17</v>
       </c>
-      <c r="C1" s="14" t="s">
+      <c r="C1" s="15" t="s">
         <v>19</v>
       </c>
-      <c r="D1" s="13" t="s">
+      <c r="D1" s="14" t="s">
         <v>20</v>
       </c>
       <c r="E1" s="6" t="s">
@@ -595,10 +598,10 @@
       </c>
     </row>
     <row r="2" spans="1:11" x14ac:dyDescent="0.2">
-      <c r="A2" s="12"/>
-      <c r="B2" s="13"/>
-      <c r="C2" s="14"/>
-      <c r="D2" s="13"/>
+      <c r="A2" s="13"/>
+      <c r="B2" s="14"/>
+      <c r="C2" s="15"/>
+      <c r="D2" s="14"/>
       <c r="E2" s="6" t="s">
         <v>6</v>
       </c>
@@ -629,7 +632,7 @@
       <c r="B3" s="8">
         <v>43101</v>
       </c>
-      <c r="C3" s="15">
+      <c r="C3" s="12">
         <v>0.70833333333333337</v>
       </c>
       <c r="D3" s="8" t="s">
@@ -665,7 +668,7 @@
       <c r="B4" s="8">
         <v>43108</v>
       </c>
-      <c r="C4" s="15">
+      <c r="C4" s="12">
         <v>0.70833333333333337</v>
       </c>
       <c r="D4" s="8" t="s">
@@ -701,7 +704,7 @@
       <c r="B5" s="8">
         <v>43115</v>
       </c>
-      <c r="C5" s="15">
+      <c r="C5" s="12">
         <v>0.70833333333333337</v>
       </c>
       <c r="D5" s="8" t="s">
@@ -737,7 +740,7 @@
       <c r="B6" s="8">
         <v>43122</v>
       </c>
-      <c r="C6" s="15">
+      <c r="C6" s="12">
         <v>0.70833333333333337</v>
       </c>
       <c r="D6" s="8" t="s">
@@ -773,7 +776,7 @@
       <c r="B7" s="8">
         <v>43129</v>
       </c>
-      <c r="C7" s="15">
+      <c r="C7" s="12">
         <v>0.70833333333333337</v>
       </c>
       <c r="D7" s="8" t="s">
@@ -809,7 +812,7 @@
       <c r="B8" s="8">
         <v>43136</v>
       </c>
-      <c r="C8" s="15">
+      <c r="C8" s="12">
         <v>0.70833333333333337</v>
       </c>
       <c r="D8" s="8" t="s">
@@ -845,7 +848,7 @@
       <c r="B9" s="8">
         <v>43143</v>
       </c>
-      <c r="C9" s="15">
+      <c r="C9" s="12">
         <v>0.70833333333333337</v>
       </c>
       <c r="D9" s="8" t="s">
@@ -881,7 +884,7 @@
       <c r="B10" s="8">
         <v>43150</v>
       </c>
-      <c r="C10" s="15">
+      <c r="C10" s="12">
         <v>0.70833333333333337</v>
       </c>
       <c r="D10" s="8" t="s">
@@ -917,7 +920,7 @@
       <c r="B11" s="8">
         <v>43157</v>
       </c>
-      <c r="C11" s="15">
+      <c r="C11" s="12">
         <v>0.70833333333333337</v>
       </c>
       <c r="D11" s="8" t="s">
@@ -953,7 +956,7 @@
       <c r="B12" s="8">
         <v>43164</v>
       </c>
-      <c r="C12" s="15">
+      <c r="C12" s="12">
         <v>0.70833333333333337</v>
       </c>
       <c r="D12" s="8" t="s">
@@ -989,7 +992,7 @@
       <c r="B13" s="8">
         <v>43171</v>
       </c>
-      <c r="C13" s="15">
+      <c r="C13" s="12">
         <v>0.70833333333333337</v>
       </c>
       <c r="D13" s="8" t="s">
@@ -1025,7 +1028,7 @@
       <c r="B14" s="8">
         <v>43178</v>
       </c>
-      <c r="C14" s="15">
+      <c r="C14" s="12">
         <v>0.70833333333333337</v>
       </c>
       <c r="D14" s="8" t="s">
@@ -1061,7 +1064,7 @@
       <c r="B15" s="8">
         <v>43185</v>
       </c>
-      <c r="C15" s="15">
+      <c r="C15" s="12">
         <v>0.70833333333333337</v>
       </c>
       <c r="D15" s="8" t="s">
@@ -1097,7 +1100,7 @@
       <c r="B16" s="8">
         <v>43192</v>
       </c>
-      <c r="C16" s="15">
+      <c r="C16" s="12">
         <v>0.70833333333333337</v>
       </c>
       <c r="D16" s="8" t="s">
@@ -1133,7 +1136,7 @@
       <c r="B17" s="8">
         <v>43199</v>
       </c>
-      <c r="C17" s="15">
+      <c r="C17" s="12">
         <v>0.70833333333333337</v>
       </c>
       <c r="D17" s="8" t="s">
@@ -1169,7 +1172,7 @@
       <c r="B18" s="8">
         <v>43206</v>
       </c>
-      <c r="C18" s="15">
+      <c r="C18" s="12">
         <v>0.70833333333333337</v>
       </c>
       <c r="D18" s="8" t="s">
@@ -1205,7 +1208,7 @@
       <c r="B19" s="8">
         <v>43213</v>
       </c>
-      <c r="C19" s="15">
+      <c r="C19" s="12">
         <v>0.70833333333333337</v>
       </c>
       <c r="D19" s="8" t="s">
@@ -1241,7 +1244,7 @@
       <c r="B20" s="8">
         <v>43220</v>
       </c>
-      <c r="C20" s="15">
+      <c r="C20" s="12">
         <v>0.70833333333333337</v>
       </c>
       <c r="D20" s="8" t="s">
@@ -1277,7 +1280,7 @@
       <c r="B21" s="8">
         <v>43227</v>
       </c>
-      <c r="C21" s="15">
+      <c r="C21" s="12">
         <v>0.70833333333333337</v>
       </c>
       <c r="D21" s="8" t="s">
@@ -1313,7 +1316,7 @@
       <c r="B22" s="8">
         <v>43234</v>
       </c>
-      <c r="C22" s="15">
+      <c r="C22" s="12">
         <v>0.70833333333333337</v>
       </c>
       <c r="D22" s="8" t="s">
@@ -1349,7 +1352,7 @@
       <c r="B23" s="8">
         <v>43241</v>
       </c>
-      <c r="C23" s="15">
+      <c r="C23" s="12">
         <v>0.70833333333333337</v>
       </c>
       <c r="D23" s="8" t="s">
@@ -1385,7 +1388,7 @@
       <c r="B24" s="8">
         <v>43248</v>
       </c>
-      <c r="C24" s="15">
+      <c r="C24" s="12">
         <v>0.70833333333333337</v>
       </c>
       <c r="D24" s="8" t="s">
@@ -1421,7 +1424,7 @@
       <c r="B25" s="8">
         <v>43255</v>
       </c>
-      <c r="C25" s="15">
+      <c r="C25" s="12">
         <v>0.70833333333333337</v>
       </c>
       <c r="D25" s="8" t="s">
@@ -1457,7 +1460,7 @@
       <c r="B26" s="8">
         <v>43262</v>
       </c>
-      <c r="C26" s="15">
+      <c r="C26" s="12">
         <v>0.70833333333333337</v>
       </c>
       <c r="D26" s="8" t="s">
@@ -1493,7 +1496,7 @@
       <c r="B27" s="8">
         <v>43269</v>
       </c>
-      <c r="C27" s="15">
+      <c r="C27" s="12">
         <v>0.70833333333333337</v>
       </c>
       <c r="D27" s="8" t="s">
@@ -1529,7 +1532,7 @@
       <c r="B28" s="8">
         <v>43276</v>
       </c>
-      <c r="C28" s="15">
+      <c r="C28" s="12">
         <v>0.70833333333333337</v>
       </c>
       <c r="D28" s="8" t="s">
@@ -1565,7 +1568,7 @@
       <c r="B29" s="8">
         <v>43283</v>
       </c>
-      <c r="C29" s="15">
+      <c r="C29" s="12">
         <v>0.70833333333333337</v>
       </c>
       <c r="D29" s="8" t="s">
@@ -1601,7 +1604,7 @@
       <c r="B30" s="8">
         <v>43290</v>
       </c>
-      <c r="C30" s="15">
+      <c r="C30" s="12">
         <v>0.70833333333333337</v>
       </c>
       <c r="D30" s="8" t="s">
@@ -1637,7 +1640,7 @@
       <c r="B31" s="8">
         <v>43297</v>
       </c>
-      <c r="C31" s="15">
+      <c r="C31" s="12">
         <v>0.70833333333333337</v>
       </c>
       <c r="D31" s="8" t="s">
@@ -1673,7 +1676,7 @@
       <c r="B32" s="8">
         <v>43304</v>
       </c>
-      <c r="C32" s="15">
+      <c r="C32" s="12">
         <v>0.70833333333333337</v>
       </c>
       <c r="D32" s="8" t="s">
@@ -1709,7 +1712,7 @@
       <c r="B33" s="8">
         <v>43311</v>
       </c>
-      <c r="C33" s="15">
+      <c r="C33" s="12">
         <v>0.70833333333333337</v>
       </c>
       <c r="D33" s="8" t="s">
@@ -1745,7 +1748,7 @@
       <c r="B34" s="8">
         <v>43318</v>
       </c>
-      <c r="C34" s="15">
+      <c r="C34" s="12">
         <v>0.70833333333333337</v>
       </c>
       <c r="D34" s="8" t="s">
@@ -1781,7 +1784,7 @@
       <c r="B35" s="8">
         <v>43325</v>
       </c>
-      <c r="C35" s="15">
+      <c r="C35" s="12">
         <v>0.70833333333333337</v>
       </c>
       <c r="D35" s="8" t="s">
@@ -1817,7 +1820,7 @@
       <c r="B36" s="8">
         <v>43332</v>
       </c>
-      <c r="C36" s="15">
+      <c r="C36" s="12">
         <v>0.70833333333333337</v>
       </c>
       <c r="D36" s="8" t="s">
@@ -1853,7 +1856,7 @@
       <c r="B37" s="8">
         <v>43339</v>
       </c>
-      <c r="C37" s="15">
+      <c r="C37" s="12">
         <v>0.70833333333333337</v>
       </c>
       <c r="D37" s="8" t="s">
@@ -1889,7 +1892,7 @@
       <c r="B38" s="8">
         <v>43346</v>
       </c>
-      <c r="C38" s="15">
+      <c r="C38" s="12">
         <v>0.70833333333333337</v>
       </c>
       <c r="D38" s="8" t="s">
@@ -1925,7 +1928,7 @@
       <c r="B39" s="8">
         <v>43353</v>
       </c>
-      <c r="C39" s="15">
+      <c r="C39" s="12">
         <v>0.70833333333333337</v>
       </c>
       <c r="D39" s="8" t="s">
@@ -1961,7 +1964,7 @@
       <c r="B40" s="8">
         <v>43360</v>
       </c>
-      <c r="C40" s="15">
+      <c r="C40" s="12">
         <v>0.70833333333333337</v>
       </c>
       <c r="D40" s="8" t="s">
@@ -1997,7 +2000,7 @@
       <c r="B41" s="8">
         <v>43367</v>
       </c>
-      <c r="C41" s="15">
+      <c r="C41" s="12">
         <v>0.70833333333333337</v>
       </c>
       <c r="D41" s="8" t="s">
@@ -2033,7 +2036,7 @@
       <c r="B42" s="8">
         <v>43374</v>
       </c>
-      <c r="C42" s="15">
+      <c r="C42" s="12">
         <v>0.70833333333333337</v>
       </c>
       <c r="D42" s="8" t="s">
@@ -2069,7 +2072,7 @@
       <c r="B43" s="8">
         <v>43381</v>
       </c>
-      <c r="C43" s="15">
+      <c r="C43" s="12">
         <v>0.70833333333333337</v>
       </c>
       <c r="D43" s="8" t="s">
@@ -2105,7 +2108,7 @@
       <c r="B44" s="8">
         <v>43388</v>
       </c>
-      <c r="C44" s="15">
+      <c r="C44" s="12">
         <v>0.70833333333333337</v>
       </c>
       <c r="D44" s="8" t="s">
@@ -2141,7 +2144,7 @@
       <c r="B45" s="8">
         <v>43395</v>
       </c>
-      <c r="C45" s="15">
+      <c r="C45" s="12">
         <v>0.70833333333333337</v>
       </c>
       <c r="D45" s="8" t="s">
@@ -2177,7 +2180,7 @@
       <c r="B46" s="8">
         <v>43402</v>
       </c>
-      <c r="C46" s="15">
+      <c r="C46" s="12">
         <v>0.70833333333333337</v>
       </c>
       <c r="D46" s="8" t="s">
@@ -2213,7 +2216,7 @@
       <c r="B47" s="8">
         <v>43409</v>
       </c>
-      <c r="C47" s="15">
+      <c r="C47" s="12">
         <v>0.70833333333333337</v>
       </c>
       <c r="D47" s="8" t="s">
@@ -2249,7 +2252,7 @@
       <c r="B48" s="8">
         <v>43416</v>
       </c>
-      <c r="C48" s="15">
+      <c r="C48" s="12">
         <v>0.70833333333333337</v>
       </c>
       <c r="D48" s="8" t="s">
@@ -2285,7 +2288,7 @@
       <c r="B49" s="8">
         <v>43423</v>
       </c>
-      <c r="C49" s="15">
+      <c r="C49" s="12">
         <v>0.70833333333333337</v>
       </c>
       <c r="D49" s="8" t="s">
@@ -2321,7 +2324,7 @@
       <c r="B50" s="8">
         <v>43430</v>
       </c>
-      <c r="C50" s="15">
+      <c r="C50" s="12">
         <v>0.70833333333333337</v>
       </c>
       <c r="D50" s="8" t="s">
@@ -2357,7 +2360,7 @@
       <c r="B51" s="8">
         <v>43437</v>
       </c>
-      <c r="C51" s="15">
+      <c r="C51" s="12">
         <v>0.70833333333333337</v>
       </c>
       <c r="D51" s="8" t="s">
@@ -2393,7 +2396,7 @@
       <c r="B52" s="8">
         <v>43444</v>
       </c>
-      <c r="C52" s="15">
+      <c r="C52" s="12">
         <v>0.70833333333333337</v>
       </c>
       <c r="D52" s="8" t="s">
@@ -2429,7 +2432,7 @@
       <c r="B53" s="8">
         <v>43451</v>
       </c>
-      <c r="C53" s="15">
+      <c r="C53" s="12">
         <v>0.70833333333333337</v>
       </c>
       <c r="D53" s="8" t="s">
@@ -2465,7 +2468,7 @@
       <c r="B54" s="8">
         <v>43458</v>
       </c>
-      <c r="C54" s="15">
+      <c r="C54" s="12">
         <v>0.70833333333333337</v>
       </c>
       <c r="D54" s="8" t="s">
@@ -2501,7 +2504,7 @@
       <c r="B55" s="8">
         <v>43465</v>
       </c>
-      <c r="C55" s="15">
+      <c r="C55" s="12">
         <v>0.70833333333333337</v>
       </c>
       <c r="D55" s="8" t="s">
@@ -2537,7 +2540,7 @@
       <c r="B56" s="8">
         <v>43472</v>
       </c>
-      <c r="C56" s="15">
+      <c r="C56" s="12">
         <v>0.70833333333333337</v>
       </c>
       <c r="D56" s="8" t="s">
@@ -2573,7 +2576,7 @@
       <c r="B57" s="8">
         <v>43479</v>
       </c>
-      <c r="C57" s="15">
+      <c r="C57" s="12">
         <v>0.70833333333333337</v>
       </c>
       <c r="D57" s="8" t="s">
@@ -2609,7 +2612,7 @@
       <c r="B58" s="8">
         <v>43486</v>
       </c>
-      <c r="C58" s="15">
+      <c r="C58" s="12">
         <v>0.70833333333333337</v>
       </c>
       <c r="D58" s="8" t="s">
@@ -2645,7 +2648,7 @@
       <c r="B59" s="8">
         <v>43493</v>
       </c>
-      <c r="C59" s="15">
+      <c r="C59" s="12">
         <v>0.70833333333333337</v>
       </c>
       <c r="D59" s="8" t="s">
@@ -2681,7 +2684,7 @@
       <c r="B60" s="8">
         <v>43500</v>
       </c>
-      <c r="C60" s="15">
+      <c r="C60" s="12">
         <v>0.70833333333333337</v>
       </c>
       <c r="D60" s="8" t="s">
@@ -2717,7 +2720,7 @@
       <c r="B61" s="8">
         <v>43507</v>
       </c>
-      <c r="C61" s="15">
+      <c r="C61" s="12">
         <v>0.70833333333333337</v>
       </c>
       <c r="D61" s="8" t="s">
@@ -2753,7 +2756,7 @@
       <c r="B62" s="8">
         <v>43514</v>
       </c>
-      <c r="C62" s="15">
+      <c r="C62" s="12">
         <v>0.70833333333333337</v>
       </c>
       <c r="D62" s="8" t="s">
@@ -2789,7 +2792,7 @@
       <c r="B63" s="8">
         <v>43521</v>
       </c>
-      <c r="C63" s="15">
+      <c r="C63" s="12">
         <v>0.70833333333333337</v>
       </c>
       <c r="D63" s="8" t="s">
@@ -2825,7 +2828,7 @@
       <c r="B64" s="8">
         <v>43528</v>
       </c>
-      <c r="C64" s="15">
+      <c r="C64" s="12">
         <v>0.70833333333333337</v>
       </c>
       <c r="D64" s="8" t="s">
@@ -2861,7 +2864,7 @@
       <c r="B65" s="8">
         <v>43535</v>
       </c>
-      <c r="C65" s="15">
+      <c r="C65" s="12">
         <v>0.70833333333333337</v>
       </c>
       <c r="D65" s="8" t="s">
@@ -2897,7 +2900,7 @@
       <c r="B66" s="8">
         <v>43542</v>
       </c>
-      <c r="C66" s="15">
+      <c r="C66" s="12">
         <v>0.70833333333333337</v>
       </c>
       <c r="D66" s="8" t="s">
@@ -2933,7 +2936,7 @@
       <c r="B67" s="8">
         <v>43549</v>
       </c>
-      <c r="C67" s="15">
+      <c r="C67" s="12">
         <v>0.70833333333333337</v>
       </c>
       <c r="D67" s="8" t="s">
@@ -2969,7 +2972,7 @@
       <c r="B68" s="8">
         <v>43556</v>
       </c>
-      <c r="C68" s="15">
+      <c r="C68" s="12">
         <v>0.70833333333333337</v>
       </c>
       <c r="D68" s="8" t="s">
@@ -3005,7 +3008,7 @@
       <c r="B69" s="8">
         <v>43563</v>
       </c>
-      <c r="C69" s="15">
+      <c r="C69" s="12">
         <v>0.70833333333333337</v>
       </c>
       <c r="D69" s="8" t="s">
@@ -3041,7 +3044,7 @@
       <c r="B70" s="8">
         <v>43570</v>
       </c>
-      <c r="C70" s="15">
+      <c r="C70" s="12">
         <v>0.70833333333333337</v>
       </c>
       <c r="D70" s="8" t="s">
@@ -3077,7 +3080,7 @@
       <c r="B71" s="8">
         <v>43577</v>
       </c>
-      <c r="C71" s="15">
+      <c r="C71" s="12">
         <v>0.70833333333333337</v>
       </c>
       <c r="D71" s="8" t="s">
@@ -3113,7 +3116,7 @@
       <c r="B72" s="8">
         <v>43584</v>
       </c>
-      <c r="C72" s="15">
+      <c r="C72" s="12">
         <v>0.70833333333333337</v>
       </c>
       <c r="D72" s="8" t="s">
@@ -3149,7 +3152,7 @@
       <c r="B73" s="8">
         <v>43591</v>
       </c>
-      <c r="C73" s="15">
+      <c r="C73" s="12">
         <v>0.70833333333333337</v>
       </c>
       <c r="D73" s="8" t="s">
@@ -3185,7 +3188,7 @@
       <c r="B74" s="8">
         <v>43598</v>
       </c>
-      <c r="C74" s="15">
+      <c r="C74" s="12">
         <v>0.70833333333333337</v>
       </c>
       <c r="D74" s="8" t="s">
@@ -3221,7 +3224,7 @@
       <c r="B75" s="8">
         <v>43605</v>
       </c>
-      <c r="C75" s="15">
+      <c r="C75" s="12">
         <v>0.70833333333333337</v>
       </c>
       <c r="D75" s="8" t="s">
@@ -3257,7 +3260,7 @@
       <c r="B76" s="8">
         <v>43612</v>
       </c>
-      <c r="C76" s="15">
+      <c r="C76" s="12">
         <v>0.70833333333333337</v>
       </c>
       <c r="D76" s="8" t="s">
@@ -3293,7 +3296,7 @@
       <c r="B77" s="8">
         <v>43619</v>
       </c>
-      <c r="C77" s="15">
+      <c r="C77" s="12">
         <v>0.70833333333333337</v>
       </c>
       <c r="D77" s="8" t="s">
@@ -3329,7 +3332,7 @@
       <c r="B78" s="8">
         <v>43626</v>
       </c>
-      <c r="C78" s="15">
+      <c r="C78" s="12">
         <v>0.70833333333333337</v>
       </c>
       <c r="D78" s="8" t="s">
@@ -3365,7 +3368,7 @@
       <c r="B79" s="8">
         <v>43633</v>
       </c>
-      <c r="C79" s="15">
+      <c r="C79" s="12">
         <v>0.70833333333333337</v>
       </c>
       <c r="D79" s="8" t="s">
@@ -3401,7 +3404,7 @@
       <c r="B80" s="8">
         <v>43640</v>
       </c>
-      <c r="C80" s="15">
+      <c r="C80" s="12">
         <v>0.70833333333333337</v>
       </c>
       <c r="D80" s="8" t="s">
@@ -3437,7 +3440,7 @@
       <c r="B81" s="8">
         <v>43647</v>
       </c>
-      <c r="C81" s="15">
+      <c r="C81" s="12">
         <v>0.70833333333333337</v>
       </c>
       <c r="D81" s="8" t="s">
@@ -3473,7 +3476,7 @@
       <c r="B82" s="8">
         <v>43654</v>
       </c>
-      <c r="C82" s="15">
+      <c r="C82" s="12">
         <v>0.70833333333333337</v>
       </c>
       <c r="D82" s="8" t="s">
@@ -3509,7 +3512,7 @@
       <c r="B83" s="8">
         <v>43661</v>
       </c>
-      <c r="C83" s="15">
+      <c r="C83" s="12">
         <v>0.70833333333333337</v>
       </c>
       <c r="D83" s="8" t="s">
@@ -3545,7 +3548,7 @@
       <c r="B84" s="8">
         <v>43668</v>
       </c>
-      <c r="C84" s="15">
+      <c r="C84" s="12">
         <v>0.70833333333333337</v>
       </c>
       <c r="D84" s="8" t="s">
@@ -3581,7 +3584,7 @@
       <c r="B85" s="8">
         <v>43675</v>
       </c>
-      <c r="C85" s="15">
+      <c r="C85" s="12">
         <v>0.70833333333333337</v>
       </c>
       <c r="D85" s="8" t="s">
@@ -3617,7 +3620,7 @@
       <c r="B86" s="8">
         <v>43682</v>
       </c>
-      <c r="C86" s="15">
+      <c r="C86" s="12">
         <v>0.70833333333333337</v>
       </c>
       <c r="D86" s="8" t="s">
@@ -3653,7 +3656,7 @@
       <c r="B87" s="8">
         <v>43689</v>
       </c>
-      <c r="C87" s="15">
+      <c r="C87" s="12">
         <v>0.70833333333333337</v>
       </c>
       <c r="D87" s="8" t="s">
@@ -3689,7 +3692,7 @@
       <c r="B88" s="8">
         <v>43696</v>
       </c>
-      <c r="C88" s="15">
+      <c r="C88" s="12">
         <v>0.70833333333333337</v>
       </c>
       <c r="D88" s="8" t="s">
@@ -3725,7 +3728,7 @@
       <c r="B89" s="8">
         <v>43703</v>
       </c>
-      <c r="C89" s="15">
+      <c r="C89" s="12">
         <v>0.70833333333333337</v>
       </c>
       <c r="D89" s="8" t="s">
@@ -3761,7 +3764,7 @@
       <c r="B90" s="8">
         <v>43710</v>
       </c>
-      <c r="C90" s="15">
+      <c r="C90" s="12">
         <v>0.70833333333333337</v>
       </c>
       <c r="D90" s="8" t="s">
@@ -3797,7 +3800,7 @@
       <c r="B91" s="8">
         <v>43717</v>
       </c>
-      <c r="C91" s="15">
+      <c r="C91" s="12">
         <v>0.70833333333333337</v>
       </c>
       <c r="D91" s="8" t="s">
@@ -3833,7 +3836,7 @@
       <c r="B92" s="8">
         <v>43724</v>
       </c>
-      <c r="C92" s="15">
+      <c r="C92" s="12">
         <v>0.70833333333333337</v>
       </c>
       <c r="D92" s="8" t="s">
@@ -3869,7 +3872,7 @@
       <c r="B93" s="8">
         <v>43731</v>
       </c>
-      <c r="C93" s="15">
+      <c r="C93" s="12">
         <v>0.70833333333333337</v>
       </c>
       <c r="D93" s="8" t="s">
@@ -3905,7 +3908,7 @@
       <c r="B94" s="8">
         <v>43738</v>
       </c>
-      <c r="C94" s="15">
+      <c r="C94" s="12">
         <v>0.70833333333333337</v>
       </c>
       <c r="D94" s="8" t="s">
@@ -3941,7 +3944,7 @@
       <c r="B95" s="8">
         <v>43745</v>
       </c>
-      <c r="C95" s="15">
+      <c r="C95" s="12">
         <v>0.70833333333333337</v>
       </c>
       <c r="D95" s="8" t="s">
@@ -3977,7 +3980,7 @@
       <c r="B96" s="8">
         <v>43752</v>
       </c>
-      <c r="C96" s="15">
+      <c r="C96" s="12">
         <v>0.70833333333333337</v>
       </c>
       <c r="D96" s="8" t="s">
@@ -4013,7 +4016,7 @@
       <c r="B97" s="8">
         <v>43759</v>
       </c>
-      <c r="C97" s="15">
+      <c r="C97" s="12">
         <v>0.70833333333333337</v>
       </c>
       <c r="D97" s="8" t="s">
@@ -4049,7 +4052,7 @@
       <c r="B98" s="8">
         <v>43766</v>
       </c>
-      <c r="C98" s="15">
+      <c r="C98" s="12">
         <v>0.70833333333333337</v>
       </c>
       <c r="D98" s="8" t="s">
@@ -4085,7 +4088,7 @@
       <c r="B99" s="8">
         <v>43773</v>
       </c>
-      <c r="C99" s="15">
+      <c r="C99" s="12">
         <v>0.70833333333333337</v>
       </c>
       <c r="D99" s="8" t="s">
@@ -4121,7 +4124,7 @@
       <c r="B100" s="8">
         <v>43780</v>
       </c>
-      <c r="C100" s="15">
+      <c r="C100" s="12">
         <v>0.70833333333333337</v>
       </c>
       <c r="D100" s="8" t="s">
@@ -4157,7 +4160,7 @@
       <c r="B101" s="8">
         <v>43787</v>
       </c>
-      <c r="C101" s="15">
+      <c r="C101" s="12">
         <v>0.70833333333333337</v>
       </c>
       <c r="D101" s="8" t="s">
@@ -4193,7 +4196,7 @@
       <c r="B102" s="8">
         <v>43794</v>
       </c>
-      <c r="C102" s="15">
+      <c r="C102" s="12">
         <v>0.70833333333333337</v>
       </c>
       <c r="D102" s="8" t="s">
@@ -4229,7 +4232,7 @@
       <c r="B103" s="8">
         <v>43801</v>
       </c>
-      <c r="C103" s="15">
+      <c r="C103" s="12">
         <v>0.70833333333333337</v>
       </c>
       <c r="D103" s="8" t="s">
@@ -4265,7 +4268,7 @@
       <c r="B104" s="8">
         <v>43808</v>
       </c>
-      <c r="C104" s="15">
+      <c r="C104" s="12">
         <v>0.70833333333333337</v>
       </c>
       <c r="D104" s="8" t="s">
@@ -4301,7 +4304,7 @@
       <c r="B105" s="8">
         <v>43815</v>
       </c>
-      <c r="C105" s="15">
+      <c r="C105" s="12">
         <v>0.70833333333333337</v>
       </c>
       <c r="D105" s="8" t="s">
@@ -4337,7 +4340,7 @@
       <c r="B106" s="8">
         <v>43822</v>
       </c>
-      <c r="C106" s="15">
+      <c r="C106" s="12">
         <v>0.70833333333333337</v>
       </c>
       <c r="D106" s="8" t="s">
@@ -4373,7 +4376,7 @@
       <c r="B107" s="8">
         <v>43829</v>
       </c>
-      <c r="C107" s="15">
+      <c r="C107" s="12">
         <v>0.70833333333333337</v>
       </c>
       <c r="D107" s="8" t="s">
@@ -4409,7 +4412,7 @@
       <c r="B108" s="8">
         <v>43836</v>
       </c>
-      <c r="C108" s="15">
+      <c r="C108" s="12">
         <v>0.70833333333333337</v>
       </c>
       <c r="D108" s="8" t="s">
@@ -4445,7 +4448,7 @@
       <c r="B109" s="8">
         <v>43843</v>
       </c>
-      <c r="C109" s="15">
+      <c r="C109" s="12">
         <v>0.70833333333333337</v>
       </c>
       <c r="D109" s="8" t="s">
@@ -4481,7 +4484,7 @@
       <c r="B110" s="8">
         <v>43850</v>
       </c>
-      <c r="C110" s="15">
+      <c r="C110" s="12">
         <v>0.70833333333333337</v>
       </c>
       <c r="D110" s="8" t="s">
@@ -4517,7 +4520,7 @@
       <c r="B111" s="8">
         <v>43857</v>
       </c>
-      <c r="C111" s="15">
+      <c r="C111" s="12">
         <v>0.70833333333333337</v>
       </c>
       <c r="D111" s="8" t="s">
@@ -4553,7 +4556,7 @@
       <c r="B112" s="8">
         <v>43864</v>
       </c>
-      <c r="C112" s="15">
+      <c r="C112" s="12">
         <v>0.70833333333333337</v>
       </c>
       <c r="D112" s="8" t="s">
@@ -4589,7 +4592,7 @@
       <c r="B113" s="8">
         <v>43871</v>
       </c>
-      <c r="C113" s="15">
+      <c r="C113" s="12">
         <v>0.70833333333333337</v>
       </c>
       <c r="D113" s="8" t="s">
@@ -4625,7 +4628,7 @@
       <c r="B114" s="8">
         <v>43878</v>
       </c>
-      <c r="C114" s="15">
+      <c r="C114" s="12">
         <v>0.70833333333333337</v>
       </c>
       <c r="D114" s="8" t="s">
@@ -4661,7 +4664,7 @@
       <c r="B115" s="8">
         <v>43885</v>
       </c>
-      <c r="C115" s="15">
+      <c r="C115" s="12">
         <v>0.70833333333333337</v>
       </c>
       <c r="D115" s="8" t="s">
@@ -4697,7 +4700,7 @@
       <c r="B116" s="8">
         <v>43892</v>
       </c>
-      <c r="C116" s="15">
+      <c r="C116" s="12">
         <v>0.70833333333333337</v>
       </c>
       <c r="D116" s="8" t="s">
@@ -4733,7 +4736,7 @@
       <c r="B117" s="8">
         <v>43899</v>
       </c>
-      <c r="C117" s="15">
+      <c r="C117" s="12">
         <v>0.70833333333333337</v>
       </c>
       <c r="D117" s="8" t="s">
@@ -4769,7 +4772,7 @@
       <c r="B118" s="8">
         <v>43906</v>
       </c>
-      <c r="C118" s="15">
+      <c r="C118" s="12">
         <v>0.70833333333333337</v>
       </c>
       <c r="D118" s="8" t="s">
@@ -4805,7 +4808,7 @@
       <c r="B119" s="8">
         <v>43913</v>
       </c>
-      <c r="C119" s="15">
+      <c r="C119" s="12">
         <v>0.70833333333333337</v>
       </c>
       <c r="D119" s="8" t="s">
@@ -4841,7 +4844,7 @@
       <c r="B120" s="8">
         <v>43920</v>
       </c>
-      <c r="C120" s="15">
+      <c r="C120" s="12">
         <v>0.70833333333333337</v>
       </c>
       <c r="D120" s="8" t="s">
@@ -4877,7 +4880,7 @@
       <c r="B121" s="8">
         <v>43927</v>
       </c>
-      <c r="C121" s="15">
+      <c r="C121" s="12">
         <v>0.70833333333333337</v>
       </c>
       <c r="D121" s="8" t="s">
@@ -4913,7 +4916,7 @@
       <c r="B122" s="8">
         <v>43934</v>
       </c>
-      <c r="C122" s="15">
+      <c r="C122" s="12">
         <v>0.70833333333333337</v>
       </c>
       <c r="D122" s="8" t="s">
@@ -4949,7 +4952,7 @@
       <c r="B123" s="8">
         <v>43941</v>
       </c>
-      <c r="C123" s="15">
+      <c r="C123" s="12">
         <v>0.70833333333333337</v>
       </c>
       <c r="D123" s="8" t="s">
@@ -4985,7 +4988,7 @@
       <c r="B124" s="8">
         <v>43948</v>
       </c>
-      <c r="C124" s="15">
+      <c r="C124" s="12">
         <v>0.70833333333333337</v>
       </c>
       <c r="D124" s="8" t="s">
@@ -5021,7 +5024,7 @@
       <c r="B125" s="8">
         <v>43955</v>
       </c>
-      <c r="C125" s="15">
+      <c r="C125" s="12">
         <v>0.70833333333333337</v>
       </c>
       <c r="D125" s="8" t="s">
@@ -5057,7 +5060,7 @@
       <c r="B126" s="8">
         <v>43962</v>
       </c>
-      <c r="C126" s="15">
+      <c r="C126" s="12">
         <v>0.70833333333333337</v>
       </c>
       <c r="D126" s="8" t="s">
@@ -5093,7 +5096,7 @@
       <c r="B127" s="8">
         <v>43969</v>
       </c>
-      <c r="C127" s="15">
+      <c r="C127" s="12">
         <v>0.70833333333333337</v>
       </c>
       <c r="D127" s="8" t="s">
@@ -5129,7 +5132,7 @@
       <c r="B128" s="8">
         <v>43976</v>
       </c>
-      <c r="C128" s="15">
+      <c r="C128" s="12">
         <v>0.70833333333333337</v>
       </c>
       <c r="D128" s="8" t="s">
@@ -5165,7 +5168,7 @@
       <c r="B129" s="8">
         <v>43983</v>
       </c>
-      <c r="C129" s="15">
+      <c r="C129" s="12">
         <v>0.70833333333333337</v>
       </c>
       <c r="D129" s="8" t="s">
@@ -5201,7 +5204,7 @@
       <c r="B130" s="8">
         <v>43990</v>
       </c>
-      <c r="C130" s="15">
+      <c r="C130" s="12">
         <v>0.70833333333333337</v>
       </c>
       <c r="D130" s="8" t="s">
@@ -5237,7 +5240,7 @@
       <c r="B131" s="8">
         <v>43997</v>
       </c>
-      <c r="C131" s="15">
+      <c r="C131" s="12">
         <v>0.70833333333333337</v>
       </c>
       <c r="D131" s="8" t="s">
@@ -5273,7 +5276,7 @@
       <c r="B132" s="8">
         <v>44004</v>
       </c>
-      <c r="C132" s="15">
+      <c r="C132" s="12">
         <v>0.70833333333333337</v>
       </c>
       <c r="D132" s="8" t="s">
@@ -5309,7 +5312,7 @@
       <c r="B133" s="8">
         <v>44011</v>
       </c>
-      <c r="C133" s="15">
+      <c r="C133" s="12">
         <v>0.70833333333333337</v>
       </c>
       <c r="D133" s="8" t="s">
@@ -5345,7 +5348,7 @@
       <c r="B134" s="8">
         <v>44018</v>
       </c>
-      <c r="C134" s="15">
+      <c r="C134" s="12">
         <v>0.70833333333333337</v>
       </c>
       <c r="D134" s="8" t="s">
@@ -5381,7 +5384,7 @@
       <c r="B135" s="8">
         <v>44025</v>
       </c>
-      <c r="C135" s="15">
+      <c r="C135" s="12">
         <v>0.70833333333333337</v>
       </c>
       <c r="D135" s="8" t="s">
@@ -5417,7 +5420,7 @@
       <c r="B136" s="8">
         <v>44032</v>
       </c>
-      <c r="C136" s="15">
+      <c r="C136" s="12">
         <v>0.70833333333333337</v>
       </c>
       <c r="D136" s="8" t="s">
@@ -5453,7 +5456,7 @@
       <c r="B137" s="8">
         <v>44039</v>
       </c>
-      <c r="C137" s="15">
+      <c r="C137" s="12">
         <v>0.70833333333333337</v>
       </c>
       <c r="D137" s="8" t="s">
@@ -5489,7 +5492,7 @@
       <c r="B138" s="8">
         <v>44046</v>
       </c>
-      <c r="C138" s="15">
+      <c r="C138" s="12">
         <v>0.70833333333333337</v>
       </c>
       <c r="D138" s="8" t="s">
@@ -5525,7 +5528,7 @@
       <c r="B139" s="8">
         <v>44053</v>
       </c>
-      <c r="C139" s="15">
+      <c r="C139" s="12">
         <v>0.70833333333333337</v>
       </c>
       <c r="D139" s="8" t="s">
@@ -5561,7 +5564,7 @@
       <c r="B140" s="8">
         <v>44060</v>
       </c>
-      <c r="C140" s="15">
+      <c r="C140" s="12">
         <v>0.70833333333333337</v>
       </c>
       <c r="D140" s="8" t="s">
@@ -5597,7 +5600,7 @@
       <c r="B141" s="8">
         <v>44067</v>
       </c>
-      <c r="C141" s="15">
+      <c r="C141" s="12">
         <v>0.70833333333333337</v>
       </c>
       <c r="D141" s="8" t="s">
@@ -5633,7 +5636,7 @@
       <c r="B142" s="8">
         <v>44074</v>
       </c>
-      <c r="C142" s="15">
+      <c r="C142" s="12">
         <v>0.70833333333333337</v>
       </c>
       <c r="D142" s="8" t="s">
@@ -5669,7 +5672,7 @@
       <c r="B143" s="8">
         <v>44081</v>
       </c>
-      <c r="C143" s="15">
+      <c r="C143" s="12">
         <v>0.70833333333333337</v>
       </c>
       <c r="D143" s="8" t="s">
@@ -5705,7 +5708,7 @@
       <c r="B144" s="8">
         <v>44088</v>
       </c>
-      <c r="C144" s="15">
+      <c r="C144" s="12">
         <v>0.70833333333333337</v>
       </c>
       <c r="D144" s="8" t="s">
@@ -5741,7 +5744,7 @@
       <c r="B145" s="8">
         <v>44095</v>
       </c>
-      <c r="C145" s="15">
+      <c r="C145" s="12">
         <v>0.70833333333333337</v>
       </c>
       <c r="D145" s="8" t="s">
@@ -5777,7 +5780,7 @@
       <c r="B146" s="8">
         <v>44102</v>
       </c>
-      <c r="C146" s="15">
+      <c r="C146" s="12">
         <v>0.70833333333333337</v>
       </c>
       <c r="D146" s="8" t="s">
@@ -5813,7 +5816,7 @@
       <c r="B147" s="8">
         <v>44109</v>
       </c>
-      <c r="C147" s="15">
+      <c r="C147" s="12">
         <v>0.70833333333333337</v>
       </c>
       <c r="D147" s="8" t="s">
@@ -5849,7 +5852,7 @@
       <c r="B148" s="8">
         <v>44116</v>
       </c>
-      <c r="C148" s="15">
+      <c r="C148" s="12">
         <v>0.70833333333333337</v>
       </c>
       <c r="D148" s="8" t="s">
@@ -5885,7 +5888,7 @@
       <c r="B149" s="8">
         <v>44123</v>
       </c>
-      <c r="C149" s="15">
+      <c r="C149" s="12">
         <v>0.70833333333333337</v>
       </c>
       <c r="D149" s="8" t="s">
@@ -5921,7 +5924,7 @@
       <c r="B150" s="8">
         <v>44130</v>
       </c>
-      <c r="C150" s="15">
+      <c r="C150" s="12">
         <v>0.70833333333333337</v>
       </c>
       <c r="D150" s="8" t="s">
@@ -5957,7 +5960,7 @@
       <c r="B151" s="8">
         <v>44137</v>
       </c>
-      <c r="C151" s="15">
+      <c r="C151" s="12">
         <v>0.70833333333333337</v>
       </c>
       <c r="D151" s="8" t="s">
@@ -5993,7 +5996,7 @@
       <c r="B152" s="8">
         <v>44144</v>
       </c>
-      <c r="C152" s="15">
+      <c r="C152" s="12">
         <v>0.70833333333333337</v>
       </c>
       <c r="D152" s="8" t="s">
@@ -6029,7 +6032,7 @@
       <c r="B153" s="8">
         <v>44151</v>
       </c>
-      <c r="C153" s="15">
+      <c r="C153" s="12">
         <v>0.70833333333333337</v>
       </c>
       <c r="D153" s="8" t="s">
@@ -6065,7 +6068,7 @@
       <c r="B154" s="8">
         <v>44158</v>
       </c>
-      <c r="C154" s="15">
+      <c r="C154" s="12">
         <v>0.70833333333333337</v>
       </c>
       <c r="D154" s="8" t="s">
@@ -6101,7 +6104,7 @@
       <c r="B155" s="8">
         <v>44165</v>
       </c>
-      <c r="C155" s="15">
+      <c r="C155" s="12">
         <v>0.70833333333333337</v>
       </c>
       <c r="D155" s="8" t="s">
@@ -6137,7 +6140,7 @@
       <c r="B156" s="8">
         <v>44172</v>
       </c>
-      <c r="C156" s="15">
+      <c r="C156" s="12">
         <v>0.70833333333333337</v>
       </c>
       <c r="D156" s="8" t="s">
@@ -6173,7 +6176,7 @@
       <c r="B157" s="8">
         <v>44179</v>
       </c>
-      <c r="C157" s="15">
+      <c r="C157" s="12">
         <v>0.70833333333333337</v>
       </c>
       <c r="D157" s="8" t="s">
@@ -6209,7 +6212,7 @@
       <c r="B158" s="8">
         <v>44186</v>
       </c>
-      <c r="C158" s="15">
+      <c r="C158" s="12">
         <v>0.70833333333333337</v>
       </c>
       <c r="D158" s="8" t="s">
@@ -6245,7 +6248,7 @@
       <c r="B159" s="8">
         <v>44193</v>
       </c>
-      <c r="C159" s="15">
+      <c r="C159" s="12">
         <v>0.70833333333333337</v>
       </c>
       <c r="D159" s="8" t="s">
@@ -6281,7 +6284,7 @@
       <c r="B160" s="8">
         <v>44200</v>
       </c>
-      <c r="C160" s="15">
+      <c r="C160" s="12">
         <v>0.70833333333333337</v>
       </c>
       <c r="D160" s="8" t="s">
@@ -6317,7 +6320,7 @@
       <c r="B161" s="8">
         <v>44207</v>
       </c>
-      <c r="C161" s="15">
+      <c r="C161" s="12">
         <v>0.70833333333333337</v>
       </c>
       <c r="D161" s="8" t="s">
@@ -6353,7 +6356,7 @@
       <c r="B162" s="8">
         <v>44214</v>
       </c>
-      <c r="C162" s="15">
+      <c r="C162" s="12">
         <v>0.70833333333333337</v>
       </c>
       <c r="D162" s="8" t="s">
@@ -6389,7 +6392,7 @@
       <c r="B163" s="8">
         <v>44221</v>
       </c>
-      <c r="C163" s="15">
+      <c r="C163" s="12">
         <v>0.70833333333333337</v>
       </c>
       <c r="D163" s="8" t="s">
@@ -6425,7 +6428,7 @@
       <c r="B164" s="8">
         <v>44228</v>
       </c>
-      <c r="C164" s="15">
+      <c r="C164" s="12">
         <v>0.70833333333333337</v>
       </c>
       <c r="D164" s="8" t="s">
@@ -6461,7 +6464,7 @@
       <c r="B165" s="8">
         <v>44235</v>
       </c>
-      <c r="C165" s="15">
+      <c r="C165" s="12">
         <v>0.70833333333333337</v>
       </c>
       <c r="D165" s="8" t="s">
@@ -6497,7 +6500,7 @@
       <c r="B166" s="8">
         <v>44242</v>
       </c>
-      <c r="C166" s="15">
+      <c r="C166" s="12">
         <v>0.70833333333333337</v>
       </c>
       <c r="D166" s="8" t="s">
@@ -6533,7 +6536,7 @@
       <c r="B167" s="8">
         <v>44249</v>
       </c>
-      <c r="C167" s="15">
+      <c r="C167" s="12">
         <v>0.70833333333333337</v>
       </c>
       <c r="D167" s="8" t="s">
@@ -6569,7 +6572,7 @@
       <c r="B168" s="8">
         <v>44256</v>
       </c>
-      <c r="C168" s="15">
+      <c r="C168" s="12">
         <v>0.70833333333333337</v>
       </c>
       <c r="D168" s="8" t="s">
@@ -6605,7 +6608,7 @@
       <c r="B169" s="8">
         <v>44263</v>
       </c>
-      <c r="C169" s="15">
+      <c r="C169" s="12">
         <v>0.70833333333333337</v>
       </c>
       <c r="D169" s="8" t="s">
@@ -6641,7 +6644,7 @@
       <c r="B170" s="8">
         <v>44270</v>
       </c>
-      <c r="C170" s="15">
+      <c r="C170" s="12">
         <v>0.70833333333333337</v>
       </c>
       <c r="D170" s="8" t="s">
@@ -6677,7 +6680,7 @@
       <c r="B171" s="8">
         <v>44277</v>
       </c>
-      <c r="C171" s="15">
+      <c r="C171" s="12">
         <v>0.70833333333333337</v>
       </c>
       <c r="D171" s="8" t="s">
@@ -6713,7 +6716,7 @@
       <c r="B172" s="8">
         <v>44284</v>
       </c>
-      <c r="C172" s="15">
+      <c r="C172" s="12">
         <v>0.70833333333333337</v>
       </c>
       <c r="D172" s="8" t="s">
@@ -6749,7 +6752,7 @@
       <c r="B173" s="8">
         <v>44291</v>
       </c>
-      <c r="C173" s="15">
+      <c r="C173" s="12">
         <v>0.70833333333333337</v>
       </c>
       <c r="D173" s="8" t="s">
@@ -6785,7 +6788,7 @@
       <c r="B174" s="8">
         <v>44298</v>
       </c>
-      <c r="C174" s="15">
+      <c r="C174" s="12">
         <v>0.70833333333333337</v>
       </c>
       <c r="D174" s="8" t="s">
@@ -6821,7 +6824,7 @@
       <c r="B175" s="8">
         <v>44305</v>
       </c>
-      <c r="C175" s="15">
+      <c r="C175" s="12">
         <v>0.70833333333333337</v>
       </c>
       <c r="D175" s="8" t="s">
@@ -6857,7 +6860,7 @@
       <c r="B176" s="8">
         <v>44312</v>
       </c>
-      <c r="C176" s="15">
+      <c r="C176" s="12">
         <v>0.70833333333333337</v>
       </c>
       <c r="D176" s="8" t="s">
@@ -6893,7 +6896,7 @@
       <c r="B177" s="8">
         <v>44319</v>
       </c>
-      <c r="C177" s="15">
+      <c r="C177" s="12">
         <v>0.70833333333333337</v>
       </c>
       <c r="D177" s="8" t="s">
@@ -6929,7 +6932,7 @@
       <c r="B178" s="8">
         <v>44326</v>
       </c>
-      <c r="C178" s="15">
+      <c r="C178" s="12">
         <v>0.70833333333333337</v>
       </c>
       <c r="D178" s="8" t="s">
@@ -6965,7 +6968,7 @@
       <c r="B179" s="8">
         <v>44333</v>
       </c>
-      <c r="C179" s="15">
+      <c r="C179" s="12">
         <v>0.70833333333333337</v>
       </c>
       <c r="D179" s="8" t="s">
@@ -7001,7 +7004,7 @@
       <c r="B180" s="8">
         <v>44340</v>
       </c>
-      <c r="C180" s="15">
+      <c r="C180" s="12">
         <v>0.70833333333333337</v>
       </c>
       <c r="D180" s="8" t="s">
@@ -7037,7 +7040,7 @@
       <c r="B181" s="8">
         <v>44347</v>
       </c>
-      <c r="C181" s="15">
+      <c r="C181" s="12">
         <v>0.70833333333333337</v>
       </c>
       <c r="D181" s="8" t="s">
@@ -7073,7 +7076,7 @@
       <c r="B182" s="8">
         <v>44354</v>
       </c>
-      <c r="C182" s="15">
+      <c r="C182" s="12">
         <v>0.70833333333333337</v>
       </c>
       <c r="D182" s="8" t="s">
@@ -7109,7 +7112,7 @@
       <c r="B183" s="8">
         <v>44361</v>
       </c>
-      <c r="C183" s="15">
+      <c r="C183" s="12">
         <v>0.70833333333333337</v>
       </c>
       <c r="D183" s="8" t="s">
@@ -7145,7 +7148,7 @@
       <c r="B184" s="8">
         <v>44368</v>
       </c>
-      <c r="C184" s="15">
+      <c r="C184" s="12">
         <v>0.70833333333333337</v>
       </c>
       <c r="D184" s="8" t="s">
@@ -7181,7 +7184,7 @@
       <c r="B185" s="8">
         <v>44375</v>
       </c>
-      <c r="C185" s="15">
+      <c r="C185" s="12">
         <v>0.70833333333333337</v>
       </c>
       <c r="D185" s="8" t="s">
@@ -7217,7 +7220,7 @@
       <c r="B186" s="8">
         <v>44382</v>
       </c>
-      <c r="C186" s="15">
+      <c r="C186" s="12">
         <v>0.70833333333333337</v>
       </c>
       <c r="D186" s="8" t="s">
@@ -7253,7 +7256,7 @@
       <c r="B187" s="8">
         <v>44389</v>
       </c>
-      <c r="C187" s="15">
+      <c r="C187" s="12">
         <v>0.70833333333333337</v>
       </c>
       <c r="D187" s="8" t="s">
@@ -7289,7 +7292,7 @@
       <c r="B188" s="8">
         <v>44396</v>
       </c>
-      <c r="C188" s="15">
+      <c r="C188" s="12">
         <v>0.70833333333333337</v>
       </c>
       <c r="D188" s="8" t="s">
@@ -7325,7 +7328,7 @@
       <c r="B189" s="8">
         <v>44403</v>
       </c>
-      <c r="C189" s="15">
+      <c r="C189" s="12">
         <v>0.70833333333333337</v>
       </c>
       <c r="D189" s="8" t="s">
@@ -7361,7 +7364,7 @@
       <c r="B190" s="8">
         <v>44410</v>
       </c>
-      <c r="C190" s="15">
+      <c r="C190" s="12">
         <v>0.70833333333333337</v>
       </c>
       <c r="D190" s="8" t="s">
@@ -7397,7 +7400,7 @@
       <c r="B191" s="8">
         <v>44417</v>
       </c>
-      <c r="C191" s="15">
+      <c r="C191" s="12">
         <v>0.70833333333333337</v>
       </c>
       <c r="D191" s="8" t="s">
@@ -7433,7 +7436,7 @@
       <c r="B192" s="8">
         <v>44424</v>
       </c>
-      <c r="C192" s="15">
+      <c r="C192" s="12">
         <v>0.70833333333333337</v>
       </c>
       <c r="D192" s="8" t="s">
@@ -7469,7 +7472,7 @@
       <c r="B193" s="8">
         <v>44431</v>
       </c>
-      <c r="C193" s="15">
+      <c r="C193" s="12">
         <v>0.70833333333333337</v>
       </c>
       <c r="D193" s="8" t="s">
@@ -7505,7 +7508,7 @@
       <c r="B194" s="8">
         <v>44438</v>
       </c>
-      <c r="C194" s="15">
+      <c r="C194" s="12">
         <v>0.70833333333333337</v>
       </c>
       <c r="D194" s="8" t="s">
@@ -7541,7 +7544,7 @@
       <c r="B195" s="8">
         <v>44445</v>
       </c>
-      <c r="C195" s="15">
+      <c r="C195" s="12">
         <v>0.70833333333333337</v>
       </c>
       <c r="D195" s="8" t="s">
@@ -7577,7 +7580,7 @@
       <c r="B196" s="8">
         <v>44452</v>
       </c>
-      <c r="C196" s="15">
+      <c r="C196" s="12">
         <v>0.70833333333333337</v>
       </c>
       <c r="D196" s="8" t="s">
@@ -7613,7 +7616,7 @@
       <c r="B197" s="8">
         <v>44459</v>
       </c>
-      <c r="C197" s="15">
+      <c r="C197" s="12">
         <v>0.70833333333333337</v>
       </c>
       <c r="D197" s="8" t="s">
@@ -7649,7 +7652,7 @@
       <c r="B198" s="8">
         <v>44466</v>
       </c>
-      <c r="C198" s="15">
+      <c r="C198" s="12">
         <v>0.70833333333333337</v>
       </c>
       <c r="D198" s="8" t="s">
@@ -7685,7 +7688,7 @@
       <c r="B199" s="8">
         <v>44473</v>
       </c>
-      <c r="C199" s="15">
+      <c r="C199" s="12">
         <v>0.70833333333333337</v>
       </c>
       <c r="D199" s="8" t="s">
@@ -7721,7 +7724,7 @@
       <c r="B200" s="8">
         <v>44480</v>
       </c>
-      <c r="C200" s="15">
+      <c r="C200" s="12">
         <v>0.70833333333333337</v>
       </c>
       <c r="D200" s="8" t="s">
@@ -7757,7 +7760,7 @@
       <c r="B201" s="8">
         <v>44487</v>
       </c>
-      <c r="C201" s="15">
+      <c r="C201" s="12">
         <v>0.70833333333333337</v>
       </c>
       <c r="D201" s="8" t="s">
@@ -7793,7 +7796,7 @@
       <c r="B202" s="8">
         <v>44494</v>
       </c>
-      <c r="C202" s="15">
+      <c r="C202" s="12">
         <v>0.70833333333333337</v>
       </c>
       <c r="D202" s="8" t="s">
@@ -7829,7 +7832,7 @@
       <c r="B203" s="8">
         <v>44501</v>
       </c>
-      <c r="C203" s="15">
+      <c r="C203" s="12">
         <v>0.70833333333333337</v>
       </c>
       <c r="D203" s="8" t="s">
@@ -7865,7 +7868,7 @@
       <c r="B204" s="8">
         <v>44508</v>
       </c>
-      <c r="C204" s="15">
+      <c r="C204" s="12">
         <v>0.70833333333333337</v>
       </c>
       <c r="D204" s="8" t="s">
@@ -7901,7 +7904,7 @@
       <c r="B205" s="8">
         <v>44515</v>
       </c>
-      <c r="C205" s="15">
+      <c r="C205" s="12">
         <v>0.70833333333333337</v>
       </c>
       <c r="D205" s="8" t="s">
@@ -7937,7 +7940,7 @@
       <c r="B206" s="8">
         <v>44522</v>
       </c>
-      <c r="C206" s="15">
+      <c r="C206" s="12">
         <v>0.70833333333333337</v>
       </c>
       <c r="D206" s="8" t="s">
@@ -7973,7 +7976,7 @@
       <c r="B207" s="8">
         <v>44529</v>
       </c>
-      <c r="C207" s="15">
+      <c r="C207" s="12">
         <v>0.70833333333333337</v>
       </c>
       <c r="D207" s="8" t="s">
@@ -8009,7 +8012,7 @@
       <c r="B208" s="8">
         <v>44536</v>
       </c>
-      <c r="C208" s="15">
+      <c r="C208" s="12">
         <v>0.70833333333333337</v>
       </c>
       <c r="D208" s="8" t="s">
@@ -8045,7 +8048,7 @@
       <c r="B209" s="8">
         <v>44543</v>
       </c>
-      <c r="C209" s="15">
+      <c r="C209" s="12">
         <v>0.70833333333333337</v>
       </c>
       <c r="D209" s="8" t="s">
@@ -8081,7 +8084,7 @@
       <c r="B210" s="8">
         <v>44550</v>
       </c>
-      <c r="C210" s="15">
+      <c r="C210" s="12">
         <v>0.70833333333333337</v>
       </c>
       <c r="D210" s="8" t="s">
@@ -8117,7 +8120,7 @@
       <c r="B211" s="8">
         <v>44557</v>
       </c>
-      <c r="C211" s="15">
+      <c r="C211" s="12">
         <v>0.70833333333333337</v>
       </c>
       <c r="D211" s="8" t="s">
@@ -8153,7 +8156,7 @@
       <c r="B212" s="8">
         <v>44564</v>
       </c>
-      <c r="C212" s="15">
+      <c r="C212" s="12">
         <v>0.70833333333333337</v>
       </c>
       <c r="D212" s="8" t="s">
@@ -8189,7 +8192,7 @@
       <c r="B213" s="8">
         <v>44571</v>
       </c>
-      <c r="C213" s="15">
+      <c r="C213" s="12">
         <v>0.70833333333333337</v>
       </c>
       <c r="D213" s="8" t="s">
@@ -8225,7 +8228,7 @@
       <c r="B214" s="8">
         <v>44578</v>
       </c>
-      <c r="C214" s="15">
+      <c r="C214" s="12">
         <v>0.70833333333333337</v>
       </c>
       <c r="D214" s="8" t="s">
@@ -8261,7 +8264,7 @@
       <c r="B215" s="8">
         <v>44585</v>
       </c>
-      <c r="C215" s="15">
+      <c r="C215" s="12">
         <v>0.70833333333333337</v>
       </c>
       <c r="D215" s="8" t="s">
@@ -8297,7 +8300,7 @@
       <c r="B216" s="8">
         <v>44592</v>
       </c>
-      <c r="C216" s="15">
+      <c r="C216" s="12">
         <v>0.70833333333333337</v>
       </c>
       <c r="D216" s="8" t="s">
@@ -8333,7 +8336,7 @@
       <c r="B217" s="8">
         <v>44599</v>
       </c>
-      <c r="C217" s="15">
+      <c r="C217" s="12">
         <v>0.70833333333333337</v>
       </c>
       <c r="D217" s="8" t="s">
@@ -8369,7 +8372,7 @@
       <c r="B218" s="8">
         <v>44606</v>
       </c>
-      <c r="C218" s="15">
+      <c r="C218" s="12">
         <v>0.70833333333333337</v>
       </c>
       <c r="D218" s="8" t="s">
@@ -8405,7 +8408,7 @@
       <c r="B219" s="8">
         <v>44613</v>
       </c>
-      <c r="C219" s="15">
+      <c r="C219" s="12">
         <v>0.70833333333333337</v>
       </c>
       <c r="D219" s="8" t="s">
@@ -8441,7 +8444,7 @@
       <c r="B220" s="8">
         <v>44620</v>
       </c>
-      <c r="C220" s="15">
+      <c r="C220" s="12">
         <v>0.70833333333333337</v>
       </c>
       <c r="D220" s="8" t="s">
@@ -8477,7 +8480,7 @@
       <c r="B221" s="8">
         <v>44627</v>
       </c>
-      <c r="C221" s="15">
+      <c r="C221" s="12">
         <v>0.70833333333333337</v>
       </c>
       <c r="D221" s="8" t="s">
@@ -8513,7 +8516,7 @@
       <c r="B222" s="8">
         <v>44634</v>
       </c>
-      <c r="C222" s="15">
+      <c r="C222" s="12">
         <v>0.70833333333333337</v>
       </c>
       <c r="D222" s="8" t="s">
@@ -8549,7 +8552,7 @@
       <c r="B223" s="8">
         <v>44641</v>
       </c>
-      <c r="C223" s="15">
+      <c r="C223" s="12">
         <v>0.70833333333333337</v>
       </c>
       <c r="D223" s="8" t="s">
@@ -8585,7 +8588,7 @@
       <c r="B224" s="8">
         <v>44648</v>
       </c>
-      <c r="C224" s="15">
+      <c r="C224" s="12">
         <v>0.70833333333333337</v>
       </c>
       <c r="D224" s="8" t="s">
@@ -8621,7 +8624,7 @@
       <c r="B225" s="8">
         <v>44655</v>
       </c>
-      <c r="C225" s="15">
+      <c r="C225" s="12">
         <v>0.70833333333333337</v>
       </c>
       <c r="D225" s="8" t="s">
@@ -8657,7 +8660,7 @@
       <c r="B226" s="8">
         <v>44662</v>
       </c>
-      <c r="C226" s="15">
+      <c r="C226" s="12">
         <v>0.70833333333333337</v>
       </c>
       <c r="D226" s="8" t="s">
@@ -8693,7 +8696,7 @@
       <c r="B227" s="8">
         <v>44669</v>
       </c>
-      <c r="C227" s="15">
+      <c r="C227" s="12">
         <v>0.70833333333333337</v>
       </c>
       <c r="D227" s="8" t="s">
@@ -8729,7 +8732,7 @@
       <c r="B228" s="8">
         <v>44676</v>
       </c>
-      <c r="C228" s="15">
+      <c r="C228" s="12">
         <v>0.70833333333333337</v>
       </c>
       <c r="D228" s="8" t="s">
@@ -8765,7 +8768,7 @@
       <c r="B229" s="8">
         <v>44683</v>
       </c>
-      <c r="C229" s="15">
+      <c r="C229" s="12">
         <v>0.70833333333333337</v>
       </c>
       <c r="D229" s="8" t="s">
@@ -8801,7 +8804,7 @@
       <c r="B230" s="8">
         <v>44690</v>
       </c>
-      <c r="C230" s="15">
+      <c r="C230" s="12">
         <v>0.70833333333333337</v>
       </c>
       <c r="D230" s="8" t="s">
@@ -8837,7 +8840,7 @@
       <c r="B231" s="8">
         <v>44697</v>
       </c>
-      <c r="C231" s="15">
+      <c r="C231" s="12">
         <v>0.70833333333333337</v>
       </c>
       <c r="D231" s="8" t="s">
@@ -8873,7 +8876,7 @@
       <c r="B232" s="8">
         <v>44704</v>
       </c>
-      <c r="C232" s="15">
+      <c r="C232" s="12">
         <v>0.70833333333333337</v>
       </c>
       <c r="D232" s="8" t="s">
@@ -8909,7 +8912,7 @@
       <c r="B233" s="8">
         <v>44711</v>
       </c>
-      <c r="C233" s="15">
+      <c r="C233" s="12">
         <v>0.70833333333333337</v>
       </c>
       <c r="D233" s="8" t="s">
@@ -8945,7 +8948,7 @@
       <c r="B234" s="8">
         <v>44718</v>
       </c>
-      <c r="C234" s="15">
+      <c r="C234" s="12">
         <v>0.70833333333333337</v>
       </c>
       <c r="D234" s="8" t="s">
@@ -8981,7 +8984,7 @@
       <c r="B235" s="8">
         <v>44725</v>
       </c>
-      <c r="C235" s="15">
+      <c r="C235" s="12">
         <v>0.70833333333333337</v>
       </c>
       <c r="D235" s="8" t="s">
@@ -9017,7 +9020,7 @@
       <c r="B236" s="8">
         <v>44732</v>
       </c>
-      <c r="C236" s="15">
+      <c r="C236" s="12">
         <v>0.70833333333333337</v>
       </c>
       <c r="D236" s="8" t="s">
@@ -9053,7 +9056,7 @@
       <c r="B237" s="8">
         <v>44739</v>
       </c>
-      <c r="C237" s="15">
+      <c r="C237" s="12">
         <v>0.70833333333333337</v>
       </c>
       <c r="D237" s="8" t="s">
@@ -9089,7 +9092,7 @@
       <c r="B238" s="8">
         <v>44746</v>
       </c>
-      <c r="C238" s="15">
+      <c r="C238" s="12">
         <v>0.70833333333333337</v>
       </c>
       <c r="D238" s="8" t="s">
@@ -9125,7 +9128,7 @@
       <c r="B239" s="8">
         <v>44753</v>
       </c>
-      <c r="C239" s="15">
+      <c r="C239" s="12">
         <v>0.70833333333333337</v>
       </c>
       <c r="D239" s="8" t="s">
@@ -9161,7 +9164,7 @@
       <c r="B240" s="8">
         <v>44760</v>
       </c>
-      <c r="C240" s="15">
+      <c r="C240" s="12">
         <v>0.70833333333333337</v>
       </c>
       <c r="D240" s="8" t="s">
@@ -9197,7 +9200,7 @@
       <c r="B241" s="8">
         <v>44767</v>
       </c>
-      <c r="C241" s="15">
+      <c r="C241" s="12">
         <v>0.70833333333333337</v>
       </c>
       <c r="D241" s="8" t="s">
@@ -9233,7 +9236,7 @@
       <c r="B242" s="8">
         <v>44774</v>
       </c>
-      <c r="C242" s="15">
+      <c r="C242" s="12">
         <v>0.70833333333333337</v>
       </c>
       <c r="D242" s="8" t="s">
@@ -9269,7 +9272,7 @@
       <c r="B243" s="8">
         <v>44781</v>
       </c>
-      <c r="C243" s="15">
+      <c r="C243" s="12">
         <v>0.70833333333333337</v>
       </c>
       <c r="D243" s="8" t="s">
@@ -9305,7 +9308,7 @@
       <c r="B244" s="8">
         <v>44788</v>
       </c>
-      <c r="C244" s="15">
+      <c r="C244" s="12">
         <v>0.70833333333333337</v>
       </c>
       <c r="D244" s="8" t="s">
@@ -9341,7 +9344,7 @@
       <c r="B245" s="8">
         <v>44795</v>
       </c>
-      <c r="C245" s="15">
+      <c r="C245" s="12">
         <v>0.70833333333333337</v>
       </c>
       <c r="D245" s="8" t="s">
@@ -9377,7 +9380,7 @@
       <c r="B246" s="8">
         <v>44802</v>
       </c>
-      <c r="C246" s="15">
+      <c r="C246" s="12">
         <v>0.70833333333333337</v>
       </c>
       <c r="D246" s="8" t="s">
@@ -9413,7 +9416,7 @@
       <c r="B247" s="8">
         <v>44809</v>
       </c>
-      <c r="C247" s="15">
+      <c r="C247" s="12">
         <v>0.70833333333333337</v>
       </c>
       <c r="D247" s="8" t="s">
@@ -9449,7 +9452,7 @@
       <c r="B248" s="8">
         <v>44816</v>
       </c>
-      <c r="C248" s="15">
+      <c r="C248" s="12">
         <v>0.70833333333333337</v>
       </c>
       <c r="D248" s="8" t="s">
@@ -9485,7 +9488,7 @@
       <c r="B249" s="8">
         <v>44823</v>
       </c>
-      <c r="C249" s="15">
+      <c r="C249" s="12">
         <v>0.70833333333333337</v>
       </c>
       <c r="D249" s="8" t="s">
@@ -9521,7 +9524,7 @@
       <c r="B250" s="8">
         <v>44830</v>
       </c>
-      <c r="C250" s="15">
+      <c r="C250" s="12">
         <v>0.70833333333333337</v>
       </c>
       <c r="D250" s="8" t="s">
@@ -9557,7 +9560,7 @@
       <c r="B251" s="8">
         <v>44837</v>
       </c>
-      <c r="C251" s="15">
+      <c r="C251" s="12">
         <v>0.70833333333333337</v>
       </c>
       <c r="D251" s="8" t="s">
@@ -9593,7 +9596,7 @@
       <c r="B252" s="8">
         <v>44844</v>
       </c>
-      <c r="C252" s="15">
+      <c r="C252" s="12">
         <v>0.70833333333333337</v>
       </c>
       <c r="D252" s="8" t="s">
@@ -9629,7 +9632,7 @@
       <c r="B253" s="8">
         <v>44851</v>
       </c>
-      <c r="C253" s="15">
+      <c r="C253" s="12">
         <v>0.70833333333333337</v>
       </c>
       <c r="D253" s="8" t="s">
@@ -9665,7 +9668,7 @@
       <c r="B254" s="8">
         <v>44858</v>
       </c>
-      <c r="C254" s="15">
+      <c r="C254" s="12">
         <v>0.70833333333333337</v>
       </c>
       <c r="D254" s="8" t="s">
@@ -9701,7 +9704,7 @@
       <c r="B255" s="8">
         <v>44865</v>
       </c>
-      <c r="C255" s="15">
+      <c r="C255" s="12">
         <v>0.70833333333333337</v>
       </c>
       <c r="D255" s="8" t="s">
@@ -9737,7 +9740,7 @@
       <c r="B256" s="8">
         <v>44872</v>
       </c>
-      <c r="C256" s="15">
+      <c r="C256" s="12">
         <v>0.70833333333333337</v>
       </c>
       <c r="D256" s="8" t="s">
@@ -9773,7 +9776,7 @@
       <c r="B257" s="8">
         <v>44879</v>
       </c>
-      <c r="C257" s="15">
+      <c r="C257" s="12">
         <v>0.70833333333333337</v>
       </c>
       <c r="D257" s="8" t="s">
@@ -9809,7 +9812,7 @@
       <c r="B258" s="8">
         <v>44886</v>
       </c>
-      <c r="C258" s="15">
+      <c r="C258" s="12">
         <v>0.70833333333333337</v>
       </c>
       <c r="D258" s="8" t="s">
@@ -9845,7 +9848,7 @@
       <c r="B259" s="8">
         <v>44893</v>
       </c>
-      <c r="C259" s="15">
+      <c r="C259" s="12">
         <v>0.70833333333333337</v>
       </c>
       <c r="D259" s="8" t="s">
@@ -9881,7 +9884,7 @@
       <c r="B260" s="8">
         <v>44900</v>
       </c>
-      <c r="C260" s="15">
+      <c r="C260" s="12">
         <v>0.70833333333333337</v>
       </c>
       <c r="D260" s="8" t="s">
@@ -9917,7 +9920,7 @@
       <c r="B261" s="8">
         <v>44907</v>
       </c>
-      <c r="C261" s="15">
+      <c r="C261" s="12">
         <v>0.70833333333333337</v>
       </c>
       <c r="D261" s="8" t="s">
@@ -9953,7 +9956,7 @@
       <c r="B262" s="8">
         <v>44914</v>
       </c>
-      <c r="C262" s="15">
+      <c r="C262" s="12">
         <v>0.70833333333333337</v>
       </c>
       <c r="D262" s="8" t="s">
@@ -9989,7 +9992,7 @@
       <c r="B263" s="8">
         <v>44921</v>
       </c>
-      <c r="C263" s="15">
+      <c r="C263" s="12">
         <v>0.70833333333333337</v>
       </c>
       <c r="D263" s="8" t="s">
@@ -10025,7 +10028,7 @@
       <c r="B264" s="8">
         <v>44928</v>
       </c>
-      <c r="C264" s="15">
+      <c r="C264" s="12">
         <v>0.70833333333333337</v>
       </c>
       <c r="D264" s="8" t="s">
@@ -10061,7 +10064,7 @@
       <c r="B265" s="8">
         <v>44935</v>
       </c>
-      <c r="C265" s="15">
+      <c r="C265" s="12">
         <v>0.70833333333333337</v>
       </c>
       <c r="D265" s="8" t="s">
@@ -10097,7 +10100,7 @@
       <c r="B266" s="8">
         <v>44942</v>
       </c>
-      <c r="C266" s="15">
+      <c r="C266" s="12">
         <v>0.70833333333333337</v>
       </c>
       <c r="D266" s="8" t="s">
@@ -10133,7 +10136,7 @@
       <c r="B267" s="8">
         <v>44949</v>
       </c>
-      <c r="C267" s="15">
+      <c r="C267" s="12">
         <v>0.70833333333333337</v>
       </c>
       <c r="D267" s="8" t="s">
@@ -10169,7 +10172,7 @@
       <c r="B268" s="8">
         <v>44956</v>
       </c>
-      <c r="C268" s="15">
+      <c r="C268" s="12">
         <v>0.70833333333333337</v>
       </c>
       <c r="D268" s="8" t="s">
@@ -10205,7 +10208,7 @@
       <c r="B269" s="8">
         <v>44963</v>
       </c>
-      <c r="C269" s="15">
+      <c r="C269" s="12">
         <v>0.70833333333333337</v>
       </c>
       <c r="D269" s="8" t="s">
@@ -10241,7 +10244,7 @@
       <c r="B270" s="8">
         <v>44970</v>
       </c>
-      <c r="C270" s="15">
+      <c r="C270" s="12">
         <v>0.70833333333333337</v>
       </c>
       <c r="D270" s="8" t="s">
@@ -10277,7 +10280,7 @@
       <c r="B271" s="8">
         <v>44977</v>
       </c>
-      <c r="C271" s="15">
+      <c r="C271" s="12">
         <v>0.70833333333333337</v>
       </c>
       <c r="D271" s="8" t="s">
@@ -10313,7 +10316,7 @@
       <c r="B272" s="8">
         <v>44984</v>
       </c>
-      <c r="C272" s="15">
+      <c r="C272" s="12">
         <v>0.70833333333333337</v>
       </c>
       <c r="D272" s="8" t="s">
@@ -10349,7 +10352,7 @@
       <c r="B273" s="8">
         <v>44991</v>
       </c>
-      <c r="C273" s="15">
+      <c r="C273" s="12">
         <v>0.70833333333333337</v>
       </c>
       <c r="D273" s="8" t="s">
@@ -10385,7 +10388,7 @@
       <c r="B274" s="8">
         <v>44998</v>
       </c>
-      <c r="C274" s="15">
+      <c r="C274" s="12">
         <v>0.70833333333333337</v>
       </c>
       <c r="D274" s="8" t="s">
@@ -10421,7 +10424,7 @@
       <c r="B275" s="8">
         <v>45005</v>
       </c>
-      <c r="C275" s="15">
+      <c r="C275" s="12">
         <v>0.70833333333333337</v>
       </c>
       <c r="D275" s="8" t="s">
@@ -10457,7 +10460,7 @@
       <c r="B276" s="8">
         <v>45012</v>
       </c>
-      <c r="C276" s="15">
+      <c r="C276" s="12">
         <v>0.70833333333333337</v>
       </c>
       <c r="D276" s="8" t="s">
@@ -10493,7 +10496,7 @@
       <c r="B277" s="8">
         <v>45019</v>
       </c>
-      <c r="C277" s="15">
+      <c r="C277" s="12">
         <v>0.70833333333333337</v>
       </c>
       <c r="D277" s="8" t="s">
@@ -10529,7 +10532,7 @@
       <c r="B278" s="8">
         <v>45026</v>
       </c>
-      <c r="C278" s="15">
+      <c r="C278" s="12">
         <v>0.70833333333333337</v>
       </c>
       <c r="D278" s="8" t="s">
@@ -10565,7 +10568,7 @@
       <c r="B279" s="8">
         <v>45033</v>
       </c>
-      <c r="C279" s="15">
+      <c r="C279" s="12">
         <v>0.70833333333333337</v>
       </c>
       <c r="D279" s="8" t="s">
@@ -10601,7 +10604,7 @@
       <c r="B280" s="8">
         <v>45040</v>
       </c>
-      <c r="C280" s="15">
+      <c r="C280" s="12">
         <v>0.70833333333333337</v>
       </c>
       <c r="D280" s="8" t="s">
@@ -10637,7 +10640,7 @@
       <c r="B281" s="8">
         <v>45047</v>
       </c>
-      <c r="C281" s="15">
+      <c r="C281" s="12">
         <v>0.70833333333333337</v>
       </c>
       <c r="D281" s="8" t="s">
@@ -10673,7 +10676,7 @@
       <c r="B282" s="8">
         <v>45054</v>
       </c>
-      <c r="C282" s="15">
+      <c r="C282" s="12">
         <v>0.70833333333333337</v>
       </c>
       <c r="D282" s="8" t="s">
@@ -10709,7 +10712,7 @@
       <c r="B283" s="8">
         <v>45061</v>
       </c>
-      <c r="C283" s="15">
+      <c r="C283" s="12">
         <v>0.70833333333333337</v>
       </c>
       <c r="D283" s="8" t="s">
@@ -10745,7 +10748,7 @@
       <c r="B284" s="8">
         <v>45068</v>
       </c>
-      <c r="C284" s="15">
+      <c r="C284" s="12">
         <v>0.70833333333333337</v>
       </c>
       <c r="D284" s="8" t="s">
@@ -10781,7 +10784,7 @@
       <c r="B285" s="8">
         <v>45075</v>
       </c>
-      <c r="C285" s="15">
+      <c r="C285" s="12">
         <v>0.70833333333333337</v>
       </c>
       <c r="D285" s="8" t="s">
@@ -10817,7 +10820,7 @@
       <c r="B286" s="8">
         <v>45082</v>
       </c>
-      <c r="C286" s="15">
+      <c r="C286" s="12">
         <v>0.70833333333333337</v>
       </c>
       <c r="D286" s="8" t="s">
@@ -10853,7 +10856,7 @@
       <c r="B287" s="8">
         <v>45089</v>
       </c>
-      <c r="C287" s="15">
+      <c r="C287" s="12">
         <v>0.70833333333333337</v>
       </c>
       <c r="D287" s="8" t="s">
@@ -10889,7 +10892,7 @@
       <c r="B288" s="8">
         <v>45096</v>
       </c>
-      <c r="C288" s="15">
+      <c r="C288" s="12">
         <v>0.70833333333333337</v>
       </c>
       <c r="D288" s="8" t="s">
@@ -10925,7 +10928,7 @@
       <c r="B289" s="8">
         <v>45103</v>
       </c>
-      <c r="C289" s="15">
+      <c r="C289" s="12">
         <v>0.70833333333333337</v>
       </c>
       <c r="D289" s="8" t="s">
@@ -10961,7 +10964,7 @@
       <c r="B290" s="8">
         <v>45110</v>
       </c>
-      <c r="C290" s="15">
+      <c r="C290" s="12">
         <v>0.70833333333333337</v>
       </c>
       <c r="D290" s="8" t="s">
@@ -10997,7 +11000,7 @@
       <c r="B291" s="8">
         <v>45117</v>
       </c>
-      <c r="C291" s="15">
+      <c r="C291" s="12">
         <v>0.70833333333333337</v>
       </c>
       <c r="D291" s="8" t="s">
@@ -11033,7 +11036,7 @@
       <c r="B292" s="8">
         <v>45124</v>
       </c>
-      <c r="C292" s="15">
+      <c r="C292" s="12">
         <v>0.70833333333333337</v>
       </c>
       <c r="D292" s="8" t="s">
@@ -11069,7 +11072,7 @@
       <c r="B293" s="8">
         <v>45131</v>
       </c>
-      <c r="C293" s="15">
+      <c r="C293" s="12">
         <v>0.70833333333333337</v>
       </c>
       <c r="D293" s="8" t="s">
@@ -11105,7 +11108,7 @@
       <c r="B294" s="8">
         <v>45138</v>
       </c>
-      <c r="C294" s="15">
+      <c r="C294" s="12">
         <v>0.70833333333333337</v>
       </c>
       <c r="D294" s="8" t="s">
@@ -11141,7 +11144,7 @@
       <c r="B295" s="8">
         <v>45145</v>
       </c>
-      <c r="C295" s="15">
+      <c r="C295" s="12">
         <v>0.70833333333333337</v>
       </c>
       <c r="D295" s="8" t="s">
@@ -11177,7 +11180,7 @@
       <c r="B296" s="8">
         <v>45152</v>
       </c>
-      <c r="C296" s="15">
+      <c r="C296" s="12">
         <v>0.70833333333333337</v>
       </c>
       <c r="D296" s="8" t="s">
@@ -11213,7 +11216,7 @@
       <c r="B297" s="8">
         <v>45159</v>
       </c>
-      <c r="C297" s="15">
+      <c r="C297" s="12">
         <v>0.70833333333333337</v>
       </c>
       <c r="D297" s="8" t="s">
@@ -11249,7 +11252,7 @@
       <c r="B298" s="8">
         <v>45166</v>
       </c>
-      <c r="C298" s="15">
+      <c r="C298" s="12">
         <v>0.70833333333333337</v>
       </c>
       <c r="D298" s="8" t="s">
@@ -11285,7 +11288,7 @@
       <c r="B299" s="8">
         <v>45173</v>
       </c>
-      <c r="C299" s="15">
+      <c r="C299" s="12">
         <v>0.70833333333333337</v>
       </c>
       <c r="D299" s="8" t="s">
@@ -11321,7 +11324,7 @@
       <c r="B300" s="8">
         <v>45180</v>
       </c>
-      <c r="C300" s="15">
+      <c r="C300" s="12">
         <v>0.70833333333333337</v>
       </c>
       <c r="D300" s="8" t="s">
@@ -11357,7 +11360,7 @@
       <c r="B301" s="8">
         <v>45187</v>
       </c>
-      <c r="C301" s="15">
+      <c r="C301" s="12">
         <v>0.70833333333333337</v>
       </c>
       <c r="D301" s="8" t="s">
@@ -11393,7 +11396,7 @@
       <c r="B302" s="8">
         <v>45194</v>
       </c>
-      <c r="C302" s="15">
+      <c r="C302" s="12">
         <v>0.70833333333333337</v>
       </c>
       <c r="D302" s="8" t="s">
@@ -11429,7 +11432,7 @@
       <c r="B303" s="8">
         <v>45201</v>
       </c>
-      <c r="C303" s="15">
+      <c r="C303" s="12">
         <v>0.70833333333333337</v>
       </c>
       <c r="D303" s="8" t="s">
@@ -11465,7 +11468,7 @@
       <c r="B304" s="8">
         <v>45208</v>
       </c>
-      <c r="C304" s="15">
+      <c r="C304" s="12">
         <v>0.70833333333333337</v>
       </c>
       <c r="D304" s="8" t="s">
@@ -11501,7 +11504,7 @@
       <c r="B305" s="8">
         <v>45215</v>
       </c>
-      <c r="C305" s="15">
+      <c r="C305" s="12">
         <v>0.70833333333333337</v>
       </c>
       <c r="D305" s="8" t="s">
@@ -11537,7 +11540,7 @@
       <c r="B306" s="8">
         <v>45222</v>
       </c>
-      <c r="C306" s="15">
+      <c r="C306" s="12">
         <v>0.70833333333333337</v>
       </c>
       <c r="D306" s="8" t="s">
@@ -11573,7 +11576,7 @@
       <c r="B307" s="8">
         <v>45229</v>
       </c>
-      <c r="C307" s="15">
+      <c r="C307" s="12">
         <v>0.70833333333333337</v>
       </c>
       <c r="D307" s="8" t="s">
@@ -11609,7 +11612,7 @@
       <c r="B308" s="8">
         <v>45236</v>
       </c>
-      <c r="C308" s="15">
+      <c r="C308" s="12">
         <v>0.70833333333333337</v>
       </c>
       <c r="D308" s="8" t="s">
@@ -11645,7 +11648,7 @@
       <c r="B309" s="8">
         <v>45243</v>
       </c>
-      <c r="C309" s="15">
+      <c r="C309" s="12">
         <v>0.70833333333333337</v>
       </c>
       <c r="D309" s="8" t="s">
@@ -11681,7 +11684,7 @@
       <c r="B310" s="8">
         <v>45250</v>
       </c>
-      <c r="C310" s="15">
+      <c r="C310" s="12">
         <v>0.70833333333333337</v>
       </c>
       <c r="D310" s="8" t="s">
@@ -11717,7 +11720,7 @@
       <c r="B311" s="8">
         <v>45257</v>
       </c>
-      <c r="C311" s="15">
+      <c r="C311" s="12">
         <v>0.70833333333333337</v>
       </c>
       <c r="D311" s="8" t="s">
@@ -11753,7 +11756,7 @@
       <c r="B312" s="8">
         <v>45264</v>
       </c>
-      <c r="C312" s="15">
+      <c r="C312" s="12">
         <v>0.70833333333333337</v>
       </c>
       <c r="D312" s="8" t="s">
@@ -11789,7 +11792,7 @@
       <c r="B313" s="8">
         <v>45271</v>
       </c>
-      <c r="C313" s="15">
+      <c r="C313" s="12">
         <v>0.70833333333333337</v>
       </c>
       <c r="D313" s="8" t="s">
@@ -11825,7 +11828,7 @@
       <c r="B314" s="8">
         <v>45278</v>
       </c>
-      <c r="C314" s="15">
+      <c r="C314" s="12">
         <v>0.70833333333333337</v>
       </c>
       <c r="D314" s="8" t="s">
@@ -11861,7 +11864,7 @@
       <c r="B315" s="8">
         <v>45285</v>
       </c>
-      <c r="C315" s="15">
+      <c r="C315" s="12">
         <v>0.70833333333333337</v>
       </c>
       <c r="D315" s="8" t="s">
@@ -11897,7 +11900,7 @@
       <c r="B316" s="8">
         <v>45292</v>
       </c>
-      <c r="C316" s="15">
+      <c r="C316" s="12">
         <v>0.70833333333333337</v>
       </c>
       <c r="D316" s="8" t="s">
@@ -11933,7 +11936,7 @@
       <c r="B317" s="8">
         <v>45299</v>
       </c>
-      <c r="C317" s="15">
+      <c r="C317" s="12">
         <v>0.70833333333333337</v>
       </c>
       <c r="D317" s="8" t="s">
@@ -11969,7 +11972,7 @@
       <c r="B318" s="8">
         <v>45306</v>
       </c>
-      <c r="C318" s="15">
+      <c r="C318" s="12">
         <v>0.70833333333333337</v>
       </c>
       <c r="D318" s="8" t="s">
@@ -12005,7 +12008,7 @@
       <c r="B319" s="8">
         <v>45313</v>
       </c>
-      <c r="C319" s="15">
+      <c r="C319" s="12">
         <v>0.70833333333333337</v>
       </c>
       <c r="D319" s="8" t="s">
@@ -12041,7 +12044,7 @@
       <c r="B320" s="8">
         <v>45320</v>
       </c>
-      <c r="C320" s="15">
+      <c r="C320" s="12">
         <v>0.70833333333333337</v>
       </c>
       <c r="D320" s="8" t="s">
@@ -12077,7 +12080,7 @@
       <c r="B321" s="8">
         <v>45327</v>
       </c>
-      <c r="C321" s="15">
+      <c r="C321" s="12">
         <v>0.70833333333333337</v>
       </c>
       <c r="D321" s="8" t="s">
@@ -12113,7 +12116,7 @@
       <c r="B322" s="8">
         <v>45334</v>
       </c>
-      <c r="C322" s="15">
+      <c r="C322" s="12">
         <v>0.70833333333333337</v>
       </c>
       <c r="D322" s="8" t="s">
@@ -12149,7 +12152,7 @@
       <c r="B323" s="8">
         <v>45341</v>
       </c>
-      <c r="C323" s="15">
+      <c r="C323" s="12">
         <v>0.70833333333333337</v>
       </c>
       <c r="D323" s="8" t="s">
@@ -12185,7 +12188,7 @@
       <c r="B324" s="8">
         <v>45348</v>
       </c>
-      <c r="C324" s="15">
+      <c r="C324" s="12">
         <v>0.70833333333333337</v>
       </c>
       <c r="D324" s="8" t="s">
@@ -12221,7 +12224,7 @@
       <c r="B325" s="8">
         <v>45355</v>
       </c>
-      <c r="C325" s="15">
+      <c r="C325" s="12">
         <v>0.70833333333333337</v>
       </c>
       <c r="D325" s="8" t="s">
@@ -12257,7 +12260,7 @@
       <c r="B326" s="8">
         <v>45362</v>
       </c>
-      <c r="C326" s="15">
+      <c r="C326" s="12">
         <v>0.70833333333333337</v>
       </c>
       <c r="D326" s="8" t="s">
@@ -12293,7 +12296,7 @@
       <c r="B327" s="8">
         <v>45369</v>
       </c>
-      <c r="C327" s="15">
+      <c r="C327" s="12">
         <v>0.70833333333333337</v>
       </c>
       <c r="D327" s="8" t="s">
@@ -12329,7 +12332,7 @@
       <c r="B328" s="8">
         <v>45376</v>
       </c>
-      <c r="C328" s="15">
+      <c r="C328" s="12">
         <v>0.70833333333333337</v>
       </c>
       <c r="D328" s="8" t="s">
@@ -12365,7 +12368,7 @@
       <c r="B329" s="8">
         <v>45383</v>
       </c>
-      <c r="C329" s="15">
+      <c r="C329" s="12">
         <v>0.70833333333333337</v>
       </c>
       <c r="D329" s="8" t="s">
@@ -12401,7 +12404,7 @@
       <c r="B330" s="8">
         <v>45390</v>
       </c>
-      <c r="C330" s="15">
+      <c r="C330" s="12">
         <v>0.70833333333333337</v>
       </c>
       <c r="D330" s="8" t="s">
@@ -12437,7 +12440,7 @@
       <c r="B331" s="8">
         <v>45397</v>
       </c>
-      <c r="C331" s="15">
+      <c r="C331" s="12">
         <v>0.70833333333333337</v>
       </c>
       <c r="D331" s="8" t="s">
@@ -12473,7 +12476,7 @@
       <c r="B332" s="8">
         <v>45404</v>
       </c>
-      <c r="C332" s="15">
+      <c r="C332" s="12">
         <v>0.70833333333333337</v>
       </c>
       <c r="D332" s="8" t="s">
@@ -12509,7 +12512,7 @@
       <c r="B333" s="8">
         <v>45411</v>
       </c>
-      <c r="C333" s="15">
+      <c r="C333" s="12">
         <v>0.70833333333333337</v>
       </c>
       <c r="D333" s="8" t="s">
@@ -12545,7 +12548,7 @@
       <c r="B334" s="8">
         <v>45418</v>
       </c>
-      <c r="C334" s="15">
+      <c r="C334" s="12">
         <v>0.70833333333333337</v>
       </c>
       <c r="D334" s="8" t="s">
@@ -12581,7 +12584,7 @@
       <c r="B335" s="8">
         <v>45425</v>
       </c>
-      <c r="C335" s="15">
+      <c r="C335" s="12">
         <v>0.70833333333333337</v>
       </c>
       <c r="D335" s="8" t="s">
@@ -12617,7 +12620,7 @@
       <c r="B336" s="8">
         <v>45432</v>
       </c>
-      <c r="C336" s="15">
+      <c r="C336" s="12">
         <v>0.70833333333333337</v>
       </c>
       <c r="D336" s="8" t="s">
@@ -12653,7 +12656,7 @@
       <c r="B337" s="8">
         <v>45439</v>
       </c>
-      <c r="C337" s="15">
+      <c r="C337" s="12">
         <v>0.70833333333333337</v>
       </c>
       <c r="D337" s="8" t="s">
@@ -12689,7 +12692,7 @@
       <c r="B338" s="8">
         <v>45446</v>
       </c>
-      <c r="C338" s="15">
+      <c r="C338" s="12">
         <v>0.70833333333333337</v>
       </c>
       <c r="D338" s="8" t="s">
@@ -12725,7 +12728,7 @@
       <c r="B339" s="8">
         <v>45453</v>
       </c>
-      <c r="C339" s="15">
+      <c r="C339" s="12">
         <v>0.70833333333333337</v>
       </c>
       <c r="D339" s="8" t="s">
@@ -12761,7 +12764,7 @@
       <c r="B340" s="8">
         <v>45460</v>
       </c>
-      <c r="C340" s="15">
+      <c r="C340" s="12">
         <v>0.70833333333333337</v>
       </c>
       <c r="D340" s="8" t="s">
@@ -12797,7 +12800,7 @@
       <c r="B341" s="8">
         <v>45467</v>
       </c>
-      <c r="C341" s="15">
+      <c r="C341" s="12">
         <v>0.70833333333333337</v>
       </c>
       <c r="D341" s="8" t="s">
@@ -12833,7 +12836,7 @@
       <c r="B342" s="8">
         <v>45474</v>
       </c>
-      <c r="C342" s="15">
+      <c r="C342" s="12">
         <v>0.70833333333333337</v>
       </c>
       <c r="D342" s="8" t="s">
@@ -12869,7 +12872,7 @@
       <c r="B343" s="8">
         <v>45481</v>
       </c>
-      <c r="C343" s="15">
+      <c r="C343" s="12">
         <v>0.70833333333333337</v>
       </c>
       <c r="D343" s="8" t="s">
@@ -12905,7 +12908,7 @@
       <c r="B344" s="8">
         <v>45488</v>
       </c>
-      <c r="C344" s="15">
+      <c r="C344" s="12">
         <v>0.70833333333333337</v>
       </c>
       <c r="D344" s="8" t="s">
@@ -12941,7 +12944,7 @@
       <c r="B345" s="8">
         <v>45495</v>
       </c>
-      <c r="C345" s="15">
+      <c r="C345" s="12">
         <v>0.70833333333333337</v>
       </c>
       <c r="D345" s="8" t="s">
@@ -12977,7 +12980,7 @@
       <c r="B346" s="8">
         <v>45502</v>
       </c>
-      <c r="C346" s="15">
+      <c r="C346" s="12">
         <v>0.70833333333333337</v>
       </c>
       <c r="D346" s="8" t="s">
@@ -13013,7 +13016,7 @@
       <c r="B347" s="8">
         <v>45509</v>
       </c>
-      <c r="C347" s="15">
+      <c r="C347" s="12">
         <v>0.70833333333333337</v>
       </c>
       <c r="D347" s="8" t="s">
@@ -13049,7 +13052,7 @@
       <c r="B348" s="8">
         <v>45516</v>
       </c>
-      <c r="C348" s="15">
+      <c r="C348" s="12">
         <v>0.70833333333333337</v>
       </c>
       <c r="D348" s="8" t="s">
@@ -13085,7 +13088,7 @@
       <c r="B349" s="8">
         <v>45523</v>
       </c>
-      <c r="C349" s="15">
+      <c r="C349" s="12">
         <v>0.70833333333333337</v>
       </c>
       <c r="D349" s="8" t="s">
@@ -13121,7 +13124,7 @@
       <c r="B350" s="8">
         <v>45530</v>
       </c>
-      <c r="C350" s="15">
+      <c r="C350" s="12">
         <v>0.70833333333333337</v>
       </c>
       <c r="D350" s="8" t="s">
@@ -13157,7 +13160,7 @@
       <c r="B351" s="8">
         <v>45537</v>
       </c>
-      <c r="C351" s="15">
+      <c r="C351" s="12">
         <v>0.70833333333333337</v>
       </c>
       <c r="D351" s="8" t="s">
@@ -13193,7 +13196,7 @@
       <c r="B352" s="8">
         <v>45544</v>
       </c>
-      <c r="C352" s="15">
+      <c r="C352" s="12">
         <v>0.70833333333333337</v>
       </c>
       <c r="D352" s="8" t="s">
@@ -13229,7 +13232,7 @@
       <c r="B353" s="8">
         <v>45551</v>
       </c>
-      <c r="C353" s="15">
+      <c r="C353" s="12">
         <v>0.70833333333333337</v>
       </c>
       <c r="D353" s="8" t="s">
@@ -13265,7 +13268,7 @@
       <c r="B354" s="8">
         <v>45558</v>
       </c>
-      <c r="C354" s="15">
+      <c r="C354" s="12">
         <v>0.70833333333333337</v>
       </c>
       <c r="D354" s="8" t="s">
@@ -13301,7 +13304,7 @@
       <c r="B355" s="8">
         <v>45565</v>
       </c>
-      <c r="C355" s="15">
+      <c r="C355" s="12">
         <v>0.70833333333333337</v>
       </c>
       <c r="D355" s="8" t="s">
@@ -13337,7 +13340,7 @@
       <c r="B356" s="8">
         <v>45572</v>
       </c>
-      <c r="C356" s="15">
+      <c r="C356" s="12">
         <v>0.70833333333333337</v>
       </c>
       <c r="D356" s="8" t="s">
@@ -13373,7 +13376,7 @@
       <c r="B357" s="8">
         <v>45579</v>
       </c>
-      <c r="C357" s="15">
+      <c r="C357" s="12">
         <v>0.70833333333333337</v>
       </c>
       <c r="D357" s="8" t="s">
@@ -13409,7 +13412,7 @@
       <c r="B358" s="8">
         <v>45586</v>
       </c>
-      <c r="C358" s="15">
+      <c r="C358" s="12">
         <v>0.70833333333333337</v>
       </c>
       <c r="D358" s="8" t="s">
@@ -13445,7 +13448,7 @@
       <c r="B359" s="8">
         <v>45593</v>
       </c>
-      <c r="C359" s="15">
+      <c r="C359" s="12">
         <v>0.70833333333333337</v>
       </c>
       <c r="D359" s="8" t="s">
@@ -13481,7 +13484,7 @@
       <c r="B360" s="8">
         <v>45600</v>
       </c>
-      <c r="C360" s="15">
+      <c r="C360" s="12">
         <v>0.70833333333333337</v>
       </c>
       <c r="D360" s="8" t="s">
@@ -13517,7 +13520,7 @@
       <c r="B361" s="8">
         <v>45607</v>
       </c>
-      <c r="C361" s="15">
+      <c r="C361" s="12">
         <v>0.70833333333333337</v>
       </c>
       <c r="D361" s="8" t="s">
@@ -13553,7 +13556,7 @@
       <c r="B362" s="8">
         <v>45614</v>
       </c>
-      <c r="C362" s="15">
+      <c r="C362" s="12">
         <v>0.70833333333333337</v>
       </c>
       <c r="D362" s="8" t="s">
@@ -13589,7 +13592,7 @@
       <c r="B363" s="8">
         <v>45621</v>
       </c>
-      <c r="C363" s="15">
+      <c r="C363" s="12">
         <v>0.70833333333333337</v>
       </c>
       <c r="D363" s="8" t="s">
@@ -13625,7 +13628,7 @@
       <c r="B364" s="8">
         <v>45628</v>
       </c>
-      <c r="C364" s="15">
+      <c r="C364" s="12">
         <v>0.70833333333333337</v>
       </c>
       <c r="D364" s="8" t="s">
@@ -13661,7 +13664,7 @@
       <c r="B365" s="8">
         <v>45635</v>
       </c>
-      <c r="C365" s="15">
+      <c r="C365" s="12">
         <v>0.70833333333333337</v>
       </c>
       <c r="D365" s="8" t="s">
@@ -13697,7 +13700,7 @@
       <c r="B366" s="8">
         <v>45642</v>
       </c>
-      <c r="C366" s="15">
+      <c r="C366" s="12">
         <v>0.70833333333333337</v>
       </c>
       <c r="D366" s="8" t="s">
@@ -13733,7 +13736,7 @@
       <c r="B367" s="8">
         <v>45649</v>
       </c>
-      <c r="C367" s="15">
+      <c r="C367" s="12">
         <v>0.70833333333333337</v>
       </c>
       <c r="D367" s="8" t="s">
@@ -13769,7 +13772,7 @@
       <c r="B368" s="8">
         <v>45656</v>
       </c>
-      <c r="C368" s="15">
+      <c r="C368" s="12">
         <v>0.70833333333333337</v>
       </c>
       <c r="D368" s="8" t="s">
@@ -13805,7 +13808,7 @@
       <c r="B369" s="8">
         <v>45663</v>
       </c>
-      <c r="C369" s="15">
+      <c r="C369" s="12">
         <v>0.70833333333333337</v>
       </c>
       <c r="D369" s="8" t="s">
@@ -13841,7 +13844,7 @@
       <c r="B370" s="8">
         <v>45670</v>
       </c>
-      <c r="C370" s="15">
+      <c r="C370" s="12">
         <v>0.70833333333333337</v>
       </c>
       <c r="D370" s="8" t="s">
@@ -13877,7 +13880,7 @@
       <c r="B371" s="8">
         <v>45677</v>
       </c>
-      <c r="C371" s="15">
+      <c r="C371" s="12">
         <v>0.70833333333333337</v>
       </c>
       <c r="D371" s="8" t="s">
@@ -13913,7 +13916,7 @@
       <c r="B372" s="8">
         <v>45684</v>
       </c>
-      <c r="C372" s="15">
+      <c r="C372" s="12">
         <v>0.70833333333333337</v>
       </c>
       <c r="D372" s="8" t="s">
@@ -13949,7 +13952,7 @@
       <c r="B373" s="8">
         <v>45691</v>
       </c>
-      <c r="C373" s="15">
+      <c r="C373" s="12">
         <v>0.70833333333333337</v>
       </c>
       <c r="D373" s="8" t="s">
@@ -13985,7 +13988,7 @@
       <c r="B374" s="8">
         <v>45698</v>
       </c>
-      <c r="C374" s="15">
+      <c r="C374" s="12">
         <v>0.70833333333333337</v>
       </c>
       <c r="D374" s="8" t="s">
@@ -14021,7 +14024,7 @@
       <c r="B375" s="8">
         <v>45705</v>
       </c>
-      <c r="C375" s="15">
+      <c r="C375" s="12">
         <v>0.70833333333333337</v>
       </c>
       <c r="D375" s="8" t="s">
@@ -14057,7 +14060,7 @@
       <c r="B376" s="8">
         <v>45712</v>
       </c>
-      <c r="C376" s="15">
+      <c r="C376" s="12">
         <v>0.70833333333333337</v>
       </c>
       <c r="D376" s="8" t="s">
@@ -14093,7 +14096,7 @@
       <c r="B377" s="8">
         <v>45719</v>
       </c>
-      <c r="C377" s="15">
+      <c r="C377" s="12">
         <v>0.70833333333333337</v>
       </c>
       <c r="D377" s="8" t="s">
@@ -14129,7 +14132,7 @@
       <c r="B378" s="8">
         <v>45726</v>
       </c>
-      <c r="C378" s="15">
+      <c r="C378" s="12">
         <v>0.70833333333333337</v>
       </c>
       <c r="D378" s="8" t="s">
@@ -14165,7 +14168,7 @@
       <c r="B379" s="8">
         <v>45733</v>
       </c>
-      <c r="C379" s="15">
+      <c r="C379" s="12">
         <v>0.70833333333333337</v>
       </c>
       <c r="D379" s="8" t="s">
@@ -14201,7 +14204,7 @@
       <c r="B380" s="8">
         <v>45740</v>
       </c>
-      <c r="C380" s="15">
+      <c r="C380" s="12">
         <v>0.70833333333333337</v>
       </c>
       <c r="D380" s="8" t="s">
@@ -14237,7 +14240,7 @@
       <c r="B381" s="8">
         <v>45747</v>
       </c>
-      <c r="C381" s="15">
+      <c r="C381" s="12">
         <v>0.70833333333333337</v>
       </c>
       <c r="D381" s="8" t="s">
@@ -14273,7 +14276,7 @@
       <c r="B382" s="8">
         <v>45754</v>
       </c>
-      <c r="C382" s="15">
+      <c r="C382" s="12">
         <v>0.70833333333333337</v>
       </c>
       <c r="D382" s="8" t="s">
@@ -14309,7 +14312,7 @@
       <c r="B383" s="8">
         <v>45761</v>
       </c>
-      <c r="C383" s="15">
+      <c r="C383" s="12">
         <v>0.70833333333333337</v>
       </c>
       <c r="D383" s="8" t="s">
@@ -14345,7 +14348,7 @@
       <c r="B384" s="8">
         <v>45768</v>
       </c>
-      <c r="C384" s="15">
+      <c r="C384" s="12">
         <v>0.70833333333333337</v>
       </c>
       <c r="D384" s="8" t="s">
@@ -14381,7 +14384,7 @@
       <c r="B385" s="8">
         <v>45775</v>
       </c>
-      <c r="C385" s="15">
+      <c r="C385" s="12">
         <v>0.70833333333333337</v>
       </c>
       <c r="D385" s="8" t="s">
@@ -14417,7 +14420,7 @@
       <c r="B386" s="8">
         <v>45782</v>
       </c>
-      <c r="C386" s="15">
+      <c r="C386" s="12">
         <v>0.70833333333333337</v>
       </c>
       <c r="D386" s="8" t="s">
@@ -14453,7 +14456,7 @@
       <c r="B387" s="8">
         <v>45789</v>
       </c>
-      <c r="C387" s="15">
+      <c r="C387" s="12">
         <v>0.70833333333333337</v>
       </c>
       <c r="D387" s="8" t="s">
@@ -14489,7 +14492,7 @@
       <c r="B388" s="8">
         <v>45796</v>
       </c>
-      <c r="C388" s="15">
+      <c r="C388" s="12">
         <v>0.70833333333333337</v>
       </c>
       <c r="D388" s="8" t="s">
@@ -14525,7 +14528,7 @@
       <c r="B389" s="8">
         <v>45803</v>
       </c>
-      <c r="C389" s="15">
+      <c r="C389" s="12">
         <v>0.70833333333333337</v>
       </c>
       <c r="D389" s="8" t="s">
@@ -14561,7 +14564,7 @@
       <c r="B390" s="8">
         <v>45810</v>
       </c>
-      <c r="C390" s="15">
+      <c r="C390" s="12">
         <v>0.70833333333333337</v>
       </c>
       <c r="D390" s="8" t="s">
@@ -14597,7 +14600,7 @@
       <c r="B391" s="8">
         <v>45817</v>
       </c>
-      <c r="C391" s="15">
+      <c r="C391" s="12">
         <v>0.70833333333333337</v>
       </c>
       <c r="D391" s="8" t="s">
@@ -14633,7 +14636,7 @@
       <c r="B392" s="8">
         <v>45824</v>
       </c>
-      <c r="C392" s="15">
+      <c r="C392" s="12">
         <v>0.70833333333333337</v>
       </c>
       <c r="D392" s="8" t="s">
@@ -14669,7 +14672,7 @@
       <c r="B393" s="8">
         <v>45831</v>
       </c>
-      <c r="C393" s="15">
+      <c r="C393" s="12">
         <v>0.70833333333333337</v>
       </c>
       <c r="D393" s="8" t="s">
@@ -14705,7 +14708,7 @@
       <c r="B394" s="8">
         <v>45838</v>
       </c>
-      <c r="C394" s="15">
+      <c r="C394" s="12">
         <v>0.70833333333333337</v>
       </c>
       <c r="D394" s="8" t="s">
@@ -14741,7 +14744,7 @@
       <c r="B395" s="8">
         <v>45845</v>
       </c>
-      <c r="C395" s="15">
+      <c r="C395" s="12">
         <v>0.70833333333333337</v>
       </c>
       <c r="D395" s="8" t="s">
@@ -14777,7 +14780,7 @@
       <c r="B396" s="8">
         <v>45852</v>
       </c>
-      <c r="C396" s="15">
+      <c r="C396" s="12">
         <v>0.70833333333333337</v>
       </c>
       <c r="D396" s="8" t="s">
@@ -14813,7 +14816,7 @@
       <c r="B397" s="8">
         <v>45859</v>
       </c>
-      <c r="C397" s="15">
+      <c r="C397" s="12">
         <v>0.70833333333333337</v>
       </c>
       <c r="D397" s="8" t="s">
@@ -14849,7 +14852,7 @@
       <c r="B398" s="8">
         <v>45866</v>
       </c>
-      <c r="C398" s="15">
+      <c r="C398" s="12">
         <v>0.70833333333333337</v>
       </c>
       <c r="D398" s="8" t="s">
@@ -14885,7 +14888,7 @@
       <c r="B399" s="8">
         <v>45873</v>
       </c>
-      <c r="C399" s="15">
+      <c r="C399" s="12">
         <v>0.70833333333333337</v>
       </c>
       <c r="D399" s="8" t="s">
@@ -14921,7 +14924,7 @@
       <c r="B400" s="8">
         <v>45880</v>
       </c>
-      <c r="C400" s="15">
+      <c r="C400" s="12">
         <v>0.70833333333333337</v>
       </c>
       <c r="D400" s="8" t="s">
@@ -14957,7 +14960,7 @@
       <c r="B401" s="8">
         <v>45887</v>
       </c>
-      <c r="C401" s="15">
+      <c r="C401" s="12">
         <v>0.70833333333333337</v>
       </c>
       <c r="D401" s="8" t="s">
@@ -14993,7 +14996,7 @@
       <c r="B402" s="8">
         <v>45894</v>
       </c>
-      <c r="C402" s="15">
+      <c r="C402" s="12">
         <v>0.70833333333333337</v>
       </c>
       <c r="D402" s="8" t="s">
@@ -15029,7 +15032,7 @@
       <c r="B403" s="8">
         <v>45901</v>
       </c>
-      <c r="C403" s="15">
+      <c r="C403" s="12">
         <v>0.70833333333333337</v>
       </c>
       <c r="D403" s="8" t="s">
@@ -15065,7 +15068,7 @@
       <c r="B404" s="8">
         <v>45908</v>
       </c>
-      <c r="C404" s="15">
+      <c r="C404" s="12">
         <v>0.70833333333333337</v>
       </c>
       <c r="D404" s="8" t="s">
@@ -15101,7 +15104,7 @@
       <c r="B405" s="8">
         <v>45915</v>
       </c>
-      <c r="C405" s="15">
+      <c r="C405" s="12">
         <v>0.70833333333333337</v>
       </c>
       <c r="D405" s="8" t="s">
@@ -15137,7 +15140,7 @@
       <c r="B406" s="8">
         <v>45922</v>
       </c>
-      <c r="C406" s="15">
+      <c r="C406" s="12">
         <v>0.70833333333333337</v>
       </c>
       <c r="D406" s="8" t="s">
@@ -15173,7 +15176,7 @@
       <c r="B407" s="8">
         <v>45929</v>
       </c>
-      <c r="C407" s="15">
+      <c r="C407" s="12">
         <v>0.70833333333333337</v>
       </c>
       <c r="D407" s="8" t="s">
@@ -15209,7 +15212,7 @@
       <c r="B408" s="8">
         <v>45936</v>
       </c>
-      <c r="C408" s="15">
+      <c r="C408" s="12">
         <v>0.70833333333333337</v>
       </c>
       <c r="D408" s="8" t="s">
@@ -15245,7 +15248,7 @@
       <c r="B409" s="8">
         <v>45943</v>
       </c>
-      <c r="C409" s="15">
+      <c r="C409" s="12">
         <v>0.70833333333333337</v>
       </c>
       <c r="D409" s="8" t="s">
@@ -15281,7 +15284,7 @@
       <c r="B410" s="8">
         <v>45950</v>
       </c>
-      <c r="C410" s="15">
+      <c r="C410" s="12">
         <v>0.70833333333333337</v>
       </c>
       <c r="D410" s="8" t="s">
@@ -15317,7 +15320,7 @@
       <c r="B411" s="8">
         <v>45957</v>
       </c>
-      <c r="C411" s="15">
+      <c r="C411" s="12">
         <v>0.70833333333333337</v>
       </c>
       <c r="D411" s="8" t="s">
@@ -15353,7 +15356,7 @@
       <c r="B412" s="8">
         <v>45964</v>
       </c>
-      <c r="C412" s="15">
+      <c r="C412" s="12">
         <v>0.70833333333333337</v>
       </c>
       <c r="D412" s="8" t="s">
@@ -15389,7 +15392,7 @@
       <c r="B413" s="8">
         <v>45971</v>
       </c>
-      <c r="C413" s="15">
+      <c r="C413" s="12">
         <v>0.70833333333333337</v>
       </c>
       <c r="D413" s="8" t="s">
@@ -15425,7 +15428,7 @@
       <c r="B414" s="8">
         <v>45978</v>
       </c>
-      <c r="C414" s="15">
+      <c r="C414" s="12">
         <v>0.70833333333333337</v>
       </c>
       <c r="D414" s="8" t="s">
@@ -15461,7 +15464,7 @@
       <c r="B415" s="8">
         <v>45985</v>
       </c>
-      <c r="C415" s="15">
+      <c r="C415" s="12">
         <v>0.70833333333333337</v>
       </c>
       <c r="D415" s="8" t="s">
@@ -15497,7 +15500,7 @@
       <c r="B416" s="8">
         <v>45992</v>
       </c>
-      <c r="C416" s="15">
+      <c r="C416" s="12">
         <v>0.70833333333333337</v>
       </c>
       <c r="D416" s="8" t="s">
@@ -15533,7 +15536,7 @@
       <c r="B417" s="8">
         <v>45999</v>
       </c>
-      <c r="C417" s="15">
+      <c r="C417" s="12">
         <v>0.70833333333333337</v>
       </c>
       <c r="D417" s="8" t="s">
@@ -15569,7 +15572,7 @@
       <c r="B418" s="8">
         <v>46006</v>
       </c>
-      <c r="C418" s="15">
+      <c r="C418" s="12">
         <v>0.70833333333333337</v>
       </c>
       <c r="D418" s="8" t="s">
@@ -15605,7 +15608,7 @@
       <c r="B419" s="8">
         <v>46013</v>
       </c>
-      <c r="C419" s="15">
+      <c r="C419" s="12">
         <v>0.70833333333333337</v>
       </c>
       <c r="D419" s="8" t="s">
@@ -15641,7 +15644,7 @@
       <c r="B420" s="8">
         <v>46027</v>
       </c>
-      <c r="C420" s="15">
+      <c r="C420" s="12">
         <v>0.70833333333333337</v>
       </c>
       <c r="D420" s="8" t="s">
@@ -15677,7 +15680,7 @@
       <c r="B421" s="8">
         <v>46034</v>
       </c>
-      <c r="C421" s="15">
+      <c r="C421" s="12">
         <v>0.70833333333333337</v>
       </c>
       <c r="D421" s="8" t="s">
@@ -15713,7 +15716,7 @@
       <c r="B422" s="8">
         <v>46041</v>
       </c>
-      <c r="C422" s="15">
+      <c r="C422" s="12">
         <v>0.70833333333333337</v>
       </c>
       <c r="D422" s="8" t="s">
@@ -15749,7 +15752,7 @@
       <c r="B423" s="8">
         <v>46048</v>
       </c>
-      <c r="C423" s="15">
+      <c r="C423" s="12">
         <v>0.70833333333333304</v>
       </c>
       <c r="D423" s="8" t="s">
@@ -15785,7 +15788,7 @@
       <c r="B424" s="8">
         <v>46055</v>
       </c>
-      <c r="C424" s="15">
+      <c r="C424" s="12">
         <v>0.70833333333333304</v>
       </c>
       <c r="D424" s="8" t="s">
@@ -15821,7 +15824,7 @@
       <c r="B425" s="8">
         <v>46062</v>
       </c>
-      <c r="C425" s="15">
+      <c r="C425" s="12">
         <v>0.70833333333333204</v>
       </c>
       <c r="D425" s="8" t="s">
@@ -15857,7 +15860,7 @@
       <c r="B426" s="8">
         <v>46069</v>
       </c>
-      <c r="C426" s="15">
+      <c r="C426" s="12">
         <v>0.70833333333333304</v>
       </c>
       <c r="D426" s="8" t="s">
@@ -15893,7 +15896,7 @@
       <c r="B427" s="8">
         <v>46076</v>
       </c>
-      <c r="C427" s="15">
+      <c r="C427" s="12">
         <v>0.70833333333333304</v>
       </c>
       <c r="D427" s="8" t="s">
@@ -15919,6 +15922,41 @@
       </c>
       <c r="K427" s="9">
         <v>4432</v>
+      </c>
+    </row>
+    <row r="428" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="A428" s="16">
+        <v>46083</v>
+      </c>
+      <c r="B428" s="16">
+        <v>46083</v>
+      </c>
+      <c r="C428" s="12">
+        <v>0.70833333333333304</v>
+      </c>
+      <c r="D428" s="8" t="s">
+        <v>21</v>
+      </c>
+      <c r="E428" s="9">
+        <v>2007</v>
+      </c>
+      <c r="F428" s="9">
+        <v>1104</v>
+      </c>
+      <c r="G428" s="9">
+        <v>3156</v>
+      </c>
+      <c r="H428" s="9">
+        <v>1187</v>
+      </c>
+      <c r="I428" s="9">
+        <v>861</v>
+      </c>
+      <c r="J428" s="9">
+        <v>231</v>
+      </c>
+      <c r="K428" s="9">
+        <v>4445</v>
       </c>
     </row>
   </sheetData>

--- a/data/freight/Baltic air freight index.xlsx
+++ b/data/freight/Baltic air freight index.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="20417"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="10222"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\USER\PycharmProjects\AlternativeData\data\freight\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/junghunlee/Desktop/Pycharm/AlternativeData/data/freight/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8FA9BE3A-0CE3-48A2-ADA5-066702A732C3}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BCBEE705-1EB7-7F42-B7DB-4CA8B0ED5D16}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="16995" yWindow="780" windowWidth="19005" windowHeight="20760" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="17000" yWindow="780" windowWidth="19000" windowHeight="20680" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="BAI" sheetId="1" r:id="rId1"/>
@@ -20,6 +20,17 @@
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
+    </ext>
+    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
+      <xcalcf:calcFeatures>
+        <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:Single"/>
+        <xcalcf:feature name="microsoft.com:FV"/>
+        <xcalcf:feature name="microsoft.com:CNMTM"/>
+        <xcalcf:feature name="microsoft.com:LET_WF"/>
+        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
+        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
+      </xcalcf:calcFeatures>
     </ext>
   </extLst>
 </workbook>
@@ -116,29 +127,29 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <numFmts count="4">
-    <numFmt numFmtId="43" formatCode="_-* #,##0.00_-;\-* #,##0.00_-;_-* &quot;-&quot;??_-;_-@_-"/>
-    <numFmt numFmtId="176" formatCode="_(* #,##0_);_(* \(#,##0\);_(* &quot;-&quot;??_);_(@_)"/>
-    <numFmt numFmtId="177" formatCode="yyyy\-mm\-dd;@"/>
-    <numFmt numFmtId="178" formatCode="[$-409]h:mm:ss\ AM/PM;@"/>
+    <numFmt numFmtId="164" formatCode="_-* #,##0.00_-;\-* #,##0.00_-;_-* &quot;-&quot;??_-;_-@_-"/>
+    <numFmt numFmtId="165" formatCode="_(* #,##0_);_(* \(#,##0\);_(* &quot;-&quot;??_);_(@_)"/>
+    <numFmt numFmtId="166" formatCode="yyyy\-mm\-dd;@"/>
+    <numFmt numFmtId="167" formatCode="[$-409]h:mm:ss\ AM/PM;@"/>
   </numFmts>
-  <fonts count="10" x14ac:knownFonts="1">
+  <fonts count="10">
     <font>
       <sz val="11"/>
       <color theme="1"/>
-      <name val="맑은 고딕"/>
+      <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
     </font>
     <font>
       <sz val="11"/>
       <color theme="1"/>
-      <name val="맑은 고딕"/>
+      <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
     </font>
     <font>
       <sz val="8"/>
-      <name val="맑은 고딕"/>
+      <name val="Calibri"/>
       <family val="3"/>
       <charset val="129"/>
       <scheme val="minor"/>
@@ -160,7 +171,7 @@
     <font>
       <sz val="10"/>
       <color theme="1"/>
-      <name val="맑은 고딕"/>
+      <name val="Calibri"/>
       <family val="3"/>
       <charset val="129"/>
       <scheme val="minor"/>
@@ -177,7 +188,7 @@
       <b/>
       <sz val="10"/>
       <color theme="1"/>
-      <name val="맑은 고딕"/>
+      <name val="Calibri"/>
       <family val="3"/>
       <charset val="129"/>
       <scheme val="minor"/>
@@ -215,14 +226,14 @@
   </borders>
   <cellStyleXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
-    <xf numFmtId="43" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="164" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="17">
+  <cellXfs count="14">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
@@ -235,42 +246,33 @@
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="2">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="176" fontId="8" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1">
+    <xf numFmtId="165" fontId="8" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="177" fontId="9" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="166" fontId="9" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="176" fontId="9" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1">
+    <xf numFmtId="165" fontId="9" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="177" fontId="9" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="166" fontId="9" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="178" fontId="9" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="167" fontId="9" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="166" fontId="8" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="177" fontId="8" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="167" fontId="8" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="178" fontId="8" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="14" fontId="9" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="3">
-    <cellStyle name="쉼표" xfId="1" builtinId="3"/>
-    <cellStyle name="표준" xfId="0" builtinId="0"/>
-    <cellStyle name="하이퍼링크" xfId="2" builtinId="8"/>
+    <cellStyle name="Comma" xfId="1" builtinId="3"/>
+    <cellStyle name="Hyperlink" xfId="2" builtinId="8"/>
+    <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
@@ -549,30 +551,30 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:K428"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="12.75" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="9" defaultRowHeight="13"/>
   <cols>
-    <col min="1" max="1" width="11.375" style="11" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="11.33203125" style="10" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="14" style="8" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="11.125" style="12" customWidth="1"/>
-    <col min="4" max="4" width="11.125" style="8" customWidth="1"/>
-    <col min="5" max="8" width="8.625" style="9" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="11.1640625" style="11" customWidth="1"/>
+    <col min="4" max="4" width="11.1640625" style="8" customWidth="1"/>
+    <col min="5" max="8" width="8.6640625" style="9" bestFit="1" customWidth="1"/>
     <col min="9" max="9" width="9.5" style="9" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="8.625" style="9" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="8.6640625" style="9" bestFit="1" customWidth="1"/>
     <col min="11" max="11" width="9.5" style="9" bestFit="1" customWidth="1"/>
     <col min="12" max="16384" width="9" style="7"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A1" s="13" t="s">
+    <row r="1" spans="1:11" ht="15" customHeight="1">
+      <c r="A1" s="12" t="s">
         <v>18</v>
       </c>
-      <c r="B1" s="14" t="s">
+      <c r="B1" s="12" t="s">
         <v>17</v>
       </c>
-      <c r="C1" s="15" t="s">
+      <c r="C1" s="13" t="s">
         <v>19</v>
       </c>
-      <c r="D1" s="14" t="s">
+      <c r="D1" s="12" t="s">
         <v>20</v>
       </c>
       <c r="E1" s="6" t="s">
@@ -597,11 +599,11 @@
         <v>7</v>
       </c>
     </row>
-    <row r="2" spans="1:11" x14ac:dyDescent="0.2">
-      <c r="A2" s="13"/>
-      <c r="B2" s="14"/>
-      <c r="C2" s="15"/>
-      <c r="D2" s="14"/>
+    <row r="2" spans="1:11">
+      <c r="A2" s="12"/>
+      <c r="B2" s="12"/>
+      <c r="C2" s="13"/>
+      <c r="D2" s="12"/>
       <c r="E2" s="6" t="s">
         <v>6</v>
       </c>
@@ -624,7 +626,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="3" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="3" spans="1:11">
       <c r="A3" s="10">
         <f>B3-1</f>
         <v>43100</v>
@@ -632,7 +634,7 @@
       <c r="B3" s="8">
         <v>43101</v>
       </c>
-      <c r="C3" s="12">
+      <c r="C3" s="11">
         <v>0.70833333333333337</v>
       </c>
       <c r="D3" s="8" t="s">
@@ -660,7 +662,7 @@
         <v>3169</v>
       </c>
     </row>
-    <row r="4" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="4" spans="1:11">
       <c r="A4" s="10">
         <f t="shared" ref="A4:A67" si="0">B4-1</f>
         <v>43107</v>
@@ -668,7 +670,7 @@
       <c r="B4" s="8">
         <v>43108</v>
       </c>
-      <c r="C4" s="12">
+      <c r="C4" s="11">
         <v>0.70833333333333337</v>
       </c>
       <c r="D4" s="8" t="s">
@@ -696,7 +698,7 @@
         <v>2961</v>
       </c>
     </row>
-    <row r="5" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:11">
       <c r="A5" s="10">
         <f t="shared" si="0"/>
         <v>43114</v>
@@ -704,7 +706,7 @@
       <c r="B5" s="8">
         <v>43115</v>
       </c>
-      <c r="C5" s="12">
+      <c r="C5" s="11">
         <v>0.70833333333333337</v>
       </c>
       <c r="D5" s="8" t="s">
@@ -732,7 +734,7 @@
         <v>2650</v>
       </c>
     </row>
-    <row r="6" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:11">
       <c r="A6" s="10">
         <f t="shared" si="0"/>
         <v>43121</v>
@@ -740,7 +742,7 @@
       <c r="B6" s="8">
         <v>43122</v>
       </c>
-      <c r="C6" s="12">
+      <c r="C6" s="11">
         <v>0.70833333333333337</v>
       </c>
       <c r="D6" s="8" t="s">
@@ -768,7 +770,7 @@
         <v>2807</v>
       </c>
     </row>
-    <row r="7" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:11">
       <c r="A7" s="10">
         <f t="shared" si="0"/>
         <v>43128</v>
@@ -776,7 +778,7 @@
       <c r="B7" s="8">
         <v>43129</v>
       </c>
-      <c r="C7" s="12">
+      <c r="C7" s="11">
         <v>0.70833333333333337</v>
       </c>
       <c r="D7" s="8" t="s">
@@ -804,7 +806,7 @@
         <v>2904</v>
       </c>
     </row>
-    <row r="8" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:11">
       <c r="A8" s="10">
         <f t="shared" si="0"/>
         <v>43135</v>
@@ -812,7 +814,7 @@
       <c r="B8" s="8">
         <v>43136</v>
       </c>
-      <c r="C8" s="12">
+      <c r="C8" s="11">
         <v>0.70833333333333337</v>
       </c>
       <c r="D8" s="8" t="s">
@@ -840,7 +842,7 @@
         <v>2899</v>
       </c>
     </row>
-    <row r="9" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:11">
       <c r="A9" s="10">
         <f t="shared" si="0"/>
         <v>43142</v>
@@ -848,7 +850,7 @@
       <c r="B9" s="8">
         <v>43143</v>
       </c>
-      <c r="C9" s="12">
+      <c r="C9" s="11">
         <v>0.70833333333333337</v>
       </c>
       <c r="D9" s="8" t="s">
@@ -876,7 +878,7 @@
         <v>2901</v>
       </c>
     </row>
-    <row r="10" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:11">
       <c r="A10" s="10">
         <f t="shared" si="0"/>
         <v>43149</v>
@@ -884,7 +886,7 @@
       <c r="B10" s="8">
         <v>43150</v>
       </c>
-      <c r="C10" s="12">
+      <c r="C10" s="11">
         <v>0.70833333333333337</v>
       </c>
       <c r="D10" s="8" t="s">
@@ -912,7 +914,7 @@
         <v>2727</v>
       </c>
     </row>
-    <row r="11" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:11">
       <c r="A11" s="10">
         <f t="shared" si="0"/>
         <v>43156</v>
@@ -920,7 +922,7 @@
       <c r="B11" s="8">
         <v>43157</v>
       </c>
-      <c r="C11" s="12">
+      <c r="C11" s="11">
         <v>0.70833333333333337</v>
       </c>
       <c r="D11" s="8" t="s">
@@ -948,7 +950,7 @@
         <v>2761</v>
       </c>
     </row>
-    <row r="12" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:11">
       <c r="A12" s="10">
         <f t="shared" si="0"/>
         <v>43163</v>
@@ -956,7 +958,7 @@
       <c r="B12" s="8">
         <v>43164</v>
       </c>
-      <c r="C12" s="12">
+      <c r="C12" s="11">
         <v>0.70833333333333337</v>
       </c>
       <c r="D12" s="8" t="s">
@@ -984,7 +986,7 @@
         <v>2517</v>
       </c>
     </row>
-    <row r="13" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:11">
       <c r="A13" s="10">
         <f t="shared" si="0"/>
         <v>43170</v>
@@ -992,7 +994,7 @@
       <c r="B13" s="8">
         <v>43171</v>
       </c>
-      <c r="C13" s="12">
+      <c r="C13" s="11">
         <v>0.70833333333333337</v>
       </c>
       <c r="D13" s="8" t="s">
@@ -1020,7 +1022,7 @@
         <v>2740</v>
       </c>
     </row>
-    <row r="14" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:11">
       <c r="A14" s="10">
         <f t="shared" si="0"/>
         <v>43177</v>
@@ -1028,7 +1030,7 @@
       <c r="B14" s="8">
         <v>43178</v>
       </c>
-      <c r="C14" s="12">
+      <c r="C14" s="11">
         <v>0.70833333333333337</v>
       </c>
       <c r="D14" s="8" t="s">
@@ -1056,7 +1058,7 @@
         <v>2752</v>
       </c>
     </row>
-    <row r="15" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:11">
       <c r="A15" s="10">
         <f t="shared" si="0"/>
         <v>43184</v>
@@ -1064,7 +1066,7 @@
       <c r="B15" s="8">
         <v>43185</v>
       </c>
-      <c r="C15" s="12">
+      <c r="C15" s="11">
         <v>0.70833333333333337</v>
       </c>
       <c r="D15" s="8" t="s">
@@ -1092,7 +1094,7 @@
         <v>2814</v>
       </c>
     </row>
-    <row r="16" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:11">
       <c r="A16" s="10">
         <f t="shared" si="0"/>
         <v>43191</v>
@@ -1100,7 +1102,7 @@
       <c r="B16" s="8">
         <v>43192</v>
       </c>
-      <c r="C16" s="12">
+      <c r="C16" s="11">
         <v>0.70833333333333337</v>
       </c>
       <c r="D16" s="8" t="s">
@@ -1128,7 +1130,7 @@
         <v>2989</v>
       </c>
     </row>
-    <row r="17" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="17" spans="1:11">
       <c r="A17" s="10">
         <f t="shared" si="0"/>
         <v>43198</v>
@@ -1136,7 +1138,7 @@
       <c r="B17" s="8">
         <v>43199</v>
       </c>
-      <c r="C17" s="12">
+      <c r="C17" s="11">
         <v>0.70833333333333337</v>
       </c>
       <c r="D17" s="8" t="s">
@@ -1164,7 +1166,7 @@
         <v>3053</v>
       </c>
     </row>
-    <row r="18" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="18" spans="1:11">
       <c r="A18" s="10">
         <f t="shared" si="0"/>
         <v>43205</v>
@@ -1172,7 +1174,7 @@
       <c r="B18" s="8">
         <v>43206</v>
       </c>
-      <c r="C18" s="12">
+      <c r="C18" s="11">
         <v>0.70833333333333337</v>
       </c>
       <c r="D18" s="8" t="s">
@@ -1200,7 +1202,7 @@
         <v>2992</v>
       </c>
     </row>
-    <row r="19" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="19" spans="1:11">
       <c r="A19" s="10">
         <f t="shared" si="0"/>
         <v>43212</v>
@@ -1208,7 +1210,7 @@
       <c r="B19" s="8">
         <v>43213</v>
       </c>
-      <c r="C19" s="12">
+      <c r="C19" s="11">
         <v>0.70833333333333337</v>
       </c>
       <c r="D19" s="8" t="s">
@@ -1236,7 +1238,7 @@
         <v>3134</v>
       </c>
     </row>
-    <row r="20" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="20" spans="1:11">
       <c r="A20" s="10">
         <f t="shared" si="0"/>
         <v>43219</v>
@@ -1244,7 +1246,7 @@
       <c r="B20" s="8">
         <v>43220</v>
       </c>
-      <c r="C20" s="12">
+      <c r="C20" s="11">
         <v>0.70833333333333337</v>
       </c>
       <c r="D20" s="8" t="s">
@@ -1272,7 +1274,7 @@
         <v>3103</v>
       </c>
     </row>
-    <row r="21" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="21" spans="1:11">
       <c r="A21" s="10">
         <f t="shared" si="0"/>
         <v>43226</v>
@@ -1280,7 +1282,7 @@
       <c r="B21" s="8">
         <v>43227</v>
       </c>
-      <c r="C21" s="12">
+      <c r="C21" s="11">
         <v>0.70833333333333337</v>
       </c>
       <c r="D21" s="8" t="s">
@@ -1308,7 +1310,7 @@
         <v>2954</v>
       </c>
     </row>
-    <row r="22" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="22" spans="1:11">
       <c r="A22" s="10">
         <f t="shared" si="0"/>
         <v>43233</v>
@@ -1316,7 +1318,7 @@
       <c r="B22" s="8">
         <v>43234</v>
       </c>
-      <c r="C22" s="12">
+      <c r="C22" s="11">
         <v>0.70833333333333337</v>
       </c>
       <c r="D22" s="8" t="s">
@@ -1344,7 +1346,7 @@
         <v>2913</v>
       </c>
     </row>
-    <row r="23" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="23" spans="1:11">
       <c r="A23" s="10">
         <f t="shared" si="0"/>
         <v>43240</v>
@@ -1352,7 +1354,7 @@
       <c r="B23" s="8">
         <v>43241</v>
       </c>
-      <c r="C23" s="12">
+      <c r="C23" s="11">
         <v>0.70833333333333337</v>
       </c>
       <c r="D23" s="8" t="s">
@@ -1380,7 +1382,7 @@
         <v>2924</v>
       </c>
     </row>
-    <row r="24" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="24" spans="1:11">
       <c r="A24" s="10">
         <f t="shared" si="0"/>
         <v>43247</v>
@@ -1388,7 +1390,7 @@
       <c r="B24" s="8">
         <v>43248</v>
       </c>
-      <c r="C24" s="12">
+      <c r="C24" s="11">
         <v>0.70833333333333337</v>
       </c>
       <c r="D24" s="8" t="s">
@@ -1416,7 +1418,7 @@
         <v>2888</v>
       </c>
     </row>
-    <row r="25" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="25" spans="1:11">
       <c r="A25" s="10">
         <f t="shared" si="0"/>
         <v>43254</v>
@@ -1424,7 +1426,7 @@
       <c r="B25" s="8">
         <v>43255</v>
       </c>
-      <c r="C25" s="12">
+      <c r="C25" s="11">
         <v>0.70833333333333337</v>
       </c>
       <c r="D25" s="8" t="s">
@@ -1452,7 +1454,7 @@
         <v>2904</v>
       </c>
     </row>
-    <row r="26" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="26" spans="1:11">
       <c r="A26" s="10">
         <f t="shared" si="0"/>
         <v>43261</v>
@@ -1460,7 +1462,7 @@
       <c r="B26" s="8">
         <v>43262</v>
       </c>
-      <c r="C26" s="12">
+      <c r="C26" s="11">
         <v>0.70833333333333337</v>
       </c>
       <c r="D26" s="8" t="s">
@@ -1488,7 +1490,7 @@
         <v>2959</v>
       </c>
     </row>
-    <row r="27" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="27" spans="1:11">
       <c r="A27" s="10">
         <f t="shared" si="0"/>
         <v>43268</v>
@@ -1496,7 +1498,7 @@
       <c r="B27" s="8">
         <v>43269</v>
       </c>
-      <c r="C27" s="12">
+      <c r="C27" s="11">
         <v>0.70833333333333337</v>
       </c>
       <c r="D27" s="8" t="s">
@@ -1524,7 +1526,7 @@
         <v>2873</v>
       </c>
     </row>
-    <row r="28" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="28" spans="1:11">
       <c r="A28" s="10">
         <f t="shared" si="0"/>
         <v>43275</v>
@@ -1532,7 +1534,7 @@
       <c r="B28" s="8">
         <v>43276</v>
       </c>
-      <c r="C28" s="12">
+      <c r="C28" s="11">
         <v>0.70833333333333337</v>
       </c>
       <c r="D28" s="8" t="s">
@@ -1560,7 +1562,7 @@
         <v>2769</v>
       </c>
     </row>
-    <row r="29" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="29" spans="1:11">
       <c r="A29" s="10">
         <f t="shared" si="0"/>
         <v>43282</v>
@@ -1568,7 +1570,7 @@
       <c r="B29" s="8">
         <v>43283</v>
       </c>
-      <c r="C29" s="12">
+      <c r="C29" s="11">
         <v>0.70833333333333337</v>
       </c>
       <c r="D29" s="8" t="s">
@@ -1596,7 +1598,7 @@
         <v>3014</v>
       </c>
     </row>
-    <row r="30" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="30" spans="1:11">
       <c r="A30" s="10">
         <f t="shared" si="0"/>
         <v>43289</v>
@@ -1604,7 +1606,7 @@
       <c r="B30" s="8">
         <v>43290</v>
       </c>
-      <c r="C30" s="12">
+      <c r="C30" s="11">
         <v>0.70833333333333337</v>
       </c>
       <c r="D30" s="8" t="s">
@@ -1632,7 +1634,7 @@
         <v>3033</v>
       </c>
     </row>
-    <row r="31" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="31" spans="1:11">
       <c r="A31" s="10">
         <f t="shared" si="0"/>
         <v>43296</v>
@@ -1640,7 +1642,7 @@
       <c r="B31" s="8">
         <v>43297</v>
       </c>
-      <c r="C31" s="12">
+      <c r="C31" s="11">
         <v>0.70833333333333337</v>
       </c>
       <c r="D31" s="8" t="s">
@@ -1668,7 +1670,7 @@
         <v>2930</v>
       </c>
     </row>
-    <row r="32" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="32" spans="1:11">
       <c r="A32" s="10">
         <f t="shared" si="0"/>
         <v>43303</v>
@@ -1676,7 +1678,7 @@
       <c r="B32" s="8">
         <v>43304</v>
       </c>
-      <c r="C32" s="12">
+      <c r="C32" s="11">
         <v>0.70833333333333337</v>
       </c>
       <c r="D32" s="8" t="s">
@@ -1704,7 +1706,7 @@
         <v>3182</v>
       </c>
     </row>
-    <row r="33" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="33" spans="1:11">
       <c r="A33" s="10">
         <f t="shared" si="0"/>
         <v>43310</v>
@@ -1712,7 +1714,7 @@
       <c r="B33" s="8">
         <v>43311</v>
       </c>
-      <c r="C33" s="12">
+      <c r="C33" s="11">
         <v>0.70833333333333337</v>
       </c>
       <c r="D33" s="8" t="s">
@@ -1740,7 +1742,7 @@
         <v>3174</v>
       </c>
     </row>
-    <row r="34" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="34" spans="1:11">
       <c r="A34" s="10">
         <f t="shared" si="0"/>
         <v>43317</v>
@@ -1748,7 +1750,7 @@
       <c r="B34" s="8">
         <v>43318</v>
       </c>
-      <c r="C34" s="12">
+      <c r="C34" s="11">
         <v>0.70833333333333337</v>
       </c>
       <c r="D34" s="8" t="s">
@@ -1776,7 +1778,7 @@
         <v>3183</v>
       </c>
     </row>
-    <row r="35" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="35" spans="1:11">
       <c r="A35" s="10">
         <f t="shared" si="0"/>
         <v>43324</v>
@@ -1784,7 +1786,7 @@
       <c r="B35" s="8">
         <v>43325</v>
       </c>
-      <c r="C35" s="12">
+      <c r="C35" s="11">
         <v>0.70833333333333337</v>
       </c>
       <c r="D35" s="8" t="s">
@@ -1812,7 +1814,7 @@
         <v>3078</v>
       </c>
     </row>
-    <row r="36" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="36" spans="1:11">
       <c r="A36" s="10">
         <f t="shared" si="0"/>
         <v>43331</v>
@@ -1820,7 +1822,7 @@
       <c r="B36" s="8">
         <v>43332</v>
       </c>
-      <c r="C36" s="12">
+      <c r="C36" s="11">
         <v>0.70833333333333337</v>
       </c>
       <c r="D36" s="8" t="s">
@@ -1848,7 +1850,7 @@
         <v>3135</v>
       </c>
     </row>
-    <row r="37" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="37" spans="1:11">
       <c r="A37" s="10">
         <f t="shared" si="0"/>
         <v>43338</v>
@@ -1856,7 +1858,7 @@
       <c r="B37" s="8">
         <v>43339</v>
       </c>
-      <c r="C37" s="12">
+      <c r="C37" s="11">
         <v>0.70833333333333337</v>
       </c>
       <c r="D37" s="8" t="s">
@@ -1884,7 +1886,7 @@
         <v>3138</v>
       </c>
     </row>
-    <row r="38" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="38" spans="1:11">
       <c r="A38" s="10">
         <f t="shared" si="0"/>
         <v>43345</v>
@@ -1892,7 +1894,7 @@
       <c r="B38" s="8">
         <v>43346</v>
       </c>
-      <c r="C38" s="12">
+      <c r="C38" s="11">
         <v>0.70833333333333337</v>
       </c>
       <c r="D38" s="8" t="s">
@@ -1920,7 +1922,7 @@
         <v>3417</v>
       </c>
     </row>
-    <row r="39" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="39" spans="1:11">
       <c r="A39" s="10">
         <f t="shared" si="0"/>
         <v>43352</v>
@@ -1928,7 +1930,7 @@
       <c r="B39" s="8">
         <v>43353</v>
       </c>
-      <c r="C39" s="12">
+      <c r="C39" s="11">
         <v>0.70833333333333337</v>
       </c>
       <c r="D39" s="8" t="s">
@@ -1956,7 +1958,7 @@
         <v>3427</v>
       </c>
     </row>
-    <row r="40" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="40" spans="1:11">
       <c r="A40" s="10">
         <f t="shared" si="0"/>
         <v>43359</v>
@@ -1964,7 +1966,7 @@
       <c r="B40" s="8">
         <v>43360</v>
       </c>
-      <c r="C40" s="12">
+      <c r="C40" s="11">
         <v>0.70833333333333337</v>
       </c>
       <c r="D40" s="8" t="s">
@@ -1992,7 +1994,7 @@
         <v>3254</v>
       </c>
     </row>
-    <row r="41" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="41" spans="1:11">
       <c r="A41" s="10">
         <f t="shared" si="0"/>
         <v>43366</v>
@@ -2000,7 +2002,7 @@
       <c r="B41" s="8">
         <v>43367</v>
       </c>
-      <c r="C41" s="12">
+      <c r="C41" s="11">
         <v>0.70833333333333337</v>
       </c>
       <c r="D41" s="8" t="s">
@@ -2028,7 +2030,7 @@
         <v>3334</v>
       </c>
     </row>
-    <row r="42" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="42" spans="1:11">
       <c r="A42" s="10">
         <f t="shared" si="0"/>
         <v>43373</v>
@@ -2036,7 +2038,7 @@
       <c r="B42" s="8">
         <v>43374</v>
       </c>
-      <c r="C42" s="12">
+      <c r="C42" s="11">
         <v>0.70833333333333337</v>
       </c>
       <c r="D42" s="8" t="s">
@@ -2064,7 +2066,7 @@
         <v>3450</v>
       </c>
     </row>
-    <row r="43" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="43" spans="1:11">
       <c r="A43" s="10">
         <f t="shared" si="0"/>
         <v>43380</v>
@@ -2072,7 +2074,7 @@
       <c r="B43" s="8">
         <v>43381</v>
       </c>
-      <c r="C43" s="12">
+      <c r="C43" s="11">
         <v>0.70833333333333337</v>
       </c>
       <c r="D43" s="8" t="s">
@@ -2100,7 +2102,7 @@
         <v>3267</v>
       </c>
     </row>
-    <row r="44" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="44" spans="1:11">
       <c r="A44" s="10">
         <f t="shared" si="0"/>
         <v>43387</v>
@@ -2108,7 +2110,7 @@
       <c r="B44" s="8">
         <v>43388</v>
       </c>
-      <c r="C44" s="12">
+      <c r="C44" s="11">
         <v>0.70833333333333337</v>
       </c>
       <c r="D44" s="8" t="s">
@@ -2136,7 +2138,7 @@
         <v>3296</v>
       </c>
     </row>
-    <row r="45" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="45" spans="1:11">
       <c r="A45" s="10">
         <f t="shared" si="0"/>
         <v>43394</v>
@@ -2144,7 +2146,7 @@
       <c r="B45" s="8">
         <v>43395</v>
       </c>
-      <c r="C45" s="12">
+      <c r="C45" s="11">
         <v>0.70833333333333337</v>
       </c>
       <c r="D45" s="8" t="s">
@@ -2172,7 +2174,7 @@
         <v>3511</v>
       </c>
     </row>
-    <row r="46" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="46" spans="1:11">
       <c r="A46" s="10">
         <f t="shared" si="0"/>
         <v>43401</v>
@@ -2180,7 +2182,7 @@
       <c r="B46" s="8">
         <v>43402</v>
       </c>
-      <c r="C46" s="12">
+      <c r="C46" s="11">
         <v>0.70833333333333337</v>
       </c>
       <c r="D46" s="8" t="s">
@@ -2208,7 +2210,7 @@
         <v>3658</v>
       </c>
     </row>
-    <row r="47" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="47" spans="1:11">
       <c r="A47" s="10">
         <f t="shared" si="0"/>
         <v>43408</v>
@@ -2216,7 +2218,7 @@
       <c r="B47" s="8">
         <v>43409</v>
       </c>
-      <c r="C47" s="12">
+      <c r="C47" s="11">
         <v>0.70833333333333337</v>
       </c>
       <c r="D47" s="8" t="s">
@@ -2244,7 +2246,7 @@
         <v>3881</v>
       </c>
     </row>
-    <row r="48" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="48" spans="1:11">
       <c r="A48" s="10">
         <f t="shared" si="0"/>
         <v>43415</v>
@@ -2252,7 +2254,7 @@
       <c r="B48" s="8">
         <v>43416</v>
       </c>
-      <c r="C48" s="12">
+      <c r="C48" s="11">
         <v>0.70833333333333337</v>
       </c>
       <c r="D48" s="8" t="s">
@@ -2280,7 +2282,7 @@
         <v>3696</v>
       </c>
     </row>
-    <row r="49" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="49" spans="1:11">
       <c r="A49" s="10">
         <f t="shared" si="0"/>
         <v>43422</v>
@@ -2288,7 +2290,7 @@
       <c r="B49" s="8">
         <v>43423</v>
       </c>
-      <c r="C49" s="12">
+      <c r="C49" s="11">
         <v>0.70833333333333337</v>
       </c>
       <c r="D49" s="8" t="s">
@@ -2316,7 +2318,7 @@
         <v>3795</v>
       </c>
     </row>
-    <row r="50" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="50" spans="1:11">
       <c r="A50" s="10">
         <f t="shared" si="0"/>
         <v>43429</v>
@@ -2324,7 +2326,7 @@
       <c r="B50" s="8">
         <v>43430</v>
       </c>
-      <c r="C50" s="12">
+      <c r="C50" s="11">
         <v>0.70833333333333337</v>
       </c>
       <c r="D50" s="8" t="s">
@@ -2352,7 +2354,7 @@
         <v>3690</v>
       </c>
     </row>
-    <row r="51" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="51" spans="1:11">
       <c r="A51" s="10">
         <f t="shared" si="0"/>
         <v>43436</v>
@@ -2360,7 +2362,7 @@
       <c r="B51" s="8">
         <v>43437</v>
       </c>
-      <c r="C51" s="12">
+      <c r="C51" s="11">
         <v>0.70833333333333337</v>
       </c>
       <c r="D51" s="8" t="s">
@@ -2388,7 +2390,7 @@
         <v>3542</v>
       </c>
     </row>
-    <row r="52" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="52" spans="1:11">
       <c r="A52" s="10">
         <f t="shared" si="0"/>
         <v>43443</v>
@@ -2396,7 +2398,7 @@
       <c r="B52" s="8">
         <v>43444</v>
       </c>
-      <c r="C52" s="12">
+      <c r="C52" s="11">
         <v>0.70833333333333337</v>
       </c>
       <c r="D52" s="8" t="s">
@@ -2424,7 +2426,7 @@
         <v>3372</v>
       </c>
     </row>
-    <row r="53" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="53" spans="1:11">
       <c r="A53" s="10">
         <f t="shared" si="0"/>
         <v>43450</v>
@@ -2432,7 +2434,7 @@
       <c r="B53" s="8">
         <v>43451</v>
       </c>
-      <c r="C53" s="12">
+      <c r="C53" s="11">
         <v>0.70833333333333337</v>
       </c>
       <c r="D53" s="8" t="s">
@@ -2460,7 +2462,7 @@
         <v>3495</v>
       </c>
     </row>
-    <row r="54" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="54" spans="1:11">
       <c r="A54" s="10">
         <f t="shared" si="0"/>
         <v>43457</v>
@@ -2468,7 +2470,7 @@
       <c r="B54" s="8">
         <v>43458</v>
       </c>
-      <c r="C54" s="12">
+      <c r="C54" s="11">
         <v>0.70833333333333337</v>
       </c>
       <c r="D54" s="8" t="s">
@@ -2496,7 +2498,7 @@
         <v>3197</v>
       </c>
     </row>
-    <row r="55" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="55" spans="1:11">
       <c r="A55" s="10">
         <f t="shared" si="0"/>
         <v>43464</v>
@@ -2504,7 +2506,7 @@
       <c r="B55" s="8">
         <v>43465</v>
       </c>
-      <c r="C55" s="12">
+      <c r="C55" s="11">
         <v>0.70833333333333337</v>
       </c>
       <c r="D55" s="8" t="s">
@@ -2532,7 +2534,7 @@
         <v>3164</v>
       </c>
     </row>
-    <row r="56" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="56" spans="1:11">
       <c r="A56" s="10">
         <f t="shared" si="0"/>
         <v>43471</v>
@@ -2540,7 +2542,7 @@
       <c r="B56" s="8">
         <v>43472</v>
       </c>
-      <c r="C56" s="12">
+      <c r="C56" s="11">
         <v>0.70833333333333337</v>
       </c>
       <c r="D56" s="8" t="s">
@@ -2568,7 +2570,7 @@
         <v>3171</v>
       </c>
     </row>
-    <row r="57" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="57" spans="1:11">
       <c r="A57" s="10">
         <f t="shared" si="0"/>
         <v>43478</v>
@@ -2576,7 +2578,7 @@
       <c r="B57" s="8">
         <v>43479</v>
       </c>
-      <c r="C57" s="12">
+      <c r="C57" s="11">
         <v>0.70833333333333337</v>
       </c>
       <c r="D57" s="8" t="s">
@@ -2604,7 +2606,7 @@
         <v>3147</v>
       </c>
     </row>
-    <row r="58" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="58" spans="1:11">
       <c r="A58" s="10">
         <f t="shared" si="0"/>
         <v>43485</v>
@@ -2612,7 +2614,7 @@
       <c r="B58" s="8">
         <v>43486</v>
       </c>
-      <c r="C58" s="12">
+      <c r="C58" s="11">
         <v>0.70833333333333337</v>
       </c>
       <c r="D58" s="8" t="s">
@@ -2640,7 +2642,7 @@
         <v>3195</v>
       </c>
     </row>
-    <row r="59" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="59" spans="1:11">
       <c r="A59" s="10">
         <f t="shared" si="0"/>
         <v>43492</v>
@@ -2648,7 +2650,7 @@
       <c r="B59" s="8">
         <v>43493</v>
       </c>
-      <c r="C59" s="12">
+      <c r="C59" s="11">
         <v>0.70833333333333337</v>
       </c>
       <c r="D59" s="8" t="s">
@@ -2676,7 +2678,7 @@
         <v>3054</v>
       </c>
     </row>
-    <row r="60" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="60" spans="1:11">
       <c r="A60" s="10">
         <f t="shared" si="0"/>
         <v>43499</v>
@@ -2684,7 +2686,7 @@
       <c r="B60" s="8">
         <v>43500</v>
       </c>
-      <c r="C60" s="12">
+      <c r="C60" s="11">
         <v>0.70833333333333337</v>
       </c>
       <c r="D60" s="8" t="s">
@@ -2712,7 +2714,7 @@
         <v>3148</v>
       </c>
     </row>
-    <row r="61" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="61" spans="1:11">
       <c r="A61" s="10">
         <f t="shared" si="0"/>
         <v>43506</v>
@@ -2720,7 +2722,7 @@
       <c r="B61" s="8">
         <v>43507</v>
       </c>
-      <c r="C61" s="12">
+      <c r="C61" s="11">
         <v>0.70833333333333337</v>
       </c>
       <c r="D61" s="8" t="s">
@@ -2748,7 +2750,7 @@
         <v>3187</v>
       </c>
     </row>
-    <row r="62" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="62" spans="1:11">
       <c r="A62" s="10">
         <f t="shared" si="0"/>
         <v>43513</v>
@@ -2756,7 +2758,7 @@
       <c r="B62" s="8">
         <v>43514</v>
       </c>
-      <c r="C62" s="12">
+      <c r="C62" s="11">
         <v>0.70833333333333337</v>
       </c>
       <c r="D62" s="8" t="s">
@@ -2784,7 +2786,7 @@
         <v>3215</v>
       </c>
     </row>
-    <row r="63" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="63" spans="1:11">
       <c r="A63" s="10">
         <f t="shared" si="0"/>
         <v>43520</v>
@@ -2792,7 +2794,7 @@
       <c r="B63" s="8">
         <v>43521</v>
       </c>
-      <c r="C63" s="12">
+      <c r="C63" s="11">
         <v>0.70833333333333337</v>
       </c>
       <c r="D63" s="8" t="s">
@@ -2820,7 +2822,7 @@
         <v>3068</v>
       </c>
     </row>
-    <row r="64" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="64" spans="1:11">
       <c r="A64" s="10">
         <f t="shared" si="0"/>
         <v>43527</v>
@@ -2828,7 +2830,7 @@
       <c r="B64" s="8">
         <v>43528</v>
       </c>
-      <c r="C64" s="12">
+      <c r="C64" s="11">
         <v>0.70833333333333337</v>
       </c>
       <c r="D64" s="8" t="s">
@@ -2856,7 +2858,7 @@
         <v>2976</v>
       </c>
     </row>
-    <row r="65" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="65" spans="1:11">
       <c r="A65" s="10">
         <f t="shared" si="0"/>
         <v>43534</v>
@@ -2864,7 +2866,7 @@
       <c r="B65" s="8">
         <v>43535</v>
       </c>
-      <c r="C65" s="12">
+      <c r="C65" s="11">
         <v>0.70833333333333337</v>
       </c>
       <c r="D65" s="8" t="s">
@@ -2892,7 +2894,7 @@
         <v>2897</v>
       </c>
     </row>
-    <row r="66" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="66" spans="1:11">
       <c r="A66" s="10">
         <f t="shared" si="0"/>
         <v>43541</v>
@@ -2900,7 +2902,7 @@
       <c r="B66" s="8">
         <v>43542</v>
       </c>
-      <c r="C66" s="12">
+      <c r="C66" s="11">
         <v>0.70833333333333337</v>
       </c>
       <c r="D66" s="8" t="s">
@@ -2928,7 +2930,7 @@
         <v>2954</v>
       </c>
     </row>
-    <row r="67" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="67" spans="1:11">
       <c r="A67" s="10">
         <f t="shared" si="0"/>
         <v>43548</v>
@@ -2936,7 +2938,7 @@
       <c r="B67" s="8">
         <v>43549</v>
       </c>
-      <c r="C67" s="12">
+      <c r="C67" s="11">
         <v>0.70833333333333337</v>
       </c>
       <c r="D67" s="8" t="s">
@@ -2964,7 +2966,7 @@
         <v>2955</v>
       </c>
     </row>
-    <row r="68" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="68" spans="1:11">
       <c r="A68" s="10">
         <f t="shared" ref="A68:A131" si="1">B68-1</f>
         <v>43555</v>
@@ -2972,7 +2974,7 @@
       <c r="B68" s="8">
         <v>43556</v>
       </c>
-      <c r="C68" s="12">
+      <c r="C68" s="11">
         <v>0.70833333333333337</v>
       </c>
       <c r="D68" s="8" t="s">
@@ -3000,7 +3002,7 @@
         <v>2977</v>
       </c>
     </row>
-    <row r="69" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="69" spans="1:11">
       <c r="A69" s="10">
         <f t="shared" si="1"/>
         <v>43562</v>
@@ -3008,7 +3010,7 @@
       <c r="B69" s="8">
         <v>43563</v>
       </c>
-      <c r="C69" s="12">
+      <c r="C69" s="11">
         <v>0.70833333333333337</v>
       </c>
       <c r="D69" s="8" t="s">
@@ -3036,7 +3038,7 @@
         <v>3113</v>
       </c>
     </row>
-    <row r="70" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="70" spans="1:11">
       <c r="A70" s="10">
         <f t="shared" si="1"/>
         <v>43569</v>
@@ -3044,7 +3046,7 @@
       <c r="B70" s="8">
         <v>43570</v>
       </c>
-      <c r="C70" s="12">
+      <c r="C70" s="11">
         <v>0.70833333333333337</v>
       </c>
       <c r="D70" s="8" t="s">
@@ -3072,7 +3074,7 @@
         <v>2876</v>
       </c>
     </row>
-    <row r="71" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="71" spans="1:11">
       <c r="A71" s="10">
         <f t="shared" si="1"/>
         <v>43576</v>
@@ -3080,7 +3082,7 @@
       <c r="B71" s="8">
         <v>43577</v>
       </c>
-      <c r="C71" s="12">
+      <c r="C71" s="11">
         <v>0.70833333333333337</v>
       </c>
       <c r="D71" s="8" t="s">
@@ -3108,7 +3110,7 @@
         <v>2704</v>
       </c>
     </row>
-    <row r="72" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="72" spans="1:11">
       <c r="A72" s="10">
         <f t="shared" si="1"/>
         <v>43583</v>
@@ -3116,7 +3118,7 @@
       <c r="B72" s="8">
         <v>43584</v>
       </c>
-      <c r="C72" s="12">
+      <c r="C72" s="11">
         <v>0.70833333333333337</v>
       </c>
       <c r="D72" s="8" t="s">
@@ -3144,7 +3146,7 @@
         <v>2822</v>
       </c>
     </row>
-    <row r="73" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="73" spans="1:11">
       <c r="A73" s="10">
         <f t="shared" si="1"/>
         <v>43590</v>
@@ -3152,7 +3154,7 @@
       <c r="B73" s="8">
         <v>43591</v>
       </c>
-      <c r="C73" s="12">
+      <c r="C73" s="11">
         <v>0.70833333333333337</v>
       </c>
       <c r="D73" s="8" t="s">
@@ -3180,7 +3182,7 @@
         <v>2776</v>
       </c>
     </row>
-    <row r="74" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="74" spans="1:11">
       <c r="A74" s="10">
         <f t="shared" si="1"/>
         <v>43597</v>
@@ -3188,7 +3190,7 @@
       <c r="B74" s="8">
         <v>43598</v>
       </c>
-      <c r="C74" s="12">
+      <c r="C74" s="11">
         <v>0.70833333333333337</v>
       </c>
       <c r="D74" s="8" t="s">
@@ -3216,7 +3218,7 @@
         <v>2732</v>
       </c>
     </row>
-    <row r="75" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="75" spans="1:11">
       <c r="A75" s="10">
         <f t="shared" si="1"/>
         <v>43604</v>
@@ -3224,7 +3226,7 @@
       <c r="B75" s="8">
         <v>43605</v>
       </c>
-      <c r="C75" s="12">
+      <c r="C75" s="11">
         <v>0.70833333333333337</v>
       </c>
       <c r="D75" s="8" t="s">
@@ -3252,7 +3254,7 @@
         <v>2772</v>
       </c>
     </row>
-    <row r="76" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="76" spans="1:11">
       <c r="A76" s="10">
         <f t="shared" si="1"/>
         <v>43611</v>
@@ -3260,7 +3262,7 @@
       <c r="B76" s="8">
         <v>43612</v>
       </c>
-      <c r="C76" s="12">
+      <c r="C76" s="11">
         <v>0.70833333333333337</v>
       </c>
       <c r="D76" s="8" t="s">
@@ -3288,7 +3290,7 @@
         <v>2788</v>
       </c>
     </row>
-    <row r="77" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="77" spans="1:11">
       <c r="A77" s="10">
         <f t="shared" si="1"/>
         <v>43618</v>
@@ -3296,7 +3298,7 @@
       <c r="B77" s="8">
         <v>43619</v>
       </c>
-      <c r="C77" s="12">
+      <c r="C77" s="11">
         <v>0.70833333333333337</v>
       </c>
       <c r="D77" s="8" t="s">
@@ -3324,7 +3326,7 @@
         <v>2662</v>
       </c>
     </row>
-    <row r="78" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="78" spans="1:11">
       <c r="A78" s="10">
         <f t="shared" si="1"/>
         <v>43625</v>
@@ -3332,7 +3334,7 @@
       <c r="B78" s="8">
         <v>43626</v>
       </c>
-      <c r="C78" s="12">
+      <c r="C78" s="11">
         <v>0.70833333333333337</v>
       </c>
       <c r="D78" s="8" t="s">
@@ -3360,7 +3362,7 @@
         <v>2677</v>
       </c>
     </row>
-    <row r="79" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="79" spans="1:11">
       <c r="A79" s="10">
         <f t="shared" si="1"/>
         <v>43632</v>
@@ -3368,7 +3370,7 @@
       <c r="B79" s="8">
         <v>43633</v>
       </c>
-      <c r="C79" s="12">
+      <c r="C79" s="11">
         <v>0.70833333333333337</v>
       </c>
       <c r="D79" s="8" t="s">
@@ -3396,7 +3398,7 @@
         <v>2532</v>
       </c>
     </row>
-    <row r="80" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="80" spans="1:11">
       <c r="A80" s="10">
         <f t="shared" si="1"/>
         <v>43639</v>
@@ -3404,7 +3406,7 @@
       <c r="B80" s="8">
         <v>43640</v>
       </c>
-      <c r="C80" s="12">
+      <c r="C80" s="11">
         <v>0.70833333333333337</v>
       </c>
       <c r="D80" s="8" t="s">
@@ -3432,7 +3434,7 @@
         <v>2732</v>
       </c>
     </row>
-    <row r="81" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="81" spans="1:11">
       <c r="A81" s="10">
         <f t="shared" si="1"/>
         <v>43646</v>
@@ -3440,7 +3442,7 @@
       <c r="B81" s="8">
         <v>43647</v>
       </c>
-      <c r="C81" s="12">
+      <c r="C81" s="11">
         <v>0.70833333333333337</v>
       </c>
       <c r="D81" s="8" t="s">
@@ -3468,7 +3470,7 @@
         <v>2742</v>
       </c>
     </row>
-    <row r="82" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="82" spans="1:11">
       <c r="A82" s="10">
         <f t="shared" si="1"/>
         <v>43653</v>
@@ -3476,7 +3478,7 @@
       <c r="B82" s="8">
         <v>43654</v>
       </c>
-      <c r="C82" s="12">
+      <c r="C82" s="11">
         <v>0.70833333333333337</v>
       </c>
       <c r="D82" s="8" t="s">
@@ -3504,7 +3506,7 @@
         <v>2772</v>
       </c>
     </row>
-    <row r="83" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="83" spans="1:11">
       <c r="A83" s="10">
         <f t="shared" si="1"/>
         <v>43660</v>
@@ -3512,7 +3514,7 @@
       <c r="B83" s="8">
         <v>43661</v>
       </c>
-      <c r="C83" s="12">
+      <c r="C83" s="11">
         <v>0.70833333333333337</v>
       </c>
       <c r="D83" s="8" t="s">
@@ -3540,7 +3542,7 @@
         <v>2766</v>
       </c>
     </row>
-    <row r="84" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="84" spans="1:11">
       <c r="A84" s="10">
         <f t="shared" si="1"/>
         <v>43667</v>
@@ -3548,7 +3550,7 @@
       <c r="B84" s="8">
         <v>43668</v>
       </c>
-      <c r="C84" s="12">
+      <c r="C84" s="11">
         <v>0.70833333333333337</v>
       </c>
       <c r="D84" s="8" t="s">
@@ -3576,7 +3578,7 @@
         <v>2587</v>
       </c>
     </row>
-    <row r="85" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="85" spans="1:11">
       <c r="A85" s="10">
         <f t="shared" si="1"/>
         <v>43674</v>
@@ -3584,7 +3586,7 @@
       <c r="B85" s="8">
         <v>43675</v>
       </c>
-      <c r="C85" s="12">
+      <c r="C85" s="11">
         <v>0.70833333333333337</v>
       </c>
       <c r="D85" s="8" t="s">
@@ -3612,7 +3614,7 @@
         <v>2668</v>
       </c>
     </row>
-    <row r="86" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="86" spans="1:11">
       <c r="A86" s="10">
         <f t="shared" si="1"/>
         <v>43681</v>
@@ -3620,7 +3622,7 @@
       <c r="B86" s="8">
         <v>43682</v>
       </c>
-      <c r="C86" s="12">
+      <c r="C86" s="11">
         <v>0.70833333333333337</v>
       </c>
       <c r="D86" s="8" t="s">
@@ -3648,7 +3650,7 @@
         <v>2605</v>
       </c>
     </row>
-    <row r="87" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="87" spans="1:11">
       <c r="A87" s="10">
         <f t="shared" si="1"/>
         <v>43688</v>
@@ -3656,7 +3658,7 @@
       <c r="B87" s="8">
         <v>43689</v>
       </c>
-      <c r="C87" s="12">
+      <c r="C87" s="11">
         <v>0.70833333333333337</v>
       </c>
       <c r="D87" s="8" t="s">
@@ -3684,7 +3686,7 @@
         <v>2551</v>
       </c>
     </row>
-    <row r="88" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="88" spans="1:11">
       <c r="A88" s="10">
         <f t="shared" si="1"/>
         <v>43695</v>
@@ -3692,7 +3694,7 @@
       <c r="B88" s="8">
         <v>43696</v>
       </c>
-      <c r="C88" s="12">
+      <c r="C88" s="11">
         <v>0.70833333333333337</v>
       </c>
       <c r="D88" s="8" t="s">
@@ -3720,7 +3722,7 @@
         <v>2628</v>
       </c>
     </row>
-    <row r="89" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="89" spans="1:11">
       <c r="A89" s="10">
         <f t="shared" si="1"/>
         <v>43702</v>
@@ -3728,7 +3730,7 @@
       <c r="B89" s="8">
         <v>43703</v>
       </c>
-      <c r="C89" s="12">
+      <c r="C89" s="11">
         <v>0.70833333333333337</v>
       </c>
       <c r="D89" s="8" t="s">
@@ -3756,7 +3758,7 @@
         <v>2656</v>
       </c>
     </row>
-    <row r="90" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="90" spans="1:11">
       <c r="A90" s="10">
         <f t="shared" si="1"/>
         <v>43709</v>
@@ -3764,7 +3766,7 @@
       <c r="B90" s="8">
         <v>43710</v>
       </c>
-      <c r="C90" s="12">
+      <c r="C90" s="11">
         <v>0.70833333333333337</v>
       </c>
       <c r="D90" s="8" t="s">
@@ -3792,7 +3794,7 @@
         <v>2608</v>
       </c>
     </row>
-    <row r="91" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="91" spans="1:11">
       <c r="A91" s="10">
         <f t="shared" si="1"/>
         <v>43716</v>
@@ -3800,7 +3802,7 @@
       <c r="B91" s="8">
         <v>43717</v>
       </c>
-      <c r="C91" s="12">
+      <c r="C91" s="11">
         <v>0.70833333333333337</v>
       </c>
       <c r="D91" s="8" t="s">
@@ -3828,7 +3830,7 @@
         <v>2611</v>
       </c>
     </row>
-    <row r="92" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="92" spans="1:11">
       <c r="A92" s="10">
         <f t="shared" si="1"/>
         <v>43723</v>
@@ -3836,7 +3838,7 @@
       <c r="B92" s="8">
         <v>43724</v>
       </c>
-      <c r="C92" s="12">
+      <c r="C92" s="11">
         <v>0.70833333333333337</v>
       </c>
       <c r="D92" s="8" t="s">
@@ -3864,7 +3866,7 @@
         <v>2550</v>
       </c>
     </row>
-    <row r="93" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="93" spans="1:11">
       <c r="A93" s="10">
         <f t="shared" si="1"/>
         <v>43730</v>
@@ -3872,7 +3874,7 @@
       <c r="B93" s="8">
         <v>43731</v>
       </c>
-      <c r="C93" s="12">
+      <c r="C93" s="11">
         <v>0.70833333333333337</v>
       </c>
       <c r="D93" s="8" t="s">
@@ -3900,7 +3902,7 @@
         <v>2572</v>
       </c>
     </row>
-    <row r="94" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="94" spans="1:11">
       <c r="A94" s="10">
         <f t="shared" si="1"/>
         <v>43737</v>
@@ -3908,7 +3910,7 @@
       <c r="B94" s="8">
         <v>43738</v>
       </c>
-      <c r="C94" s="12">
+      <c r="C94" s="11">
         <v>0.70833333333333337</v>
       </c>
       <c r="D94" s="8" t="s">
@@ -3936,7 +3938,7 @@
         <v>2703</v>
       </c>
     </row>
-    <row r="95" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="95" spans="1:11">
       <c r="A95" s="10">
         <f t="shared" si="1"/>
         <v>43744</v>
@@ -3944,7 +3946,7 @@
       <c r="B95" s="8">
         <v>43745</v>
       </c>
-      <c r="C95" s="12">
+      <c r="C95" s="11">
         <v>0.70833333333333337</v>
       </c>
       <c r="D95" s="8" t="s">
@@ -3972,7 +3974,7 @@
         <v>2804</v>
       </c>
     </row>
-    <row r="96" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="96" spans="1:11">
       <c r="A96" s="10">
         <f t="shared" si="1"/>
         <v>43751</v>
@@ -3980,7 +3982,7 @@
       <c r="B96" s="8">
         <v>43752</v>
       </c>
-      <c r="C96" s="12">
+      <c r="C96" s="11">
         <v>0.70833333333333337</v>
       </c>
       <c r="D96" s="8" t="s">
@@ -4008,7 +4010,7 @@
         <v>2781</v>
       </c>
     </row>
-    <row r="97" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="97" spans="1:11">
       <c r="A97" s="10">
         <f t="shared" si="1"/>
         <v>43758</v>
@@ -4016,7 +4018,7 @@
       <c r="B97" s="8">
         <v>43759</v>
       </c>
-      <c r="C97" s="12">
+      <c r="C97" s="11">
         <v>0.70833333333333337</v>
       </c>
       <c r="D97" s="8" t="s">
@@ -4044,7 +4046,7 @@
         <v>2915</v>
       </c>
     </row>
-    <row r="98" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="98" spans="1:11">
       <c r="A98" s="10">
         <f t="shared" si="1"/>
         <v>43765</v>
@@ -4052,7 +4054,7 @@
       <c r="B98" s="8">
         <v>43766</v>
       </c>
-      <c r="C98" s="12">
+      <c r="C98" s="11">
         <v>0.70833333333333337</v>
       </c>
       <c r="D98" s="8" t="s">
@@ -4080,7 +4082,7 @@
         <v>3032</v>
       </c>
     </row>
-    <row r="99" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="99" spans="1:11">
       <c r="A99" s="10">
         <f t="shared" si="1"/>
         <v>43772</v>
@@ -4088,7 +4090,7 @@
       <c r="B99" s="8">
         <v>43773</v>
       </c>
-      <c r="C99" s="12">
+      <c r="C99" s="11">
         <v>0.70833333333333337</v>
       </c>
       <c r="D99" s="8" t="s">
@@ -4116,7 +4118,7 @@
         <v>3120</v>
       </c>
     </row>
-    <row r="100" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="100" spans="1:11">
       <c r="A100" s="10">
         <f t="shared" si="1"/>
         <v>43779</v>
@@ -4124,7 +4126,7 @@
       <c r="B100" s="8">
         <v>43780</v>
       </c>
-      <c r="C100" s="12">
+      <c r="C100" s="11">
         <v>0.70833333333333337</v>
       </c>
       <c r="D100" s="8" t="s">
@@ -4152,7 +4154,7 @@
         <v>3031</v>
       </c>
     </row>
-    <row r="101" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="101" spans="1:11">
       <c r="A101" s="10">
         <f t="shared" si="1"/>
         <v>43786</v>
@@ -4160,7 +4162,7 @@
       <c r="B101" s="8">
         <v>43787</v>
       </c>
-      <c r="C101" s="12">
+      <c r="C101" s="11">
         <v>0.70833333333333337</v>
       </c>
       <c r="D101" s="8" t="s">
@@ -4188,7 +4190,7 @@
         <v>3117</v>
       </c>
     </row>
-    <row r="102" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="102" spans="1:11">
       <c r="A102" s="10">
         <f t="shared" si="1"/>
         <v>43793</v>
@@ -4196,7 +4198,7 @@
       <c r="B102" s="8">
         <v>43794</v>
       </c>
-      <c r="C102" s="12">
+      <c r="C102" s="11">
         <v>0.70833333333333337</v>
       </c>
       <c r="D102" s="8" t="s">
@@ -4224,7 +4226,7 @@
         <v>3143</v>
       </c>
     </row>
-    <row r="103" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="103" spans="1:11">
       <c r="A103" s="10">
         <f t="shared" si="1"/>
         <v>43800</v>
@@ -4232,7 +4234,7 @@
       <c r="B103" s="8">
         <v>43801</v>
       </c>
-      <c r="C103" s="12">
+      <c r="C103" s="11">
         <v>0.70833333333333337</v>
       </c>
       <c r="D103" s="8" t="s">
@@ -4260,7 +4262,7 @@
         <v>3079</v>
       </c>
     </row>
-    <row r="104" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="104" spans="1:11">
       <c r="A104" s="10">
         <f t="shared" si="1"/>
         <v>43807</v>
@@ -4268,7 +4270,7 @@
       <c r="B104" s="8">
         <v>43808</v>
       </c>
-      <c r="C104" s="12">
+      <c r="C104" s="11">
         <v>0.70833333333333337</v>
       </c>
       <c r="D104" s="8" t="s">
@@ -4296,7 +4298,7 @@
         <v>3019</v>
       </c>
     </row>
-    <row r="105" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="105" spans="1:11">
       <c r="A105" s="10">
         <f t="shared" si="1"/>
         <v>43814</v>
@@ -4304,7 +4306,7 @@
       <c r="B105" s="8">
         <v>43815</v>
       </c>
-      <c r="C105" s="12">
+      <c r="C105" s="11">
         <v>0.70833333333333337</v>
       </c>
       <c r="D105" s="8" t="s">
@@ -4332,7 +4334,7 @@
         <v>2964</v>
       </c>
     </row>
-    <row r="106" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="106" spans="1:11">
       <c r="A106" s="10">
         <f t="shared" si="1"/>
         <v>43821</v>
@@ -4340,7 +4342,7 @@
       <c r="B106" s="8">
         <v>43822</v>
       </c>
-      <c r="C106" s="12">
+      <c r="C106" s="11">
         <v>0.70833333333333337</v>
       </c>
       <c r="D106" s="8" t="s">
@@ -4368,7 +4370,7 @@
         <v>2821</v>
       </c>
     </row>
-    <row r="107" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="107" spans="1:11">
       <c r="A107" s="10">
         <f t="shared" si="1"/>
         <v>43828</v>
@@ -4376,7 +4378,7 @@
       <c r="B107" s="8">
         <v>43829</v>
       </c>
-      <c r="C107" s="12">
+      <c r="C107" s="11">
         <v>0.70833333333333337</v>
       </c>
       <c r="D107" s="8" t="s">
@@ -4404,7 +4406,7 @@
         <v>2760</v>
       </c>
     </row>
-    <row r="108" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="108" spans="1:11">
       <c r="A108" s="10">
         <f t="shared" si="1"/>
         <v>43835</v>
@@ -4412,7 +4414,7 @@
       <c r="B108" s="8">
         <v>43836</v>
       </c>
-      <c r="C108" s="12">
+      <c r="C108" s="11">
         <v>0.70833333333333337</v>
       </c>
       <c r="D108" s="8" t="s">
@@ -4440,7 +4442,7 @@
         <v>2776</v>
       </c>
     </row>
-    <row r="109" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="109" spans="1:11">
       <c r="A109" s="10">
         <f t="shared" si="1"/>
         <v>43842</v>
@@ -4448,7 +4450,7 @@
       <c r="B109" s="8">
         <v>43843</v>
       </c>
-      <c r="C109" s="12">
+      <c r="C109" s="11">
         <v>0.70833333333333337</v>
       </c>
       <c r="D109" s="8" t="s">
@@ -4476,7 +4478,7 @@
         <v>2636</v>
       </c>
     </row>
-    <row r="110" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="110" spans="1:11">
       <c r="A110" s="10">
         <f t="shared" si="1"/>
         <v>43849</v>
@@ -4484,7 +4486,7 @@
       <c r="B110" s="8">
         <v>43850</v>
       </c>
-      <c r="C110" s="12">
+      <c r="C110" s="11">
         <v>0.70833333333333337</v>
       </c>
       <c r="D110" s="8" t="s">
@@ -4512,7 +4514,7 @@
         <v>2698</v>
       </c>
     </row>
-    <row r="111" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="111" spans="1:11">
       <c r="A111" s="10">
         <f t="shared" si="1"/>
         <v>43856</v>
@@ -4520,7 +4522,7 @@
       <c r="B111" s="8">
         <v>43857</v>
       </c>
-      <c r="C111" s="12">
+      <c r="C111" s="11">
         <v>0.70833333333333337</v>
       </c>
       <c r="D111" s="8" t="s">
@@ -4548,7 +4550,7 @@
         <v>2838</v>
       </c>
     </row>
-    <row r="112" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="112" spans="1:11">
       <c r="A112" s="10">
         <f t="shared" si="1"/>
         <v>43863</v>
@@ -4556,7 +4558,7 @@
       <c r="B112" s="8">
         <v>43864</v>
       </c>
-      <c r="C112" s="12">
+      <c r="C112" s="11">
         <v>0.70833333333333337</v>
       </c>
       <c r="D112" s="8" t="s">
@@ -4584,7 +4586,7 @@
         <v>2587</v>
       </c>
     </row>
-    <row r="113" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="113" spans="1:11">
       <c r="A113" s="10">
         <f t="shared" si="1"/>
         <v>43870</v>
@@ -4592,7 +4594,7 @@
       <c r="B113" s="8">
         <v>43871</v>
       </c>
-      <c r="C113" s="12">
+      <c r="C113" s="11">
         <v>0.70833333333333337</v>
       </c>
       <c r="D113" s="8" t="s">
@@ -4620,7 +4622,7 @@
         <v>2498</v>
       </c>
     </row>
-    <row r="114" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="114" spans="1:11">
       <c r="A114" s="10">
         <f t="shared" si="1"/>
         <v>43877</v>
@@ -4628,7 +4630,7 @@
       <c r="B114" s="8">
         <v>43878</v>
       </c>
-      <c r="C114" s="12">
+      <c r="C114" s="11">
         <v>0.70833333333333337</v>
       </c>
       <c r="D114" s="8" t="s">
@@ -4656,7 +4658,7 @@
         <v>2427</v>
       </c>
     </row>
-    <row r="115" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="115" spans="1:11">
       <c r="A115" s="10">
         <f t="shared" si="1"/>
         <v>43884</v>
@@ -4664,7 +4666,7 @@
       <c r="B115" s="8">
         <v>43885</v>
       </c>
-      <c r="C115" s="12">
+      <c r="C115" s="11">
         <v>0.70833333333333337</v>
       </c>
       <c r="D115" s="8" t="s">
@@ -4692,7 +4694,7 @@
         <v>2239</v>
       </c>
     </row>
-    <row r="116" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="116" spans="1:11">
       <c r="A116" s="10">
         <f t="shared" si="1"/>
         <v>43891</v>
@@ -4700,7 +4702,7 @@
       <c r="B116" s="8">
         <v>43892</v>
       </c>
-      <c r="C116" s="12">
+      <c r="C116" s="11">
         <v>0.70833333333333337</v>
       </c>
       <c r="D116" s="8" t="s">
@@ -4728,7 +4730,7 @@
         <v>2539</v>
       </c>
     </row>
-    <row r="117" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="117" spans="1:11">
       <c r="A117" s="10">
         <f t="shared" si="1"/>
         <v>43898</v>
@@ -4736,7 +4738,7 @@
       <c r="B117" s="8">
         <v>43899</v>
       </c>
-      <c r="C117" s="12">
+      <c r="C117" s="11">
         <v>0.70833333333333337</v>
       </c>
       <c r="D117" s="8" t="s">
@@ -4764,7 +4766,7 @@
         <v>3154</v>
       </c>
     </row>
-    <row r="118" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="118" spans="1:11">
       <c r="A118" s="10">
         <f t="shared" si="1"/>
         <v>43905</v>
@@ -4772,7 +4774,7 @@
       <c r="B118" s="8">
         <v>43906</v>
       </c>
-      <c r="C118" s="12">
+      <c r="C118" s="11">
         <v>0.70833333333333337</v>
       </c>
       <c r="D118" s="8" t="s">
@@ -4800,7 +4802,7 @@
         <v>3858</v>
       </c>
     </row>
-    <row r="119" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="119" spans="1:11">
       <c r="A119" s="10">
         <f t="shared" si="1"/>
         <v>43912</v>
@@ -4808,7 +4810,7 @@
       <c r="B119" s="8">
         <v>43913</v>
       </c>
-      <c r="C119" s="12">
+      <c r="C119" s="11">
         <v>0.70833333333333337</v>
       </c>
       <c r="D119" s="8" t="s">
@@ -4836,7 +4838,7 @@
         <v>4713</v>
       </c>
     </row>
-    <row r="120" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="120" spans="1:11">
       <c r="A120" s="10">
         <f t="shared" si="1"/>
         <v>43919</v>
@@ -4844,7 +4846,7 @@
       <c r="B120" s="8">
         <v>43920</v>
       </c>
-      <c r="C120" s="12">
+      <c r="C120" s="11">
         <v>0.70833333333333337</v>
       </c>
       <c r="D120" s="8" t="s">
@@ -4872,7 +4874,7 @@
         <v>5641</v>
       </c>
     </row>
-    <row r="121" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="121" spans="1:11">
       <c r="A121" s="10">
         <f t="shared" si="1"/>
         <v>43926</v>
@@ -4880,7 +4882,7 @@
       <c r="B121" s="8">
         <v>43927</v>
       </c>
-      <c r="C121" s="12">
+      <c r="C121" s="11">
         <v>0.70833333333333337</v>
       </c>
       <c r="D121" s="8" t="s">
@@ -4908,7 +4910,7 @@
         <v>6426</v>
       </c>
     </row>
-    <row r="122" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="122" spans="1:11">
       <c r="A122" s="10">
         <f t="shared" si="1"/>
         <v>43933</v>
@@ -4916,7 +4918,7 @@
       <c r="B122" s="8">
         <v>43934</v>
       </c>
-      <c r="C122" s="12">
+      <c r="C122" s="11">
         <v>0.70833333333333337</v>
       </c>
       <c r="D122" s="8" t="s">
@@ -4944,7 +4946,7 @@
         <v>7284</v>
       </c>
     </row>
-    <row r="123" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="123" spans="1:11">
       <c r="A123" s="10">
         <f t="shared" si="1"/>
         <v>43940</v>
@@ -4952,7 +4954,7 @@
       <c r="B123" s="8">
         <v>43941</v>
       </c>
-      <c r="C123" s="12">
+      <c r="C123" s="11">
         <v>0.70833333333333337</v>
       </c>
       <c r="D123" s="8" t="s">
@@ -4980,7 +4982,7 @@
         <v>7946</v>
       </c>
     </row>
-    <row r="124" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="124" spans="1:11">
       <c r="A124" s="10">
         <f t="shared" si="1"/>
         <v>43947</v>
@@ -4988,7 +4990,7 @@
       <c r="B124" s="8">
         <v>43948</v>
       </c>
-      <c r="C124" s="12">
+      <c r="C124" s="11">
         <v>0.70833333333333337</v>
       </c>
       <c r="D124" s="8" t="s">
@@ -5016,7 +5018,7 @@
         <v>8608</v>
       </c>
     </row>
-    <row r="125" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="125" spans="1:11">
       <c r="A125" s="10">
         <f t="shared" si="1"/>
         <v>43954</v>
@@ -5024,7 +5026,7 @@
       <c r="B125" s="8">
         <v>43955</v>
       </c>
-      <c r="C125" s="12">
+      <c r="C125" s="11">
         <v>0.70833333333333337</v>
       </c>
       <c r="D125" s="8" t="s">
@@ -5052,7 +5054,7 @@
         <v>9951</v>
       </c>
     </row>
-    <row r="126" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="126" spans="1:11">
       <c r="A126" s="10">
         <f t="shared" si="1"/>
         <v>43961</v>
@@ -5060,7 +5062,7 @@
       <c r="B126" s="8">
         <v>43962</v>
       </c>
-      <c r="C126" s="12">
+      <c r="C126" s="11">
         <v>0.70833333333333337</v>
       </c>
       <c r="D126" s="8" t="s">
@@ -5088,7 +5090,7 @@
         <v>10351</v>
       </c>
     </row>
-    <row r="127" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="127" spans="1:11">
       <c r="A127" s="10">
         <f t="shared" si="1"/>
         <v>43968</v>
@@ -5096,7 +5098,7 @@
       <c r="B127" s="8">
         <v>43969</v>
       </c>
-      <c r="C127" s="12">
+      <c r="C127" s="11">
         <v>0.70833333333333337</v>
       </c>
       <c r="D127" s="8" t="s">
@@ -5124,7 +5126,7 @@
         <v>11202</v>
       </c>
     </row>
-    <row r="128" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="128" spans="1:11">
       <c r="A128" s="10">
         <f t="shared" si="1"/>
         <v>43975</v>
@@ -5132,7 +5134,7 @@
       <c r="B128" s="8">
         <v>43976</v>
       </c>
-      <c r="C128" s="12">
+      <c r="C128" s="11">
         <v>0.70833333333333337</v>
       </c>
       <c r="D128" s="8" t="s">
@@ -5160,7 +5162,7 @@
         <v>9824</v>
       </c>
     </row>
-    <row r="129" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="129" spans="1:11">
       <c r="A129" s="10">
         <f t="shared" si="1"/>
         <v>43982</v>
@@ -5168,7 +5170,7 @@
       <c r="B129" s="8">
         <v>43983</v>
       </c>
-      <c r="C129" s="12">
+      <c r="C129" s="11">
         <v>0.70833333333333337</v>
       </c>
       <c r="D129" s="8" t="s">
@@ -5196,7 +5198,7 @@
         <v>7635</v>
       </c>
     </row>
-    <row r="130" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="130" spans="1:11">
       <c r="A130" s="10">
         <f t="shared" si="1"/>
         <v>43989</v>
@@ -5204,7 +5206,7 @@
       <c r="B130" s="8">
         <v>43990</v>
       </c>
-      <c r="C130" s="12">
+      <c r="C130" s="11">
         <v>0.70833333333333337</v>
       </c>
       <c r="D130" s="8" t="s">
@@ -5232,7 +5234,7 @@
         <v>5993</v>
       </c>
     </row>
-    <row r="131" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="131" spans="1:11">
       <c r="A131" s="10">
         <f t="shared" si="1"/>
         <v>43996</v>
@@ -5240,7 +5242,7 @@
       <c r="B131" s="8">
         <v>43997</v>
       </c>
-      <c r="C131" s="12">
+      <c r="C131" s="11">
         <v>0.70833333333333337</v>
       </c>
       <c r="D131" s="8" t="s">
@@ -5268,7 +5270,7 @@
         <v>4905</v>
       </c>
     </row>
-    <row r="132" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="132" spans="1:11">
       <c r="A132" s="10">
         <f t="shared" ref="A132:A195" si="2">B132-1</f>
         <v>44003</v>
@@ -5276,7 +5278,7 @@
       <c r="B132" s="8">
         <v>44004</v>
       </c>
-      <c r="C132" s="12">
+      <c r="C132" s="11">
         <v>0.70833333333333337</v>
       </c>
       <c r="D132" s="8" t="s">
@@ -5304,7 +5306,7 @@
         <v>4035</v>
       </c>
     </row>
-    <row r="133" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="133" spans="1:11">
       <c r="A133" s="10">
         <f t="shared" si="2"/>
         <v>44010</v>
@@ -5312,7 +5314,7 @@
       <c r="B133" s="8">
         <v>44011</v>
       </c>
-      <c r="C133" s="12">
+      <c r="C133" s="11">
         <v>0.70833333333333337</v>
       </c>
       <c r="D133" s="8" t="s">
@@ -5340,7 +5342,7 @@
         <v>3835</v>
       </c>
     </row>
-    <row r="134" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="134" spans="1:11">
       <c r="A134" s="10">
         <f t="shared" si="2"/>
         <v>44017</v>
@@ -5348,7 +5350,7 @@
       <c r="B134" s="8">
         <v>44018</v>
       </c>
-      <c r="C134" s="12">
+      <c r="C134" s="11">
         <v>0.70833333333333337</v>
       </c>
       <c r="D134" s="8" t="s">
@@ -5376,7 +5378,7 @@
         <v>3711</v>
       </c>
     </row>
-    <row r="135" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="135" spans="1:11">
       <c r="A135" s="10">
         <f t="shared" si="2"/>
         <v>44024</v>
@@ -5384,7 +5386,7 @@
       <c r="B135" s="8">
         <v>44025</v>
       </c>
-      <c r="C135" s="12">
+      <c r="C135" s="11">
         <v>0.70833333333333337</v>
       </c>
       <c r="D135" s="8" t="s">
@@ -5412,7 +5414,7 @@
         <v>3775</v>
       </c>
     </row>
-    <row r="136" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="136" spans="1:11">
       <c r="A136" s="10">
         <f t="shared" si="2"/>
         <v>44031</v>
@@ -5420,7 +5422,7 @@
       <c r="B136" s="8">
         <v>44032</v>
       </c>
-      <c r="C136" s="12">
+      <c r="C136" s="11">
         <v>0.70833333333333337</v>
       </c>
       <c r="D136" s="8" t="s">
@@ -5448,7 +5450,7 @@
         <v>3862</v>
       </c>
     </row>
-    <row r="137" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="137" spans="1:11">
       <c r="A137" s="10">
         <f t="shared" si="2"/>
         <v>44038</v>
@@ -5456,7 +5458,7 @@
       <c r="B137" s="8">
         <v>44039</v>
       </c>
-      <c r="C137" s="12">
+      <c r="C137" s="11">
         <v>0.70833333333333337</v>
       </c>
       <c r="D137" s="8" t="s">
@@ -5484,7 +5486,7 @@
         <v>4050</v>
       </c>
     </row>
-    <row r="138" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="138" spans="1:11">
       <c r="A138" s="10">
         <f t="shared" si="2"/>
         <v>44045</v>
@@ -5492,7 +5494,7 @@
       <c r="B138" s="8">
         <v>44046</v>
       </c>
-      <c r="C138" s="12">
+      <c r="C138" s="11">
         <v>0.70833333333333337</v>
       </c>
       <c r="D138" s="8" t="s">
@@ -5520,7 +5522,7 @@
         <v>4535</v>
       </c>
     </row>
-    <row r="139" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="139" spans="1:11">
       <c r="A139" s="10">
         <f t="shared" si="2"/>
         <v>44052</v>
@@ -5528,7 +5530,7 @@
       <c r="B139" s="8">
         <v>44053</v>
       </c>
-      <c r="C139" s="12">
+      <c r="C139" s="11">
         <v>0.70833333333333337</v>
       </c>
       <c r="D139" s="8" t="s">
@@ -5556,7 +5558,7 @@
         <v>4425</v>
       </c>
     </row>
-    <row r="140" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="140" spans="1:11">
       <c r="A140" s="10">
         <f t="shared" si="2"/>
         <v>44059</v>
@@ -5564,7 +5566,7 @@
       <c r="B140" s="8">
         <v>44060</v>
       </c>
-      <c r="C140" s="12">
+      <c r="C140" s="11">
         <v>0.70833333333333337</v>
       </c>
       <c r="D140" s="8" t="s">
@@ -5592,7 +5594,7 @@
         <v>4121</v>
       </c>
     </row>
-    <row r="141" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="141" spans="1:11">
       <c r="A141" s="10">
         <f t="shared" si="2"/>
         <v>44066</v>
@@ -5600,7 +5602,7 @@
       <c r="B141" s="8">
         <v>44067</v>
       </c>
-      <c r="C141" s="12">
+      <c r="C141" s="11">
         <v>0.70833333333333337</v>
       </c>
       <c r="D141" s="8" t="s">
@@ -5628,7 +5630,7 @@
         <v>3819</v>
       </c>
     </row>
-    <row r="142" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="142" spans="1:11">
       <c r="A142" s="10">
         <f t="shared" si="2"/>
         <v>44073</v>
@@ -5636,7 +5638,7 @@
       <c r="B142" s="8">
         <v>44074</v>
       </c>
-      <c r="C142" s="12">
+      <c r="C142" s="11">
         <v>0.70833333333333337</v>
       </c>
       <c r="D142" s="8" t="s">
@@ -5664,7 +5666,7 @@
         <v>4332</v>
       </c>
     </row>
-    <row r="143" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="143" spans="1:11">
       <c r="A143" s="10">
         <f t="shared" si="2"/>
         <v>44080</v>
@@ -5672,7 +5674,7 @@
       <c r="B143" s="8">
         <v>44081</v>
       </c>
-      <c r="C143" s="12">
+      <c r="C143" s="11">
         <v>0.70833333333333337</v>
       </c>
       <c r="D143" s="8" t="s">
@@ -5700,7 +5702,7 @@
         <v>4498</v>
       </c>
     </row>
-    <row r="144" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="144" spans="1:11">
       <c r="A144" s="10">
         <f t="shared" si="2"/>
         <v>44087</v>
@@ -5708,7 +5710,7 @@
       <c r="B144" s="8">
         <v>44088</v>
       </c>
-      <c r="C144" s="12">
+      <c r="C144" s="11">
         <v>0.70833333333333337</v>
       </c>
       <c r="D144" s="8" t="s">
@@ -5736,7 +5738,7 @@
         <v>4225</v>
       </c>
     </row>
-    <row r="145" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="145" spans="1:11">
       <c r="A145" s="10">
         <f t="shared" si="2"/>
         <v>44094</v>
@@ -5744,7 +5746,7 @@
       <c r="B145" s="8">
         <v>44095</v>
       </c>
-      <c r="C145" s="12">
+      <c r="C145" s="11">
         <v>0.70833333333333337</v>
       </c>
       <c r="D145" s="8" t="s">
@@ -5772,7 +5774,7 @@
         <v>4242</v>
       </c>
     </row>
-    <row r="146" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="146" spans="1:11">
       <c r="A146" s="10">
         <f t="shared" si="2"/>
         <v>44101</v>
@@ -5780,7 +5782,7 @@
       <c r="B146" s="8">
         <v>44102</v>
       </c>
-      <c r="C146" s="12">
+      <c r="C146" s="11">
         <v>0.70833333333333337</v>
       </c>
       <c r="D146" s="8" t="s">
@@ -5808,7 +5810,7 @@
         <v>4340</v>
       </c>
     </row>
-    <row r="147" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="147" spans="1:11">
       <c r="A147" s="10">
         <f t="shared" si="2"/>
         <v>44108</v>
@@ -5816,7 +5818,7 @@
       <c r="B147" s="8">
         <v>44109</v>
       </c>
-      <c r="C147" s="12">
+      <c r="C147" s="11">
         <v>0.70833333333333337</v>
       </c>
       <c r="D147" s="8" t="s">
@@ -5844,7 +5846,7 @@
         <v>4375</v>
       </c>
     </row>
-    <row r="148" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="148" spans="1:11">
       <c r="A148" s="10">
         <f t="shared" si="2"/>
         <v>44115</v>
@@ -5852,7 +5854,7 @@
       <c r="B148" s="8">
         <v>44116</v>
       </c>
-      <c r="C148" s="12">
+      <c r="C148" s="11">
         <v>0.70833333333333337</v>
       </c>
       <c r="D148" s="8" t="s">
@@ -5880,7 +5882,7 @@
         <v>4297</v>
       </c>
     </row>
-    <row r="149" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="149" spans="1:11">
       <c r="A149" s="10">
         <f t="shared" si="2"/>
         <v>44122</v>
@@ -5888,7 +5890,7 @@
       <c r="B149" s="8">
         <v>44123</v>
       </c>
-      <c r="C149" s="12">
+      <c r="C149" s="11">
         <v>0.70833333333333337</v>
       </c>
       <c r="D149" s="8" t="s">
@@ -5916,7 +5918,7 @@
         <v>4957</v>
       </c>
     </row>
-    <row r="150" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="150" spans="1:11">
       <c r="A150" s="10">
         <f t="shared" si="2"/>
         <v>44129</v>
@@ -5924,7 +5926,7 @@
       <c r="B150" s="8">
         <v>44130</v>
       </c>
-      <c r="C150" s="12">
+      <c r="C150" s="11">
         <v>0.70833333333333337</v>
       </c>
       <c r="D150" s="8" t="s">
@@ -5952,7 +5954,7 @@
         <v>5696</v>
       </c>
     </row>
-    <row r="151" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="151" spans="1:11">
       <c r="A151" s="10">
         <f t="shared" si="2"/>
         <v>44136</v>
@@ -5960,7 +5962,7 @@
       <c r="B151" s="8">
         <v>44137</v>
       </c>
-      <c r="C151" s="12">
+      <c r="C151" s="11">
         <v>0.70833333333333337</v>
       </c>
       <c r="D151" s="8" t="s">
@@ -5988,7 +5990,7 @@
         <v>6193</v>
       </c>
     </row>
-    <row r="152" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="152" spans="1:11">
       <c r="A152" s="10">
         <f t="shared" si="2"/>
         <v>44143</v>
@@ -5996,7 +5998,7 @@
       <c r="B152" s="8">
         <v>44144</v>
       </c>
-      <c r="C152" s="12">
+      <c r="C152" s="11">
         <v>0.70833333333333337</v>
       </c>
       <c r="D152" s="8" t="s">
@@ -6024,7 +6026,7 @@
         <v>6336</v>
       </c>
     </row>
-    <row r="153" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="153" spans="1:11">
       <c r="A153" s="10">
         <f t="shared" si="2"/>
         <v>44150</v>
@@ -6032,7 +6034,7 @@
       <c r="B153" s="8">
         <v>44151</v>
       </c>
-      <c r="C153" s="12">
+      <c r="C153" s="11">
         <v>0.70833333333333337</v>
       </c>
       <c r="D153" s="8" t="s">
@@ -6060,7 +6062,7 @@
         <v>6128</v>
       </c>
     </row>
-    <row r="154" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="154" spans="1:11">
       <c r="A154" s="10">
         <f t="shared" si="2"/>
         <v>44157</v>
@@ -6068,7 +6070,7 @@
       <c r="B154" s="8">
         <v>44158</v>
       </c>
-      <c r="C154" s="12">
+      <c r="C154" s="11">
         <v>0.70833333333333337</v>
       </c>
       <c r="D154" s="8" t="s">
@@ -6096,7 +6098,7 @@
         <v>5805</v>
       </c>
     </row>
-    <row r="155" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="155" spans="1:11">
       <c r="A155" s="10">
         <f t="shared" si="2"/>
         <v>44164</v>
@@ -6104,7 +6106,7 @@
       <c r="B155" s="8">
         <v>44165</v>
       </c>
-      <c r="C155" s="12">
+      <c r="C155" s="11">
         <v>0.70833333333333337</v>
       </c>
       <c r="D155" s="8" t="s">
@@ -6132,7 +6134,7 @@
         <v>6359</v>
       </c>
     </row>
-    <row r="156" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="156" spans="1:11">
       <c r="A156" s="10">
         <f t="shared" si="2"/>
         <v>44171</v>
@@ -6140,7 +6142,7 @@
       <c r="B156" s="8">
         <v>44172</v>
       </c>
-      <c r="C156" s="12">
+      <c r="C156" s="11">
         <v>0.70833333333333337</v>
       </c>
       <c r="D156" s="8" t="s">
@@ -6168,7 +6170,7 @@
         <v>6501</v>
       </c>
     </row>
-    <row r="157" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="157" spans="1:11">
       <c r="A157" s="10">
         <f t="shared" si="2"/>
         <v>44178</v>
@@ -6176,7 +6178,7 @@
       <c r="B157" s="8">
         <v>44179</v>
       </c>
-      <c r="C157" s="12">
+      <c r="C157" s="11">
         <v>0.70833333333333337</v>
       </c>
       <c r="D157" s="8" t="s">
@@ -6204,7 +6206,7 @@
         <v>6639</v>
       </c>
     </row>
-    <row r="158" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="158" spans="1:11">
       <c r="A158" s="10">
         <f t="shared" si="2"/>
         <v>44185</v>
@@ -6212,7 +6214,7 @@
       <c r="B158" s="8">
         <v>44186</v>
       </c>
-      <c r="C158" s="12">
+      <c r="C158" s="11">
         <v>0.70833333333333337</v>
       </c>
       <c r="D158" s="8" t="s">
@@ -6240,7 +6242,7 @@
         <v>6623</v>
       </c>
     </row>
-    <row r="159" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="159" spans="1:11">
       <c r="A159" s="10">
         <f t="shared" si="2"/>
         <v>44192</v>
@@ -6248,7 +6250,7 @@
       <c r="B159" s="8">
         <v>44193</v>
       </c>
-      <c r="C159" s="12">
+      <c r="C159" s="11">
         <v>0.70833333333333337</v>
       </c>
       <c r="D159" s="8" t="s">
@@ -6276,7 +6278,7 @@
         <v>6235</v>
       </c>
     </row>
-    <row r="160" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="160" spans="1:11">
       <c r="A160" s="10">
         <f t="shared" si="2"/>
         <v>44199</v>
@@ -6284,7 +6286,7 @@
       <c r="B160" s="8">
         <v>44200</v>
       </c>
-      <c r="C160" s="12">
+      <c r="C160" s="11">
         <v>0.70833333333333337</v>
       </c>
       <c r="D160" s="8" t="s">
@@ -6312,7 +6314,7 @@
         <v>6313</v>
       </c>
     </row>
-    <row r="161" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="161" spans="1:11">
       <c r="A161" s="10">
         <f t="shared" si="2"/>
         <v>44206</v>
@@ -6320,7 +6322,7 @@
       <c r="B161" s="8">
         <v>44207</v>
       </c>
-      <c r="C161" s="12">
+      <c r="C161" s="11">
         <v>0.70833333333333337</v>
       </c>
       <c r="D161" s="8" t="s">
@@ -6348,7 +6350,7 @@
         <v>5714</v>
       </c>
     </row>
-    <row r="162" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="162" spans="1:11">
       <c r="A162" s="10">
         <f t="shared" si="2"/>
         <v>44213</v>
@@ -6356,7 +6358,7 @@
       <c r="B162" s="8">
         <v>44214</v>
       </c>
-      <c r="C162" s="12">
+      <c r="C162" s="11">
         <v>0.70833333333333337</v>
       </c>
       <c r="D162" s="8" t="s">
@@ -6384,7 +6386,7 @@
         <v>4512</v>
       </c>
     </row>
-    <row r="163" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="163" spans="1:11">
       <c r="A163" s="10">
         <f t="shared" si="2"/>
         <v>44220</v>
@@ -6392,7 +6394,7 @@
       <c r="B163" s="8">
         <v>44221</v>
       </c>
-      <c r="C163" s="12">
+      <c r="C163" s="11">
         <v>0.70833333333333337</v>
       </c>
       <c r="D163" s="8" t="s">
@@ -6420,7 +6422,7 @@
         <v>4555</v>
       </c>
     </row>
-    <row r="164" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="164" spans="1:11">
       <c r="A164" s="10">
         <f t="shared" si="2"/>
         <v>44227</v>
@@ -6428,7 +6430,7 @@
       <c r="B164" s="8">
         <v>44228</v>
       </c>
-      <c r="C164" s="12">
+      <c r="C164" s="11">
         <v>0.70833333333333337</v>
       </c>
       <c r="D164" s="8" t="s">
@@ -6456,7 +6458,7 @@
         <v>5245</v>
       </c>
     </row>
-    <row r="165" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="165" spans="1:11">
       <c r="A165" s="10">
         <f t="shared" si="2"/>
         <v>44234</v>
@@ -6464,7 +6466,7 @@
       <c r="B165" s="8">
         <v>44235</v>
       </c>
-      <c r="C165" s="12">
+      <c r="C165" s="11">
         <v>0.70833333333333337</v>
       </c>
       <c r="D165" s="8" t="s">
@@ -6492,7 +6494,7 @@
         <v>5649</v>
       </c>
     </row>
-    <row r="166" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="166" spans="1:11">
       <c r="A166" s="10">
         <f t="shared" si="2"/>
         <v>44241</v>
@@ -6500,7 +6502,7 @@
       <c r="B166" s="8">
         <v>44242</v>
       </c>
-      <c r="C166" s="12">
+      <c r="C166" s="11">
         <v>0.70833333333333337</v>
       </c>
       <c r="D166" s="8" t="s">
@@ -6528,7 +6530,7 @@
         <v>6333</v>
       </c>
     </row>
-    <row r="167" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="167" spans="1:11">
       <c r="A167" s="10">
         <f t="shared" si="2"/>
         <v>44248</v>
@@ -6536,7 +6538,7 @@
       <c r="B167" s="8">
         <v>44249</v>
       </c>
-      <c r="C167" s="12">
+      <c r="C167" s="11">
         <v>0.70833333333333337</v>
       </c>
       <c r="D167" s="8" t="s">
@@ -6564,7 +6566,7 @@
         <v>4242</v>
       </c>
     </row>
-    <row r="168" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="168" spans="1:11">
       <c r="A168" s="10">
         <f t="shared" si="2"/>
         <v>44255</v>
@@ -6572,7 +6574,7 @@
       <c r="B168" s="8">
         <v>44256</v>
       </c>
-      <c r="C168" s="12">
+      <c r="C168" s="11">
         <v>0.70833333333333337</v>
       </c>
       <c r="D168" s="8" t="s">
@@ -6600,7 +6602,7 @@
         <v>4791</v>
       </c>
     </row>
-    <row r="169" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="169" spans="1:11">
       <c r="A169" s="10">
         <f t="shared" si="2"/>
         <v>44262</v>
@@ -6608,7 +6610,7 @@
       <c r="B169" s="8">
         <v>44263</v>
       </c>
-      <c r="C169" s="12">
+      <c r="C169" s="11">
         <v>0.70833333333333337</v>
       </c>
       <c r="D169" s="8" t="s">
@@ -6636,7 +6638,7 @@
         <v>4641</v>
       </c>
     </row>
-    <row r="170" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="170" spans="1:11">
       <c r="A170" s="10">
         <f t="shared" si="2"/>
         <v>44269</v>
@@ -6644,7 +6646,7 @@
       <c r="B170" s="8">
         <v>44270</v>
       </c>
-      <c r="C170" s="12">
+      <c r="C170" s="11">
         <v>0.70833333333333337</v>
       </c>
       <c r="D170" s="8" t="s">
@@ -6672,7 +6674,7 @@
         <v>4365</v>
       </c>
     </row>
-    <row r="171" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="171" spans="1:11">
       <c r="A171" s="10">
         <f t="shared" si="2"/>
         <v>44276</v>
@@ -6680,7 +6682,7 @@
       <c r="B171" s="8">
         <v>44277</v>
       </c>
-      <c r="C171" s="12">
+      <c r="C171" s="11">
         <v>0.70833333333333337</v>
       </c>
       <c r="D171" s="8" t="s">
@@ -6708,7 +6710,7 @@
         <v>4549</v>
       </c>
     </row>
-    <row r="172" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="172" spans="1:11">
       <c r="A172" s="10">
         <f t="shared" si="2"/>
         <v>44283</v>
@@ -6716,7 +6718,7 @@
       <c r="B172" s="8">
         <v>44284</v>
       </c>
-      <c r="C172" s="12">
+      <c r="C172" s="11">
         <v>0.70833333333333337</v>
       </c>
       <c r="D172" s="8" t="s">
@@ -6744,7 +6746,7 @@
         <v>4728</v>
       </c>
     </row>
-    <row r="173" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="173" spans="1:11">
       <c r="A173" s="10">
         <f t="shared" si="2"/>
         <v>44290</v>
@@ -6752,7 +6754,7 @@
       <c r="B173" s="8">
         <v>44291</v>
       </c>
-      <c r="C173" s="12">
+      <c r="C173" s="11">
         <v>0.70833333333333337</v>
       </c>
       <c r="D173" s="8" t="s">
@@ -6780,7 +6782,7 @@
         <v>5485</v>
       </c>
     </row>
-    <row r="174" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="174" spans="1:11">
       <c r="A174" s="10">
         <f t="shared" si="2"/>
         <v>44297</v>
@@ -6788,7 +6790,7 @@
       <c r="B174" s="8">
         <v>44298</v>
       </c>
-      <c r="C174" s="12">
+      <c r="C174" s="11">
         <v>0.70833333333333337</v>
       </c>
       <c r="D174" s="8" t="s">
@@ -6816,7 +6818,7 @@
         <v>6192</v>
       </c>
     </row>
-    <row r="175" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="175" spans="1:11">
       <c r="A175" s="10">
         <f t="shared" si="2"/>
         <v>44304</v>
@@ -6824,7 +6826,7 @@
       <c r="B175" s="8">
         <v>44305</v>
       </c>
-      <c r="C175" s="12">
+      <c r="C175" s="11">
         <v>0.70833333333333337</v>
       </c>
       <c r="D175" s="8" t="s">
@@ -6852,7 +6854,7 @@
         <v>5842</v>
       </c>
     </row>
-    <row r="176" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="176" spans="1:11">
       <c r="A176" s="10">
         <f t="shared" si="2"/>
         <v>44311</v>
@@ -6860,7 +6862,7 @@
       <c r="B176" s="8">
         <v>44312</v>
       </c>
-      <c r="C176" s="12">
+      <c r="C176" s="11">
         <v>0.70833333333333337</v>
       </c>
       <c r="D176" s="8" t="s">
@@ -6888,7 +6890,7 @@
         <v>6366</v>
       </c>
     </row>
-    <row r="177" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="177" spans="1:11">
       <c r="A177" s="10">
         <f t="shared" si="2"/>
         <v>44318</v>
@@ -6896,7 +6898,7 @@
       <c r="B177" s="8">
         <v>44319</v>
       </c>
-      <c r="C177" s="12">
+      <c r="C177" s="11">
         <v>0.70833333333333337</v>
       </c>
       <c r="D177" s="8" t="s">
@@ -6924,7 +6926,7 @@
         <v>6907</v>
       </c>
     </row>
-    <row r="178" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="178" spans="1:11">
       <c r="A178" s="10">
         <f t="shared" si="2"/>
         <v>44325</v>
@@ -6932,7 +6934,7 @@
       <c r="B178" s="8">
         <v>44326</v>
       </c>
-      <c r="C178" s="12">
+      <c r="C178" s="11">
         <v>0.70833333333333337</v>
       </c>
       <c r="D178" s="8" t="s">
@@ -6960,7 +6962,7 @@
         <v>6230</v>
       </c>
     </row>
-    <row r="179" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="179" spans="1:11">
       <c r="A179" s="10">
         <f t="shared" si="2"/>
         <v>44332</v>
@@ -6968,7 +6970,7 @@
       <c r="B179" s="8">
         <v>44333</v>
       </c>
-      <c r="C179" s="12">
+      <c r="C179" s="11">
         <v>0.70833333333333337</v>
       </c>
       <c r="D179" s="8" t="s">
@@ -6996,7 +6998,7 @@
         <v>6092</v>
       </c>
     </row>
-    <row r="180" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="180" spans="1:11">
       <c r="A180" s="10">
         <f t="shared" si="2"/>
         <v>44339</v>
@@ -7004,7 +7006,7 @@
       <c r="B180" s="8">
         <v>44340</v>
       </c>
-      <c r="C180" s="12">
+      <c r="C180" s="11">
         <v>0.70833333333333337</v>
       </c>
       <c r="D180" s="8" t="s">
@@ -7032,7 +7034,7 @@
         <v>6452</v>
       </c>
     </row>
-    <row r="181" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="181" spans="1:11">
       <c r="A181" s="10">
         <f t="shared" si="2"/>
         <v>44346</v>
@@ -7040,7 +7042,7 @@
       <c r="B181" s="8">
         <v>44347</v>
       </c>
-      <c r="C181" s="12">
+      <c r="C181" s="11">
         <v>0.70833333333333337</v>
       </c>
       <c r="D181" s="8" t="s">
@@ -7068,7 +7070,7 @@
         <v>5834</v>
       </c>
     </row>
-    <row r="182" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="182" spans="1:11">
       <c r="A182" s="10">
         <f t="shared" si="2"/>
         <v>44353</v>
@@ -7076,7 +7078,7 @@
       <c r="B182" s="8">
         <v>44354</v>
       </c>
-      <c r="C182" s="12">
+      <c r="C182" s="11">
         <v>0.70833333333333337</v>
       </c>
       <c r="D182" s="8" t="s">
@@ -7104,7 +7106,7 @@
         <v>5722</v>
       </c>
     </row>
-    <row r="183" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="183" spans="1:11">
       <c r="A183" s="10">
         <f t="shared" si="2"/>
         <v>44360</v>
@@ -7112,7 +7114,7 @@
       <c r="B183" s="8">
         <v>44361</v>
       </c>
-      <c r="C183" s="12">
+      <c r="C183" s="11">
         <v>0.70833333333333337</v>
       </c>
       <c r="D183" s="8" t="s">
@@ -7140,7 +7142,7 @@
         <v>5443</v>
       </c>
     </row>
-    <row r="184" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="184" spans="1:11">
       <c r="A184" s="10">
         <f t="shared" si="2"/>
         <v>44367</v>
@@ -7148,7 +7150,7 @@
       <c r="B184" s="8">
         <v>44368</v>
       </c>
-      <c r="C184" s="12">
+      <c r="C184" s="11">
         <v>0.70833333333333337</v>
       </c>
       <c r="D184" s="8" t="s">
@@ -7176,7 +7178,7 @@
         <v>4973</v>
       </c>
     </row>
-    <row r="185" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="185" spans="1:11">
       <c r="A185" s="10">
         <f t="shared" si="2"/>
         <v>44374</v>
@@ -7184,7 +7186,7 @@
       <c r="B185" s="8">
         <v>44375</v>
       </c>
-      <c r="C185" s="12">
+      <c r="C185" s="11">
         <v>0.70833333333333337</v>
       </c>
       <c r="D185" s="8" t="s">
@@ -7212,7 +7214,7 @@
         <v>5258</v>
       </c>
     </row>
-    <row r="186" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="186" spans="1:11">
       <c r="A186" s="10">
         <f t="shared" si="2"/>
         <v>44381</v>
@@ -7220,7 +7222,7 @@
       <c r="B186" s="8">
         <v>44382</v>
       </c>
-      <c r="C186" s="12">
+      <c r="C186" s="11">
         <v>0.70833333333333337</v>
       </c>
       <c r="D186" s="8" t="s">
@@ -7248,7 +7250,7 @@
         <v>5338</v>
       </c>
     </row>
-    <row r="187" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="187" spans="1:11">
       <c r="A187" s="10">
         <f t="shared" si="2"/>
         <v>44388</v>
@@ -7256,7 +7258,7 @@
       <c r="B187" s="8">
         <v>44389</v>
       </c>
-      <c r="C187" s="12">
+      <c r="C187" s="11">
         <v>0.70833333333333337</v>
       </c>
       <c r="D187" s="8" t="s">
@@ -7284,7 +7286,7 @@
         <v>5987</v>
       </c>
     </row>
-    <row r="188" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="188" spans="1:11">
       <c r="A188" s="10">
         <f t="shared" si="2"/>
         <v>44395</v>
@@ -7292,7 +7294,7 @@
       <c r="B188" s="8">
         <v>44396</v>
       </c>
-      <c r="C188" s="12">
+      <c r="C188" s="11">
         <v>0.70833333333333337</v>
       </c>
       <c r="D188" s="8" t="s">
@@ -7320,7 +7322,7 @@
         <v>5801</v>
       </c>
     </row>
-    <row r="189" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="189" spans="1:11">
       <c r="A189" s="10">
         <f t="shared" si="2"/>
         <v>44402</v>
@@ -7328,7 +7330,7 @@
       <c r="B189" s="8">
         <v>44403</v>
       </c>
-      <c r="C189" s="12">
+      <c r="C189" s="11">
         <v>0.70833333333333337</v>
       </c>
       <c r="D189" s="8" t="s">
@@ -7356,7 +7358,7 @@
         <v>5421</v>
       </c>
     </row>
-    <row r="190" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="190" spans="1:11">
       <c r="A190" s="10">
         <f t="shared" si="2"/>
         <v>44409</v>
@@ -7364,7 +7366,7 @@
       <c r="B190" s="8">
         <v>44410</v>
       </c>
-      <c r="C190" s="12">
+      <c r="C190" s="11">
         <v>0.70833333333333337</v>
       </c>
       <c r="D190" s="8" t="s">
@@ -7392,7 +7394,7 @@
         <v>5883</v>
       </c>
     </row>
-    <row r="191" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="191" spans="1:11">
       <c r="A191" s="10">
         <f t="shared" si="2"/>
         <v>44416</v>
@@ -7400,7 +7402,7 @@
       <c r="B191" s="8">
         <v>44417</v>
       </c>
-      <c r="C191" s="12">
+      <c r="C191" s="11">
         <v>0.70833333333333337</v>
       </c>
       <c r="D191" s="8" t="s">
@@ -7428,7 +7430,7 @@
         <v>5967</v>
       </c>
     </row>
-    <row r="192" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="192" spans="1:11">
       <c r="A192" s="10">
         <f t="shared" si="2"/>
         <v>44423</v>
@@ -7436,7 +7438,7 @@
       <c r="B192" s="8">
         <v>44424</v>
       </c>
-      <c r="C192" s="12">
+      <c r="C192" s="11">
         <v>0.70833333333333337</v>
       </c>
       <c r="D192" s="8" t="s">
@@ -7464,7 +7466,7 @@
         <v>6015</v>
       </c>
     </row>
-    <row r="193" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="193" spans="1:11">
       <c r="A193" s="10">
         <f t="shared" si="2"/>
         <v>44430</v>
@@ -7472,7 +7474,7 @@
       <c r="B193" s="8">
         <v>44431</v>
       </c>
-      <c r="C193" s="12">
+      <c r="C193" s="11">
         <v>0.70833333333333337</v>
       </c>
       <c r="D193" s="8" t="s">
@@ -7500,7 +7502,7 @@
         <v>6147</v>
       </c>
     </row>
-    <row r="194" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="194" spans="1:11">
       <c r="A194" s="10">
         <f t="shared" si="2"/>
         <v>44437</v>
@@ -7508,7 +7510,7 @@
       <c r="B194" s="8">
         <v>44438</v>
       </c>
-      <c r="C194" s="12">
+      <c r="C194" s="11">
         <v>0.70833333333333337</v>
       </c>
       <c r="D194" s="8" t="s">
@@ -7536,7 +7538,7 @@
         <v>7552</v>
       </c>
     </row>
-    <row r="195" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="195" spans="1:11">
       <c r="A195" s="10">
         <f t="shared" si="2"/>
         <v>44444</v>
@@ -7544,7 +7546,7 @@
       <c r="B195" s="8">
         <v>44445</v>
       </c>
-      <c r="C195" s="12">
+      <c r="C195" s="11">
         <v>0.70833333333333337</v>
       </c>
       <c r="D195" s="8" t="s">
@@ -7572,7 +7574,7 @@
         <v>8099</v>
       </c>
     </row>
-    <row r="196" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="196" spans="1:11">
       <c r="A196" s="10">
         <f t="shared" ref="A196:A259" si="3">B196-1</f>
         <v>44451</v>
@@ -7580,7 +7582,7 @@
       <c r="B196" s="8">
         <v>44452</v>
       </c>
-      <c r="C196" s="12">
+      <c r="C196" s="11">
         <v>0.70833333333333337</v>
       </c>
       <c r="D196" s="8" t="s">
@@ -7608,7 +7610,7 @@
         <v>8281</v>
       </c>
     </row>
-    <row r="197" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="197" spans="1:11">
       <c r="A197" s="10">
         <f t="shared" si="3"/>
         <v>44458</v>
@@ -7616,7 +7618,7 @@
       <c r="B197" s="8">
         <v>44459</v>
       </c>
-      <c r="C197" s="12">
+      <c r="C197" s="11">
         <v>0.70833333333333337</v>
       </c>
       <c r="D197" s="8" t="s">
@@ -7644,7 +7646,7 @@
         <v>9021</v>
       </c>
     </row>
-    <row r="198" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="198" spans="1:11">
       <c r="A198" s="10">
         <f t="shared" si="3"/>
         <v>44465</v>
@@ -7652,7 +7654,7 @@
       <c r="B198" s="8">
         <v>44466</v>
       </c>
-      <c r="C198" s="12">
+      <c r="C198" s="11">
         <v>0.70833333333333337</v>
       </c>
       <c r="D198" s="8" t="s">
@@ -7680,7 +7682,7 @@
         <v>9364</v>
       </c>
     </row>
-    <row r="199" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="199" spans="1:11">
       <c r="A199" s="10">
         <f t="shared" si="3"/>
         <v>44472</v>
@@ -7688,7 +7690,7 @@
       <c r="B199" s="8">
         <v>44473</v>
       </c>
-      <c r="C199" s="12">
+      <c r="C199" s="11">
         <v>0.70833333333333337</v>
       </c>
       <c r="D199" s="8" t="s">
@@ -7716,7 +7718,7 @@
         <v>9090</v>
       </c>
     </row>
-    <row r="200" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="200" spans="1:11">
       <c r="A200" s="10">
         <f t="shared" si="3"/>
         <v>44479</v>
@@ -7724,7 +7726,7 @@
       <c r="B200" s="8">
         <v>44480</v>
       </c>
-      <c r="C200" s="12">
+      <c r="C200" s="11">
         <v>0.70833333333333337</v>
       </c>
       <c r="D200" s="8" t="s">
@@ -7752,7 +7754,7 @@
         <v>8936</v>
       </c>
     </row>
-    <row r="201" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="201" spans="1:11">
       <c r="A201" s="10">
         <f t="shared" si="3"/>
         <v>44486</v>
@@ -7760,7 +7762,7 @@
       <c r="B201" s="8">
         <v>44487</v>
       </c>
-      <c r="C201" s="12">
+      <c r="C201" s="11">
         <v>0.70833333333333337</v>
       </c>
       <c r="D201" s="8" t="s">
@@ -7788,7 +7790,7 @@
         <v>8252</v>
       </c>
     </row>
-    <row r="202" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="202" spans="1:11">
       <c r="A202" s="10">
         <f t="shared" si="3"/>
         <v>44493</v>
@@ -7796,7 +7798,7 @@
       <c r="B202" s="8">
         <v>44494</v>
       </c>
-      <c r="C202" s="12">
+      <c r="C202" s="11">
         <v>0.70833333333333337</v>
       </c>
       <c r="D202" s="8" t="s">
@@ -7824,7 +7826,7 @@
         <v>8513</v>
       </c>
     </row>
-    <row r="203" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="203" spans="1:11">
       <c r="A203" s="10">
         <f t="shared" si="3"/>
         <v>44500</v>
@@ -7832,7 +7834,7 @@
       <c r="B203" s="8">
         <v>44501</v>
       </c>
-      <c r="C203" s="12">
+      <c r="C203" s="11">
         <v>0.70833333333333337</v>
       </c>
       <c r="D203" s="8" t="s">
@@ -7860,7 +7862,7 @@
         <v>8569</v>
       </c>
     </row>
-    <row r="204" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="204" spans="1:11">
       <c r="A204" s="10">
         <f t="shared" si="3"/>
         <v>44507</v>
@@ -7868,7 +7870,7 @@
       <c r="B204" s="8">
         <v>44508</v>
       </c>
-      <c r="C204" s="12">
+      <c r="C204" s="11">
         <v>0.70833333333333337</v>
       </c>
       <c r="D204" s="8" t="s">
@@ -7896,7 +7898,7 @@
         <v>10146</v>
       </c>
     </row>
-    <row r="205" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="205" spans="1:11">
       <c r="A205" s="10">
         <f t="shared" si="3"/>
         <v>44514</v>
@@ -7904,7 +7906,7 @@
       <c r="B205" s="8">
         <v>44515</v>
       </c>
-      <c r="C205" s="12">
+      <c r="C205" s="11">
         <v>0.70833333333333337</v>
       </c>
       <c r="D205" s="8" t="s">
@@ -7932,7 +7934,7 @@
         <v>9833</v>
       </c>
     </row>
-    <row r="206" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="206" spans="1:11">
       <c r="A206" s="10">
         <f t="shared" si="3"/>
         <v>44521</v>
@@ -7940,7 +7942,7 @@
       <c r="B206" s="8">
         <v>44522</v>
       </c>
-      <c r="C206" s="12">
+      <c r="C206" s="11">
         <v>0.70833333333333337</v>
       </c>
       <c r="D206" s="8" t="s">
@@ -7968,7 +7970,7 @@
         <v>10713</v>
       </c>
     </row>
-    <row r="207" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="207" spans="1:11">
       <c r="A207" s="10">
         <f t="shared" si="3"/>
         <v>44528</v>
@@ -7976,7 +7978,7 @@
       <c r="B207" s="8">
         <v>44529</v>
       </c>
-      <c r="C207" s="12">
+      <c r="C207" s="11">
         <v>0.70833333333333337</v>
       </c>
       <c r="D207" s="8" t="s">
@@ -8004,7 +8006,7 @@
         <v>10672</v>
       </c>
     </row>
-    <row r="208" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="208" spans="1:11">
       <c r="A208" s="10">
         <f t="shared" si="3"/>
         <v>44535</v>
@@ -8012,7 +8014,7 @@
       <c r="B208" s="8">
         <v>44536</v>
       </c>
-      <c r="C208" s="12">
+      <c r="C208" s="11">
         <v>0.70833333333333337</v>
       </c>
       <c r="D208" s="8" t="s">
@@ -8040,7 +8042,7 @@
         <v>11408</v>
       </c>
     </row>
-    <row r="209" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="209" spans="1:11">
       <c r="A209" s="10">
         <f t="shared" si="3"/>
         <v>44542</v>
@@ -8048,7 +8050,7 @@
       <c r="B209" s="8">
         <v>44543</v>
       </c>
-      <c r="C209" s="12">
+      <c r="C209" s="11">
         <v>0.70833333333333337</v>
       </c>
       <c r="D209" s="8" t="s">
@@ -8076,7 +8078,7 @@
         <v>12068</v>
       </c>
     </row>
-    <row r="210" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="210" spans="1:11">
       <c r="A210" s="10">
         <f t="shared" si="3"/>
         <v>44549</v>
@@ -8084,7 +8086,7 @@
       <c r="B210" s="8">
         <v>44550</v>
       </c>
-      <c r="C210" s="12">
+      <c r="C210" s="11">
         <v>0.70833333333333337</v>
       </c>
       <c r="D210" s="8" t="s">
@@ -8112,7 +8114,7 @@
         <v>10758</v>
       </c>
     </row>
-    <row r="211" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="211" spans="1:11">
       <c r="A211" s="10">
         <f t="shared" si="3"/>
         <v>44556</v>
@@ -8120,7 +8122,7 @@
       <c r="B211" s="8">
         <v>44557</v>
       </c>
-      <c r="C211" s="12">
+      <c r="C211" s="11">
         <v>0.70833333333333337</v>
       </c>
       <c r="D211" s="8" t="s">
@@ -8148,7 +8150,7 @@
         <v>10247</v>
       </c>
     </row>
-    <row r="212" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="212" spans="1:11">
       <c r="A212" s="10">
         <f t="shared" si="3"/>
         <v>44563</v>
@@ -8156,7 +8158,7 @@
       <c r="B212" s="8">
         <v>44564</v>
       </c>
-      <c r="C212" s="12">
+      <c r="C212" s="11">
         <v>0.70833333333333337</v>
       </c>
       <c r="D212" s="8" t="s">
@@ -8184,7 +8186,7 @@
         <v>9786</v>
       </c>
     </row>
-    <row r="213" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="213" spans="1:11">
       <c r="A213" s="10">
         <f t="shared" si="3"/>
         <v>44570</v>
@@ -8192,7 +8194,7 @@
       <c r="B213" s="8">
         <v>44571</v>
       </c>
-      <c r="C213" s="12">
+      <c r="C213" s="11">
         <v>0.70833333333333337</v>
       </c>
       <c r="D213" s="8" t="s">
@@ -8220,7 +8222,7 @@
         <v>8461</v>
       </c>
     </row>
-    <row r="214" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="214" spans="1:11">
       <c r="A214" s="10">
         <f t="shared" si="3"/>
         <v>44577</v>
@@ -8228,7 +8230,7 @@
       <c r="B214" s="8">
         <v>44578</v>
       </c>
-      <c r="C214" s="12">
+      <c r="C214" s="11">
         <v>0.70833333333333337</v>
       </c>
       <c r="D214" s="8" t="s">
@@ -8256,7 +8258,7 @@
         <v>6933</v>
       </c>
     </row>
-    <row r="215" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="215" spans="1:11">
       <c r="A215" s="10">
         <f t="shared" si="3"/>
         <v>44584</v>
@@ -8264,7 +8266,7 @@
       <c r="B215" s="8">
         <v>44585</v>
       </c>
-      <c r="C215" s="12">
+      <c r="C215" s="11">
         <v>0.70833333333333337</v>
       </c>
       <c r="D215" s="8" t="s">
@@ -8292,7 +8294,7 @@
         <v>7524</v>
       </c>
     </row>
-    <row r="216" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="216" spans="1:11">
       <c r="A216" s="10">
         <f t="shared" si="3"/>
         <v>44591</v>
@@ -8300,7 +8302,7 @@
       <c r="B216" s="8">
         <v>44592</v>
       </c>
-      <c r="C216" s="12">
+      <c r="C216" s="11">
         <v>0.70833333333333337</v>
       </c>
       <c r="D216" s="8" t="s">
@@ -8328,7 +8330,7 @@
         <v>7909</v>
       </c>
     </row>
-    <row r="217" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="217" spans="1:11">
       <c r="A217" s="10">
         <f t="shared" si="3"/>
         <v>44598</v>
@@ -8336,7 +8338,7 @@
       <c r="B217" s="8">
         <v>44599</v>
       </c>
-      <c r="C217" s="12">
+      <c r="C217" s="11">
         <v>0.70833333333333337</v>
       </c>
       <c r="D217" s="8" t="s">
@@ -8364,7 +8366,7 @@
         <v>6947</v>
       </c>
     </row>
-    <row r="218" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="218" spans="1:11">
       <c r="A218" s="10">
         <f t="shared" si="3"/>
         <v>44605</v>
@@ -8372,7 +8374,7 @@
       <c r="B218" s="8">
         <v>44606</v>
       </c>
-      <c r="C218" s="12">
+      <c r="C218" s="11">
         <v>0.70833333333333337</v>
       </c>
       <c r="D218" s="8" t="s">
@@ -8400,7 +8402,7 @@
         <v>6615</v>
       </c>
     </row>
-    <row r="219" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="219" spans="1:11">
       <c r="A219" s="10">
         <f t="shared" si="3"/>
         <v>44612</v>
@@ -8408,7 +8410,7 @@
       <c r="B219" s="8">
         <v>44613</v>
       </c>
-      <c r="C219" s="12">
+      <c r="C219" s="11">
         <v>0.70833333333333337</v>
       </c>
       <c r="D219" s="8" t="s">
@@ -8436,7 +8438,7 @@
         <v>6659</v>
       </c>
     </row>
-    <row r="220" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="220" spans="1:11">
       <c r="A220" s="10">
         <f t="shared" si="3"/>
         <v>44619</v>
@@ -8444,7 +8446,7 @@
       <c r="B220" s="8">
         <v>44620</v>
       </c>
-      <c r="C220" s="12">
+      <c r="C220" s="11">
         <v>0.70833333333333337</v>
       </c>
       <c r="D220" s="8" t="s">
@@ -8472,7 +8474,7 @@
         <v>6470</v>
       </c>
     </row>
-    <row r="221" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="221" spans="1:11">
       <c r="A221" s="10">
         <f t="shared" si="3"/>
         <v>44626</v>
@@ -8480,7 +8482,7 @@
       <c r="B221" s="8">
         <v>44627</v>
       </c>
-      <c r="C221" s="12">
+      <c r="C221" s="11">
         <v>0.70833333333333337</v>
       </c>
       <c r="D221" s="8" t="s">
@@ -8508,7 +8510,7 @@
         <v>5896</v>
       </c>
     </row>
-    <row r="222" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="222" spans="1:11">
       <c r="A222" s="10">
         <f t="shared" si="3"/>
         <v>44633</v>
@@ -8516,7 +8518,7 @@
       <c r="B222" s="8">
         <v>44634</v>
       </c>
-      <c r="C222" s="12">
+      <c r="C222" s="11">
         <v>0.70833333333333337</v>
       </c>
       <c r="D222" s="8" t="s">
@@ -8544,7 +8546,7 @@
         <v>7688</v>
       </c>
     </row>
-    <row r="223" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="223" spans="1:11">
       <c r="A223" s="10">
         <f t="shared" si="3"/>
         <v>44640</v>
@@ -8552,7 +8554,7 @@
       <c r="B223" s="8">
         <v>44641</v>
       </c>
-      <c r="C223" s="12">
+      <c r="C223" s="11">
         <v>0.70833333333333337</v>
       </c>
       <c r="D223" s="8" t="s">
@@ -8580,7 +8582,7 @@
         <v>7591</v>
       </c>
     </row>
-    <row r="224" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="224" spans="1:11">
       <c r="A224" s="10">
         <f t="shared" si="3"/>
         <v>44647</v>
@@ -8588,7 +8590,7 @@
       <c r="B224" s="8">
         <v>44648</v>
       </c>
-      <c r="C224" s="12">
+      <c r="C224" s="11">
         <v>0.70833333333333337</v>
       </c>
       <c r="D224" s="8" t="s">
@@ -8616,7 +8618,7 @@
         <v>7550</v>
       </c>
     </row>
-    <row r="225" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="225" spans="1:11">
       <c r="A225" s="10">
         <f t="shared" si="3"/>
         <v>44654</v>
@@ -8624,7 +8626,7 @@
       <c r="B225" s="8">
         <v>44655</v>
       </c>
-      <c r="C225" s="12">
+      <c r="C225" s="11">
         <v>0.70833333333333337</v>
       </c>
       <c r="D225" s="8" t="s">
@@ -8652,7 +8654,7 @@
         <v>8345</v>
       </c>
     </row>
-    <row r="226" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="226" spans="1:11">
       <c r="A226" s="10">
         <f t="shared" si="3"/>
         <v>44661</v>
@@ -8660,7 +8662,7 @@
       <c r="B226" s="8">
         <v>44662</v>
       </c>
-      <c r="C226" s="12">
+      <c r="C226" s="11">
         <v>0.70833333333333337</v>
       </c>
       <c r="D226" s="8" t="s">
@@ -8688,7 +8690,7 @@
         <v>8476</v>
       </c>
     </row>
-    <row r="227" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="227" spans="1:11">
       <c r="A227" s="10">
         <f t="shared" si="3"/>
         <v>44668</v>
@@ -8696,7 +8698,7 @@
       <c r="B227" s="8">
         <v>44669</v>
       </c>
-      <c r="C227" s="12">
+      <c r="C227" s="11">
         <v>0.70833333333333337</v>
       </c>
       <c r="D227" s="8" t="s">
@@ -8724,7 +8726,7 @@
         <v>7813</v>
       </c>
     </row>
-    <row r="228" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="228" spans="1:11">
       <c r="A228" s="10">
         <f t="shared" si="3"/>
         <v>44675</v>
@@ -8732,7 +8734,7 @@
       <c r="B228" s="8">
         <v>44676</v>
       </c>
-      <c r="C228" s="12">
+      <c r="C228" s="11">
         <v>0.70833333333333337</v>
       </c>
       <c r="D228" s="8" t="s">
@@ -8760,7 +8762,7 @@
         <v>8281</v>
       </c>
     </row>
-    <row r="229" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="229" spans="1:11">
       <c r="A229" s="10">
         <f t="shared" si="3"/>
         <v>44682</v>
@@ -8768,7 +8770,7 @@
       <c r="B229" s="8">
         <v>44683</v>
       </c>
-      <c r="C229" s="12">
+      <c r="C229" s="11">
         <v>0.70833333333333337</v>
       </c>
       <c r="D229" s="8" t="s">
@@ -8796,7 +8798,7 @@
         <v>7753</v>
       </c>
     </row>
-    <row r="230" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="230" spans="1:11">
       <c r="A230" s="10">
         <f t="shared" si="3"/>
         <v>44689</v>
@@ -8804,7 +8806,7 @@
       <c r="B230" s="8">
         <v>44690</v>
       </c>
-      <c r="C230" s="12">
+      <c r="C230" s="11">
         <v>0.70833333333333337</v>
       </c>
       <c r="D230" s="8" t="s">
@@ -8832,7 +8834,7 @@
         <v>7190</v>
       </c>
     </row>
-    <row r="231" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="231" spans="1:11">
       <c r="A231" s="10">
         <f t="shared" si="3"/>
         <v>44696</v>
@@ -8840,7 +8842,7 @@
       <c r="B231" s="8">
         <v>44697</v>
       </c>
-      <c r="C231" s="12">
+      <c r="C231" s="11">
         <v>0.70833333333333337</v>
       </c>
       <c r="D231" s="8" t="s">
@@ -8868,7 +8870,7 @@
         <v>7186</v>
       </c>
     </row>
-    <row r="232" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="232" spans="1:11">
       <c r="A232" s="10">
         <f t="shared" si="3"/>
         <v>44703</v>
@@ -8876,7 +8878,7 @@
       <c r="B232" s="8">
         <v>44704</v>
       </c>
-      <c r="C232" s="12">
+      <c r="C232" s="11">
         <v>0.70833333333333337</v>
       </c>
       <c r="D232" s="8" t="s">
@@ -8904,7 +8906,7 @@
         <v>7538</v>
       </c>
     </row>
-    <row r="233" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="233" spans="1:11">
       <c r="A233" s="10">
         <f t="shared" si="3"/>
         <v>44710</v>
@@ -8912,7 +8914,7 @@
       <c r="B233" s="8">
         <v>44711</v>
       </c>
-      <c r="C233" s="12">
+      <c r="C233" s="11">
         <v>0.70833333333333337</v>
       </c>
       <c r="D233" s="8" t="s">
@@ -8940,7 +8942,7 @@
         <v>7571</v>
       </c>
     </row>
-    <row r="234" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="234" spans="1:11">
       <c r="A234" s="10">
         <f t="shared" si="3"/>
         <v>44717</v>
@@ -8948,7 +8950,7 @@
       <c r="B234" s="8">
         <v>44718</v>
       </c>
-      <c r="C234" s="12">
+      <c r="C234" s="11">
         <v>0.70833333333333337</v>
       </c>
       <c r="D234" s="8" t="s">
@@ -8976,7 +8978,7 @@
         <v>7788</v>
       </c>
     </row>
-    <row r="235" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="235" spans="1:11">
       <c r="A235" s="10">
         <f t="shared" si="3"/>
         <v>44724</v>
@@ -8984,7 +8986,7 @@
       <c r="B235" s="8">
         <v>44725</v>
       </c>
-      <c r="C235" s="12">
+      <c r="C235" s="11">
         <v>0.70833333333333337</v>
       </c>
       <c r="D235" s="8" t="s">
@@ -9012,7 +9014,7 @@
         <v>7523</v>
       </c>
     </row>
-    <row r="236" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="236" spans="1:11">
       <c r="A236" s="10">
         <f t="shared" si="3"/>
         <v>44731</v>
@@ -9020,7 +9022,7 @@
       <c r="B236" s="8">
         <v>44732</v>
       </c>
-      <c r="C236" s="12">
+      <c r="C236" s="11">
         <v>0.70833333333333337</v>
       </c>
       <c r="D236" s="8" t="s">
@@ -9048,7 +9050,7 @@
         <v>7309</v>
       </c>
     </row>
-    <row r="237" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="237" spans="1:11">
       <c r="A237" s="10">
         <f t="shared" si="3"/>
         <v>44738</v>
@@ -9056,7 +9058,7 @@
       <c r="B237" s="8">
         <v>44739</v>
       </c>
-      <c r="C237" s="12">
+      <c r="C237" s="11">
         <v>0.70833333333333337</v>
       </c>
       <c r="D237" s="8" t="s">
@@ -9084,7 +9086,7 @@
         <v>7312</v>
       </c>
     </row>
-    <row r="238" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="238" spans="1:11">
       <c r="A238" s="10">
         <f t="shared" si="3"/>
         <v>44745</v>
@@ -9092,7 +9094,7 @@
       <c r="B238" s="8">
         <v>44746</v>
       </c>
-      <c r="C238" s="12">
+      <c r="C238" s="11">
         <v>0.70833333333333337</v>
       </c>
       <c r="D238" s="8" t="s">
@@ -9120,7 +9122,7 @@
         <v>7701</v>
       </c>
     </row>
-    <row r="239" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="239" spans="1:11">
       <c r="A239" s="10">
         <f t="shared" si="3"/>
         <v>44752</v>
@@ -9128,7 +9130,7 @@
       <c r="B239" s="8">
         <v>44753</v>
       </c>
-      <c r="C239" s="12">
+      <c r="C239" s="11">
         <v>0.70833333333333337</v>
       </c>
       <c r="D239" s="8" t="s">
@@ -9156,7 +9158,7 @@
         <v>7311</v>
       </c>
     </row>
-    <row r="240" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="240" spans="1:11">
       <c r="A240" s="10">
         <f t="shared" si="3"/>
         <v>44759</v>
@@ -9164,7 +9166,7 @@
       <c r="B240" s="8">
         <v>44760</v>
       </c>
-      <c r="C240" s="12">
+      <c r="C240" s="11">
         <v>0.70833333333333337</v>
       </c>
       <c r="D240" s="8" t="s">
@@ -9192,7 +9194,7 @@
         <v>6911</v>
       </c>
     </row>
-    <row r="241" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="241" spans="1:11">
       <c r="A241" s="10">
         <f t="shared" si="3"/>
         <v>44766</v>
@@ -9200,7 +9202,7 @@
       <c r="B241" s="8">
         <v>44767</v>
       </c>
-      <c r="C241" s="12">
+      <c r="C241" s="11">
         <v>0.70833333333333337</v>
       </c>
       <c r="D241" s="8" t="s">
@@ -9228,7 +9230,7 @@
         <v>6829</v>
       </c>
     </row>
-    <row r="242" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="242" spans="1:11">
       <c r="A242" s="10">
         <f t="shared" si="3"/>
         <v>44773</v>
@@ -9236,7 +9238,7 @@
       <c r="B242" s="8">
         <v>44774</v>
       </c>
-      <c r="C242" s="12">
+      <c r="C242" s="11">
         <v>0.70833333333333337</v>
       </c>
       <c r="D242" s="8" t="s">
@@ -9264,7 +9266,7 @@
         <v>6597</v>
       </c>
     </row>
-    <row r="243" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="243" spans="1:11">
       <c r="A243" s="10">
         <f t="shared" si="3"/>
         <v>44780</v>
@@ -9272,7 +9274,7 @@
       <c r="B243" s="8">
         <v>44781</v>
       </c>
-      <c r="C243" s="12">
+      <c r="C243" s="11">
         <v>0.70833333333333337</v>
       </c>
       <c r="D243" s="8" t="s">
@@ -9300,7 +9302,7 @@
         <v>6823</v>
       </c>
     </row>
-    <row r="244" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="244" spans="1:11">
       <c r="A244" s="10">
         <f t="shared" si="3"/>
         <v>44787</v>
@@ -9308,7 +9310,7 @@
       <c r="B244" s="8">
         <v>44788</v>
       </c>
-      <c r="C244" s="12">
+      <c r="C244" s="11">
         <v>0.70833333333333337</v>
       </c>
       <c r="D244" s="8" t="s">
@@ -9336,7 +9338,7 @@
         <v>6785</v>
       </c>
     </row>
-    <row r="245" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="245" spans="1:11">
       <c r="A245" s="10">
         <f t="shared" si="3"/>
         <v>44794</v>
@@ -9344,7 +9346,7 @@
       <c r="B245" s="8">
         <v>44795</v>
       </c>
-      <c r="C245" s="12">
+      <c r="C245" s="11">
         <v>0.70833333333333337</v>
       </c>
       <c r="D245" s="8" t="s">
@@ -9372,7 +9374,7 @@
         <v>6948</v>
       </c>
     </row>
-    <row r="246" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="246" spans="1:11">
       <c r="A246" s="10">
         <f t="shared" si="3"/>
         <v>44801</v>
@@ -9380,7 +9382,7 @@
       <c r="B246" s="8">
         <v>44802</v>
       </c>
-      <c r="C246" s="12">
+      <c r="C246" s="11">
         <v>0.70833333333333337</v>
       </c>
       <c r="D246" s="8" t="s">
@@ -9408,7 +9410,7 @@
         <v>6759</v>
       </c>
     </row>
-    <row r="247" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="247" spans="1:11">
       <c r="A247" s="10">
         <f t="shared" si="3"/>
         <v>44808</v>
@@ -9416,7 +9418,7 @@
       <c r="B247" s="8">
         <v>44809</v>
       </c>
-      <c r="C247" s="12">
+      <c r="C247" s="11">
         <v>0.70833333333333337</v>
       </c>
       <c r="D247" s="8" t="s">
@@ -9444,7 +9446,7 @@
         <v>6421</v>
       </c>
     </row>
-    <row r="248" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="248" spans="1:11">
       <c r="A248" s="10">
         <f t="shared" si="3"/>
         <v>44815</v>
@@ -9452,7 +9454,7 @@
       <c r="B248" s="8">
         <v>44816</v>
       </c>
-      <c r="C248" s="12">
+      <c r="C248" s="11">
         <v>0.70833333333333337</v>
       </c>
       <c r="D248" s="8" t="s">
@@ -9480,7 +9482,7 @@
         <v>6562</v>
       </c>
     </row>
-    <row r="249" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="249" spans="1:11">
       <c r="A249" s="10">
         <f t="shared" si="3"/>
         <v>44822</v>
@@ -9488,7 +9490,7 @@
       <c r="B249" s="8">
         <v>44823</v>
       </c>
-      <c r="C249" s="12">
+      <c r="C249" s="11">
         <v>0.70833333333333337</v>
       </c>
       <c r="D249" s="8" t="s">
@@ -9516,7 +9518,7 @@
         <v>6719</v>
       </c>
     </row>
-    <row r="250" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="250" spans="1:11">
       <c r="A250" s="10">
         <f t="shared" si="3"/>
         <v>44829</v>
@@ -9524,7 +9526,7 @@
       <c r="B250" s="8">
         <v>44830</v>
       </c>
-      <c r="C250" s="12">
+      <c r="C250" s="11">
         <v>0.70833333333333337</v>
       </c>
       <c r="D250" s="8" t="s">
@@ -9552,7 +9554,7 @@
         <v>6157</v>
       </c>
     </row>
-    <row r="251" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="251" spans="1:11">
       <c r="A251" s="10">
         <f t="shared" si="3"/>
         <v>44836</v>
@@ -9560,7 +9562,7 @@
       <c r="B251" s="8">
         <v>44837</v>
       </c>
-      <c r="C251" s="12">
+      <c r="C251" s="11">
         <v>0.70833333333333337</v>
       </c>
       <c r="D251" s="8" t="s">
@@ -9588,7 +9590,7 @@
         <v>5844</v>
       </c>
     </row>
-    <row r="252" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="252" spans="1:11">
       <c r="A252" s="10">
         <f t="shared" si="3"/>
         <v>44843</v>
@@ -9596,7 +9598,7 @@
       <c r="B252" s="8">
         <v>44844</v>
       </c>
-      <c r="C252" s="12">
+      <c r="C252" s="11">
         <v>0.70833333333333337</v>
       </c>
       <c r="D252" s="8" t="s">
@@ -9624,7 +9626,7 @@
         <v>5551</v>
       </c>
     </row>
-    <row r="253" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="253" spans="1:11">
       <c r="A253" s="10">
         <f t="shared" si="3"/>
         <v>44850</v>
@@ -9632,7 +9634,7 @@
       <c r="B253" s="8">
         <v>44851</v>
       </c>
-      <c r="C253" s="12">
+      <c r="C253" s="11">
         <v>0.70833333333333337</v>
       </c>
       <c r="D253" s="8" t="s">
@@ -9660,7 +9662,7 @@
         <v>5560</v>
       </c>
     </row>
-    <row r="254" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="254" spans="1:11">
       <c r="A254" s="10">
         <f t="shared" si="3"/>
         <v>44857</v>
@@ -9668,7 +9670,7 @@
       <c r="B254" s="8">
         <v>44858</v>
       </c>
-      <c r="C254" s="12">
+      <c r="C254" s="11">
         <v>0.70833333333333337</v>
       </c>
       <c r="D254" s="8" t="s">
@@ -9696,7 +9698,7 @@
         <v>6090</v>
       </c>
     </row>
-    <row r="255" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="255" spans="1:11">
       <c r="A255" s="10">
         <f t="shared" si="3"/>
         <v>44864</v>
@@ -9704,7 +9706,7 @@
       <c r="B255" s="8">
         <v>44865</v>
       </c>
-      <c r="C255" s="12">
+      <c r="C255" s="11">
         <v>0.70833333333333337</v>
       </c>
       <c r="D255" s="8" t="s">
@@ -9732,7 +9734,7 @@
         <v>5724</v>
       </c>
     </row>
-    <row r="256" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="256" spans="1:11">
       <c r="A256" s="10">
         <f t="shared" si="3"/>
         <v>44871</v>
@@ -9740,7 +9742,7 @@
       <c r="B256" s="8">
         <v>44872</v>
       </c>
-      <c r="C256" s="12">
+      <c r="C256" s="11">
         <v>0.70833333333333337</v>
       </c>
       <c r="D256" s="8" t="s">
@@ -9768,7 +9770,7 @@
         <v>5488</v>
       </c>
     </row>
-    <row r="257" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="257" spans="1:11">
       <c r="A257" s="10">
         <f t="shared" si="3"/>
         <v>44878</v>
@@ -9776,7 +9778,7 @@
       <c r="B257" s="8">
         <v>44879</v>
       </c>
-      <c r="C257" s="12">
+      <c r="C257" s="11">
         <v>0.70833333333333337</v>
       </c>
       <c r="D257" s="8" t="s">
@@ -9804,7 +9806,7 @@
         <v>5118</v>
       </c>
     </row>
-    <row r="258" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="258" spans="1:11">
       <c r="A258" s="10">
         <f t="shared" si="3"/>
         <v>44885</v>
@@ -9812,7 +9814,7 @@
       <c r="B258" s="8">
         <v>44886</v>
       </c>
-      <c r="C258" s="12">
+      <c r="C258" s="11">
         <v>0.70833333333333337</v>
       </c>
       <c r="D258" s="8" t="s">
@@ -9840,7 +9842,7 @@
         <v>5205</v>
       </c>
     </row>
-    <row r="259" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="259" spans="1:11">
       <c r="A259" s="10">
         <f t="shared" si="3"/>
         <v>44892</v>
@@ -9848,7 +9850,7 @@
       <c r="B259" s="8">
         <v>44893</v>
       </c>
-      <c r="C259" s="12">
+      <c r="C259" s="11">
         <v>0.70833333333333337</v>
       </c>
       <c r="D259" s="8" t="s">
@@ -9876,7 +9878,7 @@
         <v>5070</v>
       </c>
     </row>
-    <row r="260" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="260" spans="1:11">
       <c r="A260" s="10">
         <f t="shared" ref="A260:A323" si="4">B260-1</f>
         <v>44899</v>
@@ -9884,7 +9886,7 @@
       <c r="B260" s="8">
         <v>44900</v>
       </c>
-      <c r="C260" s="12">
+      <c r="C260" s="11">
         <v>0.70833333333333337</v>
       </c>
       <c r="D260" s="8" t="s">
@@ -9912,7 +9914,7 @@
         <v>5242</v>
       </c>
     </row>
-    <row r="261" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="261" spans="1:11">
       <c r="A261" s="10">
         <f t="shared" si="4"/>
         <v>44906</v>
@@ -9920,7 +9922,7 @@
       <c r="B261" s="8">
         <v>44907</v>
       </c>
-      <c r="C261" s="12">
+      <c r="C261" s="11">
         <v>0.70833333333333337</v>
       </c>
       <c r="D261" s="8" t="s">
@@ -9948,7 +9950,7 @@
         <v>4946</v>
       </c>
     </row>
-    <row r="262" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="262" spans="1:11">
       <c r="A262" s="10">
         <f t="shared" si="4"/>
         <v>44913</v>
@@ -9956,7 +9958,7 @@
       <c r="B262" s="8">
         <v>44914</v>
       </c>
-      <c r="C262" s="12">
+      <c r="C262" s="11">
         <v>0.70833333333333337</v>
       </c>
       <c r="D262" s="8" t="s">
@@ -9984,7 +9986,7 @@
         <v>5665</v>
       </c>
     </row>
-    <row r="263" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="263" spans="1:11">
       <c r="A263" s="10">
         <f t="shared" si="4"/>
         <v>44920</v>
@@ -9992,7 +9994,7 @@
       <c r="B263" s="8">
         <v>44921</v>
       </c>
-      <c r="C263" s="12">
+      <c r="C263" s="11">
         <v>0.70833333333333337</v>
       </c>
       <c r="D263" s="8" t="s">
@@ -10020,7 +10022,7 @@
         <v>5702</v>
       </c>
     </row>
-    <row r="264" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="264" spans="1:11">
       <c r="A264" s="10">
         <f t="shared" si="4"/>
         <v>44927</v>
@@ -10028,7 +10030,7 @@
       <c r="B264" s="8">
         <v>44928</v>
       </c>
-      <c r="C264" s="12">
+      <c r="C264" s="11">
         <v>0.70833333333333337</v>
       </c>
       <c r="D264" s="8" t="s">
@@ -10056,7 +10058,7 @@
         <v>5586</v>
       </c>
     </row>
-    <row r="265" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="265" spans="1:11">
       <c r="A265" s="10">
         <f t="shared" si="4"/>
         <v>44934</v>
@@ -10064,7 +10066,7 @@
       <c r="B265" s="8">
         <v>44935</v>
       </c>
-      <c r="C265" s="12">
+      <c r="C265" s="11">
         <v>0.70833333333333337</v>
       </c>
       <c r="D265" s="8" t="s">
@@ -10092,7 +10094,7 @@
         <v>5009</v>
       </c>
     </row>
-    <row r="266" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="266" spans="1:11">
       <c r="A266" s="10">
         <f t="shared" si="4"/>
         <v>44941</v>
@@ -10100,7 +10102,7 @@
       <c r="B266" s="8">
         <v>44942</v>
       </c>
-      <c r="C266" s="12">
+      <c r="C266" s="11">
         <v>0.70833333333333337</v>
       </c>
       <c r="D266" s="8" t="s">
@@ -10128,7 +10130,7 @@
         <v>5141</v>
       </c>
     </row>
-    <row r="267" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="267" spans="1:11">
       <c r="A267" s="10">
         <f t="shared" si="4"/>
         <v>44948</v>
@@ -10136,7 +10138,7 @@
       <c r="B267" s="8">
         <v>44949</v>
       </c>
-      <c r="C267" s="12">
+      <c r="C267" s="11">
         <v>0.70833333333333337</v>
       </c>
       <c r="D267" s="8" t="s">
@@ -10164,7 +10166,7 @@
         <v>4669</v>
       </c>
     </row>
-    <row r="268" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="268" spans="1:11">
       <c r="A268" s="10">
         <f t="shared" si="4"/>
         <v>44955</v>
@@ -10172,7 +10174,7 @@
       <c r="B268" s="8">
         <v>44956</v>
       </c>
-      <c r="C268" s="12">
+      <c r="C268" s="11">
         <v>0.70833333333333337</v>
       </c>
       <c r="D268" s="8" t="s">
@@ -10200,7 +10202,7 @@
         <v>4191</v>
       </c>
     </row>
-    <row r="269" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="269" spans="1:11">
       <c r="A269" s="10">
         <f t="shared" si="4"/>
         <v>44962</v>
@@ -10208,7 +10210,7 @@
       <c r="B269" s="8">
         <v>44963</v>
       </c>
-      <c r="C269" s="12">
+      <c r="C269" s="11">
         <v>0.70833333333333337</v>
       </c>
       <c r="D269" s="8" t="s">
@@ -10236,7 +10238,7 @@
         <v>4595</v>
       </c>
     </row>
-    <row r="270" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="270" spans="1:11">
       <c r="A270" s="10">
         <f t="shared" si="4"/>
         <v>44969</v>
@@ -10244,7 +10246,7 @@
       <c r="B270" s="8">
         <v>44970</v>
       </c>
-      <c r="C270" s="12">
+      <c r="C270" s="11">
         <v>0.70833333333333337</v>
       </c>
       <c r="D270" s="8" t="s">
@@ -10272,7 +10274,7 @@
         <v>4305</v>
       </c>
     </row>
-    <row r="271" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="271" spans="1:11">
       <c r="A271" s="10">
         <f t="shared" si="4"/>
         <v>44976</v>
@@ -10280,7 +10282,7 @@
       <c r="B271" s="8">
         <v>44977</v>
       </c>
-      <c r="C271" s="12">
+      <c r="C271" s="11">
         <v>0.70833333333333337</v>
       </c>
       <c r="D271" s="8" t="s">
@@ -10308,7 +10310,7 @@
         <v>4094</v>
       </c>
     </row>
-    <row r="272" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="272" spans="1:11">
       <c r="A272" s="10">
         <f t="shared" si="4"/>
         <v>44983</v>
@@ -10316,7 +10318,7 @@
       <c r="B272" s="8">
         <v>44984</v>
       </c>
-      <c r="C272" s="12">
+      <c r="C272" s="11">
         <v>0.70833333333333337</v>
       </c>
       <c r="D272" s="8" t="s">
@@ -10344,7 +10346,7 @@
         <v>3701</v>
       </c>
     </row>
-    <row r="273" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="273" spans="1:11">
       <c r="A273" s="10">
         <f t="shared" si="4"/>
         <v>44990</v>
@@ -10352,7 +10354,7 @@
       <c r="B273" s="8">
         <v>44991</v>
       </c>
-      <c r="C273" s="12">
+      <c r="C273" s="11">
         <v>0.70833333333333337</v>
       </c>
       <c r="D273" s="8" t="s">
@@ -10380,7 +10382,7 @@
         <v>4039</v>
       </c>
     </row>
-    <row r="274" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="274" spans="1:11">
       <c r="A274" s="10">
         <f t="shared" si="4"/>
         <v>44997</v>
@@ -10388,7 +10390,7 @@
       <c r="B274" s="8">
         <v>44998</v>
       </c>
-      <c r="C274" s="12">
+      <c r="C274" s="11">
         <v>0.70833333333333337</v>
       </c>
       <c r="D274" s="8" t="s">
@@ -10416,7 +10418,7 @@
         <v>4303</v>
       </c>
     </row>
-    <row r="275" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="275" spans="1:11">
       <c r="A275" s="10">
         <f t="shared" si="4"/>
         <v>45004</v>
@@ -10424,7 +10426,7 @@
       <c r="B275" s="8">
         <v>45005</v>
       </c>
-      <c r="C275" s="12">
+      <c r="C275" s="11">
         <v>0.70833333333333337</v>
       </c>
       <c r="D275" s="8" t="s">
@@ -10452,7 +10454,7 @@
         <v>4582</v>
       </c>
     </row>
-    <row r="276" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="276" spans="1:11">
       <c r="A276" s="10">
         <f t="shared" si="4"/>
         <v>45011</v>
@@ -10460,7 +10462,7 @@
       <c r="B276" s="8">
         <v>45012</v>
       </c>
-      <c r="C276" s="12">
+      <c r="C276" s="11">
         <v>0.70833333333333337</v>
       </c>
       <c r="D276" s="8" t="s">
@@ -10488,7 +10490,7 @@
         <v>4839</v>
       </c>
     </row>
-    <row r="277" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="277" spans="1:11">
       <c r="A277" s="10">
         <f t="shared" si="4"/>
         <v>45018</v>
@@ -10496,7 +10498,7 @@
       <c r="B277" s="8">
         <v>45019</v>
       </c>
-      <c r="C277" s="12">
+      <c r="C277" s="11">
         <v>0.70833333333333337</v>
       </c>
       <c r="D277" s="8" t="s">
@@ -10524,7 +10526,7 @@
         <v>4637</v>
       </c>
     </row>
-    <row r="278" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="278" spans="1:11">
       <c r="A278" s="10">
         <f t="shared" si="4"/>
         <v>45025</v>
@@ -10532,7 +10534,7 @@
       <c r="B278" s="8">
         <v>45026</v>
       </c>
-      <c r="C278" s="12">
+      <c r="C278" s="11">
         <v>0.70833333333333337</v>
       </c>
       <c r="D278" s="8" t="s">
@@ -10560,7 +10562,7 @@
         <v>4417</v>
       </c>
     </row>
-    <row r="279" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="279" spans="1:11">
       <c r="A279" s="10">
         <f t="shared" si="4"/>
         <v>45032</v>
@@ -10568,7 +10570,7 @@
       <c r="B279" s="8">
         <v>45033</v>
       </c>
-      <c r="C279" s="12">
+      <c r="C279" s="11">
         <v>0.70833333333333337</v>
       </c>
       <c r="D279" s="8" t="s">
@@ -10596,7 +10598,7 @@
         <v>4183</v>
       </c>
     </row>
-    <row r="280" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="280" spans="1:11">
       <c r="A280" s="10">
         <f t="shared" si="4"/>
         <v>45039</v>
@@ -10604,7 +10606,7 @@
       <c r="B280" s="8">
         <v>45040</v>
       </c>
-      <c r="C280" s="12">
+      <c r="C280" s="11">
         <v>0.70833333333333337</v>
       </c>
       <c r="D280" s="8" t="s">
@@ -10632,7 +10634,7 @@
         <v>4090</v>
       </c>
     </row>
-    <row r="281" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="281" spans="1:11">
       <c r="A281" s="10">
         <f t="shared" si="4"/>
         <v>45046</v>
@@ -10640,7 +10642,7 @@
       <c r="B281" s="8">
         <v>45047</v>
       </c>
-      <c r="C281" s="12">
+      <c r="C281" s="11">
         <v>0.70833333333333337</v>
       </c>
       <c r="D281" s="8" t="s">
@@ -10668,7 +10670,7 @@
         <v>3995</v>
       </c>
     </row>
-    <row r="282" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="282" spans="1:11">
       <c r="A282" s="10">
         <f t="shared" si="4"/>
         <v>45053</v>
@@ -10676,7 +10678,7 @@
       <c r="B282" s="8">
         <v>45054</v>
       </c>
-      <c r="C282" s="12">
+      <c r="C282" s="11">
         <v>0.70833333333333337</v>
       </c>
       <c r="D282" s="8" t="s">
@@ -10704,7 +10706,7 @@
         <v>3623</v>
       </c>
     </row>
-    <row r="283" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="283" spans="1:11">
       <c r="A283" s="10">
         <f t="shared" si="4"/>
         <v>45060</v>
@@ -10712,7 +10714,7 @@
       <c r="B283" s="8">
         <v>45061</v>
       </c>
-      <c r="C283" s="12">
+      <c r="C283" s="11">
         <v>0.70833333333333337</v>
       </c>
       <c r="D283" s="8" t="s">
@@ -10740,7 +10742,7 @@
         <v>3519</v>
       </c>
     </row>
-    <row r="284" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="284" spans="1:11">
       <c r="A284" s="10">
         <f t="shared" si="4"/>
         <v>45067</v>
@@ -10748,7 +10750,7 @@
       <c r="B284" s="8">
         <v>45068</v>
       </c>
-      <c r="C284" s="12">
+      <c r="C284" s="11">
         <v>0.70833333333333337</v>
       </c>
       <c r="D284" s="8" t="s">
@@ -10776,7 +10778,7 @@
         <v>3513</v>
       </c>
     </row>
-    <row r="285" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="285" spans="1:11">
       <c r="A285" s="10">
         <f t="shared" si="4"/>
         <v>45074</v>
@@ -10784,7 +10786,7 @@
       <c r="B285" s="8">
         <v>45075</v>
       </c>
-      <c r="C285" s="12">
+      <c r="C285" s="11">
         <v>0.70833333333333337</v>
       </c>
       <c r="D285" s="8" t="s">
@@ -10812,7 +10814,7 @@
         <v>3501</v>
       </c>
     </row>
-    <row r="286" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="286" spans="1:11">
       <c r="A286" s="10">
         <f t="shared" si="4"/>
         <v>45081</v>
@@ -10820,7 +10822,7 @@
       <c r="B286" s="8">
         <v>45082</v>
       </c>
-      <c r="C286" s="12">
+      <c r="C286" s="11">
         <v>0.70833333333333337</v>
       </c>
       <c r="D286" s="8" t="s">
@@ -10848,7 +10850,7 @@
         <v>3441</v>
       </c>
     </row>
-    <row r="287" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="287" spans="1:11">
       <c r="A287" s="10">
         <f t="shared" si="4"/>
         <v>45088</v>
@@ -10856,7 +10858,7 @@
       <c r="B287" s="8">
         <v>45089</v>
       </c>
-      <c r="C287" s="12">
+      <c r="C287" s="11">
         <v>0.70833333333333337</v>
       </c>
       <c r="D287" s="8" t="s">
@@ -10884,7 +10886,7 @@
         <v>3489</v>
       </c>
     </row>
-    <row r="288" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="288" spans="1:11">
       <c r="A288" s="10">
         <f t="shared" si="4"/>
         <v>45095</v>
@@ -10892,7 +10894,7 @@
       <c r="B288" s="8">
         <v>45096</v>
       </c>
-      <c r="C288" s="12">
+      <c r="C288" s="11">
         <v>0.70833333333333337</v>
       </c>
       <c r="D288" s="8" t="s">
@@ -10920,7 +10922,7 @@
         <v>3524</v>
       </c>
     </row>
-    <row r="289" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="289" spans="1:11">
       <c r="A289" s="10">
         <f t="shared" si="4"/>
         <v>45102</v>
@@ -10928,7 +10930,7 @@
       <c r="B289" s="8">
         <v>45103</v>
       </c>
-      <c r="C289" s="12">
+      <c r="C289" s="11">
         <v>0.70833333333333337</v>
       </c>
       <c r="D289" s="8" t="s">
@@ -10956,7 +10958,7 @@
         <v>3497</v>
       </c>
     </row>
-    <row r="290" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="290" spans="1:11">
       <c r="A290" s="10">
         <f t="shared" si="4"/>
         <v>45109</v>
@@ -10964,7 +10966,7 @@
       <c r="B290" s="8">
         <v>45110</v>
       </c>
-      <c r="C290" s="12">
+      <c r="C290" s="11">
         <v>0.70833333333333337</v>
       </c>
       <c r="D290" s="8" t="s">
@@ -10992,7 +10994,7 @@
         <v>3333</v>
       </c>
     </row>
-    <row r="291" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="291" spans="1:11">
       <c r="A291" s="10">
         <f t="shared" si="4"/>
         <v>45116</v>
@@ -11000,7 +11002,7 @@
       <c r="B291" s="8">
         <v>45117</v>
       </c>
-      <c r="C291" s="12">
+      <c r="C291" s="11">
         <v>0.70833333333333337</v>
       </c>
       <c r="D291" s="8" t="s">
@@ -11028,7 +11030,7 @@
         <v>3428</v>
       </c>
     </row>
-    <row r="292" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="292" spans="1:11">
       <c r="A292" s="10">
         <f t="shared" si="4"/>
         <v>45123</v>
@@ -11036,7 +11038,7 @@
       <c r="B292" s="8">
         <v>45124</v>
       </c>
-      <c r="C292" s="12">
+      <c r="C292" s="11">
         <v>0.70833333333333337</v>
       </c>
       <c r="D292" s="8" t="s">
@@ -11064,7 +11066,7 @@
         <v>3588</v>
       </c>
     </row>
-    <row r="293" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="293" spans="1:11">
       <c r="A293" s="10">
         <f t="shared" si="4"/>
         <v>45130</v>
@@ -11072,7 +11074,7 @@
       <c r="B293" s="8">
         <v>45131</v>
       </c>
-      <c r="C293" s="12">
+      <c r="C293" s="11">
         <v>0.70833333333333337</v>
       </c>
       <c r="D293" s="8" t="s">
@@ -11100,7 +11102,7 @@
         <v>3445</v>
       </c>
     </row>
-    <row r="294" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="294" spans="1:11">
       <c r="A294" s="10">
         <f t="shared" si="4"/>
         <v>45137</v>
@@ -11108,7 +11110,7 @@
       <c r="B294" s="8">
         <v>45138</v>
       </c>
-      <c r="C294" s="12">
+      <c r="C294" s="11">
         <v>0.70833333333333337</v>
       </c>
       <c r="D294" s="8" t="s">
@@ -11136,7 +11138,7 @@
         <v>3453</v>
       </c>
     </row>
-    <row r="295" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="295" spans="1:11">
       <c r="A295" s="10">
         <f t="shared" si="4"/>
         <v>45144</v>
@@ -11144,7 +11146,7 @@
       <c r="B295" s="8">
         <v>45145</v>
       </c>
-      <c r="C295" s="12">
+      <c r="C295" s="11">
         <v>0.70833333333333337</v>
       </c>
       <c r="D295" s="8" t="s">
@@ -11172,7 +11174,7 @@
         <v>3501</v>
       </c>
     </row>
-    <row r="296" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="296" spans="1:11">
       <c r="A296" s="10">
         <f t="shared" si="4"/>
         <v>45151</v>
@@ -11180,7 +11182,7 @@
       <c r="B296" s="8">
         <v>45152</v>
       </c>
-      <c r="C296" s="12">
+      <c r="C296" s="11">
         <v>0.70833333333333337</v>
       </c>
       <c r="D296" s="8" t="s">
@@ -11208,7 +11210,7 @@
         <v>3579</v>
       </c>
     </row>
-    <row r="297" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="297" spans="1:11">
       <c r="A297" s="10">
         <f t="shared" si="4"/>
         <v>45158</v>
@@ -11216,7 +11218,7 @@
       <c r="B297" s="8">
         <v>45159</v>
       </c>
-      <c r="C297" s="12">
+      <c r="C297" s="11">
         <v>0.70833333333333337</v>
       </c>
       <c r="D297" s="8" t="s">
@@ -11244,7 +11246,7 @@
         <v>3584</v>
       </c>
     </row>
-    <row r="298" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="298" spans="1:11">
       <c r="A298" s="10">
         <f t="shared" si="4"/>
         <v>45165</v>
@@ -11252,7 +11254,7 @@
       <c r="B298" s="8">
         <v>45166</v>
       </c>
-      <c r="C298" s="12">
+      <c r="C298" s="11">
         <v>0.70833333333333337</v>
       </c>
       <c r="D298" s="8" t="s">
@@ -11280,7 +11282,7 @@
         <v>3591</v>
       </c>
     </row>
-    <row r="299" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="299" spans="1:11">
       <c r="A299" s="10">
         <f t="shared" si="4"/>
         <v>45172</v>
@@ -11288,7 +11290,7 @@
       <c r="B299" s="8">
         <v>45173</v>
       </c>
-      <c r="C299" s="12">
+      <c r="C299" s="11">
         <v>0.70833333333333337</v>
       </c>
       <c r="D299" s="8" t="s">
@@ -11316,7 +11318,7 @@
         <v>3526</v>
       </c>
     </row>
-    <row r="300" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="300" spans="1:11">
       <c r="A300" s="10">
         <f t="shared" si="4"/>
         <v>45179</v>
@@ -11324,7 +11326,7 @@
       <c r="B300" s="8">
         <v>45180</v>
       </c>
-      <c r="C300" s="12">
+      <c r="C300" s="11">
         <v>0.70833333333333337</v>
       </c>
       <c r="D300" s="8" t="s">
@@ -11352,7 +11354,7 @@
         <v>3715</v>
       </c>
     </row>
-    <row r="301" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="301" spans="1:11">
       <c r="A301" s="10">
         <f t="shared" si="4"/>
         <v>45186</v>
@@ -11360,7 +11362,7 @@
       <c r="B301" s="8">
         <v>45187</v>
       </c>
-      <c r="C301" s="12">
+      <c r="C301" s="11">
         <v>0.70833333333333337</v>
       </c>
       <c r="D301" s="8" t="s">
@@ -11388,7 +11390,7 @@
         <v>3765</v>
       </c>
     </row>
-    <row r="302" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="302" spans="1:11">
       <c r="A302" s="10">
         <f t="shared" si="4"/>
         <v>45193</v>
@@ -11396,7 +11398,7 @@
       <c r="B302" s="8">
         <v>45194</v>
       </c>
-      <c r="C302" s="12">
+      <c r="C302" s="11">
         <v>0.70833333333333337</v>
       </c>
       <c r="D302" s="8" t="s">
@@ -11424,7 +11426,7 @@
         <v>3987</v>
       </c>
     </row>
-    <row r="303" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="303" spans="1:11">
       <c r="A303" s="10">
         <f t="shared" si="4"/>
         <v>45200</v>
@@ -11432,7 +11434,7 @@
       <c r="B303" s="8">
         <v>45201</v>
       </c>
-      <c r="C303" s="12">
+      <c r="C303" s="11">
         <v>0.70833333333333337</v>
       </c>
       <c r="D303" s="8" t="s">
@@ -11460,7 +11462,7 @@
         <v>4197</v>
       </c>
     </row>
-    <row r="304" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="304" spans="1:11">
       <c r="A304" s="10">
         <f t="shared" si="4"/>
         <v>45207</v>
@@ -11468,7 +11470,7 @@
       <c r="B304" s="8">
         <v>45208</v>
       </c>
-      <c r="C304" s="12">
+      <c r="C304" s="11">
         <v>0.70833333333333337</v>
       </c>
       <c r="D304" s="8" t="s">
@@ -11496,7 +11498,7 @@
         <v>4308</v>
       </c>
     </row>
-    <row r="305" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="305" spans="1:11">
       <c r="A305" s="10">
         <f t="shared" si="4"/>
         <v>45214</v>
@@ -11504,7 +11506,7 @@
       <c r="B305" s="8">
         <v>45215</v>
       </c>
-      <c r="C305" s="12">
+      <c r="C305" s="11">
         <v>0.70833333333333337</v>
       </c>
       <c r="D305" s="8" t="s">
@@ -11532,7 +11534,7 @@
         <v>4268</v>
       </c>
     </row>
-    <row r="306" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="306" spans="1:11">
       <c r="A306" s="10">
         <f t="shared" si="4"/>
         <v>45221</v>
@@ -11540,7 +11542,7 @@
       <c r="B306" s="8">
         <v>45222</v>
       </c>
-      <c r="C306" s="12">
+      <c r="C306" s="11">
         <v>0.70833333333333337</v>
       </c>
       <c r="D306" s="8" t="s">
@@ -11568,7 +11570,7 @@
         <v>4444</v>
       </c>
     </row>
-    <row r="307" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="307" spans="1:11">
       <c r="A307" s="10">
         <f t="shared" si="4"/>
         <v>45228</v>
@@ -11576,7 +11578,7 @@
       <c r="B307" s="8">
         <v>45229</v>
       </c>
-      <c r="C307" s="12">
+      <c r="C307" s="11">
         <v>0.70833333333333337</v>
       </c>
       <c r="D307" s="8" t="s">
@@ -11604,7 +11606,7 @@
         <v>4465</v>
       </c>
     </row>
-    <row r="308" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="308" spans="1:11">
       <c r="A308" s="10">
         <f t="shared" si="4"/>
         <v>45235</v>
@@ -11612,7 +11614,7 @@
       <c r="B308" s="8">
         <v>45236</v>
       </c>
-      <c r="C308" s="12">
+      <c r="C308" s="11">
         <v>0.70833333333333337</v>
       </c>
       <c r="D308" s="8" t="s">
@@ -11640,7 +11642,7 @@
         <v>4486</v>
       </c>
     </row>
-    <row r="309" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="309" spans="1:11">
       <c r="A309" s="10">
         <f t="shared" si="4"/>
         <v>45242</v>
@@ -11648,7 +11650,7 @@
       <c r="B309" s="8">
         <v>45243</v>
       </c>
-      <c r="C309" s="12">
+      <c r="C309" s="11">
         <v>0.70833333333333337</v>
       </c>
       <c r="D309" s="8" t="s">
@@ -11676,7 +11678,7 @@
         <v>4878</v>
       </c>
     </row>
-    <row r="310" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="310" spans="1:11">
       <c r="A310" s="10">
         <f t="shared" si="4"/>
         <v>45249</v>
@@ -11684,7 +11686,7 @@
       <c r="B310" s="8">
         <v>45250</v>
       </c>
-      <c r="C310" s="12">
+      <c r="C310" s="11">
         <v>0.70833333333333337</v>
       </c>
       <c r="D310" s="8" t="s">
@@ -11712,7 +11714,7 @@
         <v>5136</v>
       </c>
     </row>
-    <row r="311" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="311" spans="1:11">
       <c r="A311" s="10">
         <f t="shared" si="4"/>
         <v>45256</v>
@@ -11720,7 +11722,7 @@
       <c r="B311" s="8">
         <v>45257</v>
       </c>
-      <c r="C311" s="12">
+      <c r="C311" s="11">
         <v>0.70833333333333337</v>
       </c>
       <c r="D311" s="8" t="s">
@@ -11748,7 +11750,7 @@
         <v>5562</v>
       </c>
     </row>
-    <row r="312" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="312" spans="1:11">
       <c r="A312" s="10">
         <f t="shared" si="4"/>
         <v>45263</v>
@@ -11756,7 +11758,7 @@
       <c r="B312" s="8">
         <v>45264</v>
       </c>
-      <c r="C312" s="12">
+      <c r="C312" s="11">
         <v>0.70833333333333337</v>
       </c>
       <c r="D312" s="8" t="s">
@@ -11784,7 +11786,7 @@
         <v>5625</v>
       </c>
     </row>
-    <row r="313" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="313" spans="1:11">
       <c r="A313" s="10">
         <f t="shared" si="4"/>
         <v>45270</v>
@@ -11792,7 +11794,7 @@
       <c r="B313" s="8">
         <v>45271</v>
       </c>
-      <c r="C313" s="12">
+      <c r="C313" s="11">
         <v>0.70833333333333337</v>
       </c>
       <c r="D313" s="8" t="s">
@@ -11820,7 +11822,7 @@
         <v>5859</v>
       </c>
     </row>
-    <row r="314" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="314" spans="1:11">
       <c r="A314" s="10">
         <f t="shared" si="4"/>
         <v>45277</v>
@@ -11828,7 +11830,7 @@
       <c r="B314" s="8">
         <v>45278</v>
       </c>
-      <c r="C314" s="12">
+      <c r="C314" s="11">
         <v>0.70833333333333337</v>
       </c>
       <c r="D314" s="8" t="s">
@@ -11856,7 +11858,7 @@
         <v>5680</v>
       </c>
     </row>
-    <row r="315" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="315" spans="1:11">
       <c r="A315" s="10">
         <f t="shared" si="4"/>
         <v>45284</v>
@@ -11864,7 +11866,7 @@
       <c r="B315" s="8">
         <v>45285</v>
       </c>
-      <c r="C315" s="12">
+      <c r="C315" s="11">
         <v>0.70833333333333337</v>
       </c>
       <c r="D315" s="8" t="s">
@@ -11892,7 +11894,7 @@
         <v>5680</v>
       </c>
     </row>
-    <row r="316" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="316" spans="1:11">
       <c r="A316" s="10">
         <f t="shared" si="4"/>
         <v>45291</v>
@@ -11900,7 +11902,7 @@
       <c r="B316" s="8">
         <v>45292</v>
       </c>
-      <c r="C316" s="12">
+      <c r="C316" s="11">
         <v>0.70833333333333337</v>
       </c>
       <c r="D316" s="8" t="s">
@@ -11928,7 +11930,7 @@
         <v>3893</v>
       </c>
     </row>
-    <row r="317" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="317" spans="1:11">
       <c r="A317" s="10">
         <f t="shared" si="4"/>
         <v>45298</v>
@@ -11936,7 +11938,7 @@
       <c r="B317" s="8">
         <v>45299</v>
       </c>
-      <c r="C317" s="12">
+      <c r="C317" s="11">
         <v>0.70833333333333337</v>
       </c>
       <c r="D317" s="8" t="s">
@@ -11964,7 +11966,7 @@
         <v>3609</v>
       </c>
     </row>
-    <row r="318" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="318" spans="1:11">
       <c r="A318" s="10">
         <f t="shared" si="4"/>
         <v>45305</v>
@@ -11972,7 +11974,7 @@
       <c r="B318" s="8">
         <v>45306</v>
       </c>
-      <c r="C318" s="12">
+      <c r="C318" s="11">
         <v>0.70833333333333337</v>
       </c>
       <c r="D318" s="8" t="s">
@@ -12000,7 +12002,7 @@
         <v>3632</v>
       </c>
     </row>
-    <row r="319" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="319" spans="1:11">
       <c r="A319" s="10">
         <f t="shared" si="4"/>
         <v>45312</v>
@@ -12008,7 +12010,7 @@
       <c r="B319" s="8">
         <v>45313</v>
       </c>
-      <c r="C319" s="12">
+      <c r="C319" s="11">
         <v>0.70833333333333337</v>
       </c>
       <c r="D319" s="8" t="s">
@@ -12036,7 +12038,7 @@
         <v>3772</v>
       </c>
     </row>
-    <row r="320" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="320" spans="1:11">
       <c r="A320" s="10">
         <f t="shared" si="4"/>
         <v>45319</v>
@@ -12044,7 +12046,7 @@
       <c r="B320" s="8">
         <v>45320</v>
       </c>
-      <c r="C320" s="12">
+      <c r="C320" s="11">
         <v>0.70833333333333337</v>
       </c>
       <c r="D320" s="8" t="s">
@@ -12072,7 +12074,7 @@
         <v>4103</v>
       </c>
     </row>
-    <row r="321" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="321" spans="1:11">
       <c r="A321" s="10">
         <f t="shared" si="4"/>
         <v>45326</v>
@@ -12080,7 +12082,7 @@
       <c r="B321" s="8">
         <v>45327</v>
       </c>
-      <c r="C321" s="12">
+      <c r="C321" s="11">
         <v>0.70833333333333337</v>
       </c>
       <c r="D321" s="8" t="s">
@@ -12108,7 +12110,7 @@
         <v>4283</v>
       </c>
     </row>
-    <row r="322" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="322" spans="1:11">
       <c r="A322" s="10">
         <f t="shared" si="4"/>
         <v>45333</v>
@@ -12116,7 +12118,7 @@
       <c r="B322" s="8">
         <v>45334</v>
       </c>
-      <c r="C322" s="12">
+      <c r="C322" s="11">
         <v>0.70833333333333337</v>
       </c>
       <c r="D322" s="8" t="s">
@@ -12144,7 +12146,7 @@
         <v>4375</v>
       </c>
     </row>
-    <row r="323" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="323" spans="1:11">
       <c r="A323" s="10">
         <f t="shared" si="4"/>
         <v>45340</v>
@@ -12152,7 +12154,7 @@
       <c r="B323" s="8">
         <v>45341</v>
       </c>
-      <c r="C323" s="12">
+      <c r="C323" s="11">
         <v>0.70833333333333337</v>
       </c>
       <c r="D323" s="8" t="s">
@@ -12180,7 +12182,7 @@
         <v>3871</v>
       </c>
     </row>
-    <row r="324" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="324" spans="1:11">
       <c r="A324" s="10">
         <f t="shared" ref="A324:A387" si="5">B324-1</f>
         <v>45347</v>
@@ -12188,7 +12190,7 @@
       <c r="B324" s="8">
         <v>45348</v>
       </c>
-      <c r="C324" s="12">
+      <c r="C324" s="11">
         <v>0.70833333333333337</v>
       </c>
       <c r="D324" s="8" t="s">
@@ -12216,7 +12218,7 @@
         <v>3455</v>
       </c>
     </row>
-    <row r="325" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="325" spans="1:11">
       <c r="A325" s="10">
         <f t="shared" si="5"/>
         <v>45354</v>
@@ -12224,7 +12226,7 @@
       <c r="B325" s="8">
         <v>45355</v>
       </c>
-      <c r="C325" s="12">
+      <c r="C325" s="11">
         <v>0.70833333333333337</v>
       </c>
       <c r="D325" s="8" t="s">
@@ -12252,7 +12254,7 @@
         <v>3638</v>
       </c>
     </row>
-    <row r="326" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="326" spans="1:11">
       <c r="A326" s="10">
         <f t="shared" si="5"/>
         <v>45361</v>
@@ -12260,7 +12262,7 @@
       <c r="B326" s="8">
         <v>45362</v>
       </c>
-      <c r="C326" s="12">
+      <c r="C326" s="11">
         <v>0.70833333333333337</v>
       </c>
       <c r="D326" s="8" t="s">
@@ -12288,7 +12290,7 @@
         <v>3888</v>
       </c>
     </row>
-    <row r="327" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="327" spans="1:11">
       <c r="A327" s="10">
         <f t="shared" si="5"/>
         <v>45368</v>
@@ -12296,7 +12298,7 @@
       <c r="B327" s="8">
         <v>45369</v>
       </c>
-      <c r="C327" s="12">
+      <c r="C327" s="11">
         <v>0.70833333333333337</v>
       </c>
       <c r="D327" s="8" t="s">
@@ -12324,7 +12326,7 @@
         <v>4235</v>
       </c>
     </row>
-    <row r="328" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="328" spans="1:11">
       <c r="A328" s="10">
         <f t="shared" si="5"/>
         <v>45375</v>
@@ -12332,7 +12334,7 @@
       <c r="B328" s="8">
         <v>45376</v>
       </c>
-      <c r="C328" s="12">
+      <c r="C328" s="11">
         <v>0.70833333333333337</v>
       </c>
       <c r="D328" s="8" t="s">
@@ -12360,7 +12362,7 @@
         <v>4396</v>
       </c>
     </row>
-    <row r="329" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="329" spans="1:11">
       <c r="A329" s="10">
         <f t="shared" si="5"/>
         <v>45382</v>
@@ -12368,7 +12370,7 @@
       <c r="B329" s="8">
         <v>45383</v>
       </c>
-      <c r="C329" s="12">
+      <c r="C329" s="11">
         <v>0.70833333333333337</v>
       </c>
       <c r="D329" s="8" t="s">
@@ -12396,7 +12398,7 @@
         <v>4400</v>
       </c>
     </row>
-    <row r="330" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="330" spans="1:11">
       <c r="A330" s="10">
         <f t="shared" si="5"/>
         <v>45389</v>
@@ -12404,7 +12406,7 @@
       <c r="B330" s="8">
         <v>45390</v>
       </c>
-      <c r="C330" s="12">
+      <c r="C330" s="11">
         <v>0.70833333333333337</v>
       </c>
       <c r="D330" s="8" t="s">
@@ -12432,7 +12434,7 @@
         <v>4447</v>
       </c>
     </row>
-    <row r="331" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="331" spans="1:11">
       <c r="A331" s="10">
         <f t="shared" si="5"/>
         <v>45396</v>
@@ -12440,7 +12442,7 @@
       <c r="B331" s="8">
         <v>45397</v>
       </c>
-      <c r="C331" s="12">
+      <c r="C331" s="11">
         <v>0.70833333333333337</v>
       </c>
       <c r="D331" s="8" t="s">
@@ -12468,7 +12470,7 @@
         <v>4472</v>
       </c>
     </row>
-    <row r="332" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="332" spans="1:11">
       <c r="A332" s="10">
         <f t="shared" si="5"/>
         <v>45403</v>
@@ -12476,7 +12478,7 @@
       <c r="B332" s="8">
         <v>45404</v>
       </c>
-      <c r="C332" s="12">
+      <c r="C332" s="11">
         <v>0.70833333333333337</v>
       </c>
       <c r="D332" s="8" t="s">
@@ -12504,7 +12506,7 @@
         <v>4580</v>
       </c>
     </row>
-    <row r="333" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="333" spans="1:11">
       <c r="A333" s="10">
         <f t="shared" si="5"/>
         <v>45410</v>
@@ -12512,7 +12514,7 @@
       <c r="B333" s="8">
         <v>45411</v>
       </c>
-      <c r="C333" s="12">
+      <c r="C333" s="11">
         <v>0.70833333333333337</v>
       </c>
       <c r="D333" s="8" t="s">
@@ -12540,7 +12542,7 @@
         <v>4632</v>
       </c>
     </row>
-    <row r="334" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="334" spans="1:11">
       <c r="A334" s="10">
         <f t="shared" si="5"/>
         <v>45417</v>
@@ -12548,7 +12550,7 @@
       <c r="B334" s="8">
         <v>45418</v>
       </c>
-      <c r="C334" s="12">
+      <c r="C334" s="11">
         <v>0.70833333333333337</v>
       </c>
       <c r="D334" s="8" t="s">
@@ -12576,7 +12578,7 @@
         <v>4708</v>
       </c>
     </row>
-    <row r="335" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="335" spans="1:11">
       <c r="A335" s="10">
         <f t="shared" si="5"/>
         <v>45424</v>
@@ -12584,7 +12586,7 @@
       <c r="B335" s="8">
         <v>45425</v>
       </c>
-      <c r="C335" s="12">
+      <c r="C335" s="11">
         <v>0.70833333333333337</v>
       </c>
       <c r="D335" s="8" t="s">
@@ -12612,7 +12614,7 @@
         <v>4710</v>
       </c>
     </row>
-    <row r="336" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="336" spans="1:11">
       <c r="A336" s="10">
         <f t="shared" si="5"/>
         <v>45431</v>
@@ -12620,7 +12622,7 @@
       <c r="B336" s="8">
         <v>45432</v>
       </c>
-      <c r="C336" s="12">
+      <c r="C336" s="11">
         <v>0.70833333333333337</v>
       </c>
       <c r="D336" s="8" t="s">
@@ -12648,7 +12650,7 @@
         <v>4881</v>
       </c>
     </row>
-    <row r="337" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="337" spans="1:11">
       <c r="A337" s="10">
         <f t="shared" si="5"/>
         <v>45438</v>
@@ -12656,7 +12658,7 @@
       <c r="B337" s="8">
         <v>45439</v>
       </c>
-      <c r="C337" s="12">
+      <c r="C337" s="11">
         <v>0.70833333333333337</v>
       </c>
       <c r="D337" s="8" t="s">
@@ -12684,7 +12686,7 @@
         <v>4955</v>
       </c>
     </row>
-    <row r="338" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="338" spans="1:11">
       <c r="A338" s="10">
         <f t="shared" si="5"/>
         <v>45445</v>
@@ -12692,7 +12694,7 @@
       <c r="B338" s="8">
         <v>45446</v>
       </c>
-      <c r="C338" s="12">
+      <c r="C338" s="11">
         <v>0.70833333333333337</v>
       </c>
       <c r="D338" s="8" t="s">
@@ -12720,7 +12722,7 @@
         <v>4865</v>
       </c>
     </row>
-    <row r="339" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="339" spans="1:11">
       <c r="A339" s="10">
         <f t="shared" si="5"/>
         <v>45452</v>
@@ -12728,7 +12730,7 @@
       <c r="B339" s="8">
         <v>45453</v>
       </c>
-      <c r="C339" s="12">
+      <c r="C339" s="11">
         <v>0.70833333333333337</v>
       </c>
       <c r="D339" s="8" t="s">
@@ -12756,7 +12758,7 @@
         <v>4808</v>
       </c>
     </row>
-    <row r="340" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="340" spans="1:11">
       <c r="A340" s="10">
         <f t="shared" si="5"/>
         <v>45459</v>
@@ -12764,7 +12766,7 @@
       <c r="B340" s="8">
         <v>45460</v>
       </c>
-      <c r="C340" s="12">
+      <c r="C340" s="11">
         <v>0.70833333333333337</v>
       </c>
       <c r="D340" s="8" t="s">
@@ -12792,7 +12794,7 @@
         <v>4783</v>
       </c>
     </row>
-    <row r="341" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="341" spans="1:11">
       <c r="A341" s="10">
         <f t="shared" si="5"/>
         <v>45466</v>
@@ -12800,7 +12802,7 @@
       <c r="B341" s="8">
         <v>45467</v>
       </c>
-      <c r="C341" s="12">
+      <c r="C341" s="11">
         <v>0.70833333333333337</v>
       </c>
       <c r="D341" s="8" t="s">
@@ -12828,7 +12830,7 @@
         <v>4757</v>
       </c>
     </row>
-    <row r="342" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="342" spans="1:11">
       <c r="A342" s="10">
         <f t="shared" si="5"/>
         <v>45473</v>
@@ -12836,7 +12838,7 @@
       <c r="B342" s="8">
         <v>45474</v>
       </c>
-      <c r="C342" s="12">
+      <c r="C342" s="11">
         <v>0.70833333333333337</v>
       </c>
       <c r="D342" s="8" t="s">
@@ -12864,7 +12866,7 @@
         <v>4736</v>
       </c>
     </row>
-    <row r="343" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="343" spans="1:11">
       <c r="A343" s="10">
         <f t="shared" si="5"/>
         <v>45480</v>
@@ -12872,7 +12874,7 @@
       <c r="B343" s="8">
         <v>45481</v>
       </c>
-      <c r="C343" s="12">
+      <c r="C343" s="11">
         <v>0.70833333333333337</v>
       </c>
       <c r="D343" s="8" t="s">
@@ -12900,7 +12902,7 @@
         <v>4879</v>
       </c>
     </row>
-    <row r="344" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="344" spans="1:11">
       <c r="A344" s="10">
         <f t="shared" si="5"/>
         <v>45487</v>
@@ -12908,7 +12910,7 @@
       <c r="B344" s="8">
         <v>45488</v>
       </c>
-      <c r="C344" s="12">
+      <c r="C344" s="11">
         <v>0.70833333333333337</v>
       </c>
       <c r="D344" s="8" t="s">
@@ -12936,7 +12938,7 @@
         <v>4737</v>
       </c>
     </row>
-    <row r="345" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="345" spans="1:11">
       <c r="A345" s="10">
         <f t="shared" si="5"/>
         <v>45494</v>
@@ -12944,7 +12946,7 @@
       <c r="B345" s="8">
         <v>45495</v>
       </c>
-      <c r="C345" s="12">
+      <c r="C345" s="11">
         <v>0.70833333333333337</v>
       </c>
       <c r="D345" s="8" t="s">
@@ -12972,7 +12974,7 @@
         <v>4594</v>
       </c>
     </row>
-    <row r="346" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="346" spans="1:11">
       <c r="A346" s="10">
         <f t="shared" si="5"/>
         <v>45501</v>
@@ -12980,7 +12982,7 @@
       <c r="B346" s="8">
         <v>45502</v>
       </c>
-      <c r="C346" s="12">
+      <c r="C346" s="11">
         <v>0.70833333333333337</v>
       </c>
       <c r="D346" s="8" t="s">
@@ -13008,7 +13010,7 @@
         <v>4598</v>
       </c>
     </row>
-    <row r="347" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="347" spans="1:11">
       <c r="A347" s="10">
         <f t="shared" si="5"/>
         <v>45508</v>
@@ -13016,7 +13018,7 @@
       <c r="B347" s="8">
         <v>45509</v>
       </c>
-      <c r="C347" s="12">
+      <c r="C347" s="11">
         <v>0.70833333333333337</v>
       </c>
       <c r="D347" s="8" t="s">
@@ -13044,7 +13046,7 @@
         <v>4565</v>
       </c>
     </row>
-    <row r="348" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="348" spans="1:11">
       <c r="A348" s="10">
         <f t="shared" si="5"/>
         <v>45515</v>
@@ -13052,7 +13054,7 @@
       <c r="B348" s="8">
         <v>45516</v>
       </c>
-      <c r="C348" s="12">
+      <c r="C348" s="11">
         <v>0.70833333333333337</v>
       </c>
       <c r="D348" s="8" t="s">
@@ -13080,7 +13082,7 @@
         <v>4647</v>
       </c>
     </row>
-    <row r="349" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="349" spans="1:11">
       <c r="A349" s="10">
         <f t="shared" si="5"/>
         <v>45522</v>
@@ -13088,7 +13090,7 @@
       <c r="B349" s="8">
         <v>45523</v>
       </c>
-      <c r="C349" s="12">
+      <c r="C349" s="11">
         <v>0.70833333333333337</v>
       </c>
       <c r="D349" s="8" t="s">
@@ -13116,7 +13118,7 @@
         <v>4591</v>
       </c>
     </row>
-    <row r="350" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="350" spans="1:11">
       <c r="A350" s="10">
         <f t="shared" si="5"/>
         <v>45529</v>
@@ -13124,7 +13126,7 @@
       <c r="B350" s="8">
         <v>45530</v>
       </c>
-      <c r="C350" s="12">
+      <c r="C350" s="11">
         <v>0.70833333333333337</v>
       </c>
       <c r="D350" s="8" t="s">
@@ -13152,7 +13154,7 @@
         <v>4788</v>
       </c>
     </row>
-    <row r="351" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="351" spans="1:11">
       <c r="A351" s="10">
         <f t="shared" si="5"/>
         <v>45536</v>
@@ -13160,7 +13162,7 @@
       <c r="B351" s="8">
         <v>45537</v>
       </c>
-      <c r="C351" s="12">
+      <c r="C351" s="11">
         <v>0.70833333333333337</v>
       </c>
       <c r="D351" s="8" t="s">
@@ -13188,7 +13190,7 @@
         <v>4920</v>
       </c>
     </row>
-    <row r="352" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="352" spans="1:11">
       <c r="A352" s="10">
         <f t="shared" si="5"/>
         <v>45543</v>
@@ -13196,7 +13198,7 @@
       <c r="B352" s="8">
         <v>45544</v>
       </c>
-      <c r="C352" s="12">
+      <c r="C352" s="11">
         <v>0.70833333333333337</v>
       </c>
       <c r="D352" s="8" t="s">
@@ -13224,7 +13226,7 @@
         <v>4829</v>
       </c>
     </row>
-    <row r="353" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="353" spans="1:11">
       <c r="A353" s="10">
         <f t="shared" si="5"/>
         <v>45550</v>
@@ -13232,7 +13234,7 @@
       <c r="B353" s="8">
         <v>45551</v>
       </c>
-      <c r="C353" s="12">
+      <c r="C353" s="11">
         <v>0.70833333333333337</v>
       </c>
       <c r="D353" s="8" t="s">
@@ -13260,7 +13262,7 @@
         <v>4815</v>
       </c>
     </row>
-    <row r="354" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="354" spans="1:11">
       <c r="A354" s="10">
         <f t="shared" si="5"/>
         <v>45557</v>
@@ -13268,7 +13270,7 @@
       <c r="B354" s="8">
         <v>45558</v>
       </c>
-      <c r="C354" s="12">
+      <c r="C354" s="11">
         <v>0.70833333333333337</v>
       </c>
       <c r="D354" s="8" t="s">
@@ -13296,7 +13298,7 @@
         <v>4837</v>
       </c>
     </row>
-    <row r="355" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="355" spans="1:11">
       <c r="A355" s="10">
         <f t="shared" si="5"/>
         <v>45564</v>
@@ -13304,7 +13306,7 @@
       <c r="B355" s="8">
         <v>45565</v>
       </c>
-      <c r="C355" s="12">
+      <c r="C355" s="11">
         <v>0.70833333333333337</v>
       </c>
       <c r="D355" s="8" t="s">
@@ -13332,7 +13334,7 @@
         <v>5053</v>
       </c>
     </row>
-    <row r="356" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="356" spans="1:11">
       <c r="A356" s="10">
         <f t="shared" si="5"/>
         <v>45571</v>
@@ -13340,7 +13342,7 @@
       <c r="B356" s="8">
         <v>45572</v>
       </c>
-      <c r="C356" s="12">
+      <c r="C356" s="11">
         <v>0.70833333333333337</v>
       </c>
       <c r="D356" s="8" t="s">
@@ -13368,7 +13370,7 @@
         <v>4879</v>
       </c>
     </row>
-    <row r="357" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="357" spans="1:11">
       <c r="A357" s="10">
         <f t="shared" si="5"/>
         <v>45578</v>
@@ -13376,7 +13378,7 @@
       <c r="B357" s="8">
         <v>45579</v>
       </c>
-      <c r="C357" s="12">
+      <c r="C357" s="11">
         <v>0.70833333333333337</v>
       </c>
       <c r="D357" s="8" t="s">
@@ -13404,7 +13406,7 @@
         <v>4831</v>
       </c>
     </row>
-    <row r="358" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="358" spans="1:11">
       <c r="A358" s="10">
         <f t="shared" si="5"/>
         <v>45585</v>
@@ -13412,7 +13414,7 @@
       <c r="B358" s="8">
         <v>45586</v>
       </c>
-      <c r="C358" s="12">
+      <c r="C358" s="11">
         <v>0.70833333333333337</v>
       </c>
       <c r="D358" s="8" t="s">
@@ -13440,7 +13442,7 @@
         <v>5006</v>
       </c>
     </row>
-    <row r="359" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="359" spans="1:11">
       <c r="A359" s="10">
         <f t="shared" si="5"/>
         <v>45592</v>
@@ -13448,7 +13450,7 @@
       <c r="B359" s="8">
         <v>45593</v>
       </c>
-      <c r="C359" s="12">
+      <c r="C359" s="11">
         <v>0.70833333333333337</v>
       </c>
       <c r="D359" s="8" t="s">
@@ -13476,7 +13478,7 @@
         <v>5190</v>
       </c>
     </row>
-    <row r="360" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="360" spans="1:11">
       <c r="A360" s="10">
         <f t="shared" si="5"/>
         <v>45599</v>
@@ -13484,7 +13486,7 @@
       <c r="B360" s="8">
         <v>45600</v>
       </c>
-      <c r="C360" s="12">
+      <c r="C360" s="11">
         <v>0.70833333333333337</v>
       </c>
       <c r="D360" s="8" t="s">
@@ -13512,7 +13514,7 @@
         <v>5493</v>
       </c>
     </row>
-    <row r="361" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="361" spans="1:11">
       <c r="A361" s="10">
         <f t="shared" si="5"/>
         <v>45606</v>
@@ -13520,7 +13522,7 @@
       <c r="B361" s="8">
         <v>45607</v>
       </c>
-      <c r="C361" s="12">
+      <c r="C361" s="11">
         <v>0.70833333333333337</v>
       </c>
       <c r="D361" s="8" t="s">
@@ -13548,7 +13550,7 @@
         <v>5494</v>
       </c>
     </row>
-    <row r="362" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="362" spans="1:11">
       <c r="A362" s="10">
         <f t="shared" si="5"/>
         <v>45613</v>
@@ -13556,7 +13558,7 @@
       <c r="B362" s="8">
         <v>45614</v>
       </c>
-      <c r="C362" s="12">
+      <c r="C362" s="11">
         <v>0.70833333333333337</v>
       </c>
       <c r="D362" s="8" t="s">
@@ -13584,7 +13586,7 @@
         <v>5339</v>
       </c>
     </row>
-    <row r="363" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="363" spans="1:11">
       <c r="A363" s="10">
         <f t="shared" si="5"/>
         <v>45620</v>
@@ -13592,7 +13594,7 @@
       <c r="B363" s="8">
         <v>45621</v>
       </c>
-      <c r="C363" s="12">
+      <c r="C363" s="11">
         <v>0.70833333333333337</v>
       </c>
       <c r="D363" s="8" t="s">
@@ -13620,7 +13622,7 @@
         <v>5225</v>
       </c>
     </row>
-    <row r="364" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="364" spans="1:11">
       <c r="A364" s="10">
         <f t="shared" si="5"/>
         <v>45627</v>
@@ -13628,7 +13630,7 @@
       <c r="B364" s="8">
         <v>45628</v>
       </c>
-      <c r="C364" s="12">
+      <c r="C364" s="11">
         <v>0.70833333333333337</v>
       </c>
       <c r="D364" s="8" t="s">
@@ -13656,7 +13658,7 @@
         <v>5585</v>
       </c>
     </row>
-    <row r="365" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="365" spans="1:11">
       <c r="A365" s="10">
         <f t="shared" si="5"/>
         <v>45634</v>
@@ -13664,7 +13666,7 @@
       <c r="B365" s="8">
         <v>45635</v>
       </c>
-      <c r="C365" s="12">
+      <c r="C365" s="11">
         <v>0.70833333333333337</v>
       </c>
       <c r="D365" s="8" t="s">
@@ -13692,7 +13694,7 @@
         <v>5777</v>
       </c>
     </row>
-    <row r="366" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="366" spans="1:11">
       <c r="A366" s="10">
         <f t="shared" si="5"/>
         <v>45641</v>
@@ -13700,7 +13702,7 @@
       <c r="B366" s="8">
         <v>45642</v>
       </c>
-      <c r="C366" s="12">
+      <c r="C366" s="11">
         <v>0.70833333333333337</v>
       </c>
       <c r="D366" s="8" t="s">
@@ -13728,7 +13730,7 @@
         <v>5722</v>
       </c>
     </row>
-    <row r="367" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="367" spans="1:11">
       <c r="A367" s="10">
         <f t="shared" si="5"/>
         <v>45648</v>
@@ -13736,7 +13738,7 @@
       <c r="B367" s="8">
         <v>45649</v>
       </c>
-      <c r="C367" s="12">
+      <c r="C367" s="11">
         <v>0.70833333333333337</v>
       </c>
       <c r="D367" s="8" t="s">
@@ -13764,7 +13766,7 @@
         <v>5327</v>
       </c>
     </row>
-    <row r="368" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="368" spans="1:11">
       <c r="A368" s="10">
         <f t="shared" si="5"/>
         <v>45655</v>
@@ -13772,7 +13774,7 @@
       <c r="B368" s="8">
         <v>45656</v>
       </c>
-      <c r="C368" s="12">
+      <c r="C368" s="11">
         <v>0.70833333333333337</v>
       </c>
       <c r="D368" s="8" t="s">
@@ -13800,7 +13802,7 @@
         <v>5327</v>
       </c>
     </row>
-    <row r="369" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="369" spans="1:11">
       <c r="A369" s="10">
         <f t="shared" si="5"/>
         <v>45662</v>
@@ -13808,7 +13810,7 @@
       <c r="B369" s="8">
         <v>45663</v>
       </c>
-      <c r="C369" s="12">
+      <c r="C369" s="11">
         <v>0.70833333333333337</v>
       </c>
       <c r="D369" s="8" t="s">
@@ -13836,7 +13838,7 @@
         <v>4966</v>
       </c>
     </row>
-    <row r="370" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="370" spans="1:11">
       <c r="A370" s="10">
         <f t="shared" si="5"/>
         <v>45669</v>
@@ -13844,7 +13846,7 @@
       <c r="B370" s="8">
         <v>45670</v>
       </c>
-      <c r="C370" s="12">
+      <c r="C370" s="11">
         <v>0.70833333333333337</v>
       </c>
       <c r="D370" s="8" t="s">
@@ -13872,7 +13874,7 @@
         <v>4484</v>
       </c>
     </row>
-    <row r="371" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="371" spans="1:11">
       <c r="A371" s="10">
         <f t="shared" si="5"/>
         <v>45676</v>
@@ -13880,7 +13882,7 @@
       <c r="B371" s="8">
         <v>45677</v>
       </c>
-      <c r="C371" s="12">
+      <c r="C371" s="11">
         <v>0.70833333333333337</v>
       </c>
       <c r="D371" s="8" t="s">
@@ -13908,7 +13910,7 @@
         <v>4243</v>
       </c>
     </row>
-    <row r="372" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="372" spans="1:11">
       <c r="A372" s="10">
         <f t="shared" si="5"/>
         <v>45683</v>
@@ -13916,7 +13918,7 @@
       <c r="B372" s="8">
         <v>45684</v>
       </c>
-      <c r="C372" s="12">
+      <c r="C372" s="11">
         <v>0.70833333333333337</v>
       </c>
       <c r="D372" s="8" t="s">
@@ -13944,7 +13946,7 @@
         <v>4447</v>
       </c>
     </row>
-    <row r="373" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="373" spans="1:11">
       <c r="A373" s="10">
         <f t="shared" si="5"/>
         <v>45690</v>
@@ -13952,7 +13954,7 @@
       <c r="B373" s="8">
         <v>45691</v>
       </c>
-      <c r="C373" s="12">
+      <c r="C373" s="11">
         <v>0.70833333333333337</v>
       </c>
       <c r="D373" s="8" t="s">
@@ -13980,7 +13982,7 @@
         <v>4327</v>
       </c>
     </row>
-    <row r="374" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="374" spans="1:11">
       <c r="A374" s="10">
         <f t="shared" si="5"/>
         <v>45697</v>
@@ -13988,7 +13990,7 @@
       <c r="B374" s="8">
         <v>45698</v>
       </c>
-      <c r="C374" s="12">
+      <c r="C374" s="11">
         <v>0.70833333333333337</v>
       </c>
       <c r="D374" s="8" t="s">
@@ -14016,7 +14018,7 @@
         <v>3962</v>
       </c>
     </row>
-    <row r="375" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="375" spans="1:11">
       <c r="A375" s="10">
         <f t="shared" si="5"/>
         <v>45704</v>
@@ -14024,7 +14026,7 @@
       <c r="B375" s="8">
         <v>45705</v>
       </c>
-      <c r="C375" s="12">
+      <c r="C375" s="11">
         <v>0.70833333333333337</v>
       </c>
       <c r="D375" s="8" t="s">
@@ -14052,7 +14054,7 @@
         <v>4284</v>
       </c>
     </row>
-    <row r="376" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="376" spans="1:11">
       <c r="A376" s="10">
         <f t="shared" si="5"/>
         <v>45711</v>
@@ -14060,7 +14062,7 @@
       <c r="B376" s="8">
         <v>45712</v>
       </c>
-      <c r="C376" s="12">
+      <c r="C376" s="11">
         <v>0.70833333333333337</v>
       </c>
       <c r="D376" s="8" t="s">
@@ -14088,7 +14090,7 @@
         <v>4127</v>
       </c>
     </row>
-    <row r="377" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="377" spans="1:11">
       <c r="A377" s="10">
         <f t="shared" si="5"/>
         <v>45718</v>
@@ -14096,7 +14098,7 @@
       <c r="B377" s="8">
         <v>45719</v>
       </c>
-      <c r="C377" s="12">
+      <c r="C377" s="11">
         <v>0.70833333333333337</v>
       </c>
       <c r="D377" s="8" t="s">
@@ -14124,7 +14126,7 @@
         <v>4086</v>
       </c>
     </row>
-    <row r="378" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="378" spans="1:11">
       <c r="A378" s="10">
         <f t="shared" si="5"/>
         <v>45725</v>
@@ -14132,7 +14134,7 @@
       <c r="B378" s="8">
         <v>45726</v>
       </c>
-      <c r="C378" s="12">
+      <c r="C378" s="11">
         <v>0.70833333333333337</v>
       </c>
       <c r="D378" s="8" t="s">
@@ -14160,7 +14162,7 @@
         <v>4002</v>
       </c>
     </row>
-    <row r="379" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="379" spans="1:11">
       <c r="A379" s="10">
         <f t="shared" si="5"/>
         <v>45732</v>
@@ -14168,7 +14170,7 @@
       <c r="B379" s="8">
         <v>45733</v>
       </c>
-      <c r="C379" s="12">
+      <c r="C379" s="11">
         <v>0.70833333333333337</v>
       </c>
       <c r="D379" s="8" t="s">
@@ -14196,7 +14198,7 @@
         <v>4218</v>
       </c>
     </row>
-    <row r="380" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="380" spans="1:11">
       <c r="A380" s="10">
         <f t="shared" si="5"/>
         <v>45739</v>
@@ -14204,7 +14206,7 @@
       <c r="B380" s="8">
         <v>45740</v>
       </c>
-      <c r="C380" s="12">
+      <c r="C380" s="11">
         <v>0.70833333333333337</v>
       </c>
       <c r="D380" s="8" t="s">
@@ -14232,7 +14234,7 @@
         <v>4547</v>
       </c>
     </row>
-    <row r="381" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="381" spans="1:11">
       <c r="A381" s="10">
         <f t="shared" si="5"/>
         <v>45746</v>
@@ -14240,7 +14242,7 @@
       <c r="B381" s="8">
         <v>45747</v>
       </c>
-      <c r="C381" s="12">
+      <c r="C381" s="11">
         <v>0.70833333333333337</v>
       </c>
       <c r="D381" s="8" t="s">
@@ -14268,7 +14270,7 @@
         <v>4573</v>
       </c>
     </row>
-    <row r="382" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="382" spans="1:11">
       <c r="A382" s="10">
         <f t="shared" si="5"/>
         <v>45753</v>
@@ -14276,7 +14278,7 @@
       <c r="B382" s="8">
         <v>45754</v>
       </c>
-      <c r="C382" s="12">
+      <c r="C382" s="11">
         <v>0.70833333333333337</v>
       </c>
       <c r="D382" s="8" t="s">
@@ -14304,7 +14306,7 @@
         <v>4689</v>
       </c>
     </row>
-    <row r="383" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="383" spans="1:11">
       <c r="A383" s="10">
         <f t="shared" si="5"/>
         <v>45760</v>
@@ -14312,7 +14314,7 @@
       <c r="B383" s="8">
         <v>45761</v>
       </c>
-      <c r="C383" s="12">
+      <c r="C383" s="11">
         <v>0.70833333333333337</v>
       </c>
       <c r="D383" s="8" t="s">
@@ -14340,7 +14342,7 @@
         <v>4662</v>
       </c>
     </row>
-    <row r="384" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="384" spans="1:11">
       <c r="A384" s="10">
         <f t="shared" si="5"/>
         <v>45767</v>
@@ -14348,7 +14350,7 @@
       <c r="B384" s="8">
         <v>45768</v>
       </c>
-      <c r="C384" s="12">
+      <c r="C384" s="11">
         <v>0.70833333333333337</v>
       </c>
       <c r="D384" s="8" t="s">
@@ -14376,7 +14378,7 @@
         <v>4697</v>
       </c>
     </row>
-    <row r="385" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="385" spans="1:11">
       <c r="A385" s="10">
         <f t="shared" si="5"/>
         <v>45774</v>
@@ -14384,7 +14386,7 @@
       <c r="B385" s="8">
         <v>45775</v>
       </c>
-      <c r="C385" s="12">
+      <c r="C385" s="11">
         <v>0.70833333333333337</v>
       </c>
       <c r="D385" s="8" t="s">
@@ -14412,7 +14414,7 @@
         <v>4411</v>
       </c>
     </row>
-    <row r="386" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="386" spans="1:11">
       <c r="A386" s="10">
         <f t="shared" si="5"/>
         <v>45781</v>
@@ -14420,7 +14422,7 @@
       <c r="B386" s="8">
         <v>45782</v>
       </c>
-      <c r="C386" s="12">
+      <c r="C386" s="11">
         <v>0.70833333333333337</v>
       </c>
       <c r="D386" s="8" t="s">
@@ -14448,7 +14450,7 @@
         <v>4304</v>
       </c>
     </row>
-    <row r="387" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="387" spans="1:11">
       <c r="A387" s="10">
         <f t="shared" si="5"/>
         <v>45788</v>
@@ -14456,7 +14458,7 @@
       <c r="B387" s="8">
         <v>45789</v>
       </c>
-      <c r="C387" s="12">
+      <c r="C387" s="11">
         <v>0.70833333333333337</v>
       </c>
       <c r="D387" s="8" t="s">
@@ -14484,7 +14486,7 @@
         <v>4343</v>
       </c>
     </row>
-    <row r="388" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="388" spans="1:11">
       <c r="A388" s="10">
         <f t="shared" ref="A388:A419" si="6">B388-1</f>
         <v>45795</v>
@@ -14492,7 +14494,7 @@
       <c r="B388" s="8">
         <v>45796</v>
       </c>
-      <c r="C388" s="12">
+      <c r="C388" s="11">
         <v>0.70833333333333337</v>
       </c>
       <c r="D388" s="8" t="s">
@@ -14520,7 +14522,7 @@
         <v>4190</v>
       </c>
     </row>
-    <row r="389" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="389" spans="1:11">
       <c r="A389" s="10">
         <f t="shared" si="6"/>
         <v>45802</v>
@@ -14528,7 +14530,7 @@
       <c r="B389" s="8">
         <v>45803</v>
       </c>
-      <c r="C389" s="12">
+      <c r="C389" s="11">
         <v>0.70833333333333337</v>
       </c>
       <c r="D389" s="8" t="s">
@@ -14556,7 +14558,7 @@
         <v>4444</v>
       </c>
     </row>
-    <row r="390" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="390" spans="1:11">
       <c r="A390" s="10">
         <f t="shared" si="6"/>
         <v>45809</v>
@@ -14564,7 +14566,7 @@
       <c r="B390" s="8">
         <v>45810</v>
       </c>
-      <c r="C390" s="12">
+      <c r="C390" s="11">
         <v>0.70833333333333337</v>
       </c>
       <c r="D390" s="8" t="s">
@@ -14592,7 +14594,7 @@
         <v>4607</v>
       </c>
     </row>
-    <row r="391" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="391" spans="1:11">
       <c r="A391" s="10">
         <f t="shared" si="6"/>
         <v>45816</v>
@@ -14600,7 +14602,7 @@
       <c r="B391" s="8">
         <v>45817</v>
       </c>
-      <c r="C391" s="12">
+      <c r="C391" s="11">
         <v>0.70833333333333337</v>
       </c>
       <c r="D391" s="8" t="s">
@@ -14628,7 +14630,7 @@
         <v>4567</v>
       </c>
     </row>
-    <row r="392" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="392" spans="1:11">
       <c r="A392" s="10">
         <f t="shared" si="6"/>
         <v>45823</v>
@@ -14636,7 +14638,7 @@
       <c r="B392" s="8">
         <v>45824</v>
       </c>
-      <c r="C392" s="12">
+      <c r="C392" s="11">
         <v>0.70833333333333337</v>
       </c>
       <c r="D392" s="8" t="s">
@@ -14664,7 +14666,7 @@
         <v>4475</v>
       </c>
     </row>
-    <row r="393" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="393" spans="1:11">
       <c r="A393" s="10">
         <f t="shared" si="6"/>
         <v>45830</v>
@@ -14672,7 +14674,7 @@
       <c r="B393" s="8">
         <v>45831</v>
       </c>
-      <c r="C393" s="12">
+      <c r="C393" s="11">
         <v>0.70833333333333337</v>
       </c>
       <c r="D393" s="8" t="s">
@@ -14700,7 +14702,7 @@
         <v>4354</v>
       </c>
     </row>
-    <row r="394" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="394" spans="1:11">
       <c r="A394" s="10">
         <f t="shared" si="6"/>
         <v>45837</v>
@@ -14708,7 +14710,7 @@
       <c r="B394" s="8">
         <v>45838</v>
       </c>
-      <c r="C394" s="12">
+      <c r="C394" s="11">
         <v>0.70833333333333337</v>
       </c>
       <c r="D394" s="8" t="s">
@@ -14736,7 +14738,7 @@
         <v>4375</v>
       </c>
     </row>
-    <row r="395" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="395" spans="1:11">
       <c r="A395" s="10">
         <f t="shared" si="6"/>
         <v>45844</v>
@@ -14744,7 +14746,7 @@
       <c r="B395" s="8">
         <v>45845</v>
       </c>
-      <c r="C395" s="12">
+      <c r="C395" s="11">
         <v>0.70833333333333337</v>
       </c>
       <c r="D395" s="8" t="s">
@@ -14772,7 +14774,7 @@
         <v>4413</v>
       </c>
     </row>
-    <row r="396" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="396" spans="1:11">
       <c r="A396" s="10">
         <f t="shared" si="6"/>
         <v>45851</v>
@@ -14780,7 +14782,7 @@
       <c r="B396" s="8">
         <v>45852</v>
       </c>
-      <c r="C396" s="12">
+      <c r="C396" s="11">
         <v>0.70833333333333337</v>
       </c>
       <c r="D396" s="8" t="s">
@@ -14808,7 +14810,7 @@
         <v>4593</v>
       </c>
     </row>
-    <row r="397" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="397" spans="1:11">
       <c r="A397" s="10">
         <f t="shared" si="6"/>
         <v>45858</v>
@@ -14816,7 +14818,7 @@
       <c r="B397" s="8">
         <v>45859</v>
       </c>
-      <c r="C397" s="12">
+      <c r="C397" s="11">
         <v>0.70833333333333337</v>
       </c>
       <c r="D397" s="8" t="s">
@@ -14844,7 +14846,7 @@
         <v>4418</v>
       </c>
     </row>
-    <row r="398" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="398" spans="1:11">
       <c r="A398" s="10">
         <f t="shared" si="6"/>
         <v>45865</v>
@@ -14852,7 +14854,7 @@
       <c r="B398" s="8">
         <v>45866</v>
       </c>
-      <c r="C398" s="12">
+      <c r="C398" s="11">
         <v>0.70833333333333337</v>
       </c>
       <c r="D398" s="8" t="s">
@@ -14880,7 +14882,7 @@
         <v>4429</v>
       </c>
     </row>
-    <row r="399" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="399" spans="1:11">
       <c r="A399" s="10">
         <f t="shared" si="6"/>
         <v>45872</v>
@@ -14888,7 +14890,7 @@
       <c r="B399" s="8">
         <v>45873</v>
       </c>
-      <c r="C399" s="12">
+      <c r="C399" s="11">
         <v>0.70833333333333337</v>
       </c>
       <c r="D399" s="8" t="s">
@@ -14916,7 +14918,7 @@
         <v>4418</v>
       </c>
     </row>
-    <row r="400" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="400" spans="1:11">
       <c r="A400" s="10">
         <f t="shared" si="6"/>
         <v>45879</v>
@@ -14924,7 +14926,7 @@
       <c r="B400" s="8">
         <v>45880</v>
       </c>
-      <c r="C400" s="12">
+      <c r="C400" s="11">
         <v>0.70833333333333337</v>
       </c>
       <c r="D400" s="8" t="s">
@@ -14952,7 +14954,7 @@
         <v>4455</v>
       </c>
     </row>
-    <row r="401" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="401" spans="1:11">
       <c r="A401" s="10">
         <f t="shared" si="6"/>
         <v>45886</v>
@@ -14960,7 +14962,7 @@
       <c r="B401" s="8">
         <v>45887</v>
       </c>
-      <c r="C401" s="12">
+      <c r="C401" s="11">
         <v>0.70833333333333337</v>
       </c>
       <c r="D401" s="8" t="s">
@@ -14988,7 +14990,7 @@
         <v>4411</v>
       </c>
     </row>
-    <row r="402" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="402" spans="1:11">
       <c r="A402" s="10">
         <f t="shared" si="6"/>
         <v>45893</v>
@@ -14996,7 +14998,7 @@
       <c r="B402" s="8">
         <v>45894</v>
       </c>
-      <c r="C402" s="12">
+      <c r="C402" s="11">
         <v>0.70833333333333337</v>
       </c>
       <c r="D402" s="8" t="s">
@@ -15024,7 +15026,7 @@
         <v>4392</v>
       </c>
     </row>
-    <row r="403" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="403" spans="1:11">
       <c r="A403" s="10">
         <f t="shared" si="6"/>
         <v>45900</v>
@@ -15032,7 +15034,7 @@
       <c r="B403" s="8">
         <v>45901</v>
       </c>
-      <c r="C403" s="12">
+      <c r="C403" s="11">
         <v>0.70833333333333337</v>
       </c>
       <c r="D403" s="8" t="s">
@@ -15060,7 +15062,7 @@
         <v>4549</v>
       </c>
     </row>
-    <row r="404" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="404" spans="1:11">
       <c r="A404" s="10">
         <f t="shared" si="6"/>
         <v>45907</v>
@@ -15068,7 +15070,7 @@
       <c r="B404" s="8">
         <v>45908</v>
       </c>
-      <c r="C404" s="12">
+      <c r="C404" s="11">
         <v>0.70833333333333337</v>
       </c>
       <c r="D404" s="8" t="s">
@@ -15096,7 +15098,7 @@
         <v>4489</v>
       </c>
     </row>
-    <row r="405" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="405" spans="1:11">
       <c r="A405" s="10">
         <f t="shared" si="6"/>
         <v>45914</v>
@@ -15104,7 +15106,7 @@
       <c r="B405" s="8">
         <v>45915</v>
       </c>
-      <c r="C405" s="12">
+      <c r="C405" s="11">
         <v>0.70833333333333337</v>
       </c>
       <c r="D405" s="8" t="s">
@@ -15132,7 +15134,7 @@
         <v>4536</v>
       </c>
     </row>
-    <row r="406" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="406" spans="1:11">
       <c r="A406" s="10">
         <f t="shared" si="6"/>
         <v>45921</v>
@@ -15140,7 +15142,7 @@
       <c r="B406" s="8">
         <v>45922</v>
       </c>
-      <c r="C406" s="12">
+      <c r="C406" s="11">
         <v>0.70833333333333337</v>
       </c>
       <c r="D406" s="8" t="s">
@@ -15168,7 +15170,7 @@
         <v>4516</v>
       </c>
     </row>
-    <row r="407" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="407" spans="1:11">
       <c r="A407" s="10">
         <f t="shared" si="6"/>
         <v>45928</v>
@@ -15176,7 +15178,7 @@
       <c r="B407" s="8">
         <v>45929</v>
       </c>
-      <c r="C407" s="12">
+      <c r="C407" s="11">
         <v>0.70833333333333337</v>
       </c>
       <c r="D407" s="8" t="s">
@@ -15204,7 +15206,7 @@
         <v>4562</v>
       </c>
     </row>
-    <row r="408" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="408" spans="1:11">
       <c r="A408" s="10">
         <f t="shared" si="6"/>
         <v>45935</v>
@@ -15212,7 +15214,7 @@
       <c r="B408" s="8">
         <v>45936</v>
       </c>
-      <c r="C408" s="12">
+      <c r="C408" s="11">
         <v>0.70833333333333337</v>
       </c>
       <c r="D408" s="8" t="s">
@@ -15240,7 +15242,7 @@
         <v>4621</v>
       </c>
     </row>
-    <row r="409" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="409" spans="1:11">
       <c r="A409" s="10">
         <f t="shared" si="6"/>
         <v>45942</v>
@@ -15248,7 +15250,7 @@
       <c r="B409" s="8">
         <v>45943</v>
       </c>
-      <c r="C409" s="12">
+      <c r="C409" s="11">
         <v>0.70833333333333337</v>
       </c>
       <c r="D409" s="8" t="s">
@@ -15276,7 +15278,7 @@
         <v>4441</v>
       </c>
     </row>
-    <row r="410" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="410" spans="1:11">
       <c r="A410" s="10">
         <f t="shared" si="6"/>
         <v>45949</v>
@@ -15284,7 +15286,7 @@
       <c r="B410" s="8">
         <v>45950</v>
       </c>
-      <c r="C410" s="12">
+      <c r="C410" s="11">
         <v>0.70833333333333337</v>
       </c>
       <c r="D410" s="8" t="s">
@@ -15312,7 +15314,7 @@
         <v>4746</v>
       </c>
     </row>
-    <row r="411" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="411" spans="1:11">
       <c r="A411" s="10">
         <f t="shared" si="6"/>
         <v>45956</v>
@@ -15320,7 +15322,7 @@
       <c r="B411" s="8">
         <v>45957</v>
       </c>
-      <c r="C411" s="12">
+      <c r="C411" s="11">
         <v>0.70833333333333337</v>
       </c>
       <c r="D411" s="8" t="s">
@@ -15348,7 +15350,7 @@
         <v>5010</v>
       </c>
     </row>
-    <row r="412" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="412" spans="1:11">
       <c r="A412" s="10">
         <f t="shared" si="6"/>
         <v>45963</v>
@@ -15356,7 +15358,7 @@
       <c r="B412" s="8">
         <v>45964</v>
       </c>
-      <c r="C412" s="12">
+      <c r="C412" s="11">
         <v>0.70833333333333337</v>
       </c>
       <c r="D412" s="8" t="s">
@@ -15384,7 +15386,7 @@
         <v>5366</v>
       </c>
     </row>
-    <row r="413" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="413" spans="1:11">
       <c r="A413" s="10">
         <f t="shared" si="6"/>
         <v>45970</v>
@@ -15392,7 +15394,7 @@
       <c r="B413" s="8">
         <v>45971</v>
       </c>
-      <c r="C413" s="12">
+      <c r="C413" s="11">
         <v>0.70833333333333337</v>
       </c>
       <c r="D413" s="8" t="s">
@@ -15420,7 +15422,7 @@
         <v>5356</v>
       </c>
     </row>
-    <row r="414" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="414" spans="1:11">
       <c r="A414" s="10">
         <f t="shared" si="6"/>
         <v>45977</v>
@@ -15428,7 +15430,7 @@
       <c r="B414" s="8">
         <v>45978</v>
       </c>
-      <c r="C414" s="12">
+      <c r="C414" s="11">
         <v>0.70833333333333337</v>
       </c>
       <c r="D414" s="8" t="s">
@@ -15456,7 +15458,7 @@
         <v>5581</v>
       </c>
     </row>
-    <row r="415" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="415" spans="1:11">
       <c r="A415" s="10">
         <f t="shared" si="6"/>
         <v>45984</v>
@@ -15464,7 +15466,7 @@
       <c r="B415" s="8">
         <v>45985</v>
       </c>
-      <c r="C415" s="12">
+      <c r="C415" s="11">
         <v>0.70833333333333337</v>
       </c>
       <c r="D415" s="8" t="s">
@@ -15492,7 +15494,7 @@
         <v>5571</v>
       </c>
     </row>
-    <row r="416" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="416" spans="1:11">
       <c r="A416" s="10">
         <f t="shared" si="6"/>
         <v>45991</v>
@@ -15500,7 +15502,7 @@
       <c r="B416" s="8">
         <v>45992</v>
       </c>
-      <c r="C416" s="12">
+      <c r="C416" s="11">
         <v>0.70833333333333337</v>
       </c>
       <c r="D416" s="8" t="s">
@@ -15528,7 +15530,7 @@
         <v>5721</v>
       </c>
     </row>
-    <row r="417" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="417" spans="1:11">
       <c r="A417" s="10">
         <f t="shared" si="6"/>
         <v>45998</v>
@@ -15536,7 +15538,7 @@
       <c r="B417" s="8">
         <v>45999</v>
       </c>
-      <c r="C417" s="12">
+      <c r="C417" s="11">
         <v>0.70833333333333337</v>
       </c>
       <c r="D417" s="8" t="s">
@@ -15564,7 +15566,7 @@
         <v>6161</v>
       </c>
     </row>
-    <row r="418" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="418" spans="1:11">
       <c r="A418" s="10">
         <f t="shared" si="6"/>
         <v>46005</v>
@@ -15572,7 +15574,7 @@
       <c r="B418" s="8">
         <v>46006</v>
       </c>
-      <c r="C418" s="12">
+      <c r="C418" s="11">
         <v>0.70833333333333337</v>
       </c>
       <c r="D418" s="8" t="s">
@@ -15600,7 +15602,7 @@
         <v>6369</v>
       </c>
     </row>
-    <row r="419" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="419" spans="1:11">
       <c r="A419" s="10">
         <f t="shared" si="6"/>
         <v>46012</v>
@@ -15608,7 +15610,7 @@
       <c r="B419" s="8">
         <v>46013</v>
       </c>
-      <c r="C419" s="12">
+      <c r="C419" s="11">
         <v>0.70833333333333337</v>
       </c>
       <c r="D419" s="8" t="s">
@@ -15636,7 +15638,7 @@
         <v>5821</v>
       </c>
     </row>
-    <row r="420" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="420" spans="1:11">
       <c r="A420" s="10">
         <f t="shared" ref="A420:A422" si="7">B420-1</f>
         <v>46026</v>
@@ -15644,7 +15646,7 @@
       <c r="B420" s="8">
         <v>46027</v>
       </c>
-      <c r="C420" s="12">
+      <c r="C420" s="11">
         <v>0.70833333333333337</v>
       </c>
       <c r="D420" s="8" t="s">
@@ -15672,7 +15674,7 @@
         <v>4662</v>
       </c>
     </row>
-    <row r="421" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="421" spans="1:11">
       <c r="A421" s="10">
         <f t="shared" si="7"/>
         <v>46033</v>
@@ -15680,7 +15682,7 @@
       <c r="B421" s="8">
         <v>46034</v>
       </c>
-      <c r="C421" s="12">
+      <c r="C421" s="11">
         <v>0.70833333333333337</v>
       </c>
       <c r="D421" s="8" t="s">
@@ -15708,7 +15710,7 @@
         <v>4662</v>
       </c>
     </row>
-    <row r="422" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="422" spans="1:11">
       <c r="A422" s="10">
         <f t="shared" si="7"/>
         <v>46040</v>
@@ -15716,7 +15718,7 @@
       <c r="B422" s="8">
         <v>46041</v>
       </c>
-      <c r="C422" s="12">
+      <c r="C422" s="11">
         <v>0.70833333333333337</v>
       </c>
       <c r="D422" s="8" t="s">
@@ -15744,7 +15746,7 @@
         <v>4558</v>
       </c>
     </row>
-    <row r="423" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="423" spans="1:11">
       <c r="A423" s="10">
         <f t="shared" ref="A423:A425" si="8">B423-1</f>
         <v>46047</v>
@@ -15752,7 +15754,7 @@
       <c r="B423" s="8">
         <v>46048</v>
       </c>
-      <c r="C423" s="12">
+      <c r="C423" s="11">
         <v>0.70833333333333304</v>
       </c>
       <c r="D423" s="8" t="s">
@@ -15780,7 +15782,7 @@
         <v>4478</v>
       </c>
     </row>
-    <row r="424" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="424" spans="1:11">
       <c r="A424" s="10">
         <f t="shared" si="8"/>
         <v>46054</v>
@@ -15788,7 +15790,7 @@
       <c r="B424" s="8">
         <v>46055</v>
       </c>
-      <c r="C424" s="12">
+      <c r="C424" s="11">
         <v>0.70833333333333304</v>
       </c>
       <c r="D424" s="8" t="s">
@@ -15816,7 +15818,7 @@
         <v>4714</v>
       </c>
     </row>
-    <row r="425" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="425" spans="1:11">
       <c r="A425" s="10">
         <f t="shared" si="8"/>
         <v>46061</v>
@@ -15824,7 +15826,7 @@
       <c r="B425" s="8">
         <v>46062</v>
       </c>
-      <c r="C425" s="12">
+      <c r="C425" s="11">
         <v>0.70833333333333204</v>
       </c>
       <c r="D425" s="8" t="s">
@@ -15852,7 +15854,7 @@
         <v>4730</v>
       </c>
     </row>
-    <row r="426" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="426" spans="1:11">
       <c r="A426" s="10">
         <f t="shared" ref="A426:A427" si="9">B426-1</f>
         <v>46068</v>
@@ -15860,7 +15862,7 @@
       <c r="B426" s="8">
         <v>46069</v>
       </c>
-      <c r="C426" s="12">
+      <c r="C426" s="11">
         <v>0.70833333333333304</v>
       </c>
       <c r="D426" s="8" t="s">
@@ -15888,7 +15890,7 @@
         <v>4757</v>
       </c>
     </row>
-    <row r="427" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="427" spans="1:11">
       <c r="A427" s="10">
         <f t="shared" si="9"/>
         <v>46075</v>
@@ -15896,7 +15898,7 @@
       <c r="B427" s="8">
         <v>46076</v>
       </c>
-      <c r="C427" s="12">
+      <c r="C427" s="11">
         <v>0.70833333333333304</v>
       </c>
       <c r="D427" s="8" t="s">
@@ -15924,14 +15926,14 @@
         <v>4432</v>
       </c>
     </row>
-    <row r="428" spans="1:11" x14ac:dyDescent="0.2">
-      <c r="A428" s="16">
+    <row r="428" spans="1:11">
+      <c r="A428" s="10">
         <v>46083</v>
       </c>
-      <c r="B428" s="16">
+      <c r="B428" s="10">
         <v>46083</v>
       </c>
-      <c r="C428" s="12">
+      <c r="C428" s="11">
         <v>0.70833333333333304</v>
       </c>
       <c r="D428" s="8" t="s">
@@ -15975,12 +15977,12 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{362BE34E-9F1D-4DC0-8A14-D289984A66A9}">
   <dimension ref="B2:G3"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="9" defaultRowHeight="14"/>
   <cols>
     <col min="1" max="16384" width="9" style="1"/>
   </cols>
   <sheetData>
-    <row r="2" spans="2:7" x14ac:dyDescent="0.25">
+    <row r="2" spans="2:7" ht="15">
       <c r="B2" s="2" t="s">
         <v>16</v>
       </c>
@@ -15992,7 +15994,7 @@
       <c r="F2" s="3"/>
       <c r="G2" s="3"/>
     </row>
-    <row r="3" spans="2:7" x14ac:dyDescent="0.25">
+    <row r="3" spans="2:7">
       <c r="B3" s="4" t="s">
         <v>15</v>
       </c>

--- a/data/freight/Baltic air freight index.xlsx
+++ b/data/freight/Baltic air freight index.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\USER\PycharmProjects\AlternativeData\data\freight\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7210A73E-8569-479A-AB26-CF7EC191D943}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{52029FB2-6948-48C7-A109-F1B04EAEC6AD}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="16995" yWindow="780" windowWidth="19005" windowHeight="20685" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="449" uniqueCount="24">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="450" uniqueCount="24">
   <si>
     <t>Shanghai Pudong Outbound</t>
   </si>
@@ -258,13 +258,13 @@
     <xf numFmtId="178" fontId="9" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="177" fontId="8" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="178" fontId="8" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="3">
     <cellStyle name="쉼표" xfId="1" builtinId="3"/>
@@ -18810,6 +18810,7 @@
         <c:minorTickMark val="none"/>
         <c:tickLblPos val="nextTo"/>
         <c:crossAx val="1850654096"/>
+        <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblOffset val="100"/>
         <c:baseTimeUnit val="days"/>
@@ -19764,7 +19765,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:K429"/>
+  <dimension ref="A1:K430"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="12.75" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="11.375" style="10" bestFit="1" customWidth="1"/>
@@ -19779,16 +19780,16 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A1" s="12" t="s">
+      <c r="A1" s="13" t="s">
         <v>18</v>
       </c>
-      <c r="B1" s="12" t="s">
+      <c r="B1" s="13" t="s">
         <v>17</v>
       </c>
-      <c r="C1" s="13" t="s">
+      <c r="C1" s="14" t="s">
         <v>19</v>
       </c>
-      <c r="D1" s="12" t="s">
+      <c r="D1" s="13" t="s">
         <v>20</v>
       </c>
       <c r="E1" s="6" t="s">
@@ -19814,10 +19815,10 @@
       </c>
     </row>
     <row r="2" spans="1:11" x14ac:dyDescent="0.2">
-      <c r="A2" s="12"/>
-      <c r="B2" s="12"/>
-      <c r="C2" s="13"/>
-      <c r="D2" s="12"/>
+      <c r="A2" s="13"/>
+      <c r="B2" s="13"/>
+      <c r="C2" s="14"/>
+      <c r="D2" s="13"/>
       <c r="E2" s="6" t="s">
         <v>6</v>
       </c>
@@ -35177,7 +35178,7 @@
     </row>
     <row r="429" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A429" s="10">
-        <f t="shared" ref="A429" si="10">B429-1</f>
+        <f t="shared" ref="A429:A430" si="10">B429-1</f>
         <v>46089</v>
       </c>
       <c r="B429" s="8">
@@ -35209,6 +35210,42 @@
       </c>
       <c r="K429" s="9">
         <v>4012</v>
+      </c>
+    </row>
+    <row r="430" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="A430" s="10">
+        <f t="shared" si="10"/>
+        <v>46096</v>
+      </c>
+      <c r="B430" s="8">
+        <v>46097</v>
+      </c>
+      <c r="C430" s="11">
+        <v>0.70833333333333304</v>
+      </c>
+      <c r="D430" s="8" t="s">
+        <v>21</v>
+      </c>
+      <c r="E430" s="9">
+        <v>2065</v>
+      </c>
+      <c r="F430" s="9">
+        <v>1031</v>
+      </c>
+      <c r="G430" s="9">
+        <v>3472</v>
+      </c>
+      <c r="H430" s="9">
+        <v>1236</v>
+      </c>
+      <c r="I430" s="9">
+        <v>1072</v>
+      </c>
+      <c r="J430" s="9">
+        <v>346</v>
+      </c>
+      <c r="K430" s="9">
+        <v>4208</v>
       </c>
     </row>
   </sheetData>
@@ -35229,7 +35266,7 @@
   <dimension ref="A1"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="16384" width="9" style="14"/>
+    <col min="1" max="16384" width="9" style="12"/>
   </cols>
   <sheetData/>
   <phoneticPr fontId="2" type="noConversion"/>

--- a/data/freight/Baltic air freight index.xlsx
+++ b/data/freight/Baltic air freight index.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\USER\PycharmProjects\AlternativeData\data\freight\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{52029FB2-6948-48C7-A109-F1B04EAEC6AD}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9BC0A3B2-FE3E-4247-B698-B4C2572DABDD}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="16995" yWindow="780" windowWidth="19005" windowHeight="20685" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="450" uniqueCount="24">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="451" uniqueCount="24">
   <si>
     <t>Shanghai Pudong Outbound</t>
   </si>
@@ -335,10 +335,10 @@
           </c:marker>
           <c:cat>
             <c:numRef>
-              <c:f>BAI!$B$3:$B$429</c:f>
+              <c:f>BAI!$B$3:$B$1429</c:f>
               <c:numCache>
                 <c:formatCode>yyyy\-mm\-dd;@</c:formatCode>
-                <c:ptCount val="427"/>
+                <c:ptCount val="1427"/>
                 <c:pt idx="0">
                   <c:v>43101</c:v>
                 </c:pt>
@@ -1619,16 +1619,22 @@
                 </c:pt>
                 <c:pt idx="426">
                   <c:v>46090</c:v>
+                </c:pt>
+                <c:pt idx="427">
+                  <c:v>46097</c:v>
+                </c:pt>
+                <c:pt idx="428">
+                  <c:v>46104</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>BAI!$E$3:$E$429</c:f>
+              <c:f>BAI!$E$3:$E$1429</c:f>
               <c:numCache>
                 <c:formatCode>_(* #,##0_);_(* \(#,##0\);_(* "-"??_);_(@_)</c:formatCode>
-                <c:ptCount val="427"/>
+                <c:ptCount val="1427"/>
                 <c:pt idx="0">
                   <c:v>1833</c:v>
                 </c:pt>
@@ -2909,6 +2915,12 @@
                 </c:pt>
                 <c:pt idx="426">
                   <c:v>2012</c:v>
+                </c:pt>
+                <c:pt idx="427">
+                  <c:v>2065</c:v>
+                </c:pt>
+                <c:pt idx="428">
+                  <c:v>2192</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -2951,10 +2963,10 @@
           </c:marker>
           <c:cat>
             <c:numRef>
-              <c:f>BAI!$B$3:$B$429</c:f>
+              <c:f>BAI!$B$3:$B$1429</c:f>
               <c:numCache>
                 <c:formatCode>yyyy\-mm\-dd;@</c:formatCode>
-                <c:ptCount val="427"/>
+                <c:ptCount val="1427"/>
                 <c:pt idx="0">
                   <c:v>43101</c:v>
                 </c:pt>
@@ -4235,16 +4247,22 @@
                 </c:pt>
                 <c:pt idx="426">
                   <c:v>46090</c:v>
+                </c:pt>
+                <c:pt idx="427">
+                  <c:v>46097</c:v>
+                </c:pt>
+                <c:pt idx="428">
+                  <c:v>46104</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>BAI!$F$3:$F$429</c:f>
+              <c:f>BAI!$F$3:$F$1429</c:f>
               <c:numCache>
                 <c:formatCode>_(* #,##0_);_(* \(#,##0\);_(* "-"??_);_(@_)</c:formatCode>
-                <c:ptCount val="427"/>
+                <c:ptCount val="1427"/>
                 <c:pt idx="0">
                   <c:v>1460</c:v>
                 </c:pt>
@@ -5525,6 +5543,12 @@
                 </c:pt>
                 <c:pt idx="426">
                   <c:v>956</c:v>
+                </c:pt>
+                <c:pt idx="427">
+                  <c:v>1031</c:v>
+                </c:pt>
+                <c:pt idx="428">
+                  <c:v>1158</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -5567,10 +5591,10 @@
           </c:marker>
           <c:cat>
             <c:numRef>
-              <c:f>BAI!$B$3:$B$429</c:f>
+              <c:f>BAI!$B$3:$B$1429</c:f>
               <c:numCache>
                 <c:formatCode>yyyy\-mm\-dd;@</c:formatCode>
-                <c:ptCount val="427"/>
+                <c:ptCount val="1427"/>
                 <c:pt idx="0">
                   <c:v>43101</c:v>
                 </c:pt>
@@ -6851,16 +6875,22 @@
                 </c:pt>
                 <c:pt idx="426">
                   <c:v>46090</c:v>
+                </c:pt>
+                <c:pt idx="427">
+                  <c:v>46097</c:v>
+                </c:pt>
+                <c:pt idx="428">
+                  <c:v>46104</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>BAI!$G$3:$G$429</c:f>
+              <c:f>BAI!$G$3:$G$1429</c:f>
               <c:numCache>
                 <c:formatCode>_(* #,##0_);_(* \(#,##0\);_(* "-"??_);_(@_)</c:formatCode>
-                <c:ptCount val="427"/>
+                <c:ptCount val="1427"/>
                 <c:pt idx="0">
                   <c:v>2417</c:v>
                 </c:pt>
@@ -8141,6 +8171,12 @@
                 </c:pt>
                 <c:pt idx="426">
                   <c:v>3430</c:v>
+                </c:pt>
+                <c:pt idx="427">
+                  <c:v>3472</c:v>
+                </c:pt>
+                <c:pt idx="428">
+                  <c:v>3599</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -8183,10 +8219,10 @@
           </c:marker>
           <c:cat>
             <c:numRef>
-              <c:f>BAI!$B$3:$B$429</c:f>
+              <c:f>BAI!$B$3:$B$1429</c:f>
               <c:numCache>
                 <c:formatCode>yyyy\-mm\-dd;@</c:formatCode>
-                <c:ptCount val="427"/>
+                <c:ptCount val="1427"/>
                 <c:pt idx="0">
                   <c:v>43101</c:v>
                 </c:pt>
@@ -9467,16 +9503,22 @@
                 </c:pt>
                 <c:pt idx="426">
                   <c:v>46090</c:v>
+                </c:pt>
+                <c:pt idx="427">
+                  <c:v>46097</c:v>
+                </c:pt>
+                <c:pt idx="428">
+                  <c:v>46104</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>BAI!$H$3:$H$429</c:f>
+              <c:f>BAI!$H$3:$H$1429</c:f>
               <c:numCache>
                 <c:formatCode>_(* #,##0_);_(* \(#,##0\);_(* "-"??_);_(@_)</c:formatCode>
-                <c:ptCount val="427"/>
+                <c:ptCount val="1427"/>
                 <c:pt idx="0">
                   <c:v>1430</c:v>
                 </c:pt>
@@ -10757,6 +10799,12 @@
                 </c:pt>
                 <c:pt idx="426">
                   <c:v>1291</c:v>
+                </c:pt>
+                <c:pt idx="427">
+                  <c:v>1236</c:v>
+                </c:pt>
+                <c:pt idx="428">
+                  <c:v>1226</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -10799,10 +10847,10 @@
           </c:marker>
           <c:cat>
             <c:numRef>
-              <c:f>BAI!$B$3:$B$429</c:f>
+              <c:f>BAI!$B$3:$B$1429</c:f>
               <c:numCache>
                 <c:formatCode>yyyy\-mm\-dd;@</c:formatCode>
-                <c:ptCount val="427"/>
+                <c:ptCount val="1427"/>
                 <c:pt idx="0">
                   <c:v>43101</c:v>
                 </c:pt>
@@ -12083,16 +12131,22 @@
                 </c:pt>
                 <c:pt idx="426">
                   <c:v>46090</c:v>
+                </c:pt>
+                <c:pt idx="427">
+                  <c:v>46097</c:v>
+                </c:pt>
+                <c:pt idx="428">
+                  <c:v>46104</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>BAI!$I$3:$I$429</c:f>
+              <c:f>BAI!$I$3:$I$1429</c:f>
               <c:numCache>
                 <c:formatCode>_(* #,##0_);_(* \(#,##0\);_(* "-"??_);_(@_)</c:formatCode>
-                <c:ptCount val="427"/>
+                <c:ptCount val="1427"/>
                 <c:pt idx="0">
                   <c:v>1380</c:v>
                 </c:pt>
@@ -13373,6 +13427,12 @@
                 </c:pt>
                 <c:pt idx="426">
                   <c:v>1032</c:v>
+                </c:pt>
+                <c:pt idx="427">
+                  <c:v>1072</c:v>
+                </c:pt>
+                <c:pt idx="428">
+                  <c:v>910</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -13417,10 +13477,10 @@
           </c:marker>
           <c:cat>
             <c:numRef>
-              <c:f>BAI!$B$3:$B$429</c:f>
+              <c:f>BAI!$B$3:$B$1429</c:f>
               <c:numCache>
                 <c:formatCode>yyyy\-mm\-dd;@</c:formatCode>
-                <c:ptCount val="427"/>
+                <c:ptCount val="1427"/>
                 <c:pt idx="0">
                   <c:v>43101</c:v>
                 </c:pt>
@@ -14701,16 +14761,22 @@
                 </c:pt>
                 <c:pt idx="426">
                   <c:v>46090</c:v>
+                </c:pt>
+                <c:pt idx="427">
+                  <c:v>46097</c:v>
+                </c:pt>
+                <c:pt idx="428">
+                  <c:v>46104</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>BAI!$K$3:$K$429</c:f>
+              <c:f>BAI!$K$3:$K$1429</c:f>
               <c:numCache>
                 <c:formatCode>_(* #,##0_);_(* \(#,##0\);_(* "-"??_);_(@_)</c:formatCode>
-                <c:ptCount val="427"/>
+                <c:ptCount val="1427"/>
                 <c:pt idx="0">
                   <c:v>3169</c:v>
                 </c:pt>
@@ -15991,6 +16057,12 @@
                 </c:pt>
                 <c:pt idx="426">
                   <c:v>4012</c:v>
+                </c:pt>
+                <c:pt idx="427">
+                  <c:v>4208</c:v>
+                </c:pt>
+                <c:pt idx="428">
+                  <c:v>4794</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -16049,10 +16121,10 @@
           </c:marker>
           <c:cat>
             <c:numRef>
-              <c:f>BAI!$B$3:$B$429</c:f>
+              <c:f>BAI!$B$3:$B$1429</c:f>
               <c:numCache>
                 <c:formatCode>yyyy\-mm\-dd;@</c:formatCode>
-                <c:ptCount val="427"/>
+                <c:ptCount val="1427"/>
                 <c:pt idx="0">
                   <c:v>43101</c:v>
                 </c:pt>
@@ -17333,16 +17405,22 @@
                 </c:pt>
                 <c:pt idx="426">
                   <c:v>46090</c:v>
+                </c:pt>
+                <c:pt idx="427">
+                  <c:v>46097</c:v>
+                </c:pt>
+                <c:pt idx="428">
+                  <c:v>46104</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>BAI!$J$3:$J$429</c:f>
+              <c:f>BAI!$J$3:$J$1429</c:f>
               <c:numCache>
                 <c:formatCode>_(* #,##0_);_(* \(#,##0\);_(* "-"??_);_(@_)</c:formatCode>
-                <c:ptCount val="427"/>
+                <c:ptCount val="1427"/>
                 <c:pt idx="0">
                   <c:v>199</c:v>
                 </c:pt>
@@ -18623,6 +18701,12 @@
                 </c:pt>
                 <c:pt idx="426">
                   <c:v>341</c:v>
+                </c:pt>
+                <c:pt idx="427">
+                  <c:v>346</c:v>
+                </c:pt>
+                <c:pt idx="428">
+                  <c:v>362</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -18684,8 +18768,8 @@
                     <a:lumOff val="35000"/>
                   </a:schemeClr>
                 </a:solidFill>
-                <a:latin typeface="+mn-lt"/>
-                <a:ea typeface="+mn-ea"/>
+                <a:latin typeface="Verdana" panose="020B0604030504040204" pitchFamily="34" charset="0"/>
+                <a:ea typeface="Verdana" panose="020B0604030504040204" pitchFamily="34" charset="0"/>
                 <a:cs typeface="+mn-cs"/>
               </a:defRPr>
             </a:pPr>
@@ -18744,8 +18828,8 @@
                     <a:lumOff val="35000"/>
                   </a:schemeClr>
                 </a:solidFill>
-                <a:latin typeface="+mn-lt"/>
-                <a:ea typeface="+mn-ea"/>
+                <a:latin typeface="Verdana" panose="020B0604030504040204" pitchFamily="34" charset="0"/>
+                <a:ea typeface="Verdana" panose="020B0604030504040204" pitchFamily="34" charset="0"/>
                 <a:cs typeface="+mn-cs"/>
               </a:defRPr>
             </a:pPr>
@@ -18786,8 +18870,8 @@
                     <a:lumOff val="35000"/>
                   </a:schemeClr>
                 </a:solidFill>
-                <a:latin typeface="+mn-lt"/>
-                <a:ea typeface="+mn-ea"/>
+                <a:latin typeface="Verdana" panose="020B0604030504040204" pitchFamily="34" charset="0"/>
+                <a:ea typeface="Verdana" panose="020B0604030504040204" pitchFamily="34" charset="0"/>
                 <a:cs typeface="+mn-cs"/>
               </a:defRPr>
             </a:pPr>
@@ -18890,7 +18974,10 @@
     <a:lstStyle/>
     <a:p>
       <a:pPr>
-        <a:defRPr/>
+        <a:defRPr>
+          <a:latin typeface="Verdana" panose="020B0604030504040204" pitchFamily="34" charset="0"/>
+          <a:ea typeface="Verdana" panose="020B0604030504040204" pitchFamily="34" charset="0"/>
+        </a:defRPr>
       </a:pPr>
       <a:endParaRPr lang="ko-KR"/>
     </a:p>
@@ -19765,7 +19852,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:K430"/>
+  <dimension ref="A1:K431"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="12.75" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="11.375" style="10" bestFit="1" customWidth="1"/>
@@ -35246,6 +35333,41 @@
       </c>
       <c r="K430" s="9">
         <v>4208</v>
+      </c>
+    </row>
+    <row r="431" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="A431" s="10">
+        <v>46083</v>
+      </c>
+      <c r="B431" s="10">
+        <v>46104</v>
+      </c>
+      <c r="C431" s="11">
+        <v>0.70833333333333304</v>
+      </c>
+      <c r="D431" s="8" t="s">
+        <v>21</v>
+      </c>
+      <c r="E431" s="9">
+        <v>2192</v>
+      </c>
+      <c r="F431" s="9">
+        <v>1158</v>
+      </c>
+      <c r="G431" s="9">
+        <v>3599</v>
+      </c>
+      <c r="H431" s="9">
+        <v>1226</v>
+      </c>
+      <c r="I431" s="9">
+        <v>910</v>
+      </c>
+      <c r="J431" s="9">
+        <v>362</v>
+      </c>
+      <c r="K431" s="9">
+        <v>4794</v>
       </c>
     </row>
   </sheetData>

--- a/data/freight/Baltic air freight index.xlsx
+++ b/data/freight/Baltic air freight index.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="20417"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29822"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\USER\PycharmProjects\AlternativeData\data\freight\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Geust\PycharmProjects\AlternativeData\data\freight\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9BC0A3B2-FE3E-4247-B698-B4C2572DABDD}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7370D995-9AC5-42ED-8C5D-FF16B35400B8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="16995" yWindow="780" windowWidth="19005" windowHeight="20685" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="23260" windowHeight="14860" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="BAI" sheetId="1" r:id="rId1"/>
@@ -22,12 +22,23 @@
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
     </ext>
+    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
+      <xcalcf:calcFeatures>
+        <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:Single"/>
+        <xcalcf:feature name="microsoft.com:FV"/>
+        <xcalcf:feature name="microsoft.com:CNMTM"/>
+        <xcalcf:feature name="microsoft.com:LET_WF"/>
+        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
+        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
+      </xcalcf:calcFeatures>
+    </ext>
   </extLst>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="451" uniqueCount="24">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="452" uniqueCount="24">
   <si>
     <t>Shanghai Pudong Outbound</t>
   </si>
@@ -117,29 +128,29 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <numFmts count="4">
-    <numFmt numFmtId="43" formatCode="_-* #,##0.00_-;\-* #,##0.00_-;_-* &quot;-&quot;??_-;_-@_-"/>
-    <numFmt numFmtId="176" formatCode="_(* #,##0_);_(* \(#,##0\);_(* &quot;-&quot;??_);_(@_)"/>
-    <numFmt numFmtId="177" formatCode="yyyy\-mm\-dd;@"/>
-    <numFmt numFmtId="178" formatCode="[$-409]h:mm:ss\ AM/PM;@"/>
+    <numFmt numFmtId="164" formatCode="_-* #,##0.00_-;\-* #,##0.00_-;_-* &quot;-&quot;??_-;_-@_-"/>
+    <numFmt numFmtId="165" formatCode="_(* #,##0_);_(* \(#,##0\);_(* &quot;-&quot;??_);_(@_)"/>
+    <numFmt numFmtId="166" formatCode="yyyy\-mm\-dd;@"/>
+    <numFmt numFmtId="167" formatCode="[$-409]h:mm:ss\ AM/PM;@"/>
   </numFmts>
-  <fonts count="11" x14ac:knownFonts="1">
+  <fonts count="11">
     <font>
       <sz val="11"/>
       <color theme="1"/>
-      <name val="맑은 고딕"/>
+      <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
     </font>
     <font>
       <sz val="11"/>
       <color theme="1"/>
-      <name val="맑은 고딕"/>
+      <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
     </font>
     <font>
       <sz val="8"/>
-      <name val="맑은 고딕"/>
+      <name val="Calibri"/>
       <family val="3"/>
       <charset val="129"/>
       <scheme val="minor"/>
@@ -161,7 +172,7 @@
     <font>
       <sz val="10"/>
       <color theme="1"/>
-      <name val="맑은 고딕"/>
+      <name val="Calibri"/>
       <family val="3"/>
       <charset val="129"/>
       <scheme val="minor"/>
@@ -178,7 +189,7 @@
       <b/>
       <sz val="10"/>
       <color theme="1"/>
-      <name val="맑은 고딕"/>
+      <name val="Calibri"/>
       <family val="3"/>
       <charset val="129"/>
       <scheme val="minor"/>
@@ -222,7 +233,7 @@
   </borders>
   <cellStyleXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
-    <xf numFmtId="43" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="164" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
@@ -242,34 +253,34 @@
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="2">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="176" fontId="8" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1">
+    <xf numFmtId="165" fontId="8" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="177" fontId="9" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="166" fontId="9" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="176" fontId="9" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1">
+    <xf numFmtId="165" fontId="9" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="177" fontId="9" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="166" fontId="9" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="178" fontId="9" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="167" fontId="9" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="177" fontId="8" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="166" fontId="8" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="178" fontId="8" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="167" fontId="8" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="3">
-    <cellStyle name="쉼표" xfId="1" builtinId="3"/>
-    <cellStyle name="표준" xfId="0" builtinId="0"/>
-    <cellStyle name="하이퍼링크" xfId="2" builtinId="8"/>
+    <cellStyle name="Comma" xfId="1" builtinId="3"/>
+    <cellStyle name="Hyperlink" xfId="2" builtinId="8"/>
+    <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
@@ -287,7 +298,7 @@
 <file path=xl/charts/chart1.xml><?xml version="1.0" encoding="utf-8"?>
 <c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
   <c:date1904 val="0"/>
-  <c:lang val="ko-KR"/>
+  <c:lang val="en-US"/>
   <c:roundedCorners val="0"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart" Requires="c14">
@@ -1626,6 +1637,9 @@
                 <c:pt idx="428">
                   <c:v>46104</c:v>
                 </c:pt>
+                <c:pt idx="429">
+                  <c:v>46111</c:v>
+                </c:pt>
               </c:numCache>
             </c:numRef>
           </c:cat>
@@ -2921,6 +2935,9 @@
                 </c:pt>
                 <c:pt idx="428">
                   <c:v>2192</c:v>
+                </c:pt>
+                <c:pt idx="429">
+                  <c:v>2396</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -4254,6 +4271,9 @@
                 <c:pt idx="428">
                   <c:v>46104</c:v>
                 </c:pt>
+                <c:pt idx="429">
+                  <c:v>46111</c:v>
+                </c:pt>
               </c:numCache>
             </c:numRef>
           </c:cat>
@@ -5549,6 +5569,9 @@
                 </c:pt>
                 <c:pt idx="428">
                   <c:v>1158</c:v>
+                </c:pt>
+                <c:pt idx="429">
+                  <c:v>1198</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -6882,6 +6905,9 @@
                 <c:pt idx="428">
                   <c:v>46104</c:v>
                 </c:pt>
+                <c:pt idx="429">
+                  <c:v>46111</c:v>
+                </c:pt>
               </c:numCache>
             </c:numRef>
           </c:cat>
@@ -8177,6 +8203,9 @@
                 </c:pt>
                 <c:pt idx="428">
                   <c:v>3599</c:v>
+                </c:pt>
+                <c:pt idx="429">
+                  <c:v>3871</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -9510,6 +9539,9 @@
                 <c:pt idx="428">
                   <c:v>46104</c:v>
                 </c:pt>
+                <c:pt idx="429">
+                  <c:v>46111</c:v>
+                </c:pt>
               </c:numCache>
             </c:numRef>
           </c:cat>
@@ -10805,6 +10837,9 @@
                 </c:pt>
                 <c:pt idx="428">
                   <c:v>1226</c:v>
+                </c:pt>
+                <c:pt idx="429">
+                  <c:v>1296</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -12138,6 +12173,9 @@
                 <c:pt idx="428">
                   <c:v>46104</c:v>
                 </c:pt>
+                <c:pt idx="429">
+                  <c:v>46111</c:v>
+                </c:pt>
               </c:numCache>
             </c:numRef>
           </c:cat>
@@ -13433,6 +13471,9 @@
                 </c:pt>
                 <c:pt idx="428">
                   <c:v>910</c:v>
+                </c:pt>
+                <c:pt idx="429">
+                  <c:v>1170</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -14768,6 +14809,9 @@
                 <c:pt idx="428">
                   <c:v>46104</c:v>
                 </c:pt>
+                <c:pt idx="429">
+                  <c:v>46111</c:v>
+                </c:pt>
               </c:numCache>
             </c:numRef>
           </c:cat>
@@ -16063,6 +16107,9 @@
                 </c:pt>
                 <c:pt idx="428">
                   <c:v>4794</c:v>
+                </c:pt>
+                <c:pt idx="429">
+                  <c:v>5348</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -17412,6 +17459,9 @@
                 <c:pt idx="428">
                   <c:v>46104</c:v>
                 </c:pt>
+                <c:pt idx="429">
+                  <c:v>46111</c:v>
+                </c:pt>
               </c:numCache>
             </c:numRef>
           </c:cat>
@@ -18707,6 +18757,9 @@
                 </c:pt>
                 <c:pt idx="428">
                   <c:v>362</c:v>
+                </c:pt>
+                <c:pt idx="429">
+                  <c:v>291</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -18950,6 +19003,7 @@
     </c:legend>
     <c:plotVisOnly val="1"/>
     <c:dispBlanksAs val="gap"/>
+    <c:showDLblsOverMax val="0"/>
     <c:extLst>
       <c:ext xmlns:c16r3="http://schemas.microsoft.com/office/drawing/2017/03/chart" uri="{56B9EC1D-385E-4148-901F-78D8002777C0}">
         <c16r3:dataDisplayOptions16>
@@ -18957,7 +19011,6 @@
         </c16r3:dataDisplayOptions16>
       </c:ext>
     </c:extLst>
-    <c:showDLblsOverMax val="0"/>
   </c:chart>
   <c:spPr>
     <a:solidFill>
@@ -19852,21 +19905,21 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:K431"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="12.75" x14ac:dyDescent="0.2"/>
+  <dimension ref="A1:K432"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5"/>
   <cols>
-    <col min="1" max="1" width="11.375" style="10" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="12.08984375" style="10" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="14" style="8" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="11.125" style="11" customWidth="1"/>
-    <col min="4" max="4" width="11.125" style="8" customWidth="1"/>
-    <col min="5" max="8" width="8.625" style="9" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="9.5" style="9" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="8.625" style="9" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="9.5" style="9" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="11.81640625" style="11" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="11.08984375" style="8" customWidth="1"/>
+    <col min="5" max="8" width="8.6328125" style="9" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="9.453125" style="9" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="8.6328125" style="9" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="9.453125" style="9" bestFit="1" customWidth="1"/>
     <col min="12" max="16384" width="9" style="7"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:11" ht="15" customHeight="1">
       <c r="A1" s="13" t="s">
         <v>18</v>
       </c>
@@ -19901,7 +19954,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="2" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:11">
       <c r="A2" s="13"/>
       <c r="B2" s="13"/>
       <c r="C2" s="14"/>
@@ -19928,9 +19981,8 @@
         <v>0</v>
       </c>
     </row>
-    <row r="3" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="3" spans="1:11">
       <c r="A3" s="10">
-        <f>B3-1</f>
         <v>43100</v>
       </c>
       <c r="B3" s="8">
@@ -19964,9 +20016,8 @@
         <v>3169</v>
       </c>
     </row>
-    <row r="4" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="4" spans="1:11">
       <c r="A4" s="10">
-        <f t="shared" ref="A4:A67" si="0">B4-1</f>
         <v>43107</v>
       </c>
       <c r="B4" s="8">
@@ -20000,9 +20051,8 @@
         <v>2961</v>
       </c>
     </row>
-    <row r="5" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:11">
       <c r="A5" s="10">
-        <f t="shared" si="0"/>
         <v>43114</v>
       </c>
       <c r="B5" s="8">
@@ -20036,9 +20086,8 @@
         <v>2650</v>
       </c>
     </row>
-    <row r="6" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:11">
       <c r="A6" s="10">
-        <f t="shared" si="0"/>
         <v>43121</v>
       </c>
       <c r="B6" s="8">
@@ -20072,9 +20121,8 @@
         <v>2807</v>
       </c>
     </row>
-    <row r="7" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:11">
       <c r="A7" s="10">
-        <f t="shared" si="0"/>
         <v>43128</v>
       </c>
       <c r="B7" s="8">
@@ -20108,9 +20156,8 @@
         <v>2904</v>
       </c>
     </row>
-    <row r="8" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:11">
       <c r="A8" s="10">
-        <f t="shared" si="0"/>
         <v>43135</v>
       </c>
       <c r="B8" s="8">
@@ -20144,9 +20191,8 @@
         <v>2899</v>
       </c>
     </row>
-    <row r="9" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:11">
       <c r="A9" s="10">
-        <f t="shared" si="0"/>
         <v>43142</v>
       </c>
       <c r="B9" s="8">
@@ -20180,9 +20226,8 @@
         <v>2901</v>
       </c>
     </row>
-    <row r="10" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:11">
       <c r="A10" s="10">
-        <f t="shared" si="0"/>
         <v>43149</v>
       </c>
       <c r="B10" s="8">
@@ -20216,9 +20261,8 @@
         <v>2727</v>
       </c>
     </row>
-    <row r="11" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:11">
       <c r="A11" s="10">
-        <f t="shared" si="0"/>
         <v>43156</v>
       </c>
       <c r="B11" s="8">
@@ -20252,9 +20296,8 @@
         <v>2761</v>
       </c>
     </row>
-    <row r="12" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:11">
       <c r="A12" s="10">
-        <f t="shared" si="0"/>
         <v>43163</v>
       </c>
       <c r="B12" s="8">
@@ -20288,9 +20331,8 @@
         <v>2517</v>
       </c>
     </row>
-    <row r="13" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:11">
       <c r="A13" s="10">
-        <f t="shared" si="0"/>
         <v>43170</v>
       </c>
       <c r="B13" s="8">
@@ -20324,9 +20366,8 @@
         <v>2740</v>
       </c>
     </row>
-    <row r="14" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:11">
       <c r="A14" s="10">
-        <f t="shared" si="0"/>
         <v>43177</v>
       </c>
       <c r="B14" s="8">
@@ -20360,9 +20401,8 @@
         <v>2752</v>
       </c>
     </row>
-    <row r="15" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:11">
       <c r="A15" s="10">
-        <f t="shared" si="0"/>
         <v>43184</v>
       </c>
       <c r="B15" s="8">
@@ -20396,9 +20436,8 @@
         <v>2814</v>
       </c>
     </row>
-    <row r="16" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:11">
       <c r="A16" s="10">
-        <f t="shared" si="0"/>
         <v>43191</v>
       </c>
       <c r="B16" s="8">
@@ -20432,9 +20471,8 @@
         <v>2989</v>
       </c>
     </row>
-    <row r="17" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="17" spans="1:11">
       <c r="A17" s="10">
-        <f t="shared" si="0"/>
         <v>43198</v>
       </c>
       <c r="B17" s="8">
@@ -20468,9 +20506,8 @@
         <v>3053</v>
       </c>
     </row>
-    <row r="18" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="18" spans="1:11">
       <c r="A18" s="10">
-        <f t="shared" si="0"/>
         <v>43205</v>
       </c>
       <c r="B18" s="8">
@@ -20504,9 +20541,8 @@
         <v>2992</v>
       </c>
     </row>
-    <row r="19" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="19" spans="1:11">
       <c r="A19" s="10">
-        <f t="shared" si="0"/>
         <v>43212</v>
       </c>
       <c r="B19" s="8">
@@ -20540,9 +20576,8 @@
         <v>3134</v>
       </c>
     </row>
-    <row r="20" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="20" spans="1:11">
       <c r="A20" s="10">
-        <f t="shared" si="0"/>
         <v>43219</v>
       </c>
       <c r="B20" s="8">
@@ -20576,9 +20611,8 @@
         <v>3103</v>
       </c>
     </row>
-    <row r="21" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="21" spans="1:11">
       <c r="A21" s="10">
-        <f t="shared" si="0"/>
         <v>43226</v>
       </c>
       <c r="B21" s="8">
@@ -20612,9 +20646,8 @@
         <v>2954</v>
       </c>
     </row>
-    <row r="22" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="22" spans="1:11">
       <c r="A22" s="10">
-        <f t="shared" si="0"/>
         <v>43233</v>
       </c>
       <c r="B22" s="8">
@@ -20648,9 +20681,8 @@
         <v>2913</v>
       </c>
     </row>
-    <row r="23" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="23" spans="1:11">
       <c r="A23" s="10">
-        <f t="shared" si="0"/>
         <v>43240</v>
       </c>
       <c r="B23" s="8">
@@ -20684,9 +20716,8 @@
         <v>2924</v>
       </c>
     </row>
-    <row r="24" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="24" spans="1:11">
       <c r="A24" s="10">
-        <f t="shared" si="0"/>
         <v>43247</v>
       </c>
       <c r="B24" s="8">
@@ -20720,9 +20751,8 @@
         <v>2888</v>
       </c>
     </row>
-    <row r="25" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="25" spans="1:11">
       <c r="A25" s="10">
-        <f t="shared" si="0"/>
         <v>43254</v>
       </c>
       <c r="B25" s="8">
@@ -20756,9 +20786,8 @@
         <v>2904</v>
       </c>
     </row>
-    <row r="26" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="26" spans="1:11">
       <c r="A26" s="10">
-        <f t="shared" si="0"/>
         <v>43261</v>
       </c>
       <c r="B26" s="8">
@@ -20792,9 +20821,8 @@
         <v>2959</v>
       </c>
     </row>
-    <row r="27" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="27" spans="1:11">
       <c r="A27" s="10">
-        <f t="shared" si="0"/>
         <v>43268</v>
       </c>
       <c r="B27" s="8">
@@ -20828,9 +20856,8 @@
         <v>2873</v>
       </c>
     </row>
-    <row r="28" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="28" spans="1:11">
       <c r="A28" s="10">
-        <f t="shared" si="0"/>
         <v>43275</v>
       </c>
       <c r="B28" s="8">
@@ -20864,9 +20891,8 @@
         <v>2769</v>
       </c>
     </row>
-    <row r="29" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="29" spans="1:11">
       <c r="A29" s="10">
-        <f t="shared" si="0"/>
         <v>43282</v>
       </c>
       <c r="B29" s="8">
@@ -20900,9 +20926,8 @@
         <v>3014</v>
       </c>
     </row>
-    <row r="30" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="30" spans="1:11">
       <c r="A30" s="10">
-        <f t="shared" si="0"/>
         <v>43289</v>
       </c>
       <c r="B30" s="8">
@@ -20936,9 +20961,8 @@
         <v>3033</v>
       </c>
     </row>
-    <row r="31" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="31" spans="1:11">
       <c r="A31" s="10">
-        <f t="shared" si="0"/>
         <v>43296</v>
       </c>
       <c r="B31" s="8">
@@ -20972,9 +20996,8 @@
         <v>2930</v>
       </c>
     </row>
-    <row r="32" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="32" spans="1:11">
       <c r="A32" s="10">
-        <f t="shared" si="0"/>
         <v>43303</v>
       </c>
       <c r="B32" s="8">
@@ -21008,9 +21031,8 @@
         <v>3182</v>
       </c>
     </row>
-    <row r="33" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="33" spans="1:11">
       <c r="A33" s="10">
-        <f t="shared" si="0"/>
         <v>43310</v>
       </c>
       <c r="B33" s="8">
@@ -21044,9 +21066,8 @@
         <v>3174</v>
       </c>
     </row>
-    <row r="34" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="34" spans="1:11">
       <c r="A34" s="10">
-        <f t="shared" si="0"/>
         <v>43317</v>
       </c>
       <c r="B34" s="8">
@@ -21080,9 +21101,8 @@
         <v>3183</v>
       </c>
     </row>
-    <row r="35" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="35" spans="1:11">
       <c r="A35" s="10">
-        <f t="shared" si="0"/>
         <v>43324</v>
       </c>
       <c r="B35" s="8">
@@ -21116,9 +21136,8 @@
         <v>3078</v>
       </c>
     </row>
-    <row r="36" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="36" spans="1:11">
       <c r="A36" s="10">
-        <f t="shared" si="0"/>
         <v>43331</v>
       </c>
       <c r="B36" s="8">
@@ -21152,9 +21171,8 @@
         <v>3135</v>
       </c>
     </row>
-    <row r="37" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="37" spans="1:11">
       <c r="A37" s="10">
-        <f t="shared" si="0"/>
         <v>43338</v>
       </c>
       <c r="B37" s="8">
@@ -21188,9 +21206,8 @@
         <v>3138</v>
       </c>
     </row>
-    <row r="38" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="38" spans="1:11">
       <c r="A38" s="10">
-        <f t="shared" si="0"/>
         <v>43345</v>
       </c>
       <c r="B38" s="8">
@@ -21224,9 +21241,8 @@
         <v>3417</v>
       </c>
     </row>
-    <row r="39" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="39" spans="1:11">
       <c r="A39" s="10">
-        <f t="shared" si="0"/>
         <v>43352</v>
       </c>
       <c r="B39" s="8">
@@ -21260,9 +21276,8 @@
         <v>3427</v>
       </c>
     </row>
-    <row r="40" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="40" spans="1:11">
       <c r="A40" s="10">
-        <f t="shared" si="0"/>
         <v>43359</v>
       </c>
       <c r="B40" s="8">
@@ -21296,9 +21311,8 @@
         <v>3254</v>
       </c>
     </row>
-    <row r="41" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="41" spans="1:11">
       <c r="A41" s="10">
-        <f t="shared" si="0"/>
         <v>43366</v>
       </c>
       <c r="B41" s="8">
@@ -21332,9 +21346,8 @@
         <v>3334</v>
       </c>
     </row>
-    <row r="42" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="42" spans="1:11">
       <c r="A42" s="10">
-        <f t="shared" si="0"/>
         <v>43373</v>
       </c>
       <c r="B42" s="8">
@@ -21368,9 +21381,8 @@
         <v>3450</v>
       </c>
     </row>
-    <row r="43" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="43" spans="1:11">
       <c r="A43" s="10">
-        <f t="shared" si="0"/>
         <v>43380</v>
       </c>
       <c r="B43" s="8">
@@ -21404,9 +21416,8 @@
         <v>3267</v>
       </c>
     </row>
-    <row r="44" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="44" spans="1:11">
       <c r="A44" s="10">
-        <f t="shared" si="0"/>
         <v>43387</v>
       </c>
       <c r="B44" s="8">
@@ -21440,9 +21451,8 @@
         <v>3296</v>
       </c>
     </row>
-    <row r="45" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="45" spans="1:11">
       <c r="A45" s="10">
-        <f t="shared" si="0"/>
         <v>43394</v>
       </c>
       <c r="B45" s="8">
@@ -21476,9 +21486,8 @@
         <v>3511</v>
       </c>
     </row>
-    <row r="46" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="46" spans="1:11">
       <c r="A46" s="10">
-        <f t="shared" si="0"/>
         <v>43401</v>
       </c>
       <c r="B46" s="8">
@@ -21512,9 +21521,8 @@
         <v>3658</v>
       </c>
     </row>
-    <row r="47" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="47" spans="1:11">
       <c r="A47" s="10">
-        <f t="shared" si="0"/>
         <v>43408</v>
       </c>
       <c r="B47" s="8">
@@ -21548,9 +21556,8 @@
         <v>3881</v>
       </c>
     </row>
-    <row r="48" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="48" spans="1:11">
       <c r="A48" s="10">
-        <f t="shared" si="0"/>
         <v>43415</v>
       </c>
       <c r="B48" s="8">
@@ -21584,9 +21591,8 @@
         <v>3696</v>
       </c>
     </row>
-    <row r="49" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="49" spans="1:11">
       <c r="A49" s="10">
-        <f t="shared" si="0"/>
         <v>43422</v>
       </c>
       <c r="B49" s="8">
@@ -21620,9 +21626,8 @@
         <v>3795</v>
       </c>
     </row>
-    <row r="50" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="50" spans="1:11">
       <c r="A50" s="10">
-        <f t="shared" si="0"/>
         <v>43429</v>
       </c>
       <c r="B50" s="8">
@@ -21656,9 +21661,8 @@
         <v>3690</v>
       </c>
     </row>
-    <row r="51" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="51" spans="1:11">
       <c r="A51" s="10">
-        <f t="shared" si="0"/>
         <v>43436</v>
       </c>
       <c r="B51" s="8">
@@ -21692,9 +21696,8 @@
         <v>3542</v>
       </c>
     </row>
-    <row r="52" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="52" spans="1:11">
       <c r="A52" s="10">
-        <f t="shared" si="0"/>
         <v>43443</v>
       </c>
       <c r="B52" s="8">
@@ -21728,9 +21731,8 @@
         <v>3372</v>
       </c>
     </row>
-    <row r="53" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="53" spans="1:11">
       <c r="A53" s="10">
-        <f t="shared" si="0"/>
         <v>43450</v>
       </c>
       <c r="B53" s="8">
@@ -21764,9 +21766,8 @@
         <v>3495</v>
       </c>
     </row>
-    <row r="54" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="54" spans="1:11">
       <c r="A54" s="10">
-        <f t="shared" si="0"/>
         <v>43457</v>
       </c>
       <c r="B54" s="8">
@@ -21800,9 +21801,8 @@
         <v>3197</v>
       </c>
     </row>
-    <row r="55" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="55" spans="1:11">
       <c r="A55" s="10">
-        <f t="shared" si="0"/>
         <v>43464</v>
       </c>
       <c r="B55" s="8">
@@ -21836,9 +21836,8 @@
         <v>3164</v>
       </c>
     </row>
-    <row r="56" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="56" spans="1:11">
       <c r="A56" s="10">
-        <f t="shared" si="0"/>
         <v>43471</v>
       </c>
       <c r="B56" s="8">
@@ -21872,9 +21871,8 @@
         <v>3171</v>
       </c>
     </row>
-    <row r="57" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="57" spans="1:11">
       <c r="A57" s="10">
-        <f t="shared" si="0"/>
         <v>43478</v>
       </c>
       <c r="B57" s="8">
@@ -21908,9 +21906,8 @@
         <v>3147</v>
       </c>
     </row>
-    <row r="58" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="58" spans="1:11">
       <c r="A58" s="10">
-        <f t="shared" si="0"/>
         <v>43485</v>
       </c>
       <c r="B58" s="8">
@@ -21944,9 +21941,8 @@
         <v>3195</v>
       </c>
     </row>
-    <row r="59" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="59" spans="1:11">
       <c r="A59" s="10">
-        <f t="shared" si="0"/>
         <v>43492</v>
       </c>
       <c r="B59" s="8">
@@ -21980,9 +21976,8 @@
         <v>3054</v>
       </c>
     </row>
-    <row r="60" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="60" spans="1:11">
       <c r="A60" s="10">
-        <f t="shared" si="0"/>
         <v>43499</v>
       </c>
       <c r="B60" s="8">
@@ -22016,9 +22011,8 @@
         <v>3148</v>
       </c>
     </row>
-    <row r="61" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="61" spans="1:11">
       <c r="A61" s="10">
-        <f t="shared" si="0"/>
         <v>43506</v>
       </c>
       <c r="B61" s="8">
@@ -22052,9 +22046,8 @@
         <v>3187</v>
       </c>
     </row>
-    <row r="62" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="62" spans="1:11">
       <c r="A62" s="10">
-        <f t="shared" si="0"/>
         <v>43513</v>
       </c>
       <c r="B62" s="8">
@@ -22088,9 +22081,8 @@
         <v>3215</v>
       </c>
     </row>
-    <row r="63" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="63" spans="1:11">
       <c r="A63" s="10">
-        <f t="shared" si="0"/>
         <v>43520</v>
       </c>
       <c r="B63" s="8">
@@ -22124,9 +22116,8 @@
         <v>3068</v>
       </c>
     </row>
-    <row r="64" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="64" spans="1:11">
       <c r="A64" s="10">
-        <f t="shared" si="0"/>
         <v>43527</v>
       </c>
       <c r="B64" s="8">
@@ -22160,9 +22151,8 @@
         <v>2976</v>
       </c>
     </row>
-    <row r="65" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="65" spans="1:11">
       <c r="A65" s="10">
-        <f t="shared" si="0"/>
         <v>43534</v>
       </c>
       <c r="B65" s="8">
@@ -22196,9 +22186,8 @@
         <v>2897</v>
       </c>
     </row>
-    <row r="66" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="66" spans="1:11">
       <c r="A66" s="10">
-        <f t="shared" si="0"/>
         <v>43541</v>
       </c>
       <c r="B66" s="8">
@@ -22232,9 +22221,8 @@
         <v>2954</v>
       </c>
     </row>
-    <row r="67" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="67" spans="1:11">
       <c r="A67" s="10">
-        <f t="shared" si="0"/>
         <v>43548</v>
       </c>
       <c r="B67" s="8">
@@ -22268,9 +22256,8 @@
         <v>2955</v>
       </c>
     </row>
-    <row r="68" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="68" spans="1:11">
       <c r="A68" s="10">
-        <f t="shared" ref="A68:A131" si="1">B68-1</f>
         <v>43555</v>
       </c>
       <c r="B68" s="8">
@@ -22304,9 +22291,8 @@
         <v>2977</v>
       </c>
     </row>
-    <row r="69" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="69" spans="1:11">
       <c r="A69" s="10">
-        <f t="shared" si="1"/>
         <v>43562</v>
       </c>
       <c r="B69" s="8">
@@ -22340,9 +22326,8 @@
         <v>3113</v>
       </c>
     </row>
-    <row r="70" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="70" spans="1:11">
       <c r="A70" s="10">
-        <f t="shared" si="1"/>
         <v>43569</v>
       </c>
       <c r="B70" s="8">
@@ -22376,9 +22361,8 @@
         <v>2876</v>
       </c>
     </row>
-    <row r="71" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="71" spans="1:11">
       <c r="A71" s="10">
-        <f t="shared" si="1"/>
         <v>43576</v>
       </c>
       <c r="B71" s="8">
@@ -22412,9 +22396,8 @@
         <v>2704</v>
       </c>
     </row>
-    <row r="72" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="72" spans="1:11">
       <c r="A72" s="10">
-        <f t="shared" si="1"/>
         <v>43583</v>
       </c>
       <c r="B72" s="8">
@@ -22448,9 +22431,8 @@
         <v>2822</v>
       </c>
     </row>
-    <row r="73" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="73" spans="1:11">
       <c r="A73" s="10">
-        <f t="shared" si="1"/>
         <v>43590</v>
       </c>
       <c r="B73" s="8">
@@ -22484,9 +22466,8 @@
         <v>2776</v>
       </c>
     </row>
-    <row r="74" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="74" spans="1:11">
       <c r="A74" s="10">
-        <f t="shared" si="1"/>
         <v>43597</v>
       </c>
       <c r="B74" s="8">
@@ -22520,9 +22501,8 @@
         <v>2732</v>
       </c>
     </row>
-    <row r="75" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="75" spans="1:11">
       <c r="A75" s="10">
-        <f t="shared" si="1"/>
         <v>43604</v>
       </c>
       <c r="B75" s="8">
@@ -22556,9 +22536,8 @@
         <v>2772</v>
       </c>
     </row>
-    <row r="76" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="76" spans="1:11">
       <c r="A76" s="10">
-        <f t="shared" si="1"/>
         <v>43611</v>
       </c>
       <c r="B76" s="8">
@@ -22592,9 +22571,8 @@
         <v>2788</v>
       </c>
     </row>
-    <row r="77" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="77" spans="1:11">
       <c r="A77" s="10">
-        <f t="shared" si="1"/>
         <v>43618</v>
       </c>
       <c r="B77" s="8">
@@ -22628,9 +22606,8 @@
         <v>2662</v>
       </c>
     </row>
-    <row r="78" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="78" spans="1:11">
       <c r="A78" s="10">
-        <f t="shared" si="1"/>
         <v>43625</v>
       </c>
       <c r="B78" s="8">
@@ -22664,9 +22641,8 @@
         <v>2677</v>
       </c>
     </row>
-    <row r="79" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="79" spans="1:11">
       <c r="A79" s="10">
-        <f t="shared" si="1"/>
         <v>43632</v>
       </c>
       <c r="B79" s="8">
@@ -22700,9 +22676,8 @@
         <v>2532</v>
       </c>
     </row>
-    <row r="80" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="80" spans="1:11">
       <c r="A80" s="10">
-        <f t="shared" si="1"/>
         <v>43639</v>
       </c>
       <c r="B80" s="8">
@@ -22736,9 +22711,8 @@
         <v>2732</v>
       </c>
     </row>
-    <row r="81" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="81" spans="1:11">
       <c r="A81" s="10">
-        <f t="shared" si="1"/>
         <v>43646</v>
       </c>
       <c r="B81" s="8">
@@ -22772,9 +22746,8 @@
         <v>2742</v>
       </c>
     </row>
-    <row r="82" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="82" spans="1:11">
       <c r="A82" s="10">
-        <f t="shared" si="1"/>
         <v>43653</v>
       </c>
       <c r="B82" s="8">
@@ -22808,9 +22781,8 @@
         <v>2772</v>
       </c>
     </row>
-    <row r="83" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="83" spans="1:11">
       <c r="A83" s="10">
-        <f t="shared" si="1"/>
         <v>43660</v>
       </c>
       <c r="B83" s="8">
@@ -22844,9 +22816,8 @@
         <v>2766</v>
       </c>
     </row>
-    <row r="84" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="84" spans="1:11">
       <c r="A84" s="10">
-        <f t="shared" si="1"/>
         <v>43667</v>
       </c>
       <c r="B84" s="8">
@@ -22880,9 +22851,8 @@
         <v>2587</v>
       </c>
     </row>
-    <row r="85" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="85" spans="1:11">
       <c r="A85" s="10">
-        <f t="shared" si="1"/>
         <v>43674</v>
       </c>
       <c r="B85" s="8">
@@ -22916,9 +22886,8 @@
         <v>2668</v>
       </c>
     </row>
-    <row r="86" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="86" spans="1:11">
       <c r="A86" s="10">
-        <f t="shared" si="1"/>
         <v>43681</v>
       </c>
       <c r="B86" s="8">
@@ -22952,9 +22921,8 @@
         <v>2605</v>
       </c>
     </row>
-    <row r="87" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="87" spans="1:11">
       <c r="A87" s="10">
-        <f t="shared" si="1"/>
         <v>43688</v>
       </c>
       <c r="B87" s="8">
@@ -22988,9 +22956,8 @@
         <v>2551</v>
       </c>
     </row>
-    <row r="88" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="88" spans="1:11">
       <c r="A88" s="10">
-        <f t="shared" si="1"/>
         <v>43695</v>
       </c>
       <c r="B88" s="8">
@@ -23024,9 +22991,8 @@
         <v>2628</v>
       </c>
     </row>
-    <row r="89" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="89" spans="1:11">
       <c r="A89" s="10">
-        <f t="shared" si="1"/>
         <v>43702</v>
       </c>
       <c r="B89" s="8">
@@ -23060,9 +23026,8 @@
         <v>2656</v>
       </c>
     </row>
-    <row r="90" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="90" spans="1:11">
       <c r="A90" s="10">
-        <f t="shared" si="1"/>
         <v>43709</v>
       </c>
       <c r="B90" s="8">
@@ -23096,9 +23061,8 @@
         <v>2608</v>
       </c>
     </row>
-    <row r="91" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="91" spans="1:11">
       <c r="A91" s="10">
-        <f t="shared" si="1"/>
         <v>43716</v>
       </c>
       <c r="B91" s="8">
@@ -23132,9 +23096,8 @@
         <v>2611</v>
       </c>
     </row>
-    <row r="92" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="92" spans="1:11">
       <c r="A92" s="10">
-        <f t="shared" si="1"/>
         <v>43723</v>
       </c>
       <c r="B92" s="8">
@@ -23168,9 +23131,8 @@
         <v>2550</v>
       </c>
     </row>
-    <row r="93" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="93" spans="1:11">
       <c r="A93" s="10">
-        <f t="shared" si="1"/>
         <v>43730</v>
       </c>
       <c r="B93" s="8">
@@ -23204,9 +23166,8 @@
         <v>2572</v>
       </c>
     </row>
-    <row r="94" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="94" spans="1:11">
       <c r="A94" s="10">
-        <f t="shared" si="1"/>
         <v>43737</v>
       </c>
       <c r="B94" s="8">
@@ -23240,9 +23201,8 @@
         <v>2703</v>
       </c>
     </row>
-    <row r="95" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="95" spans="1:11">
       <c r="A95" s="10">
-        <f t="shared" si="1"/>
         <v>43744</v>
       </c>
       <c r="B95" s="8">
@@ -23276,9 +23236,8 @@
         <v>2804</v>
       </c>
     </row>
-    <row r="96" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="96" spans="1:11">
       <c r="A96" s="10">
-        <f t="shared" si="1"/>
         <v>43751</v>
       </c>
       <c r="B96" s="8">
@@ -23312,9 +23271,8 @@
         <v>2781</v>
       </c>
     </row>
-    <row r="97" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="97" spans="1:11">
       <c r="A97" s="10">
-        <f t="shared" si="1"/>
         <v>43758</v>
       </c>
       <c r="B97" s="8">
@@ -23348,9 +23306,8 @@
         <v>2915</v>
       </c>
     </row>
-    <row r="98" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="98" spans="1:11">
       <c r="A98" s="10">
-        <f t="shared" si="1"/>
         <v>43765</v>
       </c>
       <c r="B98" s="8">
@@ -23384,9 +23341,8 @@
         <v>3032</v>
       </c>
     </row>
-    <row r="99" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="99" spans="1:11">
       <c r="A99" s="10">
-        <f t="shared" si="1"/>
         <v>43772</v>
       </c>
       <c r="B99" s="8">
@@ -23420,9 +23376,8 @@
         <v>3120</v>
       </c>
     </row>
-    <row r="100" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="100" spans="1:11">
       <c r="A100" s="10">
-        <f t="shared" si="1"/>
         <v>43779</v>
       </c>
       <c r="B100" s="8">
@@ -23456,9 +23411,8 @@
         <v>3031</v>
       </c>
     </row>
-    <row r="101" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="101" spans="1:11">
       <c r="A101" s="10">
-        <f t="shared" si="1"/>
         <v>43786</v>
       </c>
       <c r="B101" s="8">
@@ -23492,9 +23446,8 @@
         <v>3117</v>
       </c>
     </row>
-    <row r="102" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="102" spans="1:11">
       <c r="A102" s="10">
-        <f t="shared" si="1"/>
         <v>43793</v>
       </c>
       <c r="B102" s="8">
@@ -23528,9 +23481,8 @@
         <v>3143</v>
       </c>
     </row>
-    <row r="103" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="103" spans="1:11">
       <c r="A103" s="10">
-        <f t="shared" si="1"/>
         <v>43800</v>
       </c>
       <c r="B103" s="8">
@@ -23564,9 +23516,8 @@
         <v>3079</v>
       </c>
     </row>
-    <row r="104" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="104" spans="1:11">
       <c r="A104" s="10">
-        <f t="shared" si="1"/>
         <v>43807</v>
       </c>
       <c r="B104" s="8">
@@ -23600,9 +23551,8 @@
         <v>3019</v>
       </c>
     </row>
-    <row r="105" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="105" spans="1:11">
       <c r="A105" s="10">
-        <f t="shared" si="1"/>
         <v>43814</v>
       </c>
       <c r="B105" s="8">
@@ -23636,9 +23586,8 @@
         <v>2964</v>
       </c>
     </row>
-    <row r="106" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="106" spans="1:11">
       <c r="A106" s="10">
-        <f t="shared" si="1"/>
         <v>43821</v>
       </c>
       <c r="B106" s="8">
@@ -23672,9 +23621,8 @@
         <v>2821</v>
       </c>
     </row>
-    <row r="107" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="107" spans="1:11">
       <c r="A107" s="10">
-        <f t="shared" si="1"/>
         <v>43828</v>
       </c>
       <c r="B107" s="8">
@@ -23708,9 +23656,8 @@
         <v>2760</v>
       </c>
     </row>
-    <row r="108" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="108" spans="1:11">
       <c r="A108" s="10">
-        <f t="shared" si="1"/>
         <v>43835</v>
       </c>
       <c r="B108" s="8">
@@ -23744,9 +23691,8 @@
         <v>2776</v>
       </c>
     </row>
-    <row r="109" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="109" spans="1:11">
       <c r="A109" s="10">
-        <f t="shared" si="1"/>
         <v>43842</v>
       </c>
       <c r="B109" s="8">
@@ -23780,9 +23726,8 @@
         <v>2636</v>
       </c>
     </row>
-    <row r="110" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="110" spans="1:11">
       <c r="A110" s="10">
-        <f t="shared" si="1"/>
         <v>43849</v>
       </c>
       <c r="B110" s="8">
@@ -23816,9 +23761,8 @@
         <v>2698</v>
       </c>
     </row>
-    <row r="111" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="111" spans="1:11">
       <c r="A111" s="10">
-        <f t="shared" si="1"/>
         <v>43856</v>
       </c>
       <c r="B111" s="8">
@@ -23852,9 +23796,8 @@
         <v>2838</v>
       </c>
     </row>
-    <row r="112" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="112" spans="1:11">
       <c r="A112" s="10">
-        <f t="shared" si="1"/>
         <v>43863</v>
       </c>
       <c r="B112" s="8">
@@ -23888,9 +23831,8 @@
         <v>2587</v>
       </c>
     </row>
-    <row r="113" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="113" spans="1:11">
       <c r="A113" s="10">
-        <f t="shared" si="1"/>
         <v>43870</v>
       </c>
       <c r="B113" s="8">
@@ -23924,9 +23866,8 @@
         <v>2498</v>
       </c>
     </row>
-    <row r="114" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="114" spans="1:11">
       <c r="A114" s="10">
-        <f t="shared" si="1"/>
         <v>43877</v>
       </c>
       <c r="B114" s="8">
@@ -23960,9 +23901,8 @@
         <v>2427</v>
       </c>
     </row>
-    <row r="115" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="115" spans="1:11">
       <c r="A115" s="10">
-        <f t="shared" si="1"/>
         <v>43884</v>
       </c>
       <c r="B115" s="8">
@@ -23996,9 +23936,8 @@
         <v>2239</v>
       </c>
     </row>
-    <row r="116" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="116" spans="1:11">
       <c r="A116" s="10">
-        <f t="shared" si="1"/>
         <v>43891</v>
       </c>
       <c r="B116" s="8">
@@ -24032,9 +23971,8 @@
         <v>2539</v>
       </c>
     </row>
-    <row r="117" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="117" spans="1:11">
       <c r="A117" s="10">
-        <f t="shared" si="1"/>
         <v>43898</v>
       </c>
       <c r="B117" s="8">
@@ -24068,9 +24006,8 @@
         <v>3154</v>
       </c>
     </row>
-    <row r="118" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="118" spans="1:11">
       <c r="A118" s="10">
-        <f t="shared" si="1"/>
         <v>43905</v>
       </c>
       <c r="B118" s="8">
@@ -24104,9 +24041,8 @@
         <v>3858</v>
       </c>
     </row>
-    <row r="119" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="119" spans="1:11">
       <c r="A119" s="10">
-        <f t="shared" si="1"/>
         <v>43912</v>
       </c>
       <c r="B119" s="8">
@@ -24140,9 +24076,8 @@
         <v>4713</v>
       </c>
     </row>
-    <row r="120" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="120" spans="1:11">
       <c r="A120" s="10">
-        <f t="shared" si="1"/>
         <v>43919</v>
       </c>
       <c r="B120" s="8">
@@ -24176,9 +24111,8 @@
         <v>5641</v>
       </c>
     </row>
-    <row r="121" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="121" spans="1:11">
       <c r="A121" s="10">
-        <f t="shared" si="1"/>
         <v>43926</v>
       </c>
       <c r="B121" s="8">
@@ -24212,9 +24146,8 @@
         <v>6426</v>
       </c>
     </row>
-    <row r="122" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="122" spans="1:11">
       <c r="A122" s="10">
-        <f t="shared" si="1"/>
         <v>43933</v>
       </c>
       <c r="B122" s="8">
@@ -24248,9 +24181,8 @@
         <v>7284</v>
       </c>
     </row>
-    <row r="123" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="123" spans="1:11">
       <c r="A123" s="10">
-        <f t="shared" si="1"/>
         <v>43940</v>
       </c>
       <c r="B123" s="8">
@@ -24284,9 +24216,8 @@
         <v>7946</v>
       </c>
     </row>
-    <row r="124" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="124" spans="1:11">
       <c r="A124" s="10">
-        <f t="shared" si="1"/>
         <v>43947</v>
       </c>
       <c r="B124" s="8">
@@ -24320,9 +24251,8 @@
         <v>8608</v>
       </c>
     </row>
-    <row r="125" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="125" spans="1:11">
       <c r="A125" s="10">
-        <f t="shared" si="1"/>
         <v>43954</v>
       </c>
       <c r="B125" s="8">
@@ -24356,9 +24286,8 @@
         <v>9951</v>
       </c>
     </row>
-    <row r="126" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="126" spans="1:11">
       <c r="A126" s="10">
-        <f t="shared" si="1"/>
         <v>43961</v>
       </c>
       <c r="B126" s="8">
@@ -24392,9 +24321,8 @@
         <v>10351</v>
       </c>
     </row>
-    <row r="127" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="127" spans="1:11">
       <c r="A127" s="10">
-        <f t="shared" si="1"/>
         <v>43968</v>
       </c>
       <c r="B127" s="8">
@@ -24428,9 +24356,8 @@
         <v>11202</v>
       </c>
     </row>
-    <row r="128" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="128" spans="1:11">
       <c r="A128" s="10">
-        <f t="shared" si="1"/>
         <v>43975</v>
       </c>
       <c r="B128" s="8">
@@ -24464,9 +24391,8 @@
         <v>9824</v>
       </c>
     </row>
-    <row r="129" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="129" spans="1:11">
       <c r="A129" s="10">
-        <f t="shared" si="1"/>
         <v>43982</v>
       </c>
       <c r="B129" s="8">
@@ -24500,9 +24426,8 @@
         <v>7635</v>
       </c>
     </row>
-    <row r="130" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="130" spans="1:11">
       <c r="A130" s="10">
-        <f t="shared" si="1"/>
         <v>43989</v>
       </c>
       <c r="B130" s="8">
@@ -24536,9 +24461,8 @@
         <v>5993</v>
       </c>
     </row>
-    <row r="131" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="131" spans="1:11">
       <c r="A131" s="10">
-        <f t="shared" si="1"/>
         <v>43996</v>
       </c>
       <c r="B131" s="8">
@@ -24572,9 +24496,8 @@
         <v>4905</v>
       </c>
     </row>
-    <row r="132" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="132" spans="1:11">
       <c r="A132" s="10">
-        <f t="shared" ref="A132:A195" si="2">B132-1</f>
         <v>44003</v>
       </c>
       <c r="B132" s="8">
@@ -24608,9 +24531,8 @@
         <v>4035</v>
       </c>
     </row>
-    <row r="133" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="133" spans="1:11">
       <c r="A133" s="10">
-        <f t="shared" si="2"/>
         <v>44010</v>
       </c>
       <c r="B133" s="8">
@@ -24644,9 +24566,8 @@
         <v>3835</v>
       </c>
     </row>
-    <row r="134" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="134" spans="1:11">
       <c r="A134" s="10">
-        <f t="shared" si="2"/>
         <v>44017</v>
       </c>
       <c r="B134" s="8">
@@ -24680,9 +24601,8 @@
         <v>3711</v>
       </c>
     </row>
-    <row r="135" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="135" spans="1:11">
       <c r="A135" s="10">
-        <f t="shared" si="2"/>
         <v>44024</v>
       </c>
       <c r="B135" s="8">
@@ -24716,9 +24636,8 @@
         <v>3775</v>
       </c>
     </row>
-    <row r="136" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="136" spans="1:11">
       <c r="A136" s="10">
-        <f t="shared" si="2"/>
         <v>44031</v>
       </c>
       <c r="B136" s="8">
@@ -24752,9 +24671,8 @@
         <v>3862</v>
       </c>
     </row>
-    <row r="137" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="137" spans="1:11">
       <c r="A137" s="10">
-        <f t="shared" si="2"/>
         <v>44038</v>
       </c>
       <c r="B137" s="8">
@@ -24788,9 +24706,8 @@
         <v>4050</v>
       </c>
     </row>
-    <row r="138" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="138" spans="1:11">
       <c r="A138" s="10">
-        <f t="shared" si="2"/>
         <v>44045</v>
       </c>
       <c r="B138" s="8">
@@ -24824,9 +24741,8 @@
         <v>4535</v>
       </c>
     </row>
-    <row r="139" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="139" spans="1:11">
       <c r="A139" s="10">
-        <f t="shared" si="2"/>
         <v>44052</v>
       </c>
       <c r="B139" s="8">
@@ -24860,9 +24776,8 @@
         <v>4425</v>
       </c>
     </row>
-    <row r="140" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="140" spans="1:11">
       <c r="A140" s="10">
-        <f t="shared" si="2"/>
         <v>44059</v>
       </c>
       <c r="B140" s="8">
@@ -24896,9 +24811,8 @@
         <v>4121</v>
       </c>
     </row>
-    <row r="141" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="141" spans="1:11">
       <c r="A141" s="10">
-        <f t="shared" si="2"/>
         <v>44066</v>
       </c>
       <c r="B141" s="8">
@@ -24932,9 +24846,8 @@
         <v>3819</v>
       </c>
     </row>
-    <row r="142" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="142" spans="1:11">
       <c r="A142" s="10">
-        <f t="shared" si="2"/>
         <v>44073</v>
       </c>
       <c r="B142" s="8">
@@ -24968,9 +24881,8 @@
         <v>4332</v>
       </c>
     </row>
-    <row r="143" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="143" spans="1:11">
       <c r="A143" s="10">
-        <f t="shared" si="2"/>
         <v>44080</v>
       </c>
       <c r="B143" s="8">
@@ -25004,9 +24916,8 @@
         <v>4498</v>
       </c>
     </row>
-    <row r="144" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="144" spans="1:11">
       <c r="A144" s="10">
-        <f t="shared" si="2"/>
         <v>44087</v>
       </c>
       <c r="B144" s="8">
@@ -25040,9 +24951,8 @@
         <v>4225</v>
       </c>
     </row>
-    <row r="145" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="145" spans="1:11">
       <c r="A145" s="10">
-        <f t="shared" si="2"/>
         <v>44094</v>
       </c>
       <c r="B145" s="8">
@@ -25076,9 +24986,8 @@
         <v>4242</v>
       </c>
     </row>
-    <row r="146" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="146" spans="1:11">
       <c r="A146" s="10">
-        <f t="shared" si="2"/>
         <v>44101</v>
       </c>
       <c r="B146" s="8">
@@ -25112,9 +25021,8 @@
         <v>4340</v>
       </c>
     </row>
-    <row r="147" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="147" spans="1:11">
       <c r="A147" s="10">
-        <f t="shared" si="2"/>
         <v>44108</v>
       </c>
       <c r="B147" s="8">
@@ -25148,9 +25056,8 @@
         <v>4375</v>
       </c>
     </row>
-    <row r="148" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="148" spans="1:11">
       <c r="A148" s="10">
-        <f t="shared" si="2"/>
         <v>44115</v>
       </c>
       <c r="B148" s="8">
@@ -25184,9 +25091,8 @@
         <v>4297</v>
       </c>
     </row>
-    <row r="149" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="149" spans="1:11">
       <c r="A149" s="10">
-        <f t="shared" si="2"/>
         <v>44122</v>
       </c>
       <c r="B149" s="8">
@@ -25220,9 +25126,8 @@
         <v>4957</v>
       </c>
     </row>
-    <row r="150" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="150" spans="1:11">
       <c r="A150" s="10">
-        <f t="shared" si="2"/>
         <v>44129</v>
       </c>
       <c r="B150" s="8">
@@ -25256,9 +25161,8 @@
         <v>5696</v>
       </c>
     </row>
-    <row r="151" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="151" spans="1:11">
       <c r="A151" s="10">
-        <f t="shared" si="2"/>
         <v>44136</v>
       </c>
       <c r="B151" s="8">
@@ -25292,9 +25196,8 @@
         <v>6193</v>
       </c>
     </row>
-    <row r="152" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="152" spans="1:11">
       <c r="A152" s="10">
-        <f t="shared" si="2"/>
         <v>44143</v>
       </c>
       <c r="B152" s="8">
@@ -25328,9 +25231,8 @@
         <v>6336</v>
       </c>
     </row>
-    <row r="153" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="153" spans="1:11">
       <c r="A153" s="10">
-        <f t="shared" si="2"/>
         <v>44150</v>
       </c>
       <c r="B153" s="8">
@@ -25364,9 +25266,8 @@
         <v>6128</v>
       </c>
     </row>
-    <row r="154" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="154" spans="1:11">
       <c r="A154" s="10">
-        <f t="shared" si="2"/>
         <v>44157</v>
       </c>
       <c r="B154" s="8">
@@ -25400,9 +25301,8 @@
         <v>5805</v>
       </c>
     </row>
-    <row r="155" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="155" spans="1:11">
       <c r="A155" s="10">
-        <f t="shared" si="2"/>
         <v>44164</v>
       </c>
       <c r="B155" s="8">
@@ -25436,9 +25336,8 @@
         <v>6359</v>
       </c>
     </row>
-    <row r="156" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="156" spans="1:11">
       <c r="A156" s="10">
-        <f t="shared" si="2"/>
         <v>44171</v>
       </c>
       <c r="B156" s="8">
@@ -25472,9 +25371,8 @@
         <v>6501</v>
       </c>
     </row>
-    <row r="157" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="157" spans="1:11">
       <c r="A157" s="10">
-        <f t="shared" si="2"/>
         <v>44178</v>
       </c>
       <c r="B157" s="8">
@@ -25508,9 +25406,8 @@
         <v>6639</v>
       </c>
     </row>
-    <row r="158" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="158" spans="1:11">
       <c r="A158" s="10">
-        <f t="shared" si="2"/>
         <v>44185</v>
       </c>
       <c r="B158" s="8">
@@ -25544,9 +25441,8 @@
         <v>6623</v>
       </c>
     </row>
-    <row r="159" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="159" spans="1:11">
       <c r="A159" s="10">
-        <f t="shared" si="2"/>
         <v>44192</v>
       </c>
       <c r="B159" s="8">
@@ -25580,9 +25476,8 @@
         <v>6235</v>
       </c>
     </row>
-    <row r="160" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="160" spans="1:11">
       <c r="A160" s="10">
-        <f t="shared" si="2"/>
         <v>44199</v>
       </c>
       <c r="B160" s="8">
@@ -25616,9 +25511,8 @@
         <v>6313</v>
       </c>
     </row>
-    <row r="161" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="161" spans="1:11">
       <c r="A161" s="10">
-        <f t="shared" si="2"/>
         <v>44206</v>
       </c>
       <c r="B161" s="8">
@@ -25652,9 +25546,8 @@
         <v>5714</v>
       </c>
     </row>
-    <row r="162" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="162" spans="1:11">
       <c r="A162" s="10">
-        <f t="shared" si="2"/>
         <v>44213</v>
       </c>
       <c r="B162" s="8">
@@ -25688,9 +25581,8 @@
         <v>4512</v>
       </c>
     </row>
-    <row r="163" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="163" spans="1:11">
       <c r="A163" s="10">
-        <f t="shared" si="2"/>
         <v>44220</v>
       </c>
       <c r="B163" s="8">
@@ -25724,9 +25616,8 @@
         <v>4555</v>
       </c>
     </row>
-    <row r="164" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="164" spans="1:11">
       <c r="A164" s="10">
-        <f t="shared" si="2"/>
         <v>44227</v>
       </c>
       <c r="B164" s="8">
@@ -25760,9 +25651,8 @@
         <v>5245</v>
       </c>
     </row>
-    <row r="165" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="165" spans="1:11">
       <c r="A165" s="10">
-        <f t="shared" si="2"/>
         <v>44234</v>
       </c>
       <c r="B165" s="8">
@@ -25796,9 +25686,8 @@
         <v>5649</v>
       </c>
     </row>
-    <row r="166" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="166" spans="1:11">
       <c r="A166" s="10">
-        <f t="shared" si="2"/>
         <v>44241</v>
       </c>
       <c r="B166" s="8">
@@ -25832,9 +25721,8 @@
         <v>6333</v>
       </c>
     </row>
-    <row r="167" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="167" spans="1:11">
       <c r="A167" s="10">
-        <f t="shared" si="2"/>
         <v>44248</v>
       </c>
       <c r="B167" s="8">
@@ -25868,9 +25756,8 @@
         <v>4242</v>
       </c>
     </row>
-    <row r="168" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="168" spans="1:11">
       <c r="A168" s="10">
-        <f t="shared" si="2"/>
         <v>44255</v>
       </c>
       <c r="B168" s="8">
@@ -25904,9 +25791,8 @@
         <v>4791</v>
       </c>
     </row>
-    <row r="169" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="169" spans="1:11">
       <c r="A169" s="10">
-        <f t="shared" si="2"/>
         <v>44262</v>
       </c>
       <c r="B169" s="8">
@@ -25940,9 +25826,8 @@
         <v>4641</v>
       </c>
     </row>
-    <row r="170" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="170" spans="1:11">
       <c r="A170" s="10">
-        <f t="shared" si="2"/>
         <v>44269</v>
       </c>
       <c r="B170" s="8">
@@ -25976,9 +25861,8 @@
         <v>4365</v>
       </c>
     </row>
-    <row r="171" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="171" spans="1:11">
       <c r="A171" s="10">
-        <f t="shared" si="2"/>
         <v>44276</v>
       </c>
       <c r="B171" s="8">
@@ -26012,9 +25896,8 @@
         <v>4549</v>
       </c>
     </row>
-    <row r="172" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="172" spans="1:11">
       <c r="A172" s="10">
-        <f t="shared" si="2"/>
         <v>44283</v>
       </c>
       <c r="B172" s="8">
@@ -26048,9 +25931,8 @@
         <v>4728</v>
       </c>
     </row>
-    <row r="173" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="173" spans="1:11">
       <c r="A173" s="10">
-        <f t="shared" si="2"/>
         <v>44290</v>
       </c>
       <c r="B173" s="8">
@@ -26084,9 +25966,8 @@
         <v>5485</v>
       </c>
     </row>
-    <row r="174" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="174" spans="1:11">
       <c r="A174" s="10">
-        <f t="shared" si="2"/>
         <v>44297</v>
       </c>
       <c r="B174" s="8">
@@ -26120,9 +26001,8 @@
         <v>6192</v>
       </c>
     </row>
-    <row r="175" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="175" spans="1:11">
       <c r="A175" s="10">
-        <f t="shared" si="2"/>
         <v>44304</v>
       </c>
       <c r="B175" s="8">
@@ -26156,9 +26036,8 @@
         <v>5842</v>
       </c>
     </row>
-    <row r="176" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="176" spans="1:11">
       <c r="A176" s="10">
-        <f t="shared" si="2"/>
         <v>44311</v>
       </c>
       <c r="B176" s="8">
@@ -26192,9 +26071,8 @@
         <v>6366</v>
       </c>
     </row>
-    <row r="177" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="177" spans="1:11">
       <c r="A177" s="10">
-        <f t="shared" si="2"/>
         <v>44318</v>
       </c>
       <c r="B177" s="8">
@@ -26228,9 +26106,8 @@
         <v>6907</v>
       </c>
     </row>
-    <row r="178" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="178" spans="1:11">
       <c r="A178" s="10">
-        <f t="shared" si="2"/>
         <v>44325</v>
       </c>
       <c r="B178" s="8">
@@ -26264,9 +26141,8 @@
         <v>6230</v>
       </c>
     </row>
-    <row r="179" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="179" spans="1:11">
       <c r="A179" s="10">
-        <f t="shared" si="2"/>
         <v>44332</v>
       </c>
       <c r="B179" s="8">
@@ -26300,9 +26176,8 @@
         <v>6092</v>
       </c>
     </row>
-    <row r="180" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="180" spans="1:11">
       <c r="A180" s="10">
-        <f t="shared" si="2"/>
         <v>44339</v>
       </c>
       <c r="B180" s="8">
@@ -26336,9 +26211,8 @@
         <v>6452</v>
       </c>
     </row>
-    <row r="181" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="181" spans="1:11">
       <c r="A181" s="10">
-        <f t="shared" si="2"/>
         <v>44346</v>
       </c>
       <c r="B181" s="8">
@@ -26372,9 +26246,8 @@
         <v>5834</v>
       </c>
     </row>
-    <row r="182" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="182" spans="1:11">
       <c r="A182" s="10">
-        <f t="shared" si="2"/>
         <v>44353</v>
       </c>
       <c r="B182" s="8">
@@ -26408,9 +26281,8 @@
         <v>5722</v>
       </c>
     </row>
-    <row r="183" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="183" spans="1:11">
       <c r="A183" s="10">
-        <f t="shared" si="2"/>
         <v>44360</v>
       </c>
       <c r="B183" s="8">
@@ -26444,9 +26316,8 @@
         <v>5443</v>
       </c>
     </row>
-    <row r="184" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="184" spans="1:11">
       <c r="A184" s="10">
-        <f t="shared" si="2"/>
         <v>44367</v>
       </c>
       <c r="B184" s="8">
@@ -26480,9 +26351,8 @@
         <v>4973</v>
       </c>
     </row>
-    <row r="185" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="185" spans="1:11">
       <c r="A185" s="10">
-        <f t="shared" si="2"/>
         <v>44374</v>
       </c>
       <c r="B185" s="8">
@@ -26516,9 +26386,8 @@
         <v>5258</v>
       </c>
     </row>
-    <row r="186" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="186" spans="1:11">
       <c r="A186" s="10">
-        <f t="shared" si="2"/>
         <v>44381</v>
       </c>
       <c r="B186" s="8">
@@ -26552,9 +26421,8 @@
         <v>5338</v>
       </c>
     </row>
-    <row r="187" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="187" spans="1:11">
       <c r="A187" s="10">
-        <f t="shared" si="2"/>
         <v>44388</v>
       </c>
       <c r="B187" s="8">
@@ -26588,9 +26456,8 @@
         <v>5987</v>
       </c>
     </row>
-    <row r="188" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="188" spans="1:11">
       <c r="A188" s="10">
-        <f t="shared" si="2"/>
         <v>44395</v>
       </c>
       <c r="B188" s="8">
@@ -26624,9 +26491,8 @@
         <v>5801</v>
       </c>
     </row>
-    <row r="189" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="189" spans="1:11">
       <c r="A189" s="10">
-        <f t="shared" si="2"/>
         <v>44402</v>
       </c>
       <c r="B189" s="8">
@@ -26660,9 +26526,8 @@
         <v>5421</v>
       </c>
     </row>
-    <row r="190" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="190" spans="1:11">
       <c r="A190" s="10">
-        <f t="shared" si="2"/>
         <v>44409</v>
       </c>
       <c r="B190" s="8">
@@ -26696,9 +26561,8 @@
         <v>5883</v>
       </c>
     </row>
-    <row r="191" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="191" spans="1:11">
       <c r="A191" s="10">
-        <f t="shared" si="2"/>
         <v>44416</v>
       </c>
       <c r="B191" s="8">
@@ -26732,9 +26596,8 @@
         <v>5967</v>
       </c>
     </row>
-    <row r="192" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="192" spans="1:11">
       <c r="A192" s="10">
-        <f t="shared" si="2"/>
         <v>44423</v>
       </c>
       <c r="B192" s="8">
@@ -26768,9 +26631,8 @@
         <v>6015</v>
       </c>
     </row>
-    <row r="193" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="193" spans="1:11">
       <c r="A193" s="10">
-        <f t="shared" si="2"/>
         <v>44430</v>
       </c>
       <c r="B193" s="8">
@@ -26804,9 +26666,8 @@
         <v>6147</v>
       </c>
     </row>
-    <row r="194" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="194" spans="1:11">
       <c r="A194" s="10">
-        <f t="shared" si="2"/>
         <v>44437</v>
       </c>
       <c r="B194" s="8">
@@ -26840,9 +26701,8 @@
         <v>7552</v>
       </c>
     </row>
-    <row r="195" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="195" spans="1:11">
       <c r="A195" s="10">
-        <f t="shared" si="2"/>
         <v>44444</v>
       </c>
       <c r="B195" s="8">
@@ -26876,9 +26736,8 @@
         <v>8099</v>
       </c>
     </row>
-    <row r="196" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="196" spans="1:11">
       <c r="A196" s="10">
-        <f t="shared" ref="A196:A259" si="3">B196-1</f>
         <v>44451</v>
       </c>
       <c r="B196" s="8">
@@ -26912,9 +26771,8 @@
         <v>8281</v>
       </c>
     </row>
-    <row r="197" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="197" spans="1:11">
       <c r="A197" s="10">
-        <f t="shared" si="3"/>
         <v>44458</v>
       </c>
       <c r="B197" s="8">
@@ -26948,9 +26806,8 @@
         <v>9021</v>
       </c>
     </row>
-    <row r="198" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="198" spans="1:11">
       <c r="A198" s="10">
-        <f t="shared" si="3"/>
         <v>44465</v>
       </c>
       <c r="B198" s="8">
@@ -26984,9 +26841,8 @@
         <v>9364</v>
       </c>
     </row>
-    <row r="199" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="199" spans="1:11">
       <c r="A199" s="10">
-        <f t="shared" si="3"/>
         <v>44472</v>
       </c>
       <c r="B199" s="8">
@@ -27020,9 +26876,8 @@
         <v>9090</v>
       </c>
     </row>
-    <row r="200" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="200" spans="1:11">
       <c r="A200" s="10">
-        <f t="shared" si="3"/>
         <v>44479</v>
       </c>
       <c r="B200" s="8">
@@ -27056,9 +26911,8 @@
         <v>8936</v>
       </c>
     </row>
-    <row r="201" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="201" spans="1:11">
       <c r="A201" s="10">
-        <f t="shared" si="3"/>
         <v>44486</v>
       </c>
       <c r="B201" s="8">
@@ -27092,9 +26946,8 @@
         <v>8252</v>
       </c>
     </row>
-    <row r="202" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="202" spans="1:11">
       <c r="A202" s="10">
-        <f t="shared" si="3"/>
         <v>44493</v>
       </c>
       <c r="B202" s="8">
@@ -27128,9 +26981,8 @@
         <v>8513</v>
       </c>
     </row>
-    <row r="203" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="203" spans="1:11">
       <c r="A203" s="10">
-        <f t="shared" si="3"/>
         <v>44500</v>
       </c>
       <c r="B203" s="8">
@@ -27164,9 +27016,8 @@
         <v>8569</v>
       </c>
     </row>
-    <row r="204" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="204" spans="1:11">
       <c r="A204" s="10">
-        <f t="shared" si="3"/>
         <v>44507</v>
       </c>
       <c r="B204" s="8">
@@ -27200,9 +27051,8 @@
         <v>10146</v>
       </c>
     </row>
-    <row r="205" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="205" spans="1:11">
       <c r="A205" s="10">
-        <f t="shared" si="3"/>
         <v>44514</v>
       </c>
       <c r="B205" s="8">
@@ -27236,9 +27086,8 @@
         <v>9833</v>
       </c>
     </row>
-    <row r="206" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="206" spans="1:11">
       <c r="A206" s="10">
-        <f t="shared" si="3"/>
         <v>44521</v>
       </c>
       <c r="B206" s="8">
@@ -27272,9 +27121,8 @@
         <v>10713</v>
       </c>
     </row>
-    <row r="207" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="207" spans="1:11">
       <c r="A207" s="10">
-        <f t="shared" si="3"/>
         <v>44528</v>
       </c>
       <c r="B207" s="8">
@@ -27308,9 +27156,8 @@
         <v>10672</v>
       </c>
     </row>
-    <row r="208" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="208" spans="1:11">
       <c r="A208" s="10">
-        <f t="shared" si="3"/>
         <v>44535</v>
       </c>
       <c r="B208" s="8">
@@ -27344,9 +27191,8 @@
         <v>11408</v>
       </c>
     </row>
-    <row r="209" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="209" spans="1:11">
       <c r="A209" s="10">
-        <f t="shared" si="3"/>
         <v>44542</v>
       </c>
       <c r="B209" s="8">
@@ -27380,9 +27226,8 @@
         <v>12068</v>
       </c>
     </row>
-    <row r="210" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="210" spans="1:11">
       <c r="A210" s="10">
-        <f t="shared" si="3"/>
         <v>44549</v>
       </c>
       <c r="B210" s="8">
@@ -27416,9 +27261,8 @@
         <v>10758</v>
       </c>
     </row>
-    <row r="211" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="211" spans="1:11">
       <c r="A211" s="10">
-        <f t="shared" si="3"/>
         <v>44556</v>
       </c>
       <c r="B211" s="8">
@@ -27452,9 +27296,8 @@
         <v>10247</v>
       </c>
     </row>
-    <row r="212" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="212" spans="1:11">
       <c r="A212" s="10">
-        <f t="shared" si="3"/>
         <v>44563</v>
       </c>
       <c r="B212" s="8">
@@ -27488,9 +27331,8 @@
         <v>9786</v>
       </c>
     </row>
-    <row r="213" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="213" spans="1:11">
       <c r="A213" s="10">
-        <f t="shared" si="3"/>
         <v>44570</v>
       </c>
       <c r="B213" s="8">
@@ -27524,9 +27366,8 @@
         <v>8461</v>
       </c>
     </row>
-    <row r="214" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="214" spans="1:11">
       <c r="A214" s="10">
-        <f t="shared" si="3"/>
         <v>44577</v>
       </c>
       <c r="B214" s="8">
@@ -27560,9 +27401,8 @@
         <v>6933</v>
       </c>
     </row>
-    <row r="215" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="215" spans="1:11">
       <c r="A215" s="10">
-        <f t="shared" si="3"/>
         <v>44584</v>
       </c>
       <c r="B215" s="8">
@@ -27596,9 +27436,8 @@
         <v>7524</v>
       </c>
     </row>
-    <row r="216" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="216" spans="1:11">
       <c r="A216" s="10">
-        <f t="shared" si="3"/>
         <v>44591</v>
       </c>
       <c r="B216" s="8">
@@ -27632,9 +27471,8 @@
         <v>7909</v>
       </c>
     </row>
-    <row r="217" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="217" spans="1:11">
       <c r="A217" s="10">
-        <f t="shared" si="3"/>
         <v>44598</v>
       </c>
       <c r="B217" s="8">
@@ -27668,9 +27506,8 @@
         <v>6947</v>
       </c>
     </row>
-    <row r="218" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="218" spans="1:11">
       <c r="A218" s="10">
-        <f t="shared" si="3"/>
         <v>44605</v>
       </c>
       <c r="B218" s="8">
@@ -27704,9 +27541,8 @@
         <v>6615</v>
       </c>
     </row>
-    <row r="219" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="219" spans="1:11">
       <c r="A219" s="10">
-        <f t="shared" si="3"/>
         <v>44612</v>
       </c>
       <c r="B219" s="8">
@@ -27740,9 +27576,8 @@
         <v>6659</v>
       </c>
     </row>
-    <row r="220" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="220" spans="1:11">
       <c r="A220" s="10">
-        <f t="shared" si="3"/>
         <v>44619</v>
       </c>
       <c r="B220" s="8">
@@ -27776,9 +27611,8 @@
         <v>6470</v>
       </c>
     </row>
-    <row r="221" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="221" spans="1:11">
       <c r="A221" s="10">
-        <f t="shared" si="3"/>
         <v>44626</v>
       </c>
       <c r="B221" s="8">
@@ -27812,9 +27646,8 @@
         <v>5896</v>
       </c>
     </row>
-    <row r="222" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="222" spans="1:11">
       <c r="A222" s="10">
-        <f t="shared" si="3"/>
         <v>44633</v>
       </c>
       <c r="B222" s="8">
@@ -27848,9 +27681,8 @@
         <v>7688</v>
       </c>
     </row>
-    <row r="223" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="223" spans="1:11">
       <c r="A223" s="10">
-        <f t="shared" si="3"/>
         <v>44640</v>
       </c>
       <c r="B223" s="8">
@@ -27884,9 +27716,8 @@
         <v>7591</v>
       </c>
     </row>
-    <row r="224" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="224" spans="1:11">
       <c r="A224" s="10">
-        <f t="shared" si="3"/>
         <v>44647</v>
       </c>
       <c r="B224" s="8">
@@ -27920,9 +27751,8 @@
         <v>7550</v>
       </c>
     </row>
-    <row r="225" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="225" spans="1:11">
       <c r="A225" s="10">
-        <f t="shared" si="3"/>
         <v>44654</v>
       </c>
       <c r="B225" s="8">
@@ -27956,9 +27786,8 @@
         <v>8345</v>
       </c>
     </row>
-    <row r="226" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="226" spans="1:11">
       <c r="A226" s="10">
-        <f t="shared" si="3"/>
         <v>44661</v>
       </c>
       <c r="B226" s="8">
@@ -27992,9 +27821,8 @@
         <v>8476</v>
       </c>
     </row>
-    <row r="227" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="227" spans="1:11">
       <c r="A227" s="10">
-        <f t="shared" si="3"/>
         <v>44668</v>
       </c>
       <c r="B227" s="8">
@@ -28028,9 +27856,8 @@
         <v>7813</v>
       </c>
     </row>
-    <row r="228" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="228" spans="1:11">
       <c r="A228" s="10">
-        <f t="shared" si="3"/>
         <v>44675</v>
       </c>
       <c r="B228" s="8">
@@ -28064,9 +27891,8 @@
         <v>8281</v>
       </c>
     </row>
-    <row r="229" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="229" spans="1:11">
       <c r="A229" s="10">
-        <f t="shared" si="3"/>
         <v>44682</v>
       </c>
       <c r="B229" s="8">
@@ -28100,9 +27926,8 @@
         <v>7753</v>
       </c>
     </row>
-    <row r="230" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="230" spans="1:11">
       <c r="A230" s="10">
-        <f t="shared" si="3"/>
         <v>44689</v>
       </c>
       <c r="B230" s="8">
@@ -28136,9 +27961,8 @@
         <v>7190</v>
       </c>
     </row>
-    <row r="231" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="231" spans="1:11">
       <c r="A231" s="10">
-        <f t="shared" si="3"/>
         <v>44696</v>
       </c>
       <c r="B231" s="8">
@@ -28172,9 +27996,8 @@
         <v>7186</v>
       </c>
     </row>
-    <row r="232" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="232" spans="1:11">
       <c r="A232" s="10">
-        <f t="shared" si="3"/>
         <v>44703</v>
       </c>
       <c r="B232" s="8">
@@ -28208,9 +28031,8 @@
         <v>7538</v>
       </c>
     </row>
-    <row r="233" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="233" spans="1:11">
       <c r="A233" s="10">
-        <f t="shared" si="3"/>
         <v>44710</v>
       </c>
       <c r="B233" s="8">
@@ -28244,9 +28066,8 @@
         <v>7571</v>
       </c>
     </row>
-    <row r="234" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="234" spans="1:11">
       <c r="A234" s="10">
-        <f t="shared" si="3"/>
         <v>44717</v>
       </c>
       <c r="B234" s="8">
@@ -28280,9 +28101,8 @@
         <v>7788</v>
       </c>
     </row>
-    <row r="235" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="235" spans="1:11">
       <c r="A235" s="10">
-        <f t="shared" si="3"/>
         <v>44724</v>
       </c>
       <c r="B235" s="8">
@@ -28316,9 +28136,8 @@
         <v>7523</v>
       </c>
     </row>
-    <row r="236" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="236" spans="1:11">
       <c r="A236" s="10">
-        <f t="shared" si="3"/>
         <v>44731</v>
       </c>
       <c r="B236" s="8">
@@ -28352,9 +28171,8 @@
         <v>7309</v>
       </c>
     </row>
-    <row r="237" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="237" spans="1:11">
       <c r="A237" s="10">
-        <f t="shared" si="3"/>
         <v>44738</v>
       </c>
       <c r="B237" s="8">
@@ -28388,9 +28206,8 @@
         <v>7312</v>
       </c>
     </row>
-    <row r="238" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="238" spans="1:11">
       <c r="A238" s="10">
-        <f t="shared" si="3"/>
         <v>44745</v>
       </c>
       <c r="B238" s="8">
@@ -28424,9 +28241,8 @@
         <v>7701</v>
       </c>
     </row>
-    <row r="239" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="239" spans="1:11">
       <c r="A239" s="10">
-        <f t="shared" si="3"/>
         <v>44752</v>
       </c>
       <c r="B239" s="8">
@@ -28460,9 +28276,8 @@
         <v>7311</v>
       </c>
     </row>
-    <row r="240" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="240" spans="1:11">
       <c r="A240" s="10">
-        <f t="shared" si="3"/>
         <v>44759</v>
       </c>
       <c r="B240" s="8">
@@ -28496,9 +28311,8 @@
         <v>6911</v>
       </c>
     </row>
-    <row r="241" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="241" spans="1:11">
       <c r="A241" s="10">
-        <f t="shared" si="3"/>
         <v>44766</v>
       </c>
       <c r="B241" s="8">
@@ -28532,9 +28346,8 @@
         <v>6829</v>
       </c>
     </row>
-    <row r="242" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="242" spans="1:11">
       <c r="A242" s="10">
-        <f t="shared" si="3"/>
         <v>44773</v>
       </c>
       <c r="B242" s="8">
@@ -28568,9 +28381,8 @@
         <v>6597</v>
       </c>
     </row>
-    <row r="243" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="243" spans="1:11">
       <c r="A243" s="10">
-        <f t="shared" si="3"/>
         <v>44780</v>
       </c>
       <c r="B243" s="8">
@@ -28604,9 +28416,8 @@
         <v>6823</v>
       </c>
     </row>
-    <row r="244" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="244" spans="1:11">
       <c r="A244" s="10">
-        <f t="shared" si="3"/>
         <v>44787</v>
       </c>
       <c r="B244" s="8">
@@ -28640,9 +28451,8 @@
         <v>6785</v>
       </c>
     </row>
-    <row r="245" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="245" spans="1:11">
       <c r="A245" s="10">
-        <f t="shared" si="3"/>
         <v>44794</v>
       </c>
       <c r="B245" s="8">
@@ -28676,9 +28486,8 @@
         <v>6948</v>
       </c>
     </row>
-    <row r="246" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="246" spans="1:11">
       <c r="A246" s="10">
-        <f t="shared" si="3"/>
         <v>44801</v>
       </c>
       <c r="B246" s="8">
@@ -28712,9 +28521,8 @@
         <v>6759</v>
       </c>
     </row>
-    <row r="247" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="247" spans="1:11">
       <c r="A247" s="10">
-        <f t="shared" si="3"/>
         <v>44808</v>
       </c>
       <c r="B247" s="8">
@@ -28748,9 +28556,8 @@
         <v>6421</v>
       </c>
     </row>
-    <row r="248" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="248" spans="1:11">
       <c r="A248" s="10">
-        <f t="shared" si="3"/>
         <v>44815</v>
       </c>
       <c r="B248" s="8">
@@ -28784,9 +28591,8 @@
         <v>6562</v>
       </c>
     </row>
-    <row r="249" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="249" spans="1:11">
       <c r="A249" s="10">
-        <f t="shared" si="3"/>
         <v>44822</v>
       </c>
       <c r="B249" s="8">
@@ -28820,9 +28626,8 @@
         <v>6719</v>
       </c>
     </row>
-    <row r="250" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="250" spans="1:11">
       <c r="A250" s="10">
-        <f t="shared" si="3"/>
         <v>44829</v>
       </c>
       <c r="B250" s="8">
@@ -28856,9 +28661,8 @@
         <v>6157</v>
       </c>
     </row>
-    <row r="251" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="251" spans="1:11">
       <c r="A251" s="10">
-        <f t="shared" si="3"/>
         <v>44836</v>
       </c>
       <c r="B251" s="8">
@@ -28892,9 +28696,8 @@
         <v>5844</v>
       </c>
     </row>
-    <row r="252" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="252" spans="1:11">
       <c r="A252" s="10">
-        <f t="shared" si="3"/>
         <v>44843</v>
       </c>
       <c r="B252" s="8">
@@ -28928,9 +28731,8 @@
         <v>5551</v>
       </c>
     </row>
-    <row r="253" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="253" spans="1:11">
       <c r="A253" s="10">
-        <f t="shared" si="3"/>
         <v>44850</v>
       </c>
       <c r="B253" s="8">
@@ -28964,9 +28766,8 @@
         <v>5560</v>
       </c>
     </row>
-    <row r="254" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="254" spans="1:11">
       <c r="A254" s="10">
-        <f t="shared" si="3"/>
         <v>44857</v>
       </c>
       <c r="B254" s="8">
@@ -29000,9 +28801,8 @@
         <v>6090</v>
       </c>
     </row>
-    <row r="255" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="255" spans="1:11">
       <c r="A255" s="10">
-        <f t="shared" si="3"/>
         <v>44864</v>
       </c>
       <c r="B255" s="8">
@@ -29036,9 +28836,8 @@
         <v>5724</v>
       </c>
     </row>
-    <row r="256" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="256" spans="1:11">
       <c r="A256" s="10">
-        <f t="shared" si="3"/>
         <v>44871</v>
       </c>
       <c r="B256" s="8">
@@ -29072,9 +28871,8 @@
         <v>5488</v>
       </c>
     </row>
-    <row r="257" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="257" spans="1:11">
       <c r="A257" s="10">
-        <f t="shared" si="3"/>
         <v>44878</v>
       </c>
       <c r="B257" s="8">
@@ -29108,9 +28906,8 @@
         <v>5118</v>
       </c>
     </row>
-    <row r="258" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="258" spans="1:11">
       <c r="A258" s="10">
-        <f t="shared" si="3"/>
         <v>44885</v>
       </c>
       <c r="B258" s="8">
@@ -29144,9 +28941,8 @@
         <v>5205</v>
       </c>
     </row>
-    <row r="259" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="259" spans="1:11">
       <c r="A259" s="10">
-        <f t="shared" si="3"/>
         <v>44892</v>
       </c>
       <c r="B259" s="8">
@@ -29180,9 +28976,8 @@
         <v>5070</v>
       </c>
     </row>
-    <row r="260" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="260" spans="1:11">
       <c r="A260" s="10">
-        <f t="shared" ref="A260:A323" si="4">B260-1</f>
         <v>44899</v>
       </c>
       <c r="B260" s="8">
@@ -29216,9 +29011,8 @@
         <v>5242</v>
       </c>
     </row>
-    <row r="261" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="261" spans="1:11">
       <c r="A261" s="10">
-        <f t="shared" si="4"/>
         <v>44906</v>
       </c>
       <c r="B261" s="8">
@@ -29252,9 +29046,8 @@
         <v>4946</v>
       </c>
     </row>
-    <row r="262" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="262" spans="1:11">
       <c r="A262" s="10">
-        <f t="shared" si="4"/>
         <v>44913</v>
       </c>
       <c r="B262" s="8">
@@ -29288,9 +29081,8 @@
         <v>5665</v>
       </c>
     </row>
-    <row r="263" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="263" spans="1:11">
       <c r="A263" s="10">
-        <f t="shared" si="4"/>
         <v>44920</v>
       </c>
       <c r="B263" s="8">
@@ -29324,9 +29116,8 @@
         <v>5702</v>
       </c>
     </row>
-    <row r="264" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="264" spans="1:11">
       <c r="A264" s="10">
-        <f t="shared" si="4"/>
         <v>44927</v>
       </c>
       <c r="B264" s="8">
@@ -29360,9 +29151,8 @@
         <v>5586</v>
       </c>
     </row>
-    <row r="265" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="265" spans="1:11">
       <c r="A265" s="10">
-        <f t="shared" si="4"/>
         <v>44934</v>
       </c>
       <c r="B265" s="8">
@@ -29396,9 +29186,8 @@
         <v>5009</v>
       </c>
     </row>
-    <row r="266" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="266" spans="1:11">
       <c r="A266" s="10">
-        <f t="shared" si="4"/>
         <v>44941</v>
       </c>
       <c r="B266" s="8">
@@ -29432,9 +29221,8 @@
         <v>5141</v>
       </c>
     </row>
-    <row r="267" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="267" spans="1:11">
       <c r="A267" s="10">
-        <f t="shared" si="4"/>
         <v>44948</v>
       </c>
       <c r="B267" s="8">
@@ -29468,9 +29256,8 @@
         <v>4669</v>
       </c>
     </row>
-    <row r="268" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="268" spans="1:11">
       <c r="A268" s="10">
-        <f t="shared" si="4"/>
         <v>44955</v>
       </c>
       <c r="B268" s="8">
@@ -29504,9 +29291,8 @@
         <v>4191</v>
       </c>
     </row>
-    <row r="269" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="269" spans="1:11">
       <c r="A269" s="10">
-        <f t="shared" si="4"/>
         <v>44962</v>
       </c>
       <c r="B269" s="8">
@@ -29540,9 +29326,8 @@
         <v>4595</v>
       </c>
     </row>
-    <row r="270" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="270" spans="1:11">
       <c r="A270" s="10">
-        <f t="shared" si="4"/>
         <v>44969</v>
       </c>
       <c r="B270" s="8">
@@ -29576,9 +29361,8 @@
         <v>4305</v>
       </c>
     </row>
-    <row r="271" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="271" spans="1:11">
       <c r="A271" s="10">
-        <f t="shared" si="4"/>
         <v>44976</v>
       </c>
       <c r="B271" s="8">
@@ -29612,9 +29396,8 @@
         <v>4094</v>
       </c>
     </row>
-    <row r="272" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="272" spans="1:11">
       <c r="A272" s="10">
-        <f t="shared" si="4"/>
         <v>44983</v>
       </c>
       <c r="B272" s="8">
@@ -29648,9 +29431,8 @@
         <v>3701</v>
       </c>
     </row>
-    <row r="273" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="273" spans="1:11">
       <c r="A273" s="10">
-        <f t="shared" si="4"/>
         <v>44990</v>
       </c>
       <c r="B273" s="8">
@@ -29684,9 +29466,8 @@
         <v>4039</v>
       </c>
     </row>
-    <row r="274" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="274" spans="1:11">
       <c r="A274" s="10">
-        <f t="shared" si="4"/>
         <v>44997</v>
       </c>
       <c r="B274" s="8">
@@ -29720,9 +29501,8 @@
         <v>4303</v>
       </c>
     </row>
-    <row r="275" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="275" spans="1:11">
       <c r="A275" s="10">
-        <f t="shared" si="4"/>
         <v>45004</v>
       </c>
       <c r="B275" s="8">
@@ -29756,9 +29536,8 @@
         <v>4582</v>
       </c>
     </row>
-    <row r="276" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="276" spans="1:11">
       <c r="A276" s="10">
-        <f t="shared" si="4"/>
         <v>45011</v>
       </c>
       <c r="B276" s="8">
@@ -29792,9 +29571,8 @@
         <v>4839</v>
       </c>
     </row>
-    <row r="277" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="277" spans="1:11">
       <c r="A277" s="10">
-        <f t="shared" si="4"/>
         <v>45018</v>
       </c>
       <c r="B277" s="8">
@@ -29828,9 +29606,8 @@
         <v>4637</v>
       </c>
     </row>
-    <row r="278" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="278" spans="1:11">
       <c r="A278" s="10">
-        <f t="shared" si="4"/>
         <v>45025</v>
       </c>
       <c r="B278" s="8">
@@ -29864,9 +29641,8 @@
         <v>4417</v>
       </c>
     </row>
-    <row r="279" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="279" spans="1:11">
       <c r="A279" s="10">
-        <f t="shared" si="4"/>
         <v>45032</v>
       </c>
       <c r="B279" s="8">
@@ -29900,9 +29676,8 @@
         <v>4183</v>
       </c>
     </row>
-    <row r="280" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="280" spans="1:11">
       <c r="A280" s="10">
-        <f t="shared" si="4"/>
         <v>45039</v>
       </c>
       <c r="B280" s="8">
@@ -29936,9 +29711,8 @@
         <v>4090</v>
       </c>
     </row>
-    <row r="281" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="281" spans="1:11">
       <c r="A281" s="10">
-        <f t="shared" si="4"/>
         <v>45046</v>
       </c>
       <c r="B281" s="8">
@@ -29972,9 +29746,8 @@
         <v>3995</v>
       </c>
     </row>
-    <row r="282" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="282" spans="1:11">
       <c r="A282" s="10">
-        <f t="shared" si="4"/>
         <v>45053</v>
       </c>
       <c r="B282" s="8">
@@ -30008,9 +29781,8 @@
         <v>3623</v>
       </c>
     </row>
-    <row r="283" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="283" spans="1:11">
       <c r="A283" s="10">
-        <f t="shared" si="4"/>
         <v>45060</v>
       </c>
       <c r="B283" s="8">
@@ -30044,9 +29816,8 @@
         <v>3519</v>
       </c>
     </row>
-    <row r="284" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="284" spans="1:11">
       <c r="A284" s="10">
-        <f t="shared" si="4"/>
         <v>45067</v>
       </c>
       <c r="B284" s="8">
@@ -30080,9 +29851,8 @@
         <v>3513</v>
       </c>
     </row>
-    <row r="285" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="285" spans="1:11">
       <c r="A285" s="10">
-        <f t="shared" si="4"/>
         <v>45074</v>
       </c>
       <c r="B285" s="8">
@@ -30116,9 +29886,8 @@
         <v>3501</v>
       </c>
     </row>
-    <row r="286" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="286" spans="1:11">
       <c r="A286" s="10">
-        <f t="shared" si="4"/>
         <v>45081</v>
       </c>
       <c r="B286" s="8">
@@ -30152,9 +29921,8 @@
         <v>3441</v>
       </c>
     </row>
-    <row r="287" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="287" spans="1:11">
       <c r="A287" s="10">
-        <f t="shared" si="4"/>
         <v>45088</v>
       </c>
       <c r="B287" s="8">
@@ -30188,9 +29956,8 @@
         <v>3489</v>
       </c>
     </row>
-    <row r="288" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="288" spans="1:11">
       <c r="A288" s="10">
-        <f t="shared" si="4"/>
         <v>45095</v>
       </c>
       <c r="B288" s="8">
@@ -30224,9 +29991,8 @@
         <v>3524</v>
       </c>
     </row>
-    <row r="289" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="289" spans="1:11">
       <c r="A289" s="10">
-        <f t="shared" si="4"/>
         <v>45102</v>
       </c>
       <c r="B289" s="8">
@@ -30260,9 +30026,8 @@
         <v>3497</v>
       </c>
     </row>
-    <row r="290" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="290" spans="1:11">
       <c r="A290" s="10">
-        <f t="shared" si="4"/>
         <v>45109</v>
       </c>
       <c r="B290" s="8">
@@ -30296,9 +30061,8 @@
         <v>3333</v>
       </c>
     </row>
-    <row r="291" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="291" spans="1:11">
       <c r="A291" s="10">
-        <f t="shared" si="4"/>
         <v>45116</v>
       </c>
       <c r="B291" s="8">
@@ -30332,9 +30096,8 @@
         <v>3428</v>
       </c>
     </row>
-    <row r="292" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="292" spans="1:11">
       <c r="A292" s="10">
-        <f t="shared" si="4"/>
         <v>45123</v>
       </c>
       <c r="B292" s="8">
@@ -30368,9 +30131,8 @@
         <v>3588</v>
       </c>
     </row>
-    <row r="293" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="293" spans="1:11">
       <c r="A293" s="10">
-        <f t="shared" si="4"/>
         <v>45130</v>
       </c>
       <c r="B293" s="8">
@@ -30404,9 +30166,8 @@
         <v>3445</v>
       </c>
     </row>
-    <row r="294" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="294" spans="1:11">
       <c r="A294" s="10">
-        <f t="shared" si="4"/>
         <v>45137</v>
       </c>
       <c r="B294" s="8">
@@ -30440,9 +30201,8 @@
         <v>3453</v>
       </c>
     </row>
-    <row r="295" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="295" spans="1:11">
       <c r="A295" s="10">
-        <f t="shared" si="4"/>
         <v>45144</v>
       </c>
       <c r="B295" s="8">
@@ -30476,9 +30236,8 @@
         <v>3501</v>
       </c>
     </row>
-    <row r="296" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="296" spans="1:11">
       <c r="A296" s="10">
-        <f t="shared" si="4"/>
         <v>45151</v>
       </c>
       <c r="B296" s="8">
@@ -30512,9 +30271,8 @@
         <v>3579</v>
       </c>
     </row>
-    <row r="297" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="297" spans="1:11">
       <c r="A297" s="10">
-        <f t="shared" si="4"/>
         <v>45158</v>
       </c>
       <c r="B297" s="8">
@@ -30548,9 +30306,8 @@
         <v>3584</v>
       </c>
     </row>
-    <row r="298" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="298" spans="1:11">
       <c r="A298" s="10">
-        <f t="shared" si="4"/>
         <v>45165</v>
       </c>
       <c r="B298" s="8">
@@ -30584,9 +30341,8 @@
         <v>3591</v>
       </c>
     </row>
-    <row r="299" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="299" spans="1:11">
       <c r="A299" s="10">
-        <f t="shared" si="4"/>
         <v>45172</v>
       </c>
       <c r="B299" s="8">
@@ -30620,9 +30376,8 @@
         <v>3526</v>
       </c>
     </row>
-    <row r="300" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="300" spans="1:11">
       <c r="A300" s="10">
-        <f t="shared" si="4"/>
         <v>45179</v>
       </c>
       <c r="B300" s="8">
@@ -30656,9 +30411,8 @@
         <v>3715</v>
       </c>
     </row>
-    <row r="301" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="301" spans="1:11">
       <c r="A301" s="10">
-        <f t="shared" si="4"/>
         <v>45186</v>
       </c>
       <c r="B301" s="8">
@@ -30692,9 +30446,8 @@
         <v>3765</v>
       </c>
     </row>
-    <row r="302" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="302" spans="1:11">
       <c r="A302" s="10">
-        <f t="shared" si="4"/>
         <v>45193</v>
       </c>
       <c r="B302" s="8">
@@ -30728,9 +30481,8 @@
         <v>3987</v>
       </c>
     </row>
-    <row r="303" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="303" spans="1:11">
       <c r="A303" s="10">
-        <f t="shared" si="4"/>
         <v>45200</v>
       </c>
       <c r="B303" s="8">
@@ -30764,9 +30516,8 @@
         <v>4197</v>
       </c>
     </row>
-    <row r="304" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="304" spans="1:11">
       <c r="A304" s="10">
-        <f t="shared" si="4"/>
         <v>45207</v>
       </c>
       <c r="B304" s="8">
@@ -30800,9 +30551,8 @@
         <v>4308</v>
       </c>
     </row>
-    <row r="305" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="305" spans="1:11">
       <c r="A305" s="10">
-        <f t="shared" si="4"/>
         <v>45214</v>
       </c>
       <c r="B305" s="8">
@@ -30836,9 +30586,8 @@
         <v>4268</v>
       </c>
     </row>
-    <row r="306" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="306" spans="1:11">
       <c r="A306" s="10">
-        <f t="shared" si="4"/>
         <v>45221</v>
       </c>
       <c r="B306" s="8">
@@ -30872,9 +30621,8 @@
         <v>4444</v>
       </c>
     </row>
-    <row r="307" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="307" spans="1:11">
       <c r="A307" s="10">
-        <f t="shared" si="4"/>
         <v>45228</v>
       </c>
       <c r="B307" s="8">
@@ -30908,9 +30656,8 @@
         <v>4465</v>
       </c>
     </row>
-    <row r="308" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="308" spans="1:11">
       <c r="A308" s="10">
-        <f t="shared" si="4"/>
         <v>45235</v>
       </c>
       <c r="B308" s="8">
@@ -30944,9 +30691,8 @@
         <v>4486</v>
       </c>
     </row>
-    <row r="309" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="309" spans="1:11">
       <c r="A309" s="10">
-        <f t="shared" si="4"/>
         <v>45242</v>
       </c>
       <c r="B309" s="8">
@@ -30980,9 +30726,8 @@
         <v>4878</v>
       </c>
     </row>
-    <row r="310" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="310" spans="1:11">
       <c r="A310" s="10">
-        <f t="shared" si="4"/>
         <v>45249</v>
       </c>
       <c r="B310" s="8">
@@ -31016,9 +30761,8 @@
         <v>5136</v>
       </c>
     </row>
-    <row r="311" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="311" spans="1:11">
       <c r="A311" s="10">
-        <f t="shared" si="4"/>
         <v>45256</v>
       </c>
       <c r="B311" s="8">
@@ -31052,9 +30796,8 @@
         <v>5562</v>
       </c>
     </row>
-    <row r="312" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="312" spans="1:11">
       <c r="A312" s="10">
-        <f t="shared" si="4"/>
         <v>45263</v>
       </c>
       <c r="B312" s="8">
@@ -31088,9 +30831,8 @@
         <v>5625</v>
       </c>
     </row>
-    <row r="313" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="313" spans="1:11">
       <c r="A313" s="10">
-        <f t="shared" si="4"/>
         <v>45270</v>
       </c>
       <c r="B313" s="8">
@@ -31124,9 +30866,8 @@
         <v>5859</v>
       </c>
     </row>
-    <row r="314" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="314" spans="1:11">
       <c r="A314" s="10">
-        <f t="shared" si="4"/>
         <v>45277</v>
       </c>
       <c r="B314" s="8">
@@ -31160,9 +30901,8 @@
         <v>5680</v>
       </c>
     </row>
-    <row r="315" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="315" spans="1:11">
       <c r="A315" s="10">
-        <f t="shared" si="4"/>
         <v>45284</v>
       </c>
       <c r="B315" s="8">
@@ -31196,9 +30936,8 @@
         <v>5680</v>
       </c>
     </row>
-    <row r="316" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="316" spans="1:11">
       <c r="A316" s="10">
-        <f t="shared" si="4"/>
         <v>45291</v>
       </c>
       <c r="B316" s="8">
@@ -31232,9 +30971,8 @@
         <v>3893</v>
       </c>
     </row>
-    <row r="317" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="317" spans="1:11">
       <c r="A317" s="10">
-        <f t="shared" si="4"/>
         <v>45298</v>
       </c>
       <c r="B317" s="8">
@@ -31268,9 +31006,8 @@
         <v>3609</v>
       </c>
     </row>
-    <row r="318" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="318" spans="1:11">
       <c r="A318" s="10">
-        <f t="shared" si="4"/>
         <v>45305</v>
       </c>
       <c r="B318" s="8">
@@ -31304,9 +31041,8 @@
         <v>3632</v>
       </c>
     </row>
-    <row r="319" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="319" spans="1:11">
       <c r="A319" s="10">
-        <f t="shared" si="4"/>
         <v>45312</v>
       </c>
       <c r="B319" s="8">
@@ -31340,9 +31076,8 @@
         <v>3772</v>
       </c>
     </row>
-    <row r="320" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="320" spans="1:11">
       <c r="A320" s="10">
-        <f t="shared" si="4"/>
         <v>45319</v>
       </c>
       <c r="B320" s="8">
@@ -31376,9 +31111,8 @@
         <v>4103</v>
       </c>
     </row>
-    <row r="321" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="321" spans="1:11">
       <c r="A321" s="10">
-        <f t="shared" si="4"/>
         <v>45326</v>
       </c>
       <c r="B321" s="8">
@@ -31412,9 +31146,8 @@
         <v>4283</v>
       </c>
     </row>
-    <row r="322" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="322" spans="1:11">
       <c r="A322" s="10">
-        <f t="shared" si="4"/>
         <v>45333</v>
       </c>
       <c r="B322" s="8">
@@ -31448,9 +31181,8 @@
         <v>4375</v>
       </c>
     </row>
-    <row r="323" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="323" spans="1:11">
       <c r="A323" s="10">
-        <f t="shared" si="4"/>
         <v>45340</v>
       </c>
       <c r="B323" s="8">
@@ -31484,9 +31216,8 @@
         <v>3871</v>
       </c>
     </row>
-    <row r="324" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="324" spans="1:11">
       <c r="A324" s="10">
-        <f t="shared" ref="A324:A387" si="5">B324-1</f>
         <v>45347</v>
       </c>
       <c r="B324" s="8">
@@ -31520,9 +31251,8 @@
         <v>3455</v>
       </c>
     </row>
-    <row r="325" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="325" spans="1:11">
       <c r="A325" s="10">
-        <f t="shared" si="5"/>
         <v>45354</v>
       </c>
       <c r="B325" s="8">
@@ -31556,9 +31286,8 @@
         <v>3638</v>
       </c>
     </row>
-    <row r="326" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="326" spans="1:11">
       <c r="A326" s="10">
-        <f t="shared" si="5"/>
         <v>45361</v>
       </c>
       <c r="B326" s="8">
@@ -31592,9 +31321,8 @@
         <v>3888</v>
       </c>
     </row>
-    <row r="327" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="327" spans="1:11">
       <c r="A327" s="10">
-        <f t="shared" si="5"/>
         <v>45368</v>
       </c>
       <c r="B327" s="8">
@@ -31628,9 +31356,8 @@
         <v>4235</v>
       </c>
     </row>
-    <row r="328" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="328" spans="1:11">
       <c r="A328" s="10">
-        <f t="shared" si="5"/>
         <v>45375</v>
       </c>
       <c r="B328" s="8">
@@ -31664,9 +31391,8 @@
         <v>4396</v>
       </c>
     </row>
-    <row r="329" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="329" spans="1:11">
       <c r="A329" s="10">
-        <f t="shared" si="5"/>
         <v>45382</v>
       </c>
       <c r="B329" s="8">
@@ -31700,9 +31426,8 @@
         <v>4400</v>
       </c>
     </row>
-    <row r="330" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="330" spans="1:11">
       <c r="A330" s="10">
-        <f t="shared" si="5"/>
         <v>45389</v>
       </c>
       <c r="B330" s="8">
@@ -31736,9 +31461,8 @@
         <v>4447</v>
       </c>
     </row>
-    <row r="331" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="331" spans="1:11">
       <c r="A331" s="10">
-        <f t="shared" si="5"/>
         <v>45396</v>
       </c>
       <c r="B331" s="8">
@@ -31772,9 +31496,8 @@
         <v>4472</v>
       </c>
     </row>
-    <row r="332" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="332" spans="1:11">
       <c r="A332" s="10">
-        <f t="shared" si="5"/>
         <v>45403</v>
       </c>
       <c r="B332" s="8">
@@ -31808,9 +31531,8 @@
         <v>4580</v>
       </c>
     </row>
-    <row r="333" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="333" spans="1:11">
       <c r="A333" s="10">
-        <f t="shared" si="5"/>
         <v>45410</v>
       </c>
       <c r="B333" s="8">
@@ -31844,9 +31566,8 @@
         <v>4632</v>
       </c>
     </row>
-    <row r="334" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="334" spans="1:11">
       <c r="A334" s="10">
-        <f t="shared" si="5"/>
         <v>45417</v>
       </c>
       <c r="B334" s="8">
@@ -31880,9 +31601,8 @@
         <v>4708</v>
       </c>
     </row>
-    <row r="335" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="335" spans="1:11">
       <c r="A335" s="10">
-        <f t="shared" si="5"/>
         <v>45424</v>
       </c>
       <c r="B335" s="8">
@@ -31916,9 +31636,8 @@
         <v>4710</v>
       </c>
     </row>
-    <row r="336" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="336" spans="1:11">
       <c r="A336" s="10">
-        <f t="shared" si="5"/>
         <v>45431</v>
       </c>
       <c r="B336" s="8">
@@ -31952,9 +31671,8 @@
         <v>4881</v>
       </c>
     </row>
-    <row r="337" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="337" spans="1:11">
       <c r="A337" s="10">
-        <f t="shared" si="5"/>
         <v>45438</v>
       </c>
       <c r="B337" s="8">
@@ -31988,9 +31706,8 @@
         <v>4955</v>
       </c>
     </row>
-    <row r="338" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="338" spans="1:11">
       <c r="A338" s="10">
-        <f t="shared" si="5"/>
         <v>45445</v>
       </c>
       <c r="B338" s="8">
@@ -32024,9 +31741,8 @@
         <v>4865</v>
       </c>
     </row>
-    <row r="339" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="339" spans="1:11">
       <c r="A339" s="10">
-        <f t="shared" si="5"/>
         <v>45452</v>
       </c>
       <c r="B339" s="8">
@@ -32060,9 +31776,8 @@
         <v>4808</v>
       </c>
     </row>
-    <row r="340" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="340" spans="1:11">
       <c r="A340" s="10">
-        <f t="shared" si="5"/>
         <v>45459</v>
       </c>
       <c r="B340" s="8">
@@ -32096,9 +31811,8 @@
         <v>4783</v>
       </c>
     </row>
-    <row r="341" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="341" spans="1:11">
       <c r="A341" s="10">
-        <f t="shared" si="5"/>
         <v>45466</v>
       </c>
       <c r="B341" s="8">
@@ -32132,9 +31846,8 @@
         <v>4757</v>
       </c>
     </row>
-    <row r="342" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="342" spans="1:11">
       <c r="A342" s="10">
-        <f t="shared" si="5"/>
         <v>45473</v>
       </c>
       <c r="B342" s="8">
@@ -32168,9 +31881,8 @@
         <v>4736</v>
       </c>
     </row>
-    <row r="343" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="343" spans="1:11">
       <c r="A343" s="10">
-        <f t="shared" si="5"/>
         <v>45480</v>
       </c>
       <c r="B343" s="8">
@@ -32204,9 +31916,8 @@
         <v>4879</v>
       </c>
     </row>
-    <row r="344" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="344" spans="1:11">
       <c r="A344" s="10">
-        <f t="shared" si="5"/>
         <v>45487</v>
       </c>
       <c r="B344" s="8">
@@ -32240,9 +31951,8 @@
         <v>4737</v>
       </c>
     </row>
-    <row r="345" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="345" spans="1:11">
       <c r="A345" s="10">
-        <f t="shared" si="5"/>
         <v>45494</v>
       </c>
       <c r="B345" s="8">
@@ -32276,9 +31986,8 @@
         <v>4594</v>
       </c>
     </row>
-    <row r="346" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="346" spans="1:11">
       <c r="A346" s="10">
-        <f t="shared" si="5"/>
         <v>45501</v>
       </c>
       <c r="B346" s="8">
@@ -32312,9 +32021,8 @@
         <v>4598</v>
       </c>
     </row>
-    <row r="347" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="347" spans="1:11">
       <c r="A347" s="10">
-        <f t="shared" si="5"/>
         <v>45508</v>
       </c>
       <c r="B347" s="8">
@@ -32348,9 +32056,8 @@
         <v>4565</v>
       </c>
     </row>
-    <row r="348" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="348" spans="1:11">
       <c r="A348" s="10">
-        <f t="shared" si="5"/>
         <v>45515</v>
       </c>
       <c r="B348" s="8">
@@ -32384,9 +32091,8 @@
         <v>4647</v>
       </c>
     </row>
-    <row r="349" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="349" spans="1:11">
       <c r="A349" s="10">
-        <f t="shared" si="5"/>
         <v>45522</v>
       </c>
       <c r="B349" s="8">
@@ -32420,9 +32126,8 @@
         <v>4591</v>
       </c>
     </row>
-    <row r="350" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="350" spans="1:11">
       <c r="A350" s="10">
-        <f t="shared" si="5"/>
         <v>45529</v>
       </c>
       <c r="B350" s="8">
@@ -32456,9 +32161,8 @@
         <v>4788</v>
       </c>
     </row>
-    <row r="351" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="351" spans="1:11">
       <c r="A351" s="10">
-        <f t="shared" si="5"/>
         <v>45536</v>
       </c>
       <c r="B351" s="8">
@@ -32492,9 +32196,8 @@
         <v>4920</v>
       </c>
     </row>
-    <row r="352" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="352" spans="1:11">
       <c r="A352" s="10">
-        <f t="shared" si="5"/>
         <v>45543</v>
       </c>
       <c r="B352" s="8">
@@ -32528,9 +32231,8 @@
         <v>4829</v>
       </c>
     </row>
-    <row r="353" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="353" spans="1:11">
       <c r="A353" s="10">
-        <f t="shared" si="5"/>
         <v>45550</v>
       </c>
       <c r="B353" s="8">
@@ -32564,9 +32266,8 @@
         <v>4815</v>
       </c>
     </row>
-    <row r="354" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="354" spans="1:11">
       <c r="A354" s="10">
-        <f t="shared" si="5"/>
         <v>45557</v>
       </c>
       <c r="B354" s="8">
@@ -32600,9 +32301,8 @@
         <v>4837</v>
       </c>
     </row>
-    <row r="355" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="355" spans="1:11">
       <c r="A355" s="10">
-        <f t="shared" si="5"/>
         <v>45564</v>
       </c>
       <c r="B355" s="8">
@@ -32636,9 +32336,8 @@
         <v>5053</v>
       </c>
     </row>
-    <row r="356" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="356" spans="1:11">
       <c r="A356" s="10">
-        <f t="shared" si="5"/>
         <v>45571</v>
       </c>
       <c r="B356" s="8">
@@ -32672,9 +32371,8 @@
         <v>4879</v>
       </c>
     </row>
-    <row r="357" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="357" spans="1:11">
       <c r="A357" s="10">
-        <f t="shared" si="5"/>
         <v>45578</v>
       </c>
       <c r="B357" s="8">
@@ -32708,9 +32406,8 @@
         <v>4831</v>
       </c>
     </row>
-    <row r="358" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="358" spans="1:11">
       <c r="A358" s="10">
-        <f t="shared" si="5"/>
         <v>45585</v>
       </c>
       <c r="B358" s="8">
@@ -32744,9 +32441,8 @@
         <v>5006</v>
       </c>
     </row>
-    <row r="359" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="359" spans="1:11">
       <c r="A359" s="10">
-        <f t="shared" si="5"/>
         <v>45592</v>
       </c>
       <c r="B359" s="8">
@@ -32780,9 +32476,8 @@
         <v>5190</v>
       </c>
     </row>
-    <row r="360" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="360" spans="1:11">
       <c r="A360" s="10">
-        <f t="shared" si="5"/>
         <v>45599</v>
       </c>
       <c r="B360" s="8">
@@ -32816,9 +32511,8 @@
         <v>5493</v>
       </c>
     </row>
-    <row r="361" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="361" spans="1:11">
       <c r="A361" s="10">
-        <f t="shared" si="5"/>
         <v>45606</v>
       </c>
       <c r="B361" s="8">
@@ -32852,9 +32546,8 @@
         <v>5494</v>
       </c>
     </row>
-    <row r="362" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="362" spans="1:11">
       <c r="A362" s="10">
-        <f t="shared" si="5"/>
         <v>45613</v>
       </c>
       <c r="B362" s="8">
@@ -32888,9 +32581,8 @@
         <v>5339</v>
       </c>
     </row>
-    <row r="363" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="363" spans="1:11">
       <c r="A363" s="10">
-        <f t="shared" si="5"/>
         <v>45620</v>
       </c>
       <c r="B363" s="8">
@@ -32924,9 +32616,8 @@
         <v>5225</v>
       </c>
     </row>
-    <row r="364" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="364" spans="1:11">
       <c r="A364" s="10">
-        <f t="shared" si="5"/>
         <v>45627</v>
       </c>
       <c r="B364" s="8">
@@ -32960,9 +32651,8 @@
         <v>5585</v>
       </c>
     </row>
-    <row r="365" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="365" spans="1:11">
       <c r="A365" s="10">
-        <f t="shared" si="5"/>
         <v>45634</v>
       </c>
       <c r="B365" s="8">
@@ -32996,9 +32686,8 @@
         <v>5777</v>
       </c>
     </row>
-    <row r="366" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="366" spans="1:11">
       <c r="A366" s="10">
-        <f t="shared" si="5"/>
         <v>45641</v>
       </c>
       <c r="B366" s="8">
@@ -33032,9 +32721,8 @@
         <v>5722</v>
       </c>
     </row>
-    <row r="367" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="367" spans="1:11">
       <c r="A367" s="10">
-        <f t="shared" si="5"/>
         <v>45648</v>
       </c>
       <c r="B367" s="8">
@@ -33068,9 +32756,8 @@
         <v>5327</v>
       </c>
     </row>
-    <row r="368" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="368" spans="1:11">
       <c r="A368" s="10">
-        <f t="shared" si="5"/>
         <v>45655</v>
       </c>
       <c r="B368" s="8">
@@ -33104,9 +32791,8 @@
         <v>5327</v>
       </c>
     </row>
-    <row r="369" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="369" spans="1:11">
       <c r="A369" s="10">
-        <f t="shared" si="5"/>
         <v>45662</v>
       </c>
       <c r="B369" s="8">
@@ -33140,9 +32826,8 @@
         <v>4966</v>
       </c>
     </row>
-    <row r="370" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="370" spans="1:11">
       <c r="A370" s="10">
-        <f t="shared" si="5"/>
         <v>45669</v>
       </c>
       <c r="B370" s="8">
@@ -33176,9 +32861,8 @@
         <v>4484</v>
       </c>
     </row>
-    <row r="371" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="371" spans="1:11">
       <c r="A371" s="10">
-        <f t="shared" si="5"/>
         <v>45676</v>
       </c>
       <c r="B371" s="8">
@@ -33212,9 +32896,8 @@
         <v>4243</v>
       </c>
     </row>
-    <row r="372" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="372" spans="1:11">
       <c r="A372" s="10">
-        <f t="shared" si="5"/>
         <v>45683</v>
       </c>
       <c r="B372" s="8">
@@ -33248,9 +32931,8 @@
         <v>4447</v>
       </c>
     </row>
-    <row r="373" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="373" spans="1:11">
       <c r="A373" s="10">
-        <f t="shared" si="5"/>
         <v>45690</v>
       </c>
       <c r="B373" s="8">
@@ -33284,9 +32966,8 @@
         <v>4327</v>
       </c>
     </row>
-    <row r="374" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="374" spans="1:11">
       <c r="A374" s="10">
-        <f t="shared" si="5"/>
         <v>45697</v>
       </c>
       <c r="B374" s="8">
@@ -33320,9 +33001,8 @@
         <v>3962</v>
       </c>
     </row>
-    <row r="375" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="375" spans="1:11">
       <c r="A375" s="10">
-        <f t="shared" si="5"/>
         <v>45704</v>
       </c>
       <c r="B375" s="8">
@@ -33356,9 +33036,8 @@
         <v>4284</v>
       </c>
     </row>
-    <row r="376" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="376" spans="1:11">
       <c r="A376" s="10">
-        <f t="shared" si="5"/>
         <v>45711</v>
       </c>
       <c r="B376" s="8">
@@ -33392,9 +33071,8 @@
         <v>4127</v>
       </c>
     </row>
-    <row r="377" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="377" spans="1:11">
       <c r="A377" s="10">
-        <f t="shared" si="5"/>
         <v>45718</v>
       </c>
       <c r="B377" s="8">
@@ -33428,9 +33106,8 @@
         <v>4086</v>
       </c>
     </row>
-    <row r="378" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="378" spans="1:11">
       <c r="A378" s="10">
-        <f t="shared" si="5"/>
         <v>45725</v>
       </c>
       <c r="B378" s="8">
@@ -33464,9 +33141,8 @@
         <v>4002</v>
       </c>
     </row>
-    <row r="379" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="379" spans="1:11">
       <c r="A379" s="10">
-        <f t="shared" si="5"/>
         <v>45732</v>
       </c>
       <c r="B379" s="8">
@@ -33500,9 +33176,8 @@
         <v>4218</v>
       </c>
     </row>
-    <row r="380" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="380" spans="1:11">
       <c r="A380" s="10">
-        <f t="shared" si="5"/>
         <v>45739</v>
       </c>
       <c r="B380" s="8">
@@ -33536,9 +33211,8 @@
         <v>4547</v>
       </c>
     </row>
-    <row r="381" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="381" spans="1:11">
       <c r="A381" s="10">
-        <f t="shared" si="5"/>
         <v>45746</v>
       </c>
       <c r="B381" s="8">
@@ -33572,9 +33246,8 @@
         <v>4573</v>
       </c>
     </row>
-    <row r="382" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="382" spans="1:11">
       <c r="A382" s="10">
-        <f t="shared" si="5"/>
         <v>45753</v>
       </c>
       <c r="B382" s="8">
@@ -33608,9 +33281,8 @@
         <v>4689</v>
       </c>
     </row>
-    <row r="383" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="383" spans="1:11">
       <c r="A383" s="10">
-        <f t="shared" si="5"/>
         <v>45760</v>
       </c>
       <c r="B383" s="8">
@@ -33644,9 +33316,8 @@
         <v>4662</v>
       </c>
     </row>
-    <row r="384" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="384" spans="1:11">
       <c r="A384" s="10">
-        <f t="shared" si="5"/>
         <v>45767</v>
       </c>
       <c r="B384" s="8">
@@ -33680,9 +33351,8 @@
         <v>4697</v>
       </c>
     </row>
-    <row r="385" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="385" spans="1:11">
       <c r="A385" s="10">
-        <f t="shared" si="5"/>
         <v>45774</v>
       </c>
       <c r="B385" s="8">
@@ -33716,9 +33386,8 @@
         <v>4411</v>
       </c>
     </row>
-    <row r="386" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="386" spans="1:11">
       <c r="A386" s="10">
-        <f t="shared" si="5"/>
         <v>45781</v>
       </c>
       <c r="B386" s="8">
@@ -33752,9 +33421,8 @@
         <v>4304</v>
       </c>
     </row>
-    <row r="387" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="387" spans="1:11">
       <c r="A387" s="10">
-        <f t="shared" si="5"/>
         <v>45788</v>
       </c>
       <c r="B387" s="8">
@@ -33788,9 +33456,8 @@
         <v>4343</v>
       </c>
     </row>
-    <row r="388" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="388" spans="1:11">
       <c r="A388" s="10">
-        <f t="shared" ref="A388:A419" si="6">B388-1</f>
         <v>45795</v>
       </c>
       <c r="B388" s="8">
@@ -33824,9 +33491,8 @@
         <v>4190</v>
       </c>
     </row>
-    <row r="389" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="389" spans="1:11">
       <c r="A389" s="10">
-        <f t="shared" si="6"/>
         <v>45802</v>
       </c>
       <c r="B389" s="8">
@@ -33860,9 +33526,8 @@
         <v>4444</v>
       </c>
     </row>
-    <row r="390" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="390" spans="1:11">
       <c r="A390" s="10">
-        <f t="shared" si="6"/>
         <v>45809</v>
       </c>
       <c r="B390" s="8">
@@ -33896,9 +33561,8 @@
         <v>4607</v>
       </c>
     </row>
-    <row r="391" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="391" spans="1:11">
       <c r="A391" s="10">
-        <f t="shared" si="6"/>
         <v>45816</v>
       </c>
       <c r="B391" s="8">
@@ -33932,9 +33596,8 @@
         <v>4567</v>
       </c>
     </row>
-    <row r="392" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="392" spans="1:11">
       <c r="A392" s="10">
-        <f t="shared" si="6"/>
         <v>45823</v>
       </c>
       <c r="B392" s="8">
@@ -33968,9 +33631,8 @@
         <v>4475</v>
       </c>
     </row>
-    <row r="393" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="393" spans="1:11">
       <c r="A393" s="10">
-        <f t="shared" si="6"/>
         <v>45830</v>
       </c>
       <c r="B393" s="8">
@@ -34004,9 +33666,8 @@
         <v>4354</v>
       </c>
     </row>
-    <row r="394" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="394" spans="1:11">
       <c r="A394" s="10">
-        <f t="shared" si="6"/>
         <v>45837</v>
       </c>
       <c r="B394" s="8">
@@ -34040,9 +33701,8 @@
         <v>4375</v>
       </c>
     </row>
-    <row r="395" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="395" spans="1:11">
       <c r="A395" s="10">
-        <f t="shared" si="6"/>
         <v>45844</v>
       </c>
       <c r="B395" s="8">
@@ -34076,9 +33736,8 @@
         <v>4413</v>
       </c>
     </row>
-    <row r="396" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="396" spans="1:11">
       <c r="A396" s="10">
-        <f t="shared" si="6"/>
         <v>45851</v>
       </c>
       <c r="B396" s="8">
@@ -34112,9 +33771,8 @@
         <v>4593</v>
       </c>
     </row>
-    <row r="397" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="397" spans="1:11">
       <c r="A397" s="10">
-        <f t="shared" si="6"/>
         <v>45858</v>
       </c>
       <c r="B397" s="8">
@@ -34148,9 +33806,8 @@
         <v>4418</v>
       </c>
     </row>
-    <row r="398" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="398" spans="1:11">
       <c r="A398" s="10">
-        <f t="shared" si="6"/>
         <v>45865</v>
       </c>
       <c r="B398" s="8">
@@ -34184,9 +33841,8 @@
         <v>4429</v>
       </c>
     </row>
-    <row r="399" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="399" spans="1:11">
       <c r="A399" s="10">
-        <f t="shared" si="6"/>
         <v>45872</v>
       </c>
       <c r="B399" s="8">
@@ -34220,9 +33876,8 @@
         <v>4418</v>
       </c>
     </row>
-    <row r="400" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="400" spans="1:11">
       <c r="A400" s="10">
-        <f t="shared" si="6"/>
         <v>45879</v>
       </c>
       <c r="B400" s="8">
@@ -34256,9 +33911,8 @@
         <v>4455</v>
       </c>
     </row>
-    <row r="401" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="401" spans="1:11">
       <c r="A401" s="10">
-        <f t="shared" si="6"/>
         <v>45886</v>
       </c>
       <c r="B401" s="8">
@@ -34292,9 +33946,8 @@
         <v>4411</v>
       </c>
     </row>
-    <row r="402" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="402" spans="1:11">
       <c r="A402" s="10">
-        <f t="shared" si="6"/>
         <v>45893</v>
       </c>
       <c r="B402" s="8">
@@ -34328,9 +33981,8 @@
         <v>4392</v>
       </c>
     </row>
-    <row r="403" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="403" spans="1:11">
       <c r="A403" s="10">
-        <f t="shared" si="6"/>
         <v>45900</v>
       </c>
       <c r="B403" s="8">
@@ -34364,9 +34016,8 @@
         <v>4549</v>
       </c>
     </row>
-    <row r="404" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="404" spans="1:11">
       <c r="A404" s="10">
-        <f t="shared" si="6"/>
         <v>45907</v>
       </c>
       <c r="B404" s="8">
@@ -34400,9 +34051,8 @@
         <v>4489</v>
       </c>
     </row>
-    <row r="405" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="405" spans="1:11">
       <c r="A405" s="10">
-        <f t="shared" si="6"/>
         <v>45914</v>
       </c>
       <c r="B405" s="8">
@@ -34436,9 +34086,8 @@
         <v>4536</v>
       </c>
     </row>
-    <row r="406" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="406" spans="1:11">
       <c r="A406" s="10">
-        <f t="shared" si="6"/>
         <v>45921</v>
       </c>
       <c r="B406" s="8">
@@ -34472,9 +34121,8 @@
         <v>4516</v>
       </c>
     </row>
-    <row r="407" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="407" spans="1:11">
       <c r="A407" s="10">
-        <f t="shared" si="6"/>
         <v>45928</v>
       </c>
       <c r="B407" s="8">
@@ -34508,9 +34156,8 @@
         <v>4562</v>
       </c>
     </row>
-    <row r="408" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="408" spans="1:11">
       <c r="A408" s="10">
-        <f t="shared" si="6"/>
         <v>45935</v>
       </c>
       <c r="B408" s="8">
@@ -34544,9 +34191,8 @@
         <v>4621</v>
       </c>
     </row>
-    <row r="409" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="409" spans="1:11">
       <c r="A409" s="10">
-        <f t="shared" si="6"/>
         <v>45942</v>
       </c>
       <c r="B409" s="8">
@@ -34580,9 +34226,8 @@
         <v>4441</v>
       </c>
     </row>
-    <row r="410" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="410" spans="1:11">
       <c r="A410" s="10">
-        <f t="shared" si="6"/>
         <v>45949</v>
       </c>
       <c r="B410" s="8">
@@ -34616,9 +34261,8 @@
         <v>4746</v>
       </c>
     </row>
-    <row r="411" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="411" spans="1:11">
       <c r="A411" s="10">
-        <f t="shared" si="6"/>
         <v>45956</v>
       </c>
       <c r="B411" s="8">
@@ -34652,9 +34296,8 @@
         <v>5010</v>
       </c>
     </row>
-    <row r="412" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="412" spans="1:11">
       <c r="A412" s="10">
-        <f t="shared" si="6"/>
         <v>45963</v>
       </c>
       <c r="B412" s="8">
@@ -34688,9 +34331,8 @@
         <v>5366</v>
       </c>
     </row>
-    <row r="413" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="413" spans="1:11">
       <c r="A413" s="10">
-        <f t="shared" si="6"/>
         <v>45970</v>
       </c>
       <c r="B413" s="8">
@@ -34724,9 +34366,8 @@
         <v>5356</v>
       </c>
     </row>
-    <row r="414" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="414" spans="1:11">
       <c r="A414" s="10">
-        <f t="shared" si="6"/>
         <v>45977</v>
       </c>
       <c r="B414" s="8">
@@ -34760,9 +34401,8 @@
         <v>5581</v>
       </c>
     </row>
-    <row r="415" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="415" spans="1:11">
       <c r="A415" s="10">
-        <f t="shared" si="6"/>
         <v>45984</v>
       </c>
       <c r="B415" s="8">
@@ -34796,9 +34436,8 @@
         <v>5571</v>
       </c>
     </row>
-    <row r="416" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="416" spans="1:11">
       <c r="A416" s="10">
-        <f t="shared" si="6"/>
         <v>45991</v>
       </c>
       <c r="B416" s="8">
@@ -34832,9 +34471,8 @@
         <v>5721</v>
       </c>
     </row>
-    <row r="417" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="417" spans="1:11">
       <c r="A417" s="10">
-        <f t="shared" si="6"/>
         <v>45998</v>
       </c>
       <c r="B417" s="8">
@@ -34868,9 +34506,8 @@
         <v>6161</v>
       </c>
     </row>
-    <row r="418" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="418" spans="1:11">
       <c r="A418" s="10">
-        <f t="shared" si="6"/>
         <v>46005</v>
       </c>
       <c r="B418" s="8">
@@ -34904,9 +34541,8 @@
         <v>6369</v>
       </c>
     </row>
-    <row r="419" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="419" spans="1:11">
       <c r="A419" s="10">
-        <f t="shared" si="6"/>
         <v>46012</v>
       </c>
       <c r="B419" s="8">
@@ -34940,9 +34576,8 @@
         <v>5821</v>
       </c>
     </row>
-    <row r="420" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="420" spans="1:11">
       <c r="A420" s="10">
-        <f t="shared" ref="A420:A422" si="7">B420-1</f>
         <v>46026</v>
       </c>
       <c r="B420" s="8">
@@ -34976,9 +34611,8 @@
         <v>4662</v>
       </c>
     </row>
-    <row r="421" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="421" spans="1:11">
       <c r="A421" s="10">
-        <f t="shared" si="7"/>
         <v>46033</v>
       </c>
       <c r="B421" s="8">
@@ -35012,9 +34646,8 @@
         <v>4662</v>
       </c>
     </row>
-    <row r="422" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="422" spans="1:11">
       <c r="A422" s="10">
-        <f t="shared" si="7"/>
         <v>46040</v>
       </c>
       <c r="B422" s="8">
@@ -35048,9 +34681,8 @@
         <v>4558</v>
       </c>
     </row>
-    <row r="423" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="423" spans="1:11">
       <c r="A423" s="10">
-        <f t="shared" ref="A423:A425" si="8">B423-1</f>
         <v>46047</v>
       </c>
       <c r="B423" s="8">
@@ -35084,9 +34716,8 @@
         <v>4478</v>
       </c>
     </row>
-    <row r="424" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="424" spans="1:11">
       <c r="A424" s="10">
-        <f t="shared" si="8"/>
         <v>46054</v>
       </c>
       <c r="B424" s="8">
@@ -35120,9 +34751,8 @@
         <v>4714</v>
       </c>
     </row>
-    <row r="425" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="425" spans="1:11">
       <c r="A425" s="10">
-        <f t="shared" si="8"/>
         <v>46061</v>
       </c>
       <c r="B425" s="8">
@@ -35156,9 +34786,8 @@
         <v>4730</v>
       </c>
     </row>
-    <row r="426" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="426" spans="1:11">
       <c r="A426" s="10">
-        <f t="shared" ref="A426:A427" si="9">B426-1</f>
         <v>46068</v>
       </c>
       <c r="B426" s="8">
@@ -35192,9 +34821,8 @@
         <v>4757</v>
       </c>
     </row>
-    <row r="427" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="427" spans="1:11">
       <c r="A427" s="10">
-        <f t="shared" si="9"/>
         <v>46075</v>
       </c>
       <c r="B427" s="8">
@@ -35228,9 +34856,9 @@
         <v>4432</v>
       </c>
     </row>
-    <row r="428" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="428" spans="1:11">
       <c r="A428" s="10">
-        <v>46083</v>
+        <v>46082</v>
       </c>
       <c r="B428" s="10">
         <v>46083</v>
@@ -35263,9 +34891,8 @@
         <v>4445</v>
       </c>
     </row>
-    <row r="429" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="429" spans="1:11">
       <c r="A429" s="10">
-        <f t="shared" ref="A429:A430" si="10">B429-1</f>
         <v>46089</v>
       </c>
       <c r="B429" s="8">
@@ -35299,9 +34926,8 @@
         <v>4012</v>
       </c>
     </row>
-    <row r="430" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="430" spans="1:11">
       <c r="A430" s="10">
-        <f t="shared" si="10"/>
         <v>46096</v>
       </c>
       <c r="B430" s="8">
@@ -35335,9 +34961,9 @@
         <v>4208</v>
       </c>
     </row>
-    <row r="431" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="431" spans="1:11">
       <c r="A431" s="10">
-        <v>46083</v>
+        <v>46103</v>
       </c>
       <c r="B431" s="10">
         <v>46104</v>
@@ -35368,6 +34994,41 @@
       </c>
       <c r="K431" s="9">
         <v>4794</v>
+      </c>
+    </row>
+    <row r="432" spans="1:11">
+      <c r="A432" s="10">
+        <v>46110</v>
+      </c>
+      <c r="B432" s="10">
+        <v>46111</v>
+      </c>
+      <c r="C432" s="11">
+        <v>0.70833333333333304</v>
+      </c>
+      <c r="D432" s="8" t="s">
+        <v>21</v>
+      </c>
+      <c r="E432" s="9">
+        <v>2396</v>
+      </c>
+      <c r="F432" s="9">
+        <v>1198</v>
+      </c>
+      <c r="G432" s="9">
+        <v>3871</v>
+      </c>
+      <c r="H432" s="9">
+        <v>1296</v>
+      </c>
+      <c r="I432" s="9">
+        <v>1170</v>
+      </c>
+      <c r="J432" s="9">
+        <v>291</v>
+      </c>
+      <c r="K432" s="9">
+        <v>5348</v>
       </c>
     </row>
   </sheetData>
@@ -35386,7 +35047,7 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{EC49EC86-403A-4933-BA0C-EED828B128BC}">
   <dimension ref="A1"/>
-  <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5"/>
   <cols>
     <col min="1" max="16384" width="9" style="12"/>
   </cols>
@@ -35401,12 +35062,12 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{362BE34E-9F1D-4DC0-8A14-D289984A66A9}">
   <dimension ref="B2:G3"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13"/>
   <cols>
     <col min="1" max="16384" width="9" style="1"/>
   </cols>
   <sheetData>
-    <row r="2" spans="2:7" x14ac:dyDescent="0.25">
+    <row r="2" spans="2:7" ht="16">
       <c r="B2" s="2" t="s">
         <v>16</v>
       </c>
@@ -35418,7 +35079,7 @@
       <c r="F2" s="3"/>
       <c r="G2" s="3"/>
     </row>
-    <row r="3" spans="2:7" x14ac:dyDescent="0.25">
+    <row r="3" spans="2:7">
       <c r="B3" s="4" t="s">
         <v>15</v>
       </c>

--- a/data/freight/Baltic air freight index.xlsx
+++ b/data/freight/Baltic air freight index.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\krm12\PycharmProjects\AlternativeData\data\freight\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1F0F834A-02FA-487C-936E-AED728F05C3A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F4285A59-043C-45FB-ABA0-B72EFC951D2D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="28680" yWindow="-5790" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -2947,6 +2947,9 @@
                 <c:pt idx="429">
                   <c:v>2396</c:v>
                 </c:pt>
+                <c:pt idx="430">
+                  <c:v>2519</c:v>
+                </c:pt>
               </c:numCache>
             </c:numRef>
           </c:val>
@@ -5584,6 +5587,9 @@
                 <c:pt idx="429">
                   <c:v>1198</c:v>
                 </c:pt>
+                <c:pt idx="430">
+                  <c:v>1173</c:v>
+                </c:pt>
               </c:numCache>
             </c:numRef>
           </c:val>
@@ -8221,6 +8227,9 @@
                 <c:pt idx="429">
                   <c:v>3871</c:v>
                 </c:pt>
+                <c:pt idx="430">
+                  <c:v>4205</c:v>
+                </c:pt>
               </c:numCache>
             </c:numRef>
           </c:val>
@@ -10858,6 +10867,9 @@
                 <c:pt idx="429">
                   <c:v>1296</c:v>
                 </c:pt>
+                <c:pt idx="430">
+                  <c:v>1292</c:v>
+                </c:pt>
               </c:numCache>
             </c:numRef>
           </c:val>
@@ -13494,6 +13506,9 @@
                 </c:pt>
                 <c:pt idx="429">
                   <c:v>1170</c:v>
+                </c:pt>
+                <c:pt idx="430">
+                  <c:v>1192</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -16133,6 +16148,9 @@
                 </c:pt>
                 <c:pt idx="429">
                   <c:v>5348</c:v>
+                </c:pt>
+                <c:pt idx="430">
+                  <c:v>5689</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -18786,6 +18804,9 @@
                 </c:pt>
                 <c:pt idx="429">
                   <c:v>291</c:v>
+                </c:pt>
+                <c:pt idx="430">
+                  <c:v>252</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -35057,7 +35078,7 @@
         <v>5348</v>
       </c>
     </row>
-    <row r="433" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="433" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A433" s="10">
         <v>46117</v>
       </c>
@@ -35069,6 +35090,27 @@
       </c>
       <c r="D433" s="8" t="s">
         <v>24</v>
+      </c>
+      <c r="E433" s="9">
+        <v>2519</v>
+      </c>
+      <c r="F433" s="9">
+        <v>1173</v>
+      </c>
+      <c r="G433" s="9">
+        <v>4205</v>
+      </c>
+      <c r="H433" s="9">
+        <v>1292</v>
+      </c>
+      <c r="I433" s="9">
+        <v>1192</v>
+      </c>
+      <c r="J433" s="9">
+        <v>252</v>
+      </c>
+      <c r="K433" s="9">
+        <v>5689</v>
       </c>
     </row>
   </sheetData>

--- a/data/freight/Baltic air freight index.xlsx
+++ b/data/freight/Baltic air freight index.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\krm\PycharmProjects\AlternativeData\data\freight\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B29BFEA9-E799-4BF6-A1BD-62857BAB0C5F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0AD82628-0CCD-44CD-82DB-6E18623543F4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="454" uniqueCount="25">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="455" uniqueCount="25">
   <si>
     <t>Shanghai Pudong Outbound</t>
   </si>
@@ -1648,6 +1648,9 @@
                 <c:pt idx="431">
                   <c:v>46125</c:v>
                 </c:pt>
+                <c:pt idx="432">
+                  <c:v>46132</c:v>
+                </c:pt>
               </c:numCache>
             </c:numRef>
           </c:cat>
@@ -2952,6 +2955,9 @@
                 </c:pt>
                 <c:pt idx="431">
                   <c:v>2555</c:v>
+                </c:pt>
+                <c:pt idx="432">
+                  <c:v>2663</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -4294,6 +4300,9 @@
                 <c:pt idx="431">
                   <c:v>46125</c:v>
                 </c:pt>
+                <c:pt idx="432">
+                  <c:v>46132</c:v>
+                </c:pt>
               </c:numCache>
             </c:numRef>
           </c:cat>
@@ -5598,6 +5607,9 @@
                 </c:pt>
                 <c:pt idx="431">
                   <c:v>1157</c:v>
+                </c:pt>
+                <c:pt idx="432">
+                  <c:v>1208</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -6940,6 +6952,9 @@
                 <c:pt idx="431">
                   <c:v>46125</c:v>
                 </c:pt>
+                <c:pt idx="432">
+                  <c:v>46132</c:v>
+                </c:pt>
               </c:numCache>
             </c:numRef>
           </c:cat>
@@ -8244,6 +8259,9 @@
                 </c:pt>
                 <c:pt idx="431">
                   <c:v>4345</c:v>
+                </c:pt>
+                <c:pt idx="432">
+                  <c:v>4575</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -9586,6 +9604,9 @@
                 <c:pt idx="431">
                   <c:v>46125</c:v>
                 </c:pt>
+                <c:pt idx="432">
+                  <c:v>46132</c:v>
+                </c:pt>
               </c:numCache>
             </c:numRef>
           </c:cat>
@@ -10890,6 +10911,9 @@
                 </c:pt>
                 <c:pt idx="431">
                   <c:v>1474</c:v>
+                </c:pt>
+                <c:pt idx="432">
+                  <c:v>1473</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -12232,6 +12256,9 @@
                 <c:pt idx="431">
                   <c:v>46125</c:v>
                 </c:pt>
+                <c:pt idx="432">
+                  <c:v>46132</c:v>
+                </c:pt>
               </c:numCache>
             </c:numRef>
           </c:cat>
@@ -13536,6 +13563,9 @@
                 </c:pt>
                 <c:pt idx="431">
                   <c:v>1127</c:v>
+                </c:pt>
+                <c:pt idx="432">
+                  <c:v>1192</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -14880,6 +14910,9 @@
                 <c:pt idx="431">
                   <c:v>46125</c:v>
                 </c:pt>
+                <c:pt idx="432">
+                  <c:v>46132</c:v>
+                </c:pt>
               </c:numCache>
             </c:numRef>
           </c:cat>
@@ -16184,6 +16217,9 @@
                 </c:pt>
                 <c:pt idx="431">
                   <c:v>5631</c:v>
+                </c:pt>
+                <c:pt idx="432">
+                  <c:v>5837</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -17542,6 +17578,9 @@
                 <c:pt idx="431">
                   <c:v>46125</c:v>
                 </c:pt>
+                <c:pt idx="432">
+                  <c:v>46132</c:v>
+                </c:pt>
               </c:numCache>
             </c:numRef>
           </c:cat>
@@ -18846,6 +18885,9 @@
                 </c:pt>
                 <c:pt idx="431">
                   <c:v>300</c:v>
+                </c:pt>
+                <c:pt idx="432">
+                  <c:v>291</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -19991,7 +20033,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:K434"/>
+  <dimension ref="A1:K435"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="12.6" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="12.09765625" style="10" bestFit="1" customWidth="1"/>
@@ -35185,6 +35227,41 @@
       </c>
       <c r="K434" s="9">
         <v>5631</v>
+      </c>
+    </row>
+    <row r="435" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="A435" s="10">
+        <v>46131</v>
+      </c>
+      <c r="B435" s="8">
+        <v>46132</v>
+      </c>
+      <c r="C435" s="11">
+        <v>0.70833333333333304</v>
+      </c>
+      <c r="D435" s="8" t="s">
+        <v>22</v>
+      </c>
+      <c r="E435" s="9">
+        <v>2663</v>
+      </c>
+      <c r="F435" s="9">
+        <v>1208</v>
+      </c>
+      <c r="G435" s="9">
+        <v>4575</v>
+      </c>
+      <c r="H435" s="9">
+        <v>1473</v>
+      </c>
+      <c r="I435" s="9">
+        <v>1192</v>
+      </c>
+      <c r="J435" s="9">
+        <v>291</v>
+      </c>
+      <c r="K435" s="9">
+        <v>5837</v>
       </c>
     </row>
   </sheetData>

--- a/data/freight/Baltic air freight index.xlsx
+++ b/data/freight/Baltic air freight index.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29822"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29929"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\krm\PycharmProjects\AlternativeData\data\freight\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0AD82628-0CCD-44CD-82DB-6E18623543F4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{11D260FA-0FAF-4464-B13C-7BDBD3D4F7F1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="455" uniqueCount="25">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="456" uniqueCount="25">
   <si>
     <t>Shanghai Pudong Outbound</t>
   </si>
@@ -1651,6 +1651,9 @@
                 <c:pt idx="432">
                   <c:v>46132</c:v>
                 </c:pt>
+                <c:pt idx="433">
+                  <c:v>46139</c:v>
+                </c:pt>
               </c:numCache>
             </c:numRef>
           </c:cat>
@@ -2958,6 +2961,9 @@
                 </c:pt>
                 <c:pt idx="432">
                   <c:v>2663</c:v>
+                </c:pt>
+                <c:pt idx="433">
+                  <c:v>2772</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -4303,6 +4309,9 @@
                 <c:pt idx="432">
                   <c:v>46132</c:v>
                 </c:pt>
+                <c:pt idx="433">
+                  <c:v>46139</c:v>
+                </c:pt>
               </c:numCache>
             </c:numRef>
           </c:cat>
@@ -5610,6 +5619,9 @@
                 </c:pt>
                 <c:pt idx="432">
                   <c:v>1208</c:v>
+                </c:pt>
+                <c:pt idx="433">
+                  <c:v>1182</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -6955,6 +6967,9 @@
                 <c:pt idx="432">
                   <c:v>46132</c:v>
                 </c:pt>
+                <c:pt idx="433">
+                  <c:v>46139</c:v>
+                </c:pt>
               </c:numCache>
             </c:numRef>
           </c:cat>
@@ -8262,6 +8277,9 @@
                 </c:pt>
                 <c:pt idx="432">
                   <c:v>4575</c:v>
+                </c:pt>
+                <c:pt idx="433">
+                  <c:v>4823</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -9607,6 +9625,9 @@
                 <c:pt idx="432">
                   <c:v>46132</c:v>
                 </c:pt>
+                <c:pt idx="433">
+                  <c:v>46139</c:v>
+                </c:pt>
               </c:numCache>
             </c:numRef>
           </c:cat>
@@ -10914,6 +10935,9 @@
                 </c:pt>
                 <c:pt idx="432">
                   <c:v>1473</c:v>
+                </c:pt>
+                <c:pt idx="433">
+                  <c:v>1500</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -12259,6 +12283,9 @@
                 <c:pt idx="432">
                   <c:v>46132</c:v>
                 </c:pt>
+                <c:pt idx="433">
+                  <c:v>46139</c:v>
+                </c:pt>
               </c:numCache>
             </c:numRef>
           </c:cat>
@@ -13566,6 +13593,9 @@
                 </c:pt>
                 <c:pt idx="432">
                   <c:v>1192</c:v>
+                </c:pt>
+                <c:pt idx="433">
+                  <c:v>1519</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -14913,6 +14943,9 @@
                 <c:pt idx="432">
                   <c:v>46132</c:v>
                 </c:pt>
+                <c:pt idx="433">
+                  <c:v>46139</c:v>
+                </c:pt>
               </c:numCache>
             </c:numRef>
           </c:cat>
@@ -16220,6 +16253,9 @@
                 </c:pt>
                 <c:pt idx="432">
                   <c:v>5837</c:v>
+                </c:pt>
+                <c:pt idx="433">
+                  <c:v>5881</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -17581,6 +17617,9 @@
                 <c:pt idx="432">
                   <c:v>46132</c:v>
                 </c:pt>
+                <c:pt idx="433">
+                  <c:v>46139</c:v>
+                </c:pt>
               </c:numCache>
             </c:numRef>
           </c:cat>
@@ -18888,6 +18927,9 @@
                 </c:pt>
                 <c:pt idx="432">
                   <c:v>291</c:v>
+                </c:pt>
+                <c:pt idx="433">
+                  <c:v>327</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -20033,7 +20075,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:K435"/>
+  <dimension ref="A1:K436"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="12.6" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="12.09765625" style="10" bestFit="1" customWidth="1"/>
@@ -35262,6 +35304,41 @@
       </c>
       <c r="K435" s="9">
         <v>5837</v>
+      </c>
+    </row>
+    <row r="436" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="A436" s="10">
+        <v>46138</v>
+      </c>
+      <c r="B436" s="8">
+        <v>46139</v>
+      </c>
+      <c r="C436" s="11">
+        <v>0.70833333333333304</v>
+      </c>
+      <c r="D436" s="8" t="s">
+        <v>22</v>
+      </c>
+      <c r="E436" s="9">
+        <v>2772</v>
+      </c>
+      <c r="F436" s="9">
+        <v>1182</v>
+      </c>
+      <c r="G436" s="9">
+        <v>4823</v>
+      </c>
+      <c r="H436" s="9">
+        <v>1500</v>
+      </c>
+      <c r="I436" s="9">
+        <v>1519</v>
+      </c>
+      <c r="J436" s="9">
+        <v>327</v>
+      </c>
+      <c r="K436" s="9">
+        <v>5881</v>
       </c>
     </row>
   </sheetData>

--- a/data/freight/Baltic air freight index.xlsx
+++ b/data/freight/Baltic air freight index.xlsx
@@ -2,15 +2,15 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29929"/>
-  <workbookPr/>
+  <workbookPr codeName="현재_통합_문서"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\krm\PycharmProjects\AlternativeData\data\freight\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{11D260FA-0FAF-4464-B13C-7BDBD3D4F7F1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EF44F996-C9A6-4C86-B215-8A2BAFC3BA16}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="BAI" sheetId="1" r:id="rId1"/>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="456" uniqueCount="25">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="457" uniqueCount="25">
   <si>
     <t>Shanghai Pudong Outbound</t>
   </si>
@@ -1654,6 +1654,9 @@
                 <c:pt idx="433">
                   <c:v>46139</c:v>
                 </c:pt>
+                <c:pt idx="434">
+                  <c:v>46146</c:v>
+                </c:pt>
               </c:numCache>
             </c:numRef>
           </c:cat>
@@ -2964,6 +2967,9 @@
                 </c:pt>
                 <c:pt idx="433">
                   <c:v>2772</c:v>
+                </c:pt>
+                <c:pt idx="434">
+                  <c:v>2738</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -4312,6 +4318,9 @@
                 <c:pt idx="433">
                   <c:v>46139</c:v>
                 </c:pt>
+                <c:pt idx="434">
+                  <c:v>46146</c:v>
+                </c:pt>
               </c:numCache>
             </c:numRef>
           </c:cat>
@@ -5622,6 +5631,9 @@
                 </c:pt>
                 <c:pt idx="433">
                   <c:v>1182</c:v>
+                </c:pt>
+                <c:pt idx="434">
+                  <c:v>1109</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -6970,6 +6982,9 @@
                 <c:pt idx="433">
                   <c:v>46139</c:v>
                 </c:pt>
+                <c:pt idx="434">
+                  <c:v>46146</c:v>
+                </c:pt>
               </c:numCache>
             </c:numRef>
           </c:cat>
@@ -8280,6 +8295,9 @@
                 </c:pt>
                 <c:pt idx="433">
                   <c:v>4823</c:v>
+                </c:pt>
+                <c:pt idx="434">
+                  <c:v>4632</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -9628,6 +9646,9 @@
                 <c:pt idx="433">
                   <c:v>46139</c:v>
                 </c:pt>
+                <c:pt idx="434">
+                  <c:v>46146</c:v>
+                </c:pt>
               </c:numCache>
             </c:numRef>
           </c:cat>
@@ -10938,6 +10959,9 @@
                 </c:pt>
                 <c:pt idx="433">
                   <c:v>1500</c:v>
+                </c:pt>
+                <c:pt idx="434">
+                  <c:v>1460</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -12286,6 +12310,9 @@
                 <c:pt idx="433">
                   <c:v>46139</c:v>
                 </c:pt>
+                <c:pt idx="434">
+                  <c:v>46146</c:v>
+                </c:pt>
               </c:numCache>
             </c:numRef>
           </c:cat>
@@ -13596,6 +13623,9 @@
                 </c:pt>
                 <c:pt idx="433">
                   <c:v>1519</c:v>
+                </c:pt>
+                <c:pt idx="434">
+                  <c:v>1515</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -14946,6 +14976,9 @@
                 <c:pt idx="433">
                   <c:v>46139</c:v>
                 </c:pt>
+                <c:pt idx="434">
+                  <c:v>46146</c:v>
+                </c:pt>
               </c:numCache>
             </c:numRef>
           </c:cat>
@@ -16256,6 +16289,9 @@
                 </c:pt>
                 <c:pt idx="433">
                   <c:v>5881</c:v>
+                </c:pt>
+                <c:pt idx="434">
+                  <c:v>6128</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -17620,6 +17656,9 @@
                 <c:pt idx="433">
                   <c:v>46139</c:v>
                 </c:pt>
+                <c:pt idx="434">
+                  <c:v>46146</c:v>
+                </c:pt>
               </c:numCache>
             </c:numRef>
           </c:cat>
@@ -18930,6 +18969,9 @@
                 </c:pt>
                 <c:pt idx="433">
                   <c:v>327</c:v>
+                </c:pt>
+                <c:pt idx="434">
+                  <c:v>261</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -20075,7 +20117,8 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:K436"/>
+  <sheetPr codeName="Sheet1"/>
+  <dimension ref="A1:K437"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="12.6" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="12.09765625" style="10" bestFit="1" customWidth="1"/>
@@ -35341,6 +35384,41 @@
         <v>5881</v>
       </c>
     </row>
+    <row r="437" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="A437" s="10">
+        <v>46145</v>
+      </c>
+      <c r="B437" s="8">
+        <v>46146</v>
+      </c>
+      <c r="C437" s="11">
+        <v>0.70833333333333304</v>
+      </c>
+      <c r="D437" s="8" t="s">
+        <v>22</v>
+      </c>
+      <c r="E437" s="9">
+        <v>2738</v>
+      </c>
+      <c r="F437" s="9">
+        <v>1109</v>
+      </c>
+      <c r="G437" s="9">
+        <v>4632</v>
+      </c>
+      <c r="H437" s="9">
+        <v>1460</v>
+      </c>
+      <c r="I437" s="9">
+        <v>1515</v>
+      </c>
+      <c r="J437" s="9">
+        <v>261</v>
+      </c>
+      <c r="K437" s="9">
+        <v>6128</v>
+      </c>
+    </row>
   </sheetData>
   <mergeCells count="4">
     <mergeCell ref="A1:A2"/>
@@ -35356,6 +35434,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{EC49EC86-403A-4933-BA0C-EED828B128BC}">
+  <sheetPr codeName="Sheet2"/>
   <dimension ref="A1"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.8" x14ac:dyDescent="0.25"/>
   <cols>
@@ -35371,6 +35450,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{362BE34E-9F1D-4DC0-8A14-D289984A66A9}">
+  <sheetPr codeName="Sheet3"/>
   <dimension ref="B2:G3"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="15.6" x14ac:dyDescent="0.35"/>
   <cols>

--- a/data/freight/Baltic air freight index.xlsx
+++ b/data/freight/Baltic air freight index.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\krm\PycharmProjects\AlternativeData\data\freight\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EF44F996-C9A6-4C86-B215-8A2BAFC3BA16}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{00DA7434-442E-41C5-BD74-9840779211E2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="BAI" sheetId="1" r:id="rId1"/>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="457" uniqueCount="25">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="458" uniqueCount="25">
   <si>
     <t>Shanghai Pudong Outbound</t>
   </si>
@@ -1657,6 +1657,9 @@
                 <c:pt idx="434">
                   <c:v>46146</c:v>
                 </c:pt>
+                <c:pt idx="435">
+                  <c:v>46153</c:v>
+                </c:pt>
               </c:numCache>
             </c:numRef>
           </c:cat>
@@ -2970,6 +2973,9 @@
                 </c:pt>
                 <c:pt idx="434">
                   <c:v>2738</c:v>
+                </c:pt>
+                <c:pt idx="435">
+                  <c:v>2750</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -4321,6 +4327,9 @@
                 <c:pt idx="434">
                   <c:v>46146</c:v>
                 </c:pt>
+                <c:pt idx="435">
+                  <c:v>46153</c:v>
+                </c:pt>
               </c:numCache>
             </c:numRef>
           </c:cat>
@@ -5634,6 +5643,9 @@
                 </c:pt>
                 <c:pt idx="434">
                   <c:v>1109</c:v>
+                </c:pt>
+                <c:pt idx="435">
+                  <c:v>1101</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -6985,6 +6997,9 @@
                 <c:pt idx="434">
                   <c:v>46146</c:v>
                 </c:pt>
+                <c:pt idx="435">
+                  <c:v>46153</c:v>
+                </c:pt>
               </c:numCache>
             </c:numRef>
           </c:cat>
@@ -8298,6 +8313,9 @@
                 </c:pt>
                 <c:pt idx="434">
                   <c:v>4632</c:v>
+                </c:pt>
+                <c:pt idx="435">
+                  <c:v>4707</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -9649,6 +9667,9 @@
                 <c:pt idx="434">
                   <c:v>46146</c:v>
                 </c:pt>
+                <c:pt idx="435">
+                  <c:v>46153</c:v>
+                </c:pt>
               </c:numCache>
             </c:numRef>
           </c:cat>
@@ -10962,6 +10983,9 @@
                 </c:pt>
                 <c:pt idx="434">
                   <c:v>1460</c:v>
+                </c:pt>
+                <c:pt idx="435">
+                  <c:v>1380</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -12313,6 +12337,9 @@
                 <c:pt idx="434">
                   <c:v>46146</c:v>
                 </c:pt>
+                <c:pt idx="435">
+                  <c:v>46153</c:v>
+                </c:pt>
               </c:numCache>
             </c:numRef>
           </c:cat>
@@ -13626,6 +13653,9 @@
                 </c:pt>
                 <c:pt idx="434">
                   <c:v>1515</c:v>
+                </c:pt>
+                <c:pt idx="435">
+                  <c:v>1728</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -14979,6 +15009,9 @@
                 <c:pt idx="434">
                   <c:v>46146</c:v>
                 </c:pt>
+                <c:pt idx="435">
+                  <c:v>46153</c:v>
+                </c:pt>
               </c:numCache>
             </c:numRef>
           </c:cat>
@@ -16292,6 +16325,9 @@
                 </c:pt>
                 <c:pt idx="434">
                   <c:v>6128</c:v>
+                </c:pt>
+                <c:pt idx="435">
+                  <c:v>5909</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -17659,6 +17695,9 @@
                 <c:pt idx="434">
                   <c:v>46146</c:v>
                 </c:pt>
+                <c:pt idx="435">
+                  <c:v>46153</c:v>
+                </c:pt>
               </c:numCache>
             </c:numRef>
           </c:cat>
@@ -18972,6 +19011,9 @@
                 </c:pt>
                 <c:pt idx="434">
                   <c:v>261</c:v>
+                </c:pt>
+                <c:pt idx="435">
+                  <c:v>268</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -20118,7 +20160,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <sheetPr codeName="Sheet1"/>
-  <dimension ref="A1:K437"/>
+  <dimension ref="A1:K438"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="12.6" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="12.09765625" style="10" bestFit="1" customWidth="1"/>
@@ -35417,6 +35459,41 @@
       </c>
       <c r="K437" s="9">
         <v>6128</v>
+      </c>
+    </row>
+    <row r="438" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="A438" s="10">
+        <v>46152</v>
+      </c>
+      <c r="B438" s="8">
+        <v>46153</v>
+      </c>
+      <c r="C438" s="11">
+        <v>0.70833333333333304</v>
+      </c>
+      <c r="D438" s="8" t="s">
+        <v>22</v>
+      </c>
+      <c r="E438" s="9">
+        <v>2750</v>
+      </c>
+      <c r="F438" s="9">
+        <v>1101</v>
+      </c>
+      <c r="G438" s="9">
+        <v>4707</v>
+      </c>
+      <c r="H438" s="9">
+        <v>1380</v>
+      </c>
+      <c r="I438" s="9">
+        <v>1728</v>
+      </c>
+      <c r="J438" s="9">
+        <v>268</v>
+      </c>
+      <c r="K438" s="9">
+        <v>5909</v>
       </c>
     </row>
   </sheetData>

--- a/data/freight/Baltic air freight index.xlsx
+++ b/data/freight/Baltic air freight index.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\krm\PycharmProjects\AlternativeData\data\freight\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{00DA7434-442E-41C5-BD74-9840779211E2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{818B1256-E9FD-4242-8C8E-C10AE7EC1445}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="458" uniqueCount="25">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="459" uniqueCount="25">
   <si>
     <t>Shanghai Pudong Outbound</t>
   </si>
@@ -130,29 +130,29 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <numFmts count="4">
-    <numFmt numFmtId="43" formatCode="_-* #,##0.00_-;\-* #,##0.00_-;_-* &quot;-&quot;??_-;_-@_-"/>
-    <numFmt numFmtId="176" formatCode="_(* #,##0_);_(* \(#,##0\);_(* &quot;-&quot;??_);_(@_)"/>
-    <numFmt numFmtId="177" formatCode="yyyy\-mm\-dd;@"/>
-    <numFmt numFmtId="178" formatCode="[$-409]h:mm:ss\ AM/PM;@"/>
+    <numFmt numFmtId="164" formatCode="_-* #,##0.00_-;\-* #,##0.00_-;_-* &quot;-&quot;??_-;_-@_-"/>
+    <numFmt numFmtId="165" formatCode="_(* #,##0_);_(* \(#,##0\);_(* &quot;-&quot;??_);_(@_)"/>
+    <numFmt numFmtId="166" formatCode="yyyy\-mm\-dd;@"/>
+    <numFmt numFmtId="167" formatCode="[$-409]h:mm:ss\ AM/PM;@"/>
   </numFmts>
-  <fonts count="11" x14ac:knownFonts="1">
+  <fonts count="11">
     <font>
       <sz val="11"/>
       <color theme="1"/>
-      <name val="맑은 고딕"/>
+      <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
     </font>
     <font>
       <sz val="11"/>
       <color theme="1"/>
-      <name val="맑은 고딕"/>
+      <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
     </font>
     <font>
       <sz val="8"/>
-      <name val="맑은 고딕"/>
+      <name val="Calibri"/>
       <family val="3"/>
       <charset val="129"/>
       <scheme val="minor"/>
@@ -174,7 +174,7 @@
     <font>
       <sz val="10"/>
       <color theme="1"/>
-      <name val="맑은 고딕"/>
+      <name val="Calibri"/>
       <family val="3"/>
       <charset val="129"/>
       <scheme val="minor"/>
@@ -191,7 +191,7 @@
       <b/>
       <sz val="10"/>
       <color theme="1"/>
-      <name val="맑은 고딕"/>
+      <name val="Calibri"/>
       <family val="3"/>
       <charset val="129"/>
       <scheme val="minor"/>
@@ -235,7 +235,7 @@
   </borders>
   <cellStyleXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
-    <xf numFmtId="43" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="164" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
@@ -255,27 +255,27 @@
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="2">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="176" fontId="8" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1">
+    <xf numFmtId="165" fontId="8" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="177" fontId="9" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="166" fontId="9" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="176" fontId="9" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1">
+    <xf numFmtId="165" fontId="9" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="177" fontId="9" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="166" fontId="9" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="178" fontId="9" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="167" fontId="9" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="177" fontId="8" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="166" fontId="8" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="178" fontId="8" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="167" fontId="8" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -1660,6 +1660,9 @@
                 <c:pt idx="435">
                   <c:v>46153</c:v>
                 </c:pt>
+                <c:pt idx="436">
+                  <c:v>46160</c:v>
+                </c:pt>
               </c:numCache>
             </c:numRef>
           </c:cat>
@@ -2976,6 +2979,9 @@
                 </c:pt>
                 <c:pt idx="435">
                   <c:v>2750</c:v>
+                </c:pt>
+                <c:pt idx="436">
+                  <c:v>2614</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -4330,6 +4336,9 @@
                 <c:pt idx="435">
                   <c:v>46153</c:v>
                 </c:pt>
+                <c:pt idx="436">
+                  <c:v>46160</c:v>
+                </c:pt>
               </c:numCache>
             </c:numRef>
           </c:cat>
@@ -5646,6 +5655,9 @@
                 </c:pt>
                 <c:pt idx="435">
                   <c:v>1101</c:v>
+                </c:pt>
+                <c:pt idx="436">
+                  <c:v>1075</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -7000,6 +7012,9 @@
                 <c:pt idx="435">
                   <c:v>46153</c:v>
                 </c:pt>
+                <c:pt idx="436">
+                  <c:v>46160</c:v>
+                </c:pt>
               </c:numCache>
             </c:numRef>
           </c:cat>
@@ -8316,6 +8331,9 @@
                 </c:pt>
                 <c:pt idx="435">
                   <c:v>4707</c:v>
+                </c:pt>
+                <c:pt idx="436">
+                  <c:v>4592</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -9670,6 +9688,9 @@
                 <c:pt idx="435">
                   <c:v>46153</c:v>
                 </c:pt>
+                <c:pt idx="436">
+                  <c:v>46160</c:v>
+                </c:pt>
               </c:numCache>
             </c:numRef>
           </c:cat>
@@ -10986,6 +11007,9 @@
                 </c:pt>
                 <c:pt idx="435">
                   <c:v>1380</c:v>
+                </c:pt>
+                <c:pt idx="436">
+                  <c:v>1190</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -12340,6 +12364,9 @@
                 <c:pt idx="435">
                   <c:v>46153</c:v>
                 </c:pt>
+                <c:pt idx="436">
+                  <c:v>46160</c:v>
+                </c:pt>
               </c:numCache>
             </c:numRef>
           </c:cat>
@@ -13656,6 +13683,9 @@
                 </c:pt>
                 <c:pt idx="435">
                   <c:v>1728</c:v>
+                </c:pt>
+                <c:pt idx="436">
+                  <c:v>1303</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -15012,6 +15042,9 @@
                 <c:pt idx="435">
                   <c:v>46153</c:v>
                 </c:pt>
+                <c:pt idx="436">
+                  <c:v>46160</c:v>
+                </c:pt>
               </c:numCache>
             </c:numRef>
           </c:cat>
@@ -16328,6 +16361,9 @@
                 </c:pt>
                 <c:pt idx="435">
                   <c:v>5909</c:v>
+                </c:pt>
+                <c:pt idx="436">
+                  <c:v>5807</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -17698,6 +17734,9 @@
                 <c:pt idx="435">
                   <c:v>46153</c:v>
                 </c:pt>
+                <c:pt idx="436">
+                  <c:v>46160</c:v>
+                </c:pt>
               </c:numCache>
             </c:numRef>
           </c:cat>
@@ -19014,6 +19053,9 @@
                 </c:pt>
                 <c:pt idx="435">
                   <c:v>268</c:v>
+                </c:pt>
+                <c:pt idx="436">
+                  <c:v>341</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -20160,21 +20202,21 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <sheetPr codeName="Sheet1"/>
-  <dimension ref="A1:K438"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="12.6" x14ac:dyDescent="0.2"/>
+  <dimension ref="A1:K439"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="12.6"/>
   <cols>
-    <col min="1" max="1" width="12.09765625" style="10" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="12.109375" style="10" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="14" style="8" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="11.8984375" style="11" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="11.09765625" style="8" customWidth="1"/>
-    <col min="5" max="8" width="8.59765625" style="9" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="9.5" style="9" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="8.59765625" style="9" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="9.5" style="9" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="11.88671875" style="11" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="11.109375" style="8" customWidth="1"/>
+    <col min="5" max="8" width="8.5546875" style="9" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="9.44140625" style="9" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="8.5546875" style="9" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="9.44140625" style="9" bestFit="1" customWidth="1"/>
     <col min="12" max="16384" width="9" style="7"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:11" ht="15" customHeight="1">
       <c r="A1" s="13" t="s">
         <v>18</v>
       </c>
@@ -20209,7 +20251,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="2" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:11">
       <c r="A2" s="13"/>
       <c r="B2" s="13"/>
       <c r="C2" s="14"/>
@@ -20236,7 +20278,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="3" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="3" spans="1:11">
       <c r="A3" s="10">
         <v>43100</v>
       </c>
@@ -20271,7 +20313,7 @@
         <v>3169</v>
       </c>
     </row>
-    <row r="4" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="4" spans="1:11">
       <c r="A4" s="10">
         <v>43107</v>
       </c>
@@ -20306,7 +20348,7 @@
         <v>2961</v>
       </c>
     </row>
-    <row r="5" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:11">
       <c r="A5" s="10">
         <v>43114</v>
       </c>
@@ -20341,7 +20383,7 @@
         <v>2650</v>
       </c>
     </row>
-    <row r="6" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:11">
       <c r="A6" s="10">
         <v>43121</v>
       </c>
@@ -20376,7 +20418,7 @@
         <v>2807</v>
       </c>
     </row>
-    <row r="7" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:11">
       <c r="A7" s="10">
         <v>43128</v>
       </c>
@@ -20411,7 +20453,7 @@
         <v>2904</v>
       </c>
     </row>
-    <row r="8" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:11">
       <c r="A8" s="10">
         <v>43135</v>
       </c>
@@ -20446,7 +20488,7 @@
         <v>2899</v>
       </c>
     </row>
-    <row r="9" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:11">
       <c r="A9" s="10">
         <v>43142</v>
       </c>
@@ -20481,7 +20523,7 @@
         <v>2901</v>
       </c>
     </row>
-    <row r="10" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:11">
       <c r="A10" s="10">
         <v>43149</v>
       </c>
@@ -20516,7 +20558,7 @@
         <v>2727</v>
       </c>
     </row>
-    <row r="11" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:11">
       <c r="A11" s="10">
         <v>43156</v>
       </c>
@@ -20551,7 +20593,7 @@
         <v>2761</v>
       </c>
     </row>
-    <row r="12" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:11">
       <c r="A12" s="10">
         <v>43163</v>
       </c>
@@ -20586,7 +20628,7 @@
         <v>2517</v>
       </c>
     </row>
-    <row r="13" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:11">
       <c r="A13" s="10">
         <v>43170</v>
       </c>
@@ -20621,7 +20663,7 @@
         <v>2740</v>
       </c>
     </row>
-    <row r="14" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:11">
       <c r="A14" s="10">
         <v>43177</v>
       </c>
@@ -20656,7 +20698,7 @@
         <v>2752</v>
       </c>
     </row>
-    <row r="15" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:11">
       <c r="A15" s="10">
         <v>43184</v>
       </c>
@@ -20691,7 +20733,7 @@
         <v>2814</v>
       </c>
     </row>
-    <row r="16" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:11">
       <c r="A16" s="10">
         <v>43191</v>
       </c>
@@ -20726,7 +20768,7 @@
         <v>2989</v>
       </c>
     </row>
-    <row r="17" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="17" spans="1:11">
       <c r="A17" s="10">
         <v>43198</v>
       </c>
@@ -20761,7 +20803,7 @@
         <v>3053</v>
       </c>
     </row>
-    <row r="18" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="18" spans="1:11">
       <c r="A18" s="10">
         <v>43205</v>
       </c>
@@ -20796,7 +20838,7 @@
         <v>2992</v>
       </c>
     </row>
-    <row r="19" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="19" spans="1:11">
       <c r="A19" s="10">
         <v>43212</v>
       </c>
@@ -20831,7 +20873,7 @@
         <v>3134</v>
       </c>
     </row>
-    <row r="20" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="20" spans="1:11">
       <c r="A20" s="10">
         <v>43219</v>
       </c>
@@ -20866,7 +20908,7 @@
         <v>3103</v>
       </c>
     </row>
-    <row r="21" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="21" spans="1:11">
       <c r="A21" s="10">
         <v>43226</v>
       </c>
@@ -20901,7 +20943,7 @@
         <v>2954</v>
       </c>
     </row>
-    <row r="22" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="22" spans="1:11">
       <c r="A22" s="10">
         <v>43233</v>
       </c>
@@ -20936,7 +20978,7 @@
         <v>2913</v>
       </c>
     </row>
-    <row r="23" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="23" spans="1:11">
       <c r="A23" s="10">
         <v>43240</v>
       </c>
@@ -20971,7 +21013,7 @@
         <v>2924</v>
       </c>
     </row>
-    <row r="24" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="24" spans="1:11">
       <c r="A24" s="10">
         <v>43247</v>
       </c>
@@ -21006,7 +21048,7 @@
         <v>2888</v>
       </c>
     </row>
-    <row r="25" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="25" spans="1:11">
       <c r="A25" s="10">
         <v>43254</v>
       </c>
@@ -21041,7 +21083,7 @@
         <v>2904</v>
       </c>
     </row>
-    <row r="26" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="26" spans="1:11">
       <c r="A26" s="10">
         <v>43261</v>
       </c>
@@ -21076,7 +21118,7 @@
         <v>2959</v>
       </c>
     </row>
-    <row r="27" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="27" spans="1:11">
       <c r="A27" s="10">
         <v>43268</v>
       </c>
@@ -21111,7 +21153,7 @@
         <v>2873</v>
       </c>
     </row>
-    <row r="28" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="28" spans="1:11">
       <c r="A28" s="10">
         <v>43275</v>
       </c>
@@ -21146,7 +21188,7 @@
         <v>2769</v>
       </c>
     </row>
-    <row r="29" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="29" spans="1:11">
       <c r="A29" s="10">
         <v>43282</v>
       </c>
@@ -21181,7 +21223,7 @@
         <v>3014</v>
       </c>
     </row>
-    <row r="30" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="30" spans="1:11">
       <c r="A30" s="10">
         <v>43289</v>
       </c>
@@ -21216,7 +21258,7 @@
         <v>3033</v>
       </c>
     </row>
-    <row r="31" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="31" spans="1:11">
       <c r="A31" s="10">
         <v>43296</v>
       </c>
@@ -21251,7 +21293,7 @@
         <v>2930</v>
       </c>
     </row>
-    <row r="32" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="32" spans="1:11">
       <c r="A32" s="10">
         <v>43303</v>
       </c>
@@ -21286,7 +21328,7 @@
         <v>3182</v>
       </c>
     </row>
-    <row r="33" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="33" spans="1:11">
       <c r="A33" s="10">
         <v>43310</v>
       </c>
@@ -21321,7 +21363,7 @@
         <v>3174</v>
       </c>
     </row>
-    <row r="34" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="34" spans="1:11">
       <c r="A34" s="10">
         <v>43317</v>
       </c>
@@ -21356,7 +21398,7 @@
         <v>3183</v>
       </c>
     </row>
-    <row r="35" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="35" spans="1:11">
       <c r="A35" s="10">
         <v>43324</v>
       </c>
@@ -21391,7 +21433,7 @@
         <v>3078</v>
       </c>
     </row>
-    <row r="36" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="36" spans="1:11">
       <c r="A36" s="10">
         <v>43331</v>
       </c>
@@ -21426,7 +21468,7 @@
         <v>3135</v>
       </c>
     </row>
-    <row r="37" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="37" spans="1:11">
       <c r="A37" s="10">
         <v>43338</v>
       </c>
@@ -21461,7 +21503,7 @@
         <v>3138</v>
       </c>
     </row>
-    <row r="38" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="38" spans="1:11">
       <c r="A38" s="10">
         <v>43345</v>
       </c>
@@ -21496,7 +21538,7 @@
         <v>3417</v>
       </c>
     </row>
-    <row r="39" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="39" spans="1:11">
       <c r="A39" s="10">
         <v>43352</v>
       </c>
@@ -21531,7 +21573,7 @@
         <v>3427</v>
       </c>
     </row>
-    <row r="40" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="40" spans="1:11">
       <c r="A40" s="10">
         <v>43359</v>
       </c>
@@ -21566,7 +21608,7 @@
         <v>3254</v>
       </c>
     </row>
-    <row r="41" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="41" spans="1:11">
       <c r="A41" s="10">
         <v>43366</v>
       </c>
@@ -21601,7 +21643,7 @@
         <v>3334</v>
       </c>
     </row>
-    <row r="42" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="42" spans="1:11">
       <c r="A42" s="10">
         <v>43373</v>
       </c>
@@ -21636,7 +21678,7 @@
         <v>3450</v>
       </c>
     </row>
-    <row r="43" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="43" spans="1:11">
       <c r="A43" s="10">
         <v>43380</v>
       </c>
@@ -21671,7 +21713,7 @@
         <v>3267</v>
       </c>
     </row>
-    <row r="44" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="44" spans="1:11">
       <c r="A44" s="10">
         <v>43387</v>
       </c>
@@ -21706,7 +21748,7 @@
         <v>3296</v>
       </c>
     </row>
-    <row r="45" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="45" spans="1:11">
       <c r="A45" s="10">
         <v>43394</v>
       </c>
@@ -21741,7 +21783,7 @@
         <v>3511</v>
       </c>
     </row>
-    <row r="46" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="46" spans="1:11">
       <c r="A46" s="10">
         <v>43401</v>
       </c>
@@ -21776,7 +21818,7 @@
         <v>3658</v>
       </c>
     </row>
-    <row r="47" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="47" spans="1:11">
       <c r="A47" s="10">
         <v>43408</v>
       </c>
@@ -21811,7 +21853,7 @@
         <v>3881</v>
       </c>
     </row>
-    <row r="48" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="48" spans="1:11">
       <c r="A48" s="10">
         <v>43415</v>
       </c>
@@ -21846,7 +21888,7 @@
         <v>3696</v>
       </c>
     </row>
-    <row r="49" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="49" spans="1:11">
       <c r="A49" s="10">
         <v>43422</v>
       </c>
@@ -21881,7 +21923,7 @@
         <v>3795</v>
       </c>
     </row>
-    <row r="50" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="50" spans="1:11">
       <c r="A50" s="10">
         <v>43429</v>
       </c>
@@ -21916,7 +21958,7 @@
         <v>3690</v>
       </c>
     </row>
-    <row r="51" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="51" spans="1:11">
       <c r="A51" s="10">
         <v>43436</v>
       </c>
@@ -21951,7 +21993,7 @@
         <v>3542</v>
       </c>
     </row>
-    <row r="52" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="52" spans="1:11">
       <c r="A52" s="10">
         <v>43443</v>
       </c>
@@ -21986,7 +22028,7 @@
         <v>3372</v>
       </c>
     </row>
-    <row r="53" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="53" spans="1:11">
       <c r="A53" s="10">
         <v>43450</v>
       </c>
@@ -22021,7 +22063,7 @@
         <v>3495</v>
       </c>
     </row>
-    <row r="54" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="54" spans="1:11">
       <c r="A54" s="10">
         <v>43457</v>
       </c>
@@ -22056,7 +22098,7 @@
         <v>3197</v>
       </c>
     </row>
-    <row r="55" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="55" spans="1:11">
       <c r="A55" s="10">
         <v>43464</v>
       </c>
@@ -22091,7 +22133,7 @@
         <v>3164</v>
       </c>
     </row>
-    <row r="56" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="56" spans="1:11">
       <c r="A56" s="10">
         <v>43471</v>
       </c>
@@ -22126,7 +22168,7 @@
         <v>3171</v>
       </c>
     </row>
-    <row r="57" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="57" spans="1:11">
       <c r="A57" s="10">
         <v>43478</v>
       </c>
@@ -22161,7 +22203,7 @@
         <v>3147</v>
       </c>
     </row>
-    <row r="58" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="58" spans="1:11">
       <c r="A58" s="10">
         <v>43485</v>
       </c>
@@ -22196,7 +22238,7 @@
         <v>3195</v>
       </c>
     </row>
-    <row r="59" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="59" spans="1:11">
       <c r="A59" s="10">
         <v>43492</v>
       </c>
@@ -22231,7 +22273,7 @@
         <v>3054</v>
       </c>
     </row>
-    <row r="60" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="60" spans="1:11">
       <c r="A60" s="10">
         <v>43499</v>
       </c>
@@ -22266,7 +22308,7 @@
         <v>3148</v>
       </c>
     </row>
-    <row r="61" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="61" spans="1:11">
       <c r="A61" s="10">
         <v>43506</v>
       </c>
@@ -22301,7 +22343,7 @@
         <v>3187</v>
       </c>
     </row>
-    <row r="62" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="62" spans="1:11">
       <c r="A62" s="10">
         <v>43513</v>
       </c>
@@ -22336,7 +22378,7 @@
         <v>3215</v>
       </c>
     </row>
-    <row r="63" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="63" spans="1:11">
       <c r="A63" s="10">
         <v>43520</v>
       </c>
@@ -22371,7 +22413,7 @@
         <v>3068</v>
       </c>
     </row>
-    <row r="64" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="64" spans="1:11">
       <c r="A64" s="10">
         <v>43527</v>
       </c>
@@ -22406,7 +22448,7 @@
         <v>2976</v>
       </c>
     </row>
-    <row r="65" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="65" spans="1:11">
       <c r="A65" s="10">
         <v>43534</v>
       </c>
@@ -22441,7 +22483,7 @@
         <v>2897</v>
       </c>
     </row>
-    <row r="66" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="66" spans="1:11">
       <c r="A66" s="10">
         <v>43541</v>
       </c>
@@ -22476,7 +22518,7 @@
         <v>2954</v>
       </c>
     </row>
-    <row r="67" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="67" spans="1:11">
       <c r="A67" s="10">
         <v>43548</v>
       </c>
@@ -22511,7 +22553,7 @@
         <v>2955</v>
       </c>
     </row>
-    <row r="68" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="68" spans="1:11">
       <c r="A68" s="10">
         <v>43555</v>
       </c>
@@ -22546,7 +22588,7 @@
         <v>2977</v>
       </c>
     </row>
-    <row r="69" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="69" spans="1:11">
       <c r="A69" s="10">
         <v>43562</v>
       </c>
@@ -22581,7 +22623,7 @@
         <v>3113</v>
       </c>
     </row>
-    <row r="70" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="70" spans="1:11">
       <c r="A70" s="10">
         <v>43569</v>
       </c>
@@ -22616,7 +22658,7 @@
         <v>2876</v>
       </c>
     </row>
-    <row r="71" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="71" spans="1:11">
       <c r="A71" s="10">
         <v>43576</v>
       </c>
@@ -22651,7 +22693,7 @@
         <v>2704</v>
       </c>
     </row>
-    <row r="72" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="72" spans="1:11">
       <c r="A72" s="10">
         <v>43583</v>
       </c>
@@ -22686,7 +22728,7 @@
         <v>2822</v>
       </c>
     </row>
-    <row r="73" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="73" spans="1:11">
       <c r="A73" s="10">
         <v>43590</v>
       </c>
@@ -22721,7 +22763,7 @@
         <v>2776</v>
       </c>
     </row>
-    <row r="74" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="74" spans="1:11">
       <c r="A74" s="10">
         <v>43597</v>
       </c>
@@ -22756,7 +22798,7 @@
         <v>2732</v>
       </c>
     </row>
-    <row r="75" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="75" spans="1:11">
       <c r="A75" s="10">
         <v>43604</v>
       </c>
@@ -22791,7 +22833,7 @@
         <v>2772</v>
       </c>
     </row>
-    <row r="76" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="76" spans="1:11">
       <c r="A76" s="10">
         <v>43611</v>
       </c>
@@ -22826,7 +22868,7 @@
         <v>2788</v>
       </c>
     </row>
-    <row r="77" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="77" spans="1:11">
       <c r="A77" s="10">
         <v>43618</v>
       </c>
@@ -22861,7 +22903,7 @@
         <v>2662</v>
       </c>
     </row>
-    <row r="78" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="78" spans="1:11">
       <c r="A78" s="10">
         <v>43625</v>
       </c>
@@ -22896,7 +22938,7 @@
         <v>2677</v>
       </c>
     </row>
-    <row r="79" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="79" spans="1:11">
       <c r="A79" s="10">
         <v>43632</v>
       </c>
@@ -22931,7 +22973,7 @@
         <v>2532</v>
       </c>
     </row>
-    <row r="80" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="80" spans="1:11">
       <c r="A80" s="10">
         <v>43639</v>
       </c>
@@ -22966,7 +23008,7 @@
         <v>2732</v>
       </c>
     </row>
-    <row r="81" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="81" spans="1:11">
       <c r="A81" s="10">
         <v>43646</v>
       </c>
@@ -23001,7 +23043,7 @@
         <v>2742</v>
       </c>
     </row>
-    <row r="82" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="82" spans="1:11">
       <c r="A82" s="10">
         <v>43653</v>
       </c>
@@ -23036,7 +23078,7 @@
         <v>2772</v>
       </c>
     </row>
-    <row r="83" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="83" spans="1:11">
       <c r="A83" s="10">
         <v>43660</v>
       </c>
@@ -23071,7 +23113,7 @@
         <v>2766</v>
       </c>
     </row>
-    <row r="84" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="84" spans="1:11">
       <c r="A84" s="10">
         <v>43667</v>
       </c>
@@ -23106,7 +23148,7 @@
         <v>2587</v>
       </c>
     </row>
-    <row r="85" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="85" spans="1:11">
       <c r="A85" s="10">
         <v>43674</v>
       </c>
@@ -23141,7 +23183,7 @@
         <v>2668</v>
       </c>
     </row>
-    <row r="86" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="86" spans="1:11">
       <c r="A86" s="10">
         <v>43681</v>
       </c>
@@ -23176,7 +23218,7 @@
         <v>2605</v>
       </c>
     </row>
-    <row r="87" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="87" spans="1:11">
       <c r="A87" s="10">
         <v>43688</v>
       </c>
@@ -23211,7 +23253,7 @@
         <v>2551</v>
       </c>
     </row>
-    <row r="88" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="88" spans="1:11">
       <c r="A88" s="10">
         <v>43695</v>
       </c>
@@ -23246,7 +23288,7 @@
         <v>2628</v>
       </c>
     </row>
-    <row r="89" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="89" spans="1:11">
       <c r="A89" s="10">
         <v>43702</v>
       </c>
@@ -23281,7 +23323,7 @@
         <v>2656</v>
       </c>
     </row>
-    <row r="90" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="90" spans="1:11">
       <c r="A90" s="10">
         <v>43709</v>
       </c>
@@ -23316,7 +23358,7 @@
         <v>2608</v>
       </c>
     </row>
-    <row r="91" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="91" spans="1:11">
       <c r="A91" s="10">
         <v>43716</v>
       </c>
@@ -23351,7 +23393,7 @@
         <v>2611</v>
       </c>
     </row>
-    <row r="92" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="92" spans="1:11">
       <c r="A92" s="10">
         <v>43723</v>
       </c>
@@ -23386,7 +23428,7 @@
         <v>2550</v>
       </c>
     </row>
-    <row r="93" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="93" spans="1:11">
       <c r="A93" s="10">
         <v>43730</v>
       </c>
@@ -23421,7 +23463,7 @@
         <v>2572</v>
       </c>
     </row>
-    <row r="94" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="94" spans="1:11">
       <c r="A94" s="10">
         <v>43737</v>
       </c>
@@ -23456,7 +23498,7 @@
         <v>2703</v>
       </c>
     </row>
-    <row r="95" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="95" spans="1:11">
       <c r="A95" s="10">
         <v>43744</v>
       </c>
@@ -23491,7 +23533,7 @@
         <v>2804</v>
       </c>
     </row>
-    <row r="96" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="96" spans="1:11">
       <c r="A96" s="10">
         <v>43751</v>
       </c>
@@ -23526,7 +23568,7 @@
         <v>2781</v>
       </c>
     </row>
-    <row r="97" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="97" spans="1:11">
       <c r="A97" s="10">
         <v>43758</v>
       </c>
@@ -23561,7 +23603,7 @@
         <v>2915</v>
       </c>
     </row>
-    <row r="98" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="98" spans="1:11">
       <c r="A98" s="10">
         <v>43765</v>
       </c>
@@ -23596,7 +23638,7 @@
         <v>3032</v>
       </c>
     </row>
-    <row r="99" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="99" spans="1:11">
       <c r="A99" s="10">
         <v>43772</v>
       </c>
@@ -23631,7 +23673,7 @@
         <v>3120</v>
       </c>
     </row>
-    <row r="100" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="100" spans="1:11">
       <c r="A100" s="10">
         <v>43779</v>
       </c>
@@ -23666,7 +23708,7 @@
         <v>3031</v>
       </c>
     </row>
-    <row r="101" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="101" spans="1:11">
       <c r="A101" s="10">
         <v>43786</v>
       </c>
@@ -23701,7 +23743,7 @@
         <v>3117</v>
       </c>
     </row>
-    <row r="102" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="102" spans="1:11">
       <c r="A102" s="10">
         <v>43793</v>
       </c>
@@ -23736,7 +23778,7 @@
         <v>3143</v>
       </c>
     </row>
-    <row r="103" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="103" spans="1:11">
       <c r="A103" s="10">
         <v>43800</v>
       </c>
@@ -23771,7 +23813,7 @@
         <v>3079</v>
       </c>
     </row>
-    <row r="104" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="104" spans="1:11">
       <c r="A104" s="10">
         <v>43807</v>
       </c>
@@ -23806,7 +23848,7 @@
         <v>3019</v>
       </c>
     </row>
-    <row r="105" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="105" spans="1:11">
       <c r="A105" s="10">
         <v>43814</v>
       </c>
@@ -23841,7 +23883,7 @@
         <v>2964</v>
       </c>
     </row>
-    <row r="106" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="106" spans="1:11">
       <c r="A106" s="10">
         <v>43821</v>
       </c>
@@ -23876,7 +23918,7 @@
         <v>2821</v>
       </c>
     </row>
-    <row r="107" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="107" spans="1:11">
       <c r="A107" s="10">
         <v>43828</v>
       </c>
@@ -23911,7 +23953,7 @@
         <v>2760</v>
       </c>
     </row>
-    <row r="108" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="108" spans="1:11">
       <c r="A108" s="10">
         <v>43835</v>
       </c>
@@ -23946,7 +23988,7 @@
         <v>2776</v>
       </c>
     </row>
-    <row r="109" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="109" spans="1:11">
       <c r="A109" s="10">
         <v>43842</v>
       </c>
@@ -23981,7 +24023,7 @@
         <v>2636</v>
       </c>
     </row>
-    <row r="110" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="110" spans="1:11">
       <c r="A110" s="10">
         <v>43849</v>
       </c>
@@ -24016,7 +24058,7 @@
         <v>2698</v>
       </c>
     </row>
-    <row r="111" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="111" spans="1:11">
       <c r="A111" s="10">
         <v>43856</v>
       </c>
@@ -24051,7 +24093,7 @@
         <v>2838</v>
       </c>
     </row>
-    <row r="112" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="112" spans="1:11">
       <c r="A112" s="10">
         <v>43863</v>
       </c>
@@ -24086,7 +24128,7 @@
         <v>2587</v>
       </c>
     </row>
-    <row r="113" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="113" spans="1:11">
       <c r="A113" s="10">
         <v>43870</v>
       </c>
@@ -24121,7 +24163,7 @@
         <v>2498</v>
       </c>
     </row>
-    <row r="114" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="114" spans="1:11">
       <c r="A114" s="10">
         <v>43877</v>
       </c>
@@ -24156,7 +24198,7 @@
         <v>2427</v>
       </c>
     </row>
-    <row r="115" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="115" spans="1:11">
       <c r="A115" s="10">
         <v>43884</v>
       </c>
@@ -24191,7 +24233,7 @@
         <v>2239</v>
       </c>
     </row>
-    <row r="116" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="116" spans="1:11">
       <c r="A116" s="10">
         <v>43891</v>
       </c>
@@ -24226,7 +24268,7 @@
         <v>2539</v>
       </c>
     </row>
-    <row r="117" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="117" spans="1:11">
       <c r="A117" s="10">
         <v>43898</v>
       </c>
@@ -24261,7 +24303,7 @@
         <v>3154</v>
       </c>
     </row>
-    <row r="118" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="118" spans="1:11">
       <c r="A118" s="10">
         <v>43905</v>
       </c>
@@ -24296,7 +24338,7 @@
         <v>3858</v>
       </c>
     </row>
-    <row r="119" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="119" spans="1:11">
       <c r="A119" s="10">
         <v>43912</v>
       </c>
@@ -24331,7 +24373,7 @@
         <v>4713</v>
       </c>
     </row>
-    <row r="120" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="120" spans="1:11">
       <c r="A120" s="10">
         <v>43919</v>
       </c>
@@ -24366,7 +24408,7 @@
         <v>5641</v>
       </c>
     </row>
-    <row r="121" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="121" spans="1:11">
       <c r="A121" s="10">
         <v>43926</v>
       </c>
@@ -24401,7 +24443,7 @@
         <v>6426</v>
       </c>
     </row>
-    <row r="122" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="122" spans="1:11">
       <c r="A122" s="10">
         <v>43933</v>
       </c>
@@ -24436,7 +24478,7 @@
         <v>7284</v>
       </c>
     </row>
-    <row r="123" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="123" spans="1:11">
       <c r="A123" s="10">
         <v>43940</v>
       </c>
@@ -24471,7 +24513,7 @@
         <v>7946</v>
       </c>
     </row>
-    <row r="124" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="124" spans="1:11">
       <c r="A124" s="10">
         <v>43947</v>
       </c>
@@ -24506,7 +24548,7 @@
         <v>8608</v>
       </c>
     </row>
-    <row r="125" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="125" spans="1:11">
       <c r="A125" s="10">
         <v>43954</v>
       </c>
@@ -24541,7 +24583,7 @@
         <v>9951</v>
       </c>
     </row>
-    <row r="126" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="126" spans="1:11">
       <c r="A126" s="10">
         <v>43961</v>
       </c>
@@ -24576,7 +24618,7 @@
         <v>10351</v>
       </c>
     </row>
-    <row r="127" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="127" spans="1:11">
       <c r="A127" s="10">
         <v>43968</v>
       </c>
@@ -24611,7 +24653,7 @@
         <v>11202</v>
       </c>
     </row>
-    <row r="128" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="128" spans="1:11">
       <c r="A128" s="10">
         <v>43975</v>
       </c>
@@ -24646,7 +24688,7 @@
         <v>9824</v>
       </c>
     </row>
-    <row r="129" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="129" spans="1:11">
       <c r="A129" s="10">
         <v>43982</v>
       </c>
@@ -24681,7 +24723,7 @@
         <v>7635</v>
       </c>
     </row>
-    <row r="130" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="130" spans="1:11">
       <c r="A130" s="10">
         <v>43989</v>
       </c>
@@ -24716,7 +24758,7 @@
         <v>5993</v>
       </c>
     </row>
-    <row r="131" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="131" spans="1:11">
       <c r="A131" s="10">
         <v>43996</v>
       </c>
@@ -24751,7 +24793,7 @@
         <v>4905</v>
       </c>
     </row>
-    <row r="132" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="132" spans="1:11">
       <c r="A132" s="10">
         <v>44003</v>
       </c>
@@ -24786,7 +24828,7 @@
         <v>4035</v>
       </c>
     </row>
-    <row r="133" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="133" spans="1:11">
       <c r="A133" s="10">
         <v>44010</v>
       </c>
@@ -24821,7 +24863,7 @@
         <v>3835</v>
       </c>
     </row>
-    <row r="134" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="134" spans="1:11">
       <c r="A134" s="10">
         <v>44017</v>
       </c>
@@ -24856,7 +24898,7 @@
         <v>3711</v>
       </c>
     </row>
-    <row r="135" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="135" spans="1:11">
       <c r="A135" s="10">
         <v>44024</v>
       </c>
@@ -24891,7 +24933,7 @@
         <v>3775</v>
       </c>
     </row>
-    <row r="136" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="136" spans="1:11">
       <c r="A136" s="10">
         <v>44031</v>
       </c>
@@ -24926,7 +24968,7 @@
         <v>3862</v>
       </c>
     </row>
-    <row r="137" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="137" spans="1:11">
       <c r="A137" s="10">
         <v>44038</v>
       </c>
@@ -24961,7 +25003,7 @@
         <v>4050</v>
       </c>
     </row>
-    <row r="138" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="138" spans="1:11">
       <c r="A138" s="10">
         <v>44045</v>
       </c>
@@ -24996,7 +25038,7 @@
         <v>4535</v>
       </c>
     </row>
-    <row r="139" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="139" spans="1:11">
       <c r="A139" s="10">
         <v>44052</v>
       </c>
@@ -25031,7 +25073,7 @@
         <v>4425</v>
       </c>
     </row>
-    <row r="140" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="140" spans="1:11">
       <c r="A140" s="10">
         <v>44059</v>
       </c>
@@ -25066,7 +25108,7 @@
         <v>4121</v>
       </c>
     </row>
-    <row r="141" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="141" spans="1:11">
       <c r="A141" s="10">
         <v>44066</v>
       </c>
@@ -25101,7 +25143,7 @@
         <v>3819</v>
       </c>
     </row>
-    <row r="142" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="142" spans="1:11">
       <c r="A142" s="10">
         <v>44073</v>
       </c>
@@ -25136,7 +25178,7 @@
         <v>4332</v>
       </c>
     </row>
-    <row r="143" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="143" spans="1:11">
       <c r="A143" s="10">
         <v>44080</v>
       </c>
@@ -25171,7 +25213,7 @@
         <v>4498</v>
       </c>
     </row>
-    <row r="144" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="144" spans="1:11">
       <c r="A144" s="10">
         <v>44087</v>
       </c>
@@ -25206,7 +25248,7 @@
         <v>4225</v>
       </c>
     </row>
-    <row r="145" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="145" spans="1:11">
       <c r="A145" s="10">
         <v>44094</v>
       </c>
@@ -25241,7 +25283,7 @@
         <v>4242</v>
       </c>
     </row>
-    <row r="146" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="146" spans="1:11">
       <c r="A146" s="10">
         <v>44101</v>
       </c>
@@ -25276,7 +25318,7 @@
         <v>4340</v>
       </c>
     </row>
-    <row r="147" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="147" spans="1:11">
       <c r="A147" s="10">
         <v>44108</v>
       </c>
@@ -25311,7 +25353,7 @@
         <v>4375</v>
       </c>
     </row>
-    <row r="148" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="148" spans="1:11">
       <c r="A148" s="10">
         <v>44115</v>
       </c>
@@ -25346,7 +25388,7 @@
         <v>4297</v>
       </c>
     </row>
-    <row r="149" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="149" spans="1:11">
       <c r="A149" s="10">
         <v>44122</v>
       </c>
@@ -25381,7 +25423,7 @@
         <v>4957</v>
       </c>
     </row>
-    <row r="150" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="150" spans="1:11">
       <c r="A150" s="10">
         <v>44129</v>
       </c>
@@ -25416,7 +25458,7 @@
         <v>5696</v>
       </c>
     </row>
-    <row r="151" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="151" spans="1:11">
       <c r="A151" s="10">
         <v>44136</v>
       </c>
@@ -25451,7 +25493,7 @@
         <v>6193</v>
       </c>
     </row>
-    <row r="152" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="152" spans="1:11">
       <c r="A152" s="10">
         <v>44143</v>
       </c>
@@ -25486,7 +25528,7 @@
         <v>6336</v>
       </c>
     </row>
-    <row r="153" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="153" spans="1:11">
       <c r="A153" s="10">
         <v>44150</v>
       </c>
@@ -25521,7 +25563,7 @@
         <v>6128</v>
       </c>
     </row>
-    <row r="154" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="154" spans="1:11">
       <c r="A154" s="10">
         <v>44157</v>
       </c>
@@ -25556,7 +25598,7 @@
         <v>5805</v>
       </c>
     </row>
-    <row r="155" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="155" spans="1:11">
       <c r="A155" s="10">
         <v>44164</v>
       </c>
@@ -25591,7 +25633,7 @@
         <v>6359</v>
       </c>
     </row>
-    <row r="156" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="156" spans="1:11">
       <c r="A156" s="10">
         <v>44171</v>
       </c>
@@ -25626,7 +25668,7 @@
         <v>6501</v>
       </c>
     </row>
-    <row r="157" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="157" spans="1:11">
       <c r="A157" s="10">
         <v>44178</v>
       </c>
@@ -25661,7 +25703,7 @@
         <v>6639</v>
       </c>
     </row>
-    <row r="158" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="158" spans="1:11">
       <c r="A158" s="10">
         <v>44185</v>
       </c>
@@ -25696,7 +25738,7 @@
         <v>6623</v>
       </c>
     </row>
-    <row r="159" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="159" spans="1:11">
       <c r="A159" s="10">
         <v>44192</v>
       </c>
@@ -25731,7 +25773,7 @@
         <v>6235</v>
       </c>
     </row>
-    <row r="160" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="160" spans="1:11">
       <c r="A160" s="10">
         <v>44199</v>
       </c>
@@ -25766,7 +25808,7 @@
         <v>6313</v>
       </c>
     </row>
-    <row r="161" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="161" spans="1:11">
       <c r="A161" s="10">
         <v>44206</v>
       </c>
@@ -25801,7 +25843,7 @@
         <v>5714</v>
       </c>
     </row>
-    <row r="162" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="162" spans="1:11">
       <c r="A162" s="10">
         <v>44213</v>
       </c>
@@ -25836,7 +25878,7 @@
         <v>4512</v>
       </c>
     </row>
-    <row r="163" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="163" spans="1:11">
       <c r="A163" s="10">
         <v>44220</v>
       </c>
@@ -25871,7 +25913,7 @@
         <v>4555</v>
       </c>
     </row>
-    <row r="164" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="164" spans="1:11">
       <c r="A164" s="10">
         <v>44227</v>
       </c>
@@ -25906,7 +25948,7 @@
         <v>5245</v>
       </c>
     </row>
-    <row r="165" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="165" spans="1:11">
       <c r="A165" s="10">
         <v>44234</v>
       </c>
@@ -25941,7 +25983,7 @@
         <v>5649</v>
       </c>
     </row>
-    <row r="166" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="166" spans="1:11">
       <c r="A166" s="10">
         <v>44241</v>
       </c>
@@ -25976,7 +26018,7 @@
         <v>6333</v>
       </c>
     </row>
-    <row r="167" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="167" spans="1:11">
       <c r="A167" s="10">
         <v>44248</v>
       </c>
@@ -26011,7 +26053,7 @@
         <v>4242</v>
       </c>
     </row>
-    <row r="168" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="168" spans="1:11">
       <c r="A168" s="10">
         <v>44255</v>
       </c>
@@ -26046,7 +26088,7 @@
         <v>4791</v>
       </c>
     </row>
-    <row r="169" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="169" spans="1:11">
       <c r="A169" s="10">
         <v>44262</v>
       </c>
@@ -26081,7 +26123,7 @@
         <v>4641</v>
       </c>
     </row>
-    <row r="170" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="170" spans="1:11">
       <c r="A170" s="10">
         <v>44269</v>
       </c>
@@ -26116,7 +26158,7 @@
         <v>4365</v>
       </c>
     </row>
-    <row r="171" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="171" spans="1:11">
       <c r="A171" s="10">
         <v>44276</v>
       </c>
@@ -26151,7 +26193,7 @@
         <v>4549</v>
       </c>
     </row>
-    <row r="172" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="172" spans="1:11">
       <c r="A172" s="10">
         <v>44283</v>
       </c>
@@ -26186,7 +26228,7 @@
         <v>4728</v>
       </c>
     </row>
-    <row r="173" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="173" spans="1:11">
       <c r="A173" s="10">
         <v>44290</v>
       </c>
@@ -26221,7 +26263,7 @@
         <v>5485</v>
       </c>
     </row>
-    <row r="174" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="174" spans="1:11">
       <c r="A174" s="10">
         <v>44297</v>
       </c>
@@ -26256,7 +26298,7 @@
         <v>6192</v>
       </c>
     </row>
-    <row r="175" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="175" spans="1:11">
       <c r="A175" s="10">
         <v>44304</v>
       </c>
@@ -26291,7 +26333,7 @@
         <v>5842</v>
       </c>
     </row>
-    <row r="176" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="176" spans="1:11">
       <c r="A176" s="10">
         <v>44311</v>
       </c>
@@ -26326,7 +26368,7 @@
         <v>6366</v>
       </c>
     </row>
-    <row r="177" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="177" spans="1:11">
       <c r="A177" s="10">
         <v>44318</v>
       </c>
@@ -26361,7 +26403,7 @@
         <v>6907</v>
       </c>
     </row>
-    <row r="178" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="178" spans="1:11">
       <c r="A178" s="10">
         <v>44325</v>
       </c>
@@ -26396,7 +26438,7 @@
         <v>6230</v>
       </c>
     </row>
-    <row r="179" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="179" spans="1:11">
       <c r="A179" s="10">
         <v>44332</v>
       </c>
@@ -26431,7 +26473,7 @@
         <v>6092</v>
       </c>
     </row>
-    <row r="180" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="180" spans="1:11">
       <c r="A180" s="10">
         <v>44339</v>
       </c>
@@ -26466,7 +26508,7 @@
         <v>6452</v>
       </c>
     </row>
-    <row r="181" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="181" spans="1:11">
       <c r="A181" s="10">
         <v>44346</v>
       </c>
@@ -26501,7 +26543,7 @@
         <v>5834</v>
       </c>
     </row>
-    <row r="182" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="182" spans="1:11">
       <c r="A182" s="10">
         <v>44353</v>
       </c>
@@ -26536,7 +26578,7 @@
         <v>5722</v>
       </c>
     </row>
-    <row r="183" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="183" spans="1:11">
       <c r="A183" s="10">
         <v>44360</v>
       </c>
@@ -26571,7 +26613,7 @@
         <v>5443</v>
       </c>
     </row>
-    <row r="184" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="184" spans="1:11">
       <c r="A184" s="10">
         <v>44367</v>
       </c>
@@ -26606,7 +26648,7 @@
         <v>4973</v>
       </c>
     </row>
-    <row r="185" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="185" spans="1:11">
       <c r="A185" s="10">
         <v>44374</v>
       </c>
@@ -26641,7 +26683,7 @@
         <v>5258</v>
       </c>
     </row>
-    <row r="186" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="186" spans="1:11">
       <c r="A186" s="10">
         <v>44381</v>
       </c>
@@ -26676,7 +26718,7 @@
         <v>5338</v>
       </c>
     </row>
-    <row r="187" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="187" spans="1:11">
       <c r="A187" s="10">
         <v>44388</v>
       </c>
@@ -26711,7 +26753,7 @@
         <v>5987</v>
       </c>
     </row>
-    <row r="188" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="188" spans="1:11">
       <c r="A188" s="10">
         <v>44395</v>
       </c>
@@ -26746,7 +26788,7 @@
         <v>5801</v>
       </c>
     </row>
-    <row r="189" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="189" spans="1:11">
       <c r="A189" s="10">
         <v>44402</v>
       </c>
@@ -26781,7 +26823,7 @@
         <v>5421</v>
       </c>
     </row>
-    <row r="190" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="190" spans="1:11">
       <c r="A190" s="10">
         <v>44409</v>
       </c>
@@ -26816,7 +26858,7 @@
         <v>5883</v>
       </c>
     </row>
-    <row r="191" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="191" spans="1:11">
       <c r="A191" s="10">
         <v>44416</v>
       </c>
@@ -26851,7 +26893,7 @@
         <v>5967</v>
       </c>
     </row>
-    <row r="192" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="192" spans="1:11">
       <c r="A192" s="10">
         <v>44423</v>
       </c>
@@ -26886,7 +26928,7 @@
         <v>6015</v>
       </c>
     </row>
-    <row r="193" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="193" spans="1:11">
       <c r="A193" s="10">
         <v>44430</v>
       </c>
@@ -26921,7 +26963,7 @@
         <v>6147</v>
       </c>
     </row>
-    <row r="194" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="194" spans="1:11">
       <c r="A194" s="10">
         <v>44437</v>
       </c>
@@ -26956,7 +26998,7 @@
         <v>7552</v>
       </c>
     </row>
-    <row r="195" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="195" spans="1:11">
       <c r="A195" s="10">
         <v>44444</v>
       </c>
@@ -26991,7 +27033,7 @@
         <v>8099</v>
       </c>
     </row>
-    <row r="196" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="196" spans="1:11">
       <c r="A196" s="10">
         <v>44451</v>
       </c>
@@ -27026,7 +27068,7 @@
         <v>8281</v>
       </c>
     </row>
-    <row r="197" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="197" spans="1:11">
       <c r="A197" s="10">
         <v>44458</v>
       </c>
@@ -27061,7 +27103,7 @@
         <v>9021</v>
       </c>
     </row>
-    <row r="198" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="198" spans="1:11">
       <c r="A198" s="10">
         <v>44465</v>
       </c>
@@ -27096,7 +27138,7 @@
         <v>9364</v>
       </c>
     </row>
-    <row r="199" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="199" spans="1:11">
       <c r="A199" s="10">
         <v>44472</v>
       </c>
@@ -27131,7 +27173,7 @@
         <v>9090</v>
       </c>
     </row>
-    <row r="200" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="200" spans="1:11">
       <c r="A200" s="10">
         <v>44479</v>
       </c>
@@ -27166,7 +27208,7 @@
         <v>8936</v>
       </c>
     </row>
-    <row r="201" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="201" spans="1:11">
       <c r="A201" s="10">
         <v>44486</v>
       </c>
@@ -27201,7 +27243,7 @@
         <v>8252</v>
       </c>
     </row>
-    <row r="202" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="202" spans="1:11">
       <c r="A202" s="10">
         <v>44493</v>
       </c>
@@ -27236,7 +27278,7 @@
         <v>8513</v>
       </c>
     </row>
-    <row r="203" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="203" spans="1:11">
       <c r="A203" s="10">
         <v>44500</v>
       </c>
@@ -27271,7 +27313,7 @@
         <v>8569</v>
       </c>
     </row>
-    <row r="204" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="204" spans="1:11">
       <c r="A204" s="10">
         <v>44507</v>
       </c>
@@ -27306,7 +27348,7 @@
         <v>10146</v>
       </c>
     </row>
-    <row r="205" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="205" spans="1:11">
       <c r="A205" s="10">
         <v>44514</v>
       </c>
@@ -27341,7 +27383,7 @@
         <v>9833</v>
       </c>
     </row>
-    <row r="206" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="206" spans="1:11">
       <c r="A206" s="10">
         <v>44521</v>
       </c>
@@ -27376,7 +27418,7 @@
         <v>10713</v>
       </c>
     </row>
-    <row r="207" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="207" spans="1:11">
       <c r="A207" s="10">
         <v>44528</v>
       </c>
@@ -27411,7 +27453,7 @@
         <v>10672</v>
       </c>
     </row>
-    <row r="208" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="208" spans="1:11">
       <c r="A208" s="10">
         <v>44535</v>
       </c>
@@ -27446,7 +27488,7 @@
         <v>11408</v>
       </c>
     </row>
-    <row r="209" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="209" spans="1:11">
       <c r="A209" s="10">
         <v>44542</v>
       </c>
@@ -27481,7 +27523,7 @@
         <v>12068</v>
       </c>
     </row>
-    <row r="210" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="210" spans="1:11">
       <c r="A210" s="10">
         <v>44549</v>
       </c>
@@ -27516,7 +27558,7 @@
         <v>10758</v>
       </c>
     </row>
-    <row r="211" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="211" spans="1:11">
       <c r="A211" s="10">
         <v>44556</v>
       </c>
@@ -27551,7 +27593,7 @@
         <v>10247</v>
       </c>
     </row>
-    <row r="212" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="212" spans="1:11">
       <c r="A212" s="10">
         <v>44563</v>
       </c>
@@ -27586,7 +27628,7 @@
         <v>9786</v>
       </c>
     </row>
-    <row r="213" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="213" spans="1:11">
       <c r="A213" s="10">
         <v>44570</v>
       </c>
@@ -27621,7 +27663,7 @@
         <v>8461</v>
       </c>
     </row>
-    <row r="214" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="214" spans="1:11">
       <c r="A214" s="10">
         <v>44577</v>
       </c>
@@ -27656,7 +27698,7 @@
         <v>6933</v>
       </c>
     </row>
-    <row r="215" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="215" spans="1:11">
       <c r="A215" s="10">
         <v>44584</v>
       </c>
@@ -27691,7 +27733,7 @@
         <v>7524</v>
       </c>
     </row>
-    <row r="216" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="216" spans="1:11">
       <c r="A216" s="10">
         <v>44591</v>
       </c>
@@ -27726,7 +27768,7 @@
         <v>7909</v>
       </c>
     </row>
-    <row r="217" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="217" spans="1:11">
       <c r="A217" s="10">
         <v>44598</v>
       </c>
@@ -27761,7 +27803,7 @@
         <v>6947</v>
       </c>
     </row>
-    <row r="218" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="218" spans="1:11">
       <c r="A218" s="10">
         <v>44605</v>
       </c>
@@ -27796,7 +27838,7 @@
         <v>6615</v>
       </c>
     </row>
-    <row r="219" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="219" spans="1:11">
       <c r="A219" s="10">
         <v>44612</v>
       </c>
@@ -27831,7 +27873,7 @@
         <v>6659</v>
       </c>
     </row>
-    <row r="220" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="220" spans="1:11">
       <c r="A220" s="10">
         <v>44619</v>
       </c>
@@ -27866,7 +27908,7 @@
         <v>6470</v>
       </c>
     </row>
-    <row r="221" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="221" spans="1:11">
       <c r="A221" s="10">
         <v>44626</v>
       </c>
@@ -27901,7 +27943,7 @@
         <v>5896</v>
       </c>
     </row>
-    <row r="222" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="222" spans="1:11">
       <c r="A222" s="10">
         <v>44633</v>
       </c>
@@ -27936,7 +27978,7 @@
         <v>7688</v>
       </c>
     </row>
-    <row r="223" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="223" spans="1:11">
       <c r="A223" s="10">
         <v>44640</v>
       </c>
@@ -27971,7 +28013,7 @@
         <v>7591</v>
       </c>
     </row>
-    <row r="224" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="224" spans="1:11">
       <c r="A224" s="10">
         <v>44647</v>
       </c>
@@ -28006,7 +28048,7 @@
         <v>7550</v>
       </c>
     </row>
-    <row r="225" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="225" spans="1:11">
       <c r="A225" s="10">
         <v>44654</v>
       </c>
@@ -28041,7 +28083,7 @@
         <v>8345</v>
       </c>
     </row>
-    <row r="226" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="226" spans="1:11">
       <c r="A226" s="10">
         <v>44661</v>
       </c>
@@ -28076,7 +28118,7 @@
         <v>8476</v>
       </c>
     </row>
-    <row r="227" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="227" spans="1:11">
       <c r="A227" s="10">
         <v>44668</v>
       </c>
@@ -28111,7 +28153,7 @@
         <v>7813</v>
       </c>
     </row>
-    <row r="228" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="228" spans="1:11">
       <c r="A228" s="10">
         <v>44675</v>
       </c>
@@ -28146,7 +28188,7 @@
         <v>8281</v>
       </c>
     </row>
-    <row r="229" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="229" spans="1:11">
       <c r="A229" s="10">
         <v>44682</v>
       </c>
@@ -28181,7 +28223,7 @@
         <v>7753</v>
       </c>
     </row>
-    <row r="230" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="230" spans="1:11">
       <c r="A230" s="10">
         <v>44689</v>
       </c>
@@ -28216,7 +28258,7 @@
         <v>7190</v>
       </c>
     </row>
-    <row r="231" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="231" spans="1:11">
       <c r="A231" s="10">
         <v>44696</v>
       </c>
@@ -28251,7 +28293,7 @@
         <v>7186</v>
       </c>
     </row>
-    <row r="232" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="232" spans="1:11">
       <c r="A232" s="10">
         <v>44703</v>
       </c>
@@ -28286,7 +28328,7 @@
         <v>7538</v>
       </c>
     </row>
-    <row r="233" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="233" spans="1:11">
       <c r="A233" s="10">
         <v>44710</v>
       </c>
@@ -28321,7 +28363,7 @@
         <v>7571</v>
       </c>
     </row>
-    <row r="234" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="234" spans="1:11">
       <c r="A234" s="10">
         <v>44717</v>
       </c>
@@ -28356,7 +28398,7 @@
         <v>7788</v>
       </c>
     </row>
-    <row r="235" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="235" spans="1:11">
       <c r="A235" s="10">
         <v>44724</v>
       </c>
@@ -28391,7 +28433,7 @@
         <v>7523</v>
       </c>
     </row>
-    <row r="236" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="236" spans="1:11">
       <c r="A236" s="10">
         <v>44731</v>
       </c>
@@ -28426,7 +28468,7 @@
         <v>7309</v>
       </c>
     </row>
-    <row r="237" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="237" spans="1:11">
       <c r="A237" s="10">
         <v>44738</v>
       </c>
@@ -28461,7 +28503,7 @@
         <v>7312</v>
       </c>
     </row>
-    <row r="238" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="238" spans="1:11">
       <c r="A238" s="10">
         <v>44745</v>
       </c>
@@ -28496,7 +28538,7 @@
         <v>7701</v>
       </c>
     </row>
-    <row r="239" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="239" spans="1:11">
       <c r="A239" s="10">
         <v>44752</v>
       </c>
@@ -28531,7 +28573,7 @@
         <v>7311</v>
       </c>
     </row>
-    <row r="240" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="240" spans="1:11">
       <c r="A240" s="10">
         <v>44759</v>
       </c>
@@ -28566,7 +28608,7 @@
         <v>6911</v>
       </c>
     </row>
-    <row r="241" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="241" spans="1:11">
       <c r="A241" s="10">
         <v>44766</v>
       </c>
@@ -28601,7 +28643,7 @@
         <v>6829</v>
       </c>
     </row>
-    <row r="242" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="242" spans="1:11">
       <c r="A242" s="10">
         <v>44773</v>
       </c>
@@ -28636,7 +28678,7 @@
         <v>6597</v>
       </c>
     </row>
-    <row r="243" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="243" spans="1:11">
       <c r="A243" s="10">
         <v>44780</v>
       </c>
@@ -28671,7 +28713,7 @@
         <v>6823</v>
       </c>
     </row>
-    <row r="244" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="244" spans="1:11">
       <c r="A244" s="10">
         <v>44787</v>
       </c>
@@ -28706,7 +28748,7 @@
         <v>6785</v>
       </c>
     </row>
-    <row r="245" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="245" spans="1:11">
       <c r="A245" s="10">
         <v>44794</v>
       </c>
@@ -28741,7 +28783,7 @@
         <v>6948</v>
       </c>
     </row>
-    <row r="246" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="246" spans="1:11">
       <c r="A246" s="10">
         <v>44801</v>
       </c>
@@ -28776,7 +28818,7 @@
         <v>6759</v>
       </c>
     </row>
-    <row r="247" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="247" spans="1:11">
       <c r="A247" s="10">
         <v>44808</v>
       </c>
@@ -28811,7 +28853,7 @@
         <v>6421</v>
       </c>
     </row>
-    <row r="248" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="248" spans="1:11">
       <c r="A248" s="10">
         <v>44815</v>
       </c>
@@ -28846,7 +28888,7 @@
         <v>6562</v>
       </c>
     </row>
-    <row r="249" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="249" spans="1:11">
       <c r="A249" s="10">
         <v>44822</v>
       </c>
@@ -28881,7 +28923,7 @@
         <v>6719</v>
       </c>
     </row>
-    <row r="250" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="250" spans="1:11">
       <c r="A250" s="10">
         <v>44829</v>
       </c>
@@ -28916,7 +28958,7 @@
         <v>6157</v>
       </c>
     </row>
-    <row r="251" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="251" spans="1:11">
       <c r="A251" s="10">
         <v>44836</v>
       </c>
@@ -28951,7 +28993,7 @@
         <v>5844</v>
       </c>
     </row>
-    <row r="252" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="252" spans="1:11">
       <c r="A252" s="10">
         <v>44843</v>
       </c>
@@ -28986,7 +29028,7 @@
         <v>5551</v>
       </c>
     </row>
-    <row r="253" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="253" spans="1:11">
       <c r="A253" s="10">
         <v>44850</v>
       </c>
@@ -29021,7 +29063,7 @@
         <v>5560</v>
       </c>
     </row>
-    <row r="254" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="254" spans="1:11">
       <c r="A254" s="10">
         <v>44857</v>
       </c>
@@ -29056,7 +29098,7 @@
         <v>6090</v>
       </c>
     </row>
-    <row r="255" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="255" spans="1:11">
       <c r="A255" s="10">
         <v>44864</v>
       </c>
@@ -29091,7 +29133,7 @@
         <v>5724</v>
       </c>
     </row>
-    <row r="256" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="256" spans="1:11">
       <c r="A256" s="10">
         <v>44871</v>
       </c>
@@ -29126,7 +29168,7 @@
         <v>5488</v>
       </c>
     </row>
-    <row r="257" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="257" spans="1:11">
       <c r="A257" s="10">
         <v>44878</v>
       </c>
@@ -29161,7 +29203,7 @@
         <v>5118</v>
       </c>
     </row>
-    <row r="258" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="258" spans="1:11">
       <c r="A258" s="10">
         <v>44885</v>
       </c>
@@ -29196,7 +29238,7 @@
         <v>5205</v>
       </c>
     </row>
-    <row r="259" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="259" spans="1:11">
       <c r="A259" s="10">
         <v>44892</v>
       </c>
@@ -29231,7 +29273,7 @@
         <v>5070</v>
       </c>
     </row>
-    <row r="260" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="260" spans="1:11">
       <c r="A260" s="10">
         <v>44899</v>
       </c>
@@ -29266,7 +29308,7 @@
         <v>5242</v>
       </c>
     </row>
-    <row r="261" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="261" spans="1:11">
       <c r="A261" s="10">
         <v>44906</v>
       </c>
@@ -29301,7 +29343,7 @@
         <v>4946</v>
       </c>
     </row>
-    <row r="262" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="262" spans="1:11">
       <c r="A262" s="10">
         <v>44913</v>
       </c>
@@ -29336,7 +29378,7 @@
         <v>5665</v>
       </c>
     </row>
-    <row r="263" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="263" spans="1:11">
       <c r="A263" s="10">
         <v>44920</v>
       </c>
@@ -29371,7 +29413,7 @@
         <v>5702</v>
       </c>
     </row>
-    <row r="264" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="264" spans="1:11">
       <c r="A264" s="10">
         <v>44927</v>
       </c>
@@ -29406,7 +29448,7 @@
         <v>5586</v>
       </c>
     </row>
-    <row r="265" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="265" spans="1:11">
       <c r="A265" s="10">
         <v>44934</v>
       </c>
@@ -29441,7 +29483,7 @@
         <v>5009</v>
       </c>
     </row>
-    <row r="266" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="266" spans="1:11">
       <c r="A266" s="10">
         <v>44941</v>
       </c>
@@ -29476,7 +29518,7 @@
         <v>5141</v>
       </c>
     </row>
-    <row r="267" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="267" spans="1:11">
       <c r="A267" s="10">
         <v>44948</v>
       </c>
@@ -29511,7 +29553,7 @@
         <v>4669</v>
       </c>
     </row>
-    <row r="268" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="268" spans="1:11">
       <c r="A268" s="10">
         <v>44955</v>
       </c>
@@ -29546,7 +29588,7 @@
         <v>4191</v>
       </c>
     </row>
-    <row r="269" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="269" spans="1:11">
       <c r="A269" s="10">
         <v>44962</v>
       </c>
@@ -29581,7 +29623,7 @@
         <v>4595</v>
       </c>
     </row>
-    <row r="270" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="270" spans="1:11">
       <c r="A270" s="10">
         <v>44969</v>
       </c>
@@ -29616,7 +29658,7 @@
         <v>4305</v>
       </c>
     </row>
-    <row r="271" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="271" spans="1:11">
       <c r="A271" s="10">
         <v>44976</v>
       </c>
@@ -29651,7 +29693,7 @@
         <v>4094</v>
       </c>
     </row>
-    <row r="272" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="272" spans="1:11">
       <c r="A272" s="10">
         <v>44983</v>
       </c>
@@ -29686,7 +29728,7 @@
         <v>3701</v>
       </c>
     </row>
-    <row r="273" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="273" spans="1:11">
       <c r="A273" s="10">
         <v>44990</v>
       </c>
@@ -29721,7 +29763,7 @@
         <v>4039</v>
       </c>
     </row>
-    <row r="274" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="274" spans="1:11">
       <c r="A274" s="10">
         <v>44997</v>
       </c>
@@ -29756,7 +29798,7 @@
         <v>4303</v>
       </c>
     </row>
-    <row r="275" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="275" spans="1:11">
       <c r="A275" s="10">
         <v>45004</v>
       </c>
@@ -29791,7 +29833,7 @@
         <v>4582</v>
       </c>
     </row>
-    <row r="276" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="276" spans="1:11">
       <c r="A276" s="10">
         <v>45011</v>
       </c>
@@ -29826,7 +29868,7 @@
         <v>4839</v>
       </c>
     </row>
-    <row r="277" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="277" spans="1:11">
       <c r="A277" s="10">
         <v>45018</v>
       </c>
@@ -29861,7 +29903,7 @@
         <v>4637</v>
       </c>
     </row>
-    <row r="278" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="278" spans="1:11">
       <c r="A278" s="10">
         <v>45025</v>
       </c>
@@ -29896,7 +29938,7 @@
         <v>4417</v>
       </c>
     </row>
-    <row r="279" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="279" spans="1:11">
       <c r="A279" s="10">
         <v>45032</v>
       </c>
@@ -29931,7 +29973,7 @@
         <v>4183</v>
       </c>
     </row>
-    <row r="280" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="280" spans="1:11">
       <c r="A280" s="10">
         <v>45039</v>
       </c>
@@ -29966,7 +30008,7 @@
         <v>4090</v>
       </c>
     </row>
-    <row r="281" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="281" spans="1:11">
       <c r="A281" s="10">
         <v>45046</v>
       </c>
@@ -30001,7 +30043,7 @@
         <v>3995</v>
       </c>
     </row>
-    <row r="282" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="282" spans="1:11">
       <c r="A282" s="10">
         <v>45053</v>
       </c>
@@ -30036,7 +30078,7 @@
         <v>3623</v>
       </c>
     </row>
-    <row r="283" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="283" spans="1:11">
       <c r="A283" s="10">
         <v>45060</v>
       </c>
@@ -30071,7 +30113,7 @@
         <v>3519</v>
       </c>
     </row>
-    <row r="284" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="284" spans="1:11">
       <c r="A284" s="10">
         <v>45067</v>
       </c>
@@ -30106,7 +30148,7 @@
         <v>3513</v>
       </c>
     </row>
-    <row r="285" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="285" spans="1:11">
       <c r="A285" s="10">
         <v>45074</v>
       </c>
@@ -30141,7 +30183,7 @@
         <v>3501</v>
       </c>
     </row>
-    <row r="286" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="286" spans="1:11">
       <c r="A286" s="10">
         <v>45081</v>
       </c>
@@ -30176,7 +30218,7 @@
         <v>3441</v>
       </c>
     </row>
-    <row r="287" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="287" spans="1:11">
       <c r="A287" s="10">
         <v>45088</v>
       </c>
@@ -30211,7 +30253,7 @@
         <v>3489</v>
       </c>
     </row>
-    <row r="288" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="288" spans="1:11">
       <c r="A288" s="10">
         <v>45095</v>
       </c>
@@ -30246,7 +30288,7 @@
         <v>3524</v>
       </c>
     </row>
-    <row r="289" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="289" spans="1:11">
       <c r="A289" s="10">
         <v>45102</v>
       </c>
@@ -30281,7 +30323,7 @@
         <v>3497</v>
       </c>
     </row>
-    <row r="290" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="290" spans="1:11">
       <c r="A290" s="10">
         <v>45109</v>
       </c>
@@ -30316,7 +30358,7 @@
         <v>3333</v>
       </c>
     </row>
-    <row r="291" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="291" spans="1:11">
       <c r="A291" s="10">
         <v>45116</v>
       </c>
@@ -30351,7 +30393,7 @@
         <v>3428</v>
       </c>
     </row>
-    <row r="292" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="292" spans="1:11">
       <c r="A292" s="10">
         <v>45123</v>
       </c>
@@ -30386,7 +30428,7 @@
         <v>3588</v>
       </c>
     </row>
-    <row r="293" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="293" spans="1:11">
       <c r="A293" s="10">
         <v>45130</v>
       </c>
@@ -30421,7 +30463,7 @@
         <v>3445</v>
       </c>
     </row>
-    <row r="294" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="294" spans="1:11">
       <c r="A294" s="10">
         <v>45137</v>
       </c>
@@ -30456,7 +30498,7 @@
         <v>3453</v>
       </c>
     </row>
-    <row r="295" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="295" spans="1:11">
       <c r="A295" s="10">
         <v>45144</v>
       </c>
@@ -30491,7 +30533,7 @@
         <v>3501</v>
       </c>
     </row>
-    <row r="296" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="296" spans="1:11">
       <c r="A296" s="10">
         <v>45151</v>
       </c>
@@ -30526,7 +30568,7 @@
         <v>3579</v>
       </c>
     </row>
-    <row r="297" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="297" spans="1:11">
       <c r="A297" s="10">
         <v>45158</v>
       </c>
@@ -30561,7 +30603,7 @@
         <v>3584</v>
       </c>
     </row>
-    <row r="298" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="298" spans="1:11">
       <c r="A298" s="10">
         <v>45165</v>
       </c>
@@ -30596,7 +30638,7 @@
         <v>3591</v>
       </c>
     </row>
-    <row r="299" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="299" spans="1:11">
       <c r="A299" s="10">
         <v>45172</v>
       </c>
@@ -30631,7 +30673,7 @@
         <v>3526</v>
       </c>
     </row>
-    <row r="300" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="300" spans="1:11">
       <c r="A300" s="10">
         <v>45179</v>
       </c>
@@ -30666,7 +30708,7 @@
         <v>3715</v>
       </c>
     </row>
-    <row r="301" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="301" spans="1:11">
       <c r="A301" s="10">
         <v>45186</v>
       </c>
@@ -30701,7 +30743,7 @@
         <v>3765</v>
       </c>
     </row>
-    <row r="302" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="302" spans="1:11">
       <c r="A302" s="10">
         <v>45193</v>
       </c>
@@ -30736,7 +30778,7 @@
         <v>3987</v>
       </c>
     </row>
-    <row r="303" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="303" spans="1:11">
       <c r="A303" s="10">
         <v>45200</v>
       </c>
@@ -30771,7 +30813,7 @@
         <v>4197</v>
       </c>
     </row>
-    <row r="304" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="304" spans="1:11">
       <c r="A304" s="10">
         <v>45207</v>
       </c>
@@ -30806,7 +30848,7 @@
         <v>4308</v>
       </c>
     </row>
-    <row r="305" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="305" spans="1:11">
       <c r="A305" s="10">
         <v>45214</v>
       </c>
@@ -30841,7 +30883,7 @@
         <v>4268</v>
       </c>
     </row>
-    <row r="306" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="306" spans="1:11">
       <c r="A306" s="10">
         <v>45221</v>
       </c>
@@ -30876,7 +30918,7 @@
         <v>4444</v>
       </c>
     </row>
-    <row r="307" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="307" spans="1:11">
       <c r="A307" s="10">
         <v>45228</v>
       </c>
@@ -30911,7 +30953,7 @@
         <v>4465</v>
       </c>
     </row>
-    <row r="308" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="308" spans="1:11">
       <c r="A308" s="10">
         <v>45235</v>
       </c>
@@ -30946,7 +30988,7 @@
         <v>4486</v>
       </c>
     </row>
-    <row r="309" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="309" spans="1:11">
       <c r="A309" s="10">
         <v>45242</v>
       </c>
@@ -30981,7 +31023,7 @@
         <v>4878</v>
       </c>
     </row>
-    <row r="310" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="310" spans="1:11">
       <c r="A310" s="10">
         <v>45249</v>
       </c>
@@ -31016,7 +31058,7 @@
         <v>5136</v>
       </c>
     </row>
-    <row r="311" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="311" spans="1:11">
       <c r="A311" s="10">
         <v>45256</v>
       </c>
@@ -31051,7 +31093,7 @@
         <v>5562</v>
       </c>
     </row>
-    <row r="312" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="312" spans="1:11">
       <c r="A312" s="10">
         <v>45263</v>
       </c>
@@ -31086,7 +31128,7 @@
         <v>5625</v>
       </c>
     </row>
-    <row r="313" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="313" spans="1:11">
       <c r="A313" s="10">
         <v>45270</v>
       </c>
@@ -31121,7 +31163,7 @@
         <v>5859</v>
       </c>
     </row>
-    <row r="314" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="314" spans="1:11">
       <c r="A314" s="10">
         <v>45277</v>
       </c>
@@ -31156,7 +31198,7 @@
         <v>5680</v>
       </c>
     </row>
-    <row r="315" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="315" spans="1:11">
       <c r="A315" s="10">
         <v>45284</v>
       </c>
@@ -31191,7 +31233,7 @@
         <v>5680</v>
       </c>
     </row>
-    <row r="316" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="316" spans="1:11">
       <c r="A316" s="10">
         <v>45291</v>
       </c>
@@ -31226,7 +31268,7 @@
         <v>3893</v>
       </c>
     </row>
-    <row r="317" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="317" spans="1:11">
       <c r="A317" s="10">
         <v>45298</v>
       </c>
@@ -31261,7 +31303,7 @@
         <v>3609</v>
       </c>
     </row>
-    <row r="318" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="318" spans="1:11">
       <c r="A318" s="10">
         <v>45305</v>
       </c>
@@ -31296,7 +31338,7 @@
         <v>3632</v>
       </c>
     </row>
-    <row r="319" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="319" spans="1:11">
       <c r="A319" s="10">
         <v>45312</v>
       </c>
@@ -31331,7 +31373,7 @@
         <v>3772</v>
       </c>
     </row>
-    <row r="320" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="320" spans="1:11">
       <c r="A320" s="10">
         <v>45319</v>
       </c>
@@ -31366,7 +31408,7 @@
         <v>4103</v>
       </c>
     </row>
-    <row r="321" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="321" spans="1:11">
       <c r="A321" s="10">
         <v>45326</v>
       </c>
@@ -31401,7 +31443,7 @@
         <v>4283</v>
       </c>
     </row>
-    <row r="322" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="322" spans="1:11">
       <c r="A322" s="10">
         <v>45333</v>
       </c>
@@ -31436,7 +31478,7 @@
         <v>4375</v>
       </c>
     </row>
-    <row r="323" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="323" spans="1:11">
       <c r="A323" s="10">
         <v>45340</v>
       </c>
@@ -31471,7 +31513,7 @@
         <v>3871</v>
       </c>
     </row>
-    <row r="324" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="324" spans="1:11">
       <c r="A324" s="10">
         <v>45347</v>
       </c>
@@ -31506,7 +31548,7 @@
         <v>3455</v>
       </c>
     </row>
-    <row r="325" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="325" spans="1:11">
       <c r="A325" s="10">
         <v>45354</v>
       </c>
@@ -31541,7 +31583,7 @@
         <v>3638</v>
       </c>
     </row>
-    <row r="326" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="326" spans="1:11">
       <c r="A326" s="10">
         <v>45361</v>
       </c>
@@ -31576,7 +31618,7 @@
         <v>3888</v>
       </c>
     </row>
-    <row r="327" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="327" spans="1:11">
       <c r="A327" s="10">
         <v>45368</v>
       </c>
@@ -31611,7 +31653,7 @@
         <v>4235</v>
       </c>
     </row>
-    <row r="328" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="328" spans="1:11">
       <c r="A328" s="10">
         <v>45375</v>
       </c>
@@ -31646,7 +31688,7 @@
         <v>4396</v>
       </c>
     </row>
-    <row r="329" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="329" spans="1:11">
       <c r="A329" s="10">
         <v>45382</v>
       </c>
@@ -31681,7 +31723,7 @@
         <v>4400</v>
       </c>
     </row>
-    <row r="330" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="330" spans="1:11">
       <c r="A330" s="10">
         <v>45389</v>
       </c>
@@ -31716,7 +31758,7 @@
         <v>4447</v>
       </c>
     </row>
-    <row r="331" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="331" spans="1:11">
       <c r="A331" s="10">
         <v>45396</v>
       </c>
@@ -31751,7 +31793,7 @@
         <v>4472</v>
       </c>
     </row>
-    <row r="332" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="332" spans="1:11">
       <c r="A332" s="10">
         <v>45403</v>
       </c>
@@ -31786,7 +31828,7 @@
         <v>4580</v>
       </c>
     </row>
-    <row r="333" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="333" spans="1:11">
       <c r="A333" s="10">
         <v>45410</v>
       </c>
@@ -31821,7 +31863,7 @@
         <v>4632</v>
       </c>
     </row>
-    <row r="334" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="334" spans="1:11">
       <c r="A334" s="10">
         <v>45417</v>
       </c>
@@ -31856,7 +31898,7 @@
         <v>4708</v>
       </c>
     </row>
-    <row r="335" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="335" spans="1:11">
       <c r="A335" s="10">
         <v>45424</v>
       </c>
@@ -31891,7 +31933,7 @@
         <v>4710</v>
       </c>
     </row>
-    <row r="336" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="336" spans="1:11">
       <c r="A336" s="10">
         <v>45431</v>
       </c>
@@ -31926,7 +31968,7 @@
         <v>4881</v>
       </c>
     </row>
-    <row r="337" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="337" spans="1:11">
       <c r="A337" s="10">
         <v>45438</v>
       </c>
@@ -31961,7 +32003,7 @@
         <v>4955</v>
       </c>
     </row>
-    <row r="338" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="338" spans="1:11">
       <c r="A338" s="10">
         <v>45445</v>
       </c>
@@ -31996,7 +32038,7 @@
         <v>4865</v>
       </c>
     </row>
-    <row r="339" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="339" spans="1:11">
       <c r="A339" s="10">
         <v>45452</v>
       </c>
@@ -32031,7 +32073,7 @@
         <v>4808</v>
       </c>
     </row>
-    <row r="340" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="340" spans="1:11">
       <c r="A340" s="10">
         <v>45459</v>
       </c>
@@ -32066,7 +32108,7 @@
         <v>4783</v>
       </c>
     </row>
-    <row r="341" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="341" spans="1:11">
       <c r="A341" s="10">
         <v>45466</v>
       </c>
@@ -32101,7 +32143,7 @@
         <v>4757</v>
       </c>
     </row>
-    <row r="342" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="342" spans="1:11">
       <c r="A342" s="10">
         <v>45473</v>
       </c>
@@ -32136,7 +32178,7 @@
         <v>4736</v>
       </c>
     </row>
-    <row r="343" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="343" spans="1:11">
       <c r="A343" s="10">
         <v>45480</v>
       </c>
@@ -32171,7 +32213,7 @@
         <v>4879</v>
       </c>
     </row>
-    <row r="344" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="344" spans="1:11">
       <c r="A344" s="10">
         <v>45487</v>
       </c>
@@ -32206,7 +32248,7 @@
         <v>4737</v>
       </c>
     </row>
-    <row r="345" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="345" spans="1:11">
       <c r="A345" s="10">
         <v>45494</v>
       </c>
@@ -32241,7 +32283,7 @@
         <v>4594</v>
       </c>
     </row>
-    <row r="346" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="346" spans="1:11">
       <c r="A346" s="10">
         <v>45501</v>
       </c>
@@ -32276,7 +32318,7 @@
         <v>4598</v>
       </c>
     </row>
-    <row r="347" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="347" spans="1:11">
       <c r="A347" s="10">
         <v>45508</v>
       </c>
@@ -32311,7 +32353,7 @@
         <v>4565</v>
       </c>
     </row>
-    <row r="348" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="348" spans="1:11">
       <c r="A348" s="10">
         <v>45515</v>
       </c>
@@ -32346,7 +32388,7 @@
         <v>4647</v>
       </c>
     </row>
-    <row r="349" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="349" spans="1:11">
       <c r="A349" s="10">
         <v>45522</v>
       </c>
@@ -32381,7 +32423,7 @@
         <v>4591</v>
       </c>
     </row>
-    <row r="350" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="350" spans="1:11">
       <c r="A350" s="10">
         <v>45529</v>
       </c>
@@ -32416,7 +32458,7 @@
         <v>4788</v>
       </c>
     </row>
-    <row r="351" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="351" spans="1:11">
       <c r="A351" s="10">
         <v>45536</v>
       </c>
@@ -32451,7 +32493,7 @@
         <v>4920</v>
       </c>
     </row>
-    <row r="352" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="352" spans="1:11">
       <c r="A352" s="10">
         <v>45543</v>
       </c>
@@ -32486,7 +32528,7 @@
         <v>4829</v>
       </c>
     </row>
-    <row r="353" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="353" spans="1:11">
       <c r="A353" s="10">
         <v>45550</v>
       </c>
@@ -32521,7 +32563,7 @@
         <v>4815</v>
       </c>
     </row>
-    <row r="354" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="354" spans="1:11">
       <c r="A354" s="10">
         <v>45557</v>
       </c>
@@ -32556,7 +32598,7 @@
         <v>4837</v>
       </c>
     </row>
-    <row r="355" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="355" spans="1:11">
       <c r="A355" s="10">
         <v>45564</v>
       </c>
@@ -32591,7 +32633,7 @@
         <v>5053</v>
       </c>
     </row>
-    <row r="356" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="356" spans="1:11">
       <c r="A356" s="10">
         <v>45571</v>
       </c>
@@ -32626,7 +32668,7 @@
         <v>4879</v>
       </c>
     </row>
-    <row r="357" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="357" spans="1:11">
       <c r="A357" s="10">
         <v>45578</v>
       </c>
@@ -32661,7 +32703,7 @@
         <v>4831</v>
       </c>
     </row>
-    <row r="358" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="358" spans="1:11">
       <c r="A358" s="10">
         <v>45585</v>
       </c>
@@ -32696,7 +32738,7 @@
         <v>5006</v>
       </c>
     </row>
-    <row r="359" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="359" spans="1:11">
       <c r="A359" s="10">
         <v>45592</v>
       </c>
@@ -32731,7 +32773,7 @@
         <v>5190</v>
       </c>
     </row>
-    <row r="360" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="360" spans="1:11">
       <c r="A360" s="10">
         <v>45599</v>
       </c>
@@ -32766,7 +32808,7 @@
         <v>5493</v>
       </c>
     </row>
-    <row r="361" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="361" spans="1:11">
       <c r="A361" s="10">
         <v>45606</v>
       </c>
@@ -32801,7 +32843,7 @@
         <v>5494</v>
       </c>
     </row>
-    <row r="362" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="362" spans="1:11">
       <c r="A362" s="10">
         <v>45613</v>
       </c>
@@ -32836,7 +32878,7 @@
         <v>5339</v>
       </c>
     </row>
-    <row r="363" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="363" spans="1:11">
       <c r="A363" s="10">
         <v>45620</v>
       </c>
@@ -32871,7 +32913,7 @@
         <v>5225</v>
       </c>
     </row>
-    <row r="364" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="364" spans="1:11">
       <c r="A364" s="10">
         <v>45627</v>
       </c>
@@ -32906,7 +32948,7 @@
         <v>5585</v>
       </c>
     </row>
-    <row r="365" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="365" spans="1:11">
       <c r="A365" s="10">
         <v>45634</v>
       </c>
@@ -32941,7 +32983,7 @@
         <v>5777</v>
       </c>
     </row>
-    <row r="366" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="366" spans="1:11">
       <c r="A366" s="10">
         <v>45641</v>
       </c>
@@ -32976,7 +33018,7 @@
         <v>5722</v>
       </c>
     </row>
-    <row r="367" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="367" spans="1:11">
       <c r="A367" s="10">
         <v>45648</v>
       </c>
@@ -33011,7 +33053,7 @@
         <v>5327</v>
       </c>
     </row>
-    <row r="368" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="368" spans="1:11">
       <c r="A368" s="10">
         <v>45655</v>
       </c>
@@ -33046,7 +33088,7 @@
         <v>5327</v>
       </c>
     </row>
-    <row r="369" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="369" spans="1:11">
       <c r="A369" s="10">
         <v>45662</v>
       </c>
@@ -33081,7 +33123,7 @@
         <v>4966</v>
       </c>
     </row>
-    <row r="370" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="370" spans="1:11">
       <c r="A370" s="10">
         <v>45669</v>
       </c>
@@ -33116,7 +33158,7 @@
         <v>4484</v>
       </c>
     </row>
-    <row r="371" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="371" spans="1:11">
       <c r="A371" s="10">
         <v>45676</v>
       </c>
@@ -33151,7 +33193,7 @@
         <v>4243</v>
       </c>
     </row>
-    <row r="372" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="372" spans="1:11">
       <c r="A372" s="10">
         <v>45683</v>
       </c>
@@ -33186,7 +33228,7 @@
         <v>4447</v>
       </c>
     </row>
-    <row r="373" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="373" spans="1:11">
       <c r="A373" s="10">
         <v>45690</v>
       </c>
@@ -33221,7 +33263,7 @@
         <v>4327</v>
       </c>
     </row>
-    <row r="374" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="374" spans="1:11">
       <c r="A374" s="10">
         <v>45697</v>
       </c>
@@ -33256,7 +33298,7 @@
         <v>3962</v>
       </c>
     </row>
-    <row r="375" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="375" spans="1:11">
       <c r="A375" s="10">
         <v>45704</v>
       </c>
@@ -33291,7 +33333,7 @@
         <v>4284</v>
       </c>
     </row>
-    <row r="376" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="376" spans="1:11">
       <c r="A376" s="10">
         <v>45711</v>
       </c>
@@ -33326,7 +33368,7 @@
         <v>4127</v>
       </c>
     </row>
-    <row r="377" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="377" spans="1:11">
       <c r="A377" s="10">
         <v>45718</v>
       </c>
@@ -33361,7 +33403,7 @@
         <v>4086</v>
       </c>
     </row>
-    <row r="378" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="378" spans="1:11">
       <c r="A378" s="10">
         <v>45725</v>
       </c>
@@ -33396,7 +33438,7 @@
         <v>4002</v>
       </c>
     </row>
-    <row r="379" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="379" spans="1:11">
       <c r="A379" s="10">
         <v>45732</v>
       </c>
@@ -33431,7 +33473,7 @@
         <v>4218</v>
       </c>
     </row>
-    <row r="380" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="380" spans="1:11">
       <c r="A380" s="10">
         <v>45739</v>
       </c>
@@ -33466,7 +33508,7 @@
         <v>4547</v>
       </c>
     </row>
-    <row r="381" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="381" spans="1:11">
       <c r="A381" s="10">
         <v>45746</v>
       </c>
@@ -33501,7 +33543,7 @@
         <v>4573</v>
       </c>
     </row>
-    <row r="382" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="382" spans="1:11">
       <c r="A382" s="10">
         <v>45753</v>
       </c>
@@ -33536,7 +33578,7 @@
         <v>4689</v>
       </c>
     </row>
-    <row r="383" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="383" spans="1:11">
       <c r="A383" s="10">
         <v>45760</v>
       </c>
@@ -33571,7 +33613,7 @@
         <v>4662</v>
       </c>
     </row>
-    <row r="384" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="384" spans="1:11">
       <c r="A384" s="10">
         <v>45767</v>
       </c>
@@ -33606,7 +33648,7 @@
         <v>4697</v>
       </c>
     </row>
-    <row r="385" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="385" spans="1:11">
       <c r="A385" s="10">
         <v>45774</v>
       </c>
@@ -33641,7 +33683,7 @@
         <v>4411</v>
       </c>
     </row>
-    <row r="386" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="386" spans="1:11">
       <c r="A386" s="10">
         <v>45781</v>
       </c>
@@ -33676,7 +33718,7 @@
         <v>4304</v>
       </c>
     </row>
-    <row r="387" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="387" spans="1:11">
       <c r="A387" s="10">
         <v>45788</v>
       </c>
@@ -33711,7 +33753,7 @@
         <v>4343</v>
       </c>
     </row>
-    <row r="388" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="388" spans="1:11">
       <c r="A388" s="10">
         <v>45795</v>
       </c>
@@ -33746,7 +33788,7 @@
         <v>4190</v>
       </c>
     </row>
-    <row r="389" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="389" spans="1:11">
       <c r="A389" s="10">
         <v>45802</v>
       </c>
@@ -33781,7 +33823,7 @@
         <v>4444</v>
       </c>
     </row>
-    <row r="390" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="390" spans="1:11">
       <c r="A390" s="10">
         <v>45809</v>
       </c>
@@ -33816,7 +33858,7 @@
         <v>4607</v>
       </c>
     </row>
-    <row r="391" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="391" spans="1:11">
       <c r="A391" s="10">
         <v>45816</v>
       </c>
@@ -33851,7 +33893,7 @@
         <v>4567</v>
       </c>
     </row>
-    <row r="392" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="392" spans="1:11">
       <c r="A392" s="10">
         <v>45823</v>
       </c>
@@ -33886,7 +33928,7 @@
         <v>4475</v>
       </c>
     </row>
-    <row r="393" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="393" spans="1:11">
       <c r="A393" s="10">
         <v>45830</v>
       </c>
@@ -33921,7 +33963,7 @@
         <v>4354</v>
       </c>
     </row>
-    <row r="394" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="394" spans="1:11">
       <c r="A394" s="10">
         <v>45837</v>
       </c>
@@ -33956,7 +33998,7 @@
         <v>4375</v>
       </c>
     </row>
-    <row r="395" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="395" spans="1:11">
       <c r="A395" s="10">
         <v>45844</v>
       </c>
@@ -33991,7 +34033,7 @@
         <v>4413</v>
       </c>
     </row>
-    <row r="396" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="396" spans="1:11">
       <c r="A396" s="10">
         <v>45851</v>
       </c>
@@ -34026,7 +34068,7 @@
         <v>4593</v>
       </c>
     </row>
-    <row r="397" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="397" spans="1:11">
       <c r="A397" s="10">
         <v>45858</v>
       </c>
@@ -34061,7 +34103,7 @@
         <v>4418</v>
       </c>
     </row>
-    <row r="398" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="398" spans="1:11">
       <c r="A398" s="10">
         <v>45865</v>
       </c>
@@ -34096,7 +34138,7 @@
         <v>4429</v>
       </c>
     </row>
-    <row r="399" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="399" spans="1:11">
       <c r="A399" s="10">
         <v>45872</v>
       </c>
@@ -34131,7 +34173,7 @@
         <v>4418</v>
       </c>
     </row>
-    <row r="400" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="400" spans="1:11">
       <c r="A400" s="10">
         <v>45879</v>
       </c>
@@ -34166,7 +34208,7 @@
         <v>4455</v>
       </c>
     </row>
-    <row r="401" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="401" spans="1:11">
       <c r="A401" s="10">
         <v>45886</v>
       </c>
@@ -34201,7 +34243,7 @@
         <v>4411</v>
       </c>
     </row>
-    <row r="402" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="402" spans="1:11">
       <c r="A402" s="10">
         <v>45893</v>
       </c>
@@ -34236,7 +34278,7 @@
         <v>4392</v>
       </c>
     </row>
-    <row r="403" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="403" spans="1:11">
       <c r="A403" s="10">
         <v>45900</v>
       </c>
@@ -34271,7 +34313,7 @@
         <v>4549</v>
       </c>
     </row>
-    <row r="404" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="404" spans="1:11">
       <c r="A404" s="10">
         <v>45907</v>
       </c>
@@ -34306,7 +34348,7 @@
         <v>4489</v>
       </c>
     </row>
-    <row r="405" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="405" spans="1:11">
       <c r="A405" s="10">
         <v>45914</v>
       </c>
@@ -34341,7 +34383,7 @@
         <v>4536</v>
       </c>
     </row>
-    <row r="406" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="406" spans="1:11">
       <c r="A406" s="10">
         <v>45921</v>
       </c>
@@ -34376,7 +34418,7 @@
         <v>4516</v>
       </c>
     </row>
-    <row r="407" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="407" spans="1:11">
       <c r="A407" s="10">
         <v>45928</v>
       </c>
@@ -34411,7 +34453,7 @@
         <v>4562</v>
       </c>
     </row>
-    <row r="408" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="408" spans="1:11">
       <c r="A408" s="10">
         <v>45935</v>
       </c>
@@ -34446,7 +34488,7 @@
         <v>4621</v>
       </c>
     </row>
-    <row r="409" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="409" spans="1:11">
       <c r="A409" s="10">
         <v>45942</v>
       </c>
@@ -34481,7 +34523,7 @@
         <v>4441</v>
       </c>
     </row>
-    <row r="410" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="410" spans="1:11">
       <c r="A410" s="10">
         <v>45949</v>
       </c>
@@ -34516,7 +34558,7 @@
         <v>4746</v>
       </c>
     </row>
-    <row r="411" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="411" spans="1:11">
       <c r="A411" s="10">
         <v>45956</v>
       </c>
@@ -34551,7 +34593,7 @@
         <v>5010</v>
       </c>
     </row>
-    <row r="412" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="412" spans="1:11">
       <c r="A412" s="10">
         <v>45963</v>
       </c>
@@ -34586,7 +34628,7 @@
         <v>5366</v>
       </c>
     </row>
-    <row r="413" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="413" spans="1:11">
       <c r="A413" s="10">
         <v>45970</v>
       </c>
@@ -34621,7 +34663,7 @@
         <v>5356</v>
       </c>
     </row>
-    <row r="414" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="414" spans="1:11">
       <c r="A414" s="10">
         <v>45977</v>
       </c>
@@ -34656,7 +34698,7 @@
         <v>5581</v>
       </c>
     </row>
-    <row r="415" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="415" spans="1:11">
       <c r="A415" s="10">
         <v>45984</v>
       </c>
@@ -34691,7 +34733,7 @@
         <v>5571</v>
       </c>
     </row>
-    <row r="416" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="416" spans="1:11">
       <c r="A416" s="10">
         <v>45991</v>
       </c>
@@ -34726,7 +34768,7 @@
         <v>5721</v>
       </c>
     </row>
-    <row r="417" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="417" spans="1:11">
       <c r="A417" s="10">
         <v>45998</v>
       </c>
@@ -34761,7 +34803,7 @@
         <v>6161</v>
       </c>
     </row>
-    <row r="418" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="418" spans="1:11">
       <c r="A418" s="10">
         <v>46005</v>
       </c>
@@ -34796,7 +34838,7 @@
         <v>6369</v>
       </c>
     </row>
-    <row r="419" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="419" spans="1:11">
       <c r="A419" s="10">
         <v>46012</v>
       </c>
@@ -34831,7 +34873,7 @@
         <v>5821</v>
       </c>
     </row>
-    <row r="420" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="420" spans="1:11">
       <c r="A420" s="10">
         <v>46026</v>
       </c>
@@ -34866,7 +34908,7 @@
         <v>4662</v>
       </c>
     </row>
-    <row r="421" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="421" spans="1:11">
       <c r="A421" s="10">
         <v>46033</v>
       </c>
@@ -34901,7 +34943,7 @@
         <v>4662</v>
       </c>
     </row>
-    <row r="422" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="422" spans="1:11">
       <c r="A422" s="10">
         <v>46040</v>
       </c>
@@ -34936,7 +34978,7 @@
         <v>4558</v>
       </c>
     </row>
-    <row r="423" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="423" spans="1:11">
       <c r="A423" s="10">
         <v>46047</v>
       </c>
@@ -34971,7 +35013,7 @@
         <v>4478</v>
       </c>
     </row>
-    <row r="424" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="424" spans="1:11">
       <c r="A424" s="10">
         <v>46054</v>
       </c>
@@ -35006,7 +35048,7 @@
         <v>4714</v>
       </c>
     </row>
-    <row r="425" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="425" spans="1:11">
       <c r="A425" s="10">
         <v>46061</v>
       </c>
@@ -35041,7 +35083,7 @@
         <v>4730</v>
       </c>
     </row>
-    <row r="426" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="426" spans="1:11">
       <c r="A426" s="10">
         <v>46068</v>
       </c>
@@ -35076,7 +35118,7 @@
         <v>4757</v>
       </c>
     </row>
-    <row r="427" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="427" spans="1:11">
       <c r="A427" s="10">
         <v>46075</v>
       </c>
@@ -35111,7 +35153,7 @@
         <v>4432</v>
       </c>
     </row>
-    <row r="428" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="428" spans="1:11">
       <c r="A428" s="10">
         <v>46082</v>
       </c>
@@ -35146,7 +35188,7 @@
         <v>4445</v>
       </c>
     </row>
-    <row r="429" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="429" spans="1:11">
       <c r="A429" s="10">
         <v>46089</v>
       </c>
@@ -35181,7 +35223,7 @@
         <v>4012</v>
       </c>
     </row>
-    <row r="430" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="430" spans="1:11">
       <c r="A430" s="10">
         <v>46096</v>
       </c>
@@ -35216,7 +35258,7 @@
         <v>4208</v>
       </c>
     </row>
-    <row r="431" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="431" spans="1:11">
       <c r="A431" s="10">
         <v>46103</v>
       </c>
@@ -35251,7 +35293,7 @@
         <v>4794</v>
       </c>
     </row>
-    <row r="432" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="432" spans="1:11">
       <c r="A432" s="10">
         <v>46110</v>
       </c>
@@ -35286,7 +35328,7 @@
         <v>5348</v>
       </c>
     </row>
-    <row r="433" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="433" spans="1:11">
       <c r="A433" s="10">
         <v>46117</v>
       </c>
@@ -35321,7 +35363,7 @@
         <v>5689</v>
       </c>
     </row>
-    <row r="434" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="434" spans="1:11">
       <c r="A434" s="10">
         <v>46124</v>
       </c>
@@ -35356,7 +35398,7 @@
         <v>5631</v>
       </c>
     </row>
-    <row r="435" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="435" spans="1:11">
       <c r="A435" s="10">
         <v>46131</v>
       </c>
@@ -35391,7 +35433,7 @@
         <v>5837</v>
       </c>
     </row>
-    <row r="436" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="436" spans="1:11">
       <c r="A436" s="10">
         <v>46138</v>
       </c>
@@ -35426,7 +35468,7 @@
         <v>5881</v>
       </c>
     </row>
-    <row r="437" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="437" spans="1:11">
       <c r="A437" s="10">
         <v>46145</v>
       </c>
@@ -35461,7 +35503,7 @@
         <v>6128</v>
       </c>
     </row>
-    <row r="438" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="438" spans="1:11">
       <c r="A438" s="10">
         <v>46152</v>
       </c>
@@ -35494,6 +35536,41 @@
       </c>
       <c r="K438" s="9">
         <v>5909</v>
+      </c>
+    </row>
+    <row r="439" spans="1:11">
+      <c r="A439" s="10">
+        <v>46159</v>
+      </c>
+      <c r="B439" s="8">
+        <v>46160</v>
+      </c>
+      <c r="C439" s="11">
+        <v>0.70833333333333304</v>
+      </c>
+      <c r="D439" s="8" t="s">
+        <v>22</v>
+      </c>
+      <c r="E439" s="9">
+        <v>2614</v>
+      </c>
+      <c r="F439" s="9">
+        <v>1075</v>
+      </c>
+      <c r="G439" s="9">
+        <v>4592</v>
+      </c>
+      <c r="H439" s="9">
+        <v>1190</v>
+      </c>
+      <c r="I439" s="9">
+        <v>1303</v>
+      </c>
+      <c r="J439" s="9">
+        <v>341</v>
+      </c>
+      <c r="K439" s="9">
+        <v>5807</v>
       </c>
     </row>
   </sheetData>
@@ -35513,7 +35590,7 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{EC49EC86-403A-4933-BA0C-EED828B128BC}">
   <sheetPr codeName="Sheet2"/>
   <dimension ref="A1"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.8" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.8"/>
   <cols>
     <col min="1" max="16384" width="9" style="12"/>
   </cols>
@@ -35529,12 +35606,12 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{362BE34E-9F1D-4DC0-8A14-D289984A66A9}">
   <sheetPr codeName="Sheet3"/>
   <dimension ref="B2:G3"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="15.6" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.8"/>
   <cols>
     <col min="1" max="16384" width="9" style="1"/>
   </cols>
   <sheetData>
-    <row r="2" spans="2:7" x14ac:dyDescent="0.35">
+    <row r="2" spans="2:7" ht="15.6">
       <c r="B2" s="2" t="s">
         <v>16</v>
       </c>
@@ -35546,7 +35623,7 @@
       <c r="F2" s="3"/>
       <c r="G2" s="3"/>
     </row>
-    <row r="3" spans="2:7" x14ac:dyDescent="0.35">
+    <row r="3" spans="2:7">
       <c r="B3" s="4" t="s">
         <v>15</v>
       </c>

--- a/data/freight/Baltic air freight index.xlsx
+++ b/data/freight/Baltic air freight index.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\krm\PycharmProjects\AlternativeData\data\freight\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{14BB7FBF-02A3-423A-AD88-C172A724DC61}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{76E9C19F-084E-4D77-9906-5BF88981D147}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="32100" yWindow="1785" windowWidth="21600" windowHeight="10875" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="BAI" sheetId="1" r:id="rId1"/>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="460" uniqueCount="25">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="461" uniqueCount="25">
   <si>
     <t>Shanghai Pudong Outbound</t>
   </si>
@@ -1666,6 +1666,9 @@
                 <c:pt idx="437">
                   <c:v>46167</c:v>
                 </c:pt>
+                <c:pt idx="438">
+                  <c:v>46174</c:v>
+                </c:pt>
               </c:numCache>
             </c:numRef>
           </c:cat>
@@ -2988,6 +2991,9 @@
                 </c:pt>
                 <c:pt idx="437">
                   <c:v>2608</c:v>
+                </c:pt>
+                <c:pt idx="438">
+                  <c:v>2680</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -4348,6 +4354,9 @@
                 <c:pt idx="437">
                   <c:v>46167</c:v>
                 </c:pt>
+                <c:pt idx="438">
+                  <c:v>46174</c:v>
+                </c:pt>
               </c:numCache>
             </c:numRef>
           </c:cat>
@@ -5670,6 +5679,9 @@
                 </c:pt>
                 <c:pt idx="437">
                   <c:v>1157</c:v>
+                </c:pt>
+                <c:pt idx="438">
+                  <c:v>1055</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -7030,6 +7042,9 @@
                 <c:pt idx="437">
                   <c:v>46167</c:v>
                 </c:pt>
+                <c:pt idx="438">
+                  <c:v>46174</c:v>
+                </c:pt>
               </c:numCache>
             </c:numRef>
           </c:cat>
@@ -8352,6 +8367,9 @@
                 </c:pt>
                 <c:pt idx="437">
                   <c:v>4552</c:v>
+                </c:pt>
+                <c:pt idx="438">
+                  <c:v>4735</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -9712,6 +9730,9 @@
                 <c:pt idx="437">
                   <c:v>46167</c:v>
                 </c:pt>
+                <c:pt idx="438">
+                  <c:v>46174</c:v>
+                </c:pt>
               </c:numCache>
             </c:numRef>
           </c:cat>
@@ -11034,6 +11055,9 @@
                 </c:pt>
                 <c:pt idx="437">
                   <c:v>1155</c:v>
+                </c:pt>
+                <c:pt idx="438">
+                  <c:v>1520</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -12394,6 +12418,9 @@
                 <c:pt idx="437">
                   <c:v>46167</c:v>
                 </c:pt>
+                <c:pt idx="438">
+                  <c:v>46174</c:v>
+                </c:pt>
               </c:numCache>
             </c:numRef>
           </c:cat>
@@ -13716,6 +13743,9 @@
                 </c:pt>
                 <c:pt idx="437">
                   <c:v>1135</c:v>
+                </c:pt>
+                <c:pt idx="438">
+                  <c:v>1161</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -15078,6 +15108,9 @@
                 <c:pt idx="437">
                   <c:v>46167</c:v>
                 </c:pt>
+                <c:pt idx="438">
+                  <c:v>46174</c:v>
+                </c:pt>
               </c:numCache>
             </c:numRef>
           </c:cat>
@@ -16400,6 +16433,9 @@
                 </c:pt>
                 <c:pt idx="437">
                   <c:v>5932</c:v>
+                </c:pt>
+                <c:pt idx="438">
+                  <c:v>5984</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -17776,6 +17812,9 @@
                 <c:pt idx="437">
                   <c:v>46167</c:v>
                 </c:pt>
+                <c:pt idx="438">
+                  <c:v>46174</c:v>
+                </c:pt>
               </c:numCache>
             </c:numRef>
           </c:cat>
@@ -19098,6 +19137,9 @@
                 </c:pt>
                 <c:pt idx="437">
                   <c:v>360</c:v>
+                </c:pt>
+                <c:pt idx="438">
+                  <c:v>261</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -20244,7 +20286,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <sheetPr codeName="Sheet1"/>
-  <dimension ref="A1:K440"/>
+  <dimension ref="A1:K441"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="12.6"/>
   <cols>
     <col min="1" max="1" width="12.109375" style="10" bestFit="1" customWidth="1"/>
@@ -35648,6 +35690,41 @@
       </c>
       <c r="K440" s="9">
         <v>5932</v>
+      </c>
+    </row>
+    <row r="441" spans="1:11">
+      <c r="A441" s="10">
+        <v>46173</v>
+      </c>
+      <c r="B441" s="8">
+        <v>46174</v>
+      </c>
+      <c r="C441" s="11">
+        <v>0.70833333333333304</v>
+      </c>
+      <c r="D441" s="8" t="s">
+        <v>22</v>
+      </c>
+      <c r="E441" s="9">
+        <v>2680</v>
+      </c>
+      <c r="F441" s="9">
+        <v>1055</v>
+      </c>
+      <c r="G441" s="9">
+        <v>4735</v>
+      </c>
+      <c r="H441" s="9">
+        <v>1520</v>
+      </c>
+      <c r="I441" s="9">
+        <v>1161</v>
+      </c>
+      <c r="J441" s="9">
+        <v>261</v>
+      </c>
+      <c r="K441" s="9">
+        <v>5984</v>
       </c>
     </row>
   </sheetData>

--- a/data/freight/Baltic air freight index.xlsx
+++ b/data/freight/Baltic air freight index.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29929"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="30026"/>
   <workbookPr codeName="현재_통합_문서"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\krm\PycharmProjects\AlternativeData\data\freight\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Geust\PycharmProjects\AlternativeData\data\freight\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{76E9C19F-084E-4D77-9906-5BF88981D147}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{26B92C3D-1AF9-4A6A-99E9-84081B3DD41F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="32100" yWindow="1785" windowWidth="21600" windowHeight="10875" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="23260" windowHeight="14860" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="BAI" sheetId="1" r:id="rId1"/>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="461" uniqueCount="25">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="462" uniqueCount="25">
   <si>
     <t>Shanghai Pudong Outbound</t>
   </si>
@@ -280,9 +280,9 @@
     </xf>
   </cellXfs>
   <cellStyles count="3">
-    <cellStyle name="쉼표" xfId="1" builtinId="3"/>
-    <cellStyle name="표준" xfId="0" builtinId="0"/>
-    <cellStyle name="하이퍼링크" xfId="2" builtinId="8"/>
+    <cellStyle name="Comma" xfId="1" builtinId="3"/>
+    <cellStyle name="Hyperlink" xfId="2" builtinId="8"/>
+    <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
@@ -300,7 +300,7 @@
 <file path=xl/charts/chart1.xml><?xml version="1.0" encoding="utf-8"?>
 <c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
   <c:date1904 val="0"/>
-  <c:lang val="ko-KR"/>
+  <c:lang val="en-US"/>
   <c:roundedCorners val="0"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart" Requires="c14">
@@ -1669,6 +1669,9 @@
                 <c:pt idx="438">
                   <c:v>46174</c:v>
                 </c:pt>
+                <c:pt idx="439">
+                  <c:v>46181</c:v>
+                </c:pt>
               </c:numCache>
             </c:numRef>
           </c:cat>
@@ -4357,6 +4360,9 @@
                 <c:pt idx="438">
                   <c:v>46174</c:v>
                 </c:pt>
+                <c:pt idx="439">
+                  <c:v>46181</c:v>
+                </c:pt>
               </c:numCache>
             </c:numRef>
           </c:cat>
@@ -7045,6 +7051,9 @@
                 <c:pt idx="438">
                   <c:v>46174</c:v>
                 </c:pt>
+                <c:pt idx="439">
+                  <c:v>46181</c:v>
+                </c:pt>
               </c:numCache>
             </c:numRef>
           </c:cat>
@@ -9733,6 +9742,9 @@
                 <c:pt idx="438">
                   <c:v>46174</c:v>
                 </c:pt>
+                <c:pt idx="439">
+                  <c:v>46181</c:v>
+                </c:pt>
               </c:numCache>
             </c:numRef>
           </c:cat>
@@ -12420,6 +12432,9 @@
                 </c:pt>
                 <c:pt idx="438">
                   <c:v>46174</c:v>
+                </c:pt>
+                <c:pt idx="439">
+                  <c:v>46181</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -15110,6 +15125,9 @@
                 </c:pt>
                 <c:pt idx="438">
                   <c:v>46174</c:v>
+                </c:pt>
+                <c:pt idx="439">
+                  <c:v>46181</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -17814,6 +17832,9 @@
                 </c:pt>
                 <c:pt idx="438">
                   <c:v>46174</c:v>
+                </c:pt>
+                <c:pt idx="439">
+                  <c:v>46181</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -20286,17 +20307,17 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <sheetPr codeName="Sheet1"/>
-  <dimension ref="A1:K441"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="12.6"/>
+  <dimension ref="A1:K442"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5"/>
   <cols>
-    <col min="1" max="1" width="12.109375" style="10" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="12.08984375" style="10" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="14" style="8" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="11.88671875" style="11" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="11.109375" style="8" customWidth="1"/>
-    <col min="5" max="8" width="8.5546875" style="9" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="9.44140625" style="9" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="8.5546875" style="9" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="9.44140625" style="9" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="11.90625" style="11" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="11.08984375" style="8" customWidth="1"/>
+    <col min="5" max="8" width="8.54296875" style="9" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="9.453125" style="9" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="8.54296875" style="9" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="9.453125" style="9" bestFit="1" customWidth="1"/>
     <col min="12" max="16384" width="9" style="7"/>
   </cols>
   <sheetData>
@@ -35725,6 +35746,20 @@
       </c>
       <c r="K441" s="9">
         <v>5984</v>
+      </c>
+    </row>
+    <row r="442" spans="1:11">
+      <c r="A442" s="10">
+        <v>46180</v>
+      </c>
+      <c r="B442" s="8">
+        <v>46181</v>
+      </c>
+      <c r="C442" s="11">
+        <v>0.70833333333333304</v>
+      </c>
+      <c r="D442" s="8" t="s">
+        <v>22</v>
       </c>
     </row>
   </sheetData>
@@ -35744,7 +35779,7 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{EC49EC86-403A-4933-BA0C-EED828B128BC}">
   <sheetPr codeName="Sheet2"/>
   <dimension ref="A1"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.8"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5"/>
   <cols>
     <col min="1" max="16384" width="9" style="12"/>
   </cols>
@@ -35760,12 +35795,12 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{362BE34E-9F1D-4DC0-8A14-D289984A66A9}">
   <sheetPr codeName="Sheet3"/>
   <dimension ref="B2:G3"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.8"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13"/>
   <cols>
     <col min="1" max="16384" width="9" style="1"/>
   </cols>
   <sheetData>
-    <row r="2" spans="2:7" ht="15.6">
+    <row r="2" spans="2:7" ht="16">
       <c r="B2" s="2" t="s">
         <v>16</v>
       </c>
